--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -152,9 +152,6 @@
   </si>
   <si>
     <t>DOWN</t>
-  </si>
-  <si>
-    <t>UP</t>
   </si>
   <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
@@ -884,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3930.7</v>
+        <v>3850.7</v>
       </c>
       <c r="D2">
-        <v>-0.61</v>
+        <v>-2.04</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -896,46 +893,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-10.16</v>
+        <v>-11.99</v>
       </c>
       <c r="H2">
-        <v>18.75</v>
+        <v>16.33</v>
       </c>
       <c r="I2">
-        <v>-0.84</v>
+        <v>-3.71</v>
       </c>
       <c r="J2">
-        <v>-3.44</v>
+        <v>-5.09</v>
       </c>
       <c r="K2">
-        <v>-5.73</v>
+        <v>-8.02</v>
       </c>
       <c r="L2">
-        <v>12.6</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M2">
-        <v>19.89</v>
+        <v>18.74</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P2">
-        <v>3950.68</v>
+        <v>3921.02</v>
       </c>
       <c r="Q2">
-        <v>4019.24</v>
+        <v>4007.44</v>
       </c>
       <c r="R2">
-        <v>3965.49</v>
+        <v>3961.68</v>
       </c>
       <c r="S2">
-        <v>3958.57</v>
+        <v>3957.71</v>
       </c>
       <c r="T2">
-        <v>-0.7</v>
+        <v>-2.7</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,43 +947,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>41.22</v>
+        <v>33.75</v>
       </c>
       <c r="Z2">
-        <v>-17.76</v>
+        <v>-26.45</v>
       </c>
       <c r="AA2">
-        <v>-3.25</v>
+        <v>-7.89</v>
       </c>
       <c r="AB2">
-        <v>-14.5</v>
+        <v>-18.56</v>
       </c>
       <c r="AC2">
         <v>10.2</v>
       </c>
       <c r="AD2">
-        <v>8.720000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AE2">
-        <v>57.56</v>
+        <v>62.26</v>
       </c>
       <c r="AF2">
-        <v>-10.76</v>
+        <v>43.61</v>
       </c>
       <c r="AG2">
-        <v>4138.99</v>
+        <v>4144.46</v>
       </c>
       <c r="AH2">
-        <v>3899.48</v>
+        <v>3870.41</v>
       </c>
       <c r="AI2">
-        <v>4087.04</v>
+        <v>4084.12</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>20.11</v>
+        <v>23.41</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,37 +994,37 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>309.1</v>
+        <v>296.8</v>
       </c>
       <c r="D3">
-        <v>-0.71</v>
+        <v>-3.98</v>
       </c>
       <c r="E3">
         <v>335.6</v>
       </c>
       <c r="F3">
-        <v>230.35</v>
+        <v>231.13</v>
       </c>
       <c r="G3">
-        <v>-7.9</v>
+        <v>-11.56</v>
       </c>
       <c r="H3">
-        <v>34.19</v>
+        <v>28.41</v>
       </c>
       <c r="I3">
-        <v>-1.56</v>
+        <v>-5.02</v>
       </c>
       <c r="J3">
-        <v>-1.98</v>
+        <v>-3.1</v>
       </c>
       <c r="K3">
-        <v>5.4</v>
+        <v>0.87</v>
       </c>
       <c r="L3">
-        <v>33.47</v>
+        <v>28.85</v>
       </c>
       <c r="M3">
-        <v>31.08</v>
+        <v>29.54</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1036,19 +1033,19 @@
         <v>77</v>
       </c>
       <c r="P3">
-        <v>310.32</v>
+        <v>307.18</v>
       </c>
       <c r="Q3">
-        <v>315.32</v>
+        <v>314.41</v>
       </c>
       <c r="R3">
-        <v>314.54</v>
+        <v>313.76</v>
       </c>
       <c r="S3">
-        <v>292.3</v>
+        <v>292.26</v>
       </c>
       <c r="T3">
-        <v>5.75</v>
+        <v>1.55</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,34 +1060,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>45.86</v>
+        <v>36.86</v>
       </c>
       <c r="Z3">
-        <v>-0.72</v>
+        <v>-1.93</v>
       </c>
       <c r="AA3">
-        <v>0.38</v>
+        <v>-0.08</v>
       </c>
       <c r="AB3">
-        <v>-1.11</v>
+        <v>-1.85</v>
       </c>
       <c r="AC3">
-        <v>15.03</v>
+        <v>9.81</v>
       </c>
       <c r="AD3">
-        <v>13.49</v>
+        <v>12.52</v>
       </c>
       <c r="AE3">
-        <v>8.19</v>
+        <v>8.65</v>
       </c>
       <c r="AF3">
-        <v>-11.1</v>
+        <v>-15.84</v>
       </c>
       <c r="AG3">
-        <v>324.81</v>
+        <v>327.01</v>
       </c>
       <c r="AH3">
-        <v>305.84</v>
+        <v>301.82</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1099,7 +1096,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>16.11</v>
+        <v>19.58</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3337.4</v>
+        <v>3312.2</v>
       </c>
       <c r="D4">
-        <v>-1.2</v>
+        <v>-0.76</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1122,46 +1119,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-28.13</v>
+        <v>-28.68</v>
       </c>
       <c r="H4">
-        <v>9.74</v>
+        <v>8.91</v>
       </c>
       <c r="I4">
-        <v>-4.46</v>
+        <v>-2.99</v>
       </c>
       <c r="J4">
-        <v>-7.42</v>
+        <v>-4.73</v>
       </c>
       <c r="K4">
-        <v>-1.71</v>
+        <v>-4.35</v>
       </c>
       <c r="L4">
-        <v>-17.28</v>
+        <v>-20.02</v>
       </c>
       <c r="M4">
-        <v>-4.13</v>
+        <v>-5.14</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P4">
-        <v>3376.52</v>
+        <v>3356.12</v>
       </c>
       <c r="Q4">
-        <v>3504.61</v>
+        <v>3496.38</v>
       </c>
       <c r="R4">
-        <v>3467.58</v>
+        <v>3470.59</v>
       </c>
       <c r="S4">
-        <v>3626.13</v>
+        <v>3621.55</v>
       </c>
       <c r="T4">
-        <v>-7.96</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,43 +1173,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>34.5</v>
+        <v>32.71</v>
       </c>
       <c r="Z4">
-        <v>-34.68</v>
+        <v>-42.68</v>
       </c>
       <c r="AA4">
-        <v>-5.95</v>
+        <v>-13.29</v>
       </c>
       <c r="AB4">
-        <v>-28.74</v>
+        <v>-29.38</v>
       </c>
       <c r="AC4">
         <v>2.74</v>
       </c>
       <c r="AD4">
-        <v>1.82</v>
+        <v>2.74</v>
       </c>
       <c r="AE4">
-        <v>87.33</v>
+        <v>91.13</v>
       </c>
       <c r="AF4">
-        <v>-66.23</v>
+        <v>-35.78</v>
       </c>
       <c r="AG4">
-        <v>3675.03</v>
+        <v>3687.14</v>
       </c>
       <c r="AH4">
-        <v>3334.19</v>
+        <v>3305.62</v>
       </c>
       <c r="AI4">
-        <v>3316.13</v>
+        <v>3608.08</v>
       </c>
       <c r="AJ4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AK4">
-        <v>27.2</v>
+        <v>23.7</v>
       </c>
     </row>
   </sheetData>
@@ -1363,7 +1360,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1373,12 +1370,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1390,16 +1387,16 @@
         <v>0</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1410,13 +1407,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-1.62</v>
+        <v>-3.44</v>
       </c>
       <c r="D7" s="5">
-        <v>-3.44</v>
+        <v>-5.09</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.82</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1427,13 +1424,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-1.86</v>
+        <v>-1.98</v>
       </c>
       <c r="D8" s="5">
-        <v>-1.98</v>
+        <v>-3.1</v>
       </c>
       <c r="E8" s="6">
-        <v>-0.12</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1444,13 +1441,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-5.62</v>
+        <v>-7.42</v>
       </c>
       <c r="D9" s="5">
-        <v>-7.42</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-1.8</v>
+        <v>-4.73</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2.69</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1461,13 +1458,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-0.5</v>
+        <v>-0.84</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.84</v>
+        <v>-3.71</v>
       </c>
       <c r="E10" s="6">
-        <v>-0.34</v>
+        <v>-2.87</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1478,13 +1475,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-1.77</v>
+        <v>-1.56</v>
       </c>
       <c r="D11" s="5">
-        <v>-1.56</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.21</v>
+        <v>-5.02</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-3.46</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1495,13 +1492,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-3.52</v>
+        <v>-4.46</v>
       </c>
       <c r="D12" s="5">
-        <v>-4.46</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-0.9399999999999999</v>
+        <v>-2.99</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.47</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1512,13 +1509,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>13.15</v>
+        <v>12.6</v>
       </c>
       <c r="D13" s="5">
-        <v>12.6</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="E13" s="6">
-        <v>-0.55</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1529,13 +1526,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>34.65</v>
+        <v>33.47</v>
       </c>
       <c r="D14" s="5">
-        <v>33.47</v>
+        <v>28.85</v>
       </c>
       <c r="E14" s="6">
-        <v>-1.18</v>
+        <v>-4.62</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1546,13 +1543,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-16.33</v>
+        <v>-17.28</v>
       </c>
       <c r="D15" s="5">
-        <v>-17.28</v>
+        <v>-20.02</v>
       </c>
       <c r="E15" s="6">
-        <v>-0.95</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1563,13 +1560,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-2.33</v>
+        <v>-5.73</v>
       </c>
       <c r="D16" s="5">
-        <v>-5.73</v>
+        <v>-8.02</v>
       </c>
       <c r="E16" s="6">
-        <v>-3.4</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1580,13 +1577,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>12.81</v>
+        <v>5.4</v>
       </c>
       <c r="D17" s="5">
-        <v>5.4</v>
+        <v>0.87</v>
       </c>
       <c r="E17" s="6">
-        <v>-7.41</v>
+        <v>-4.53</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1597,13 +1594,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>0.8</v>
+        <v>-1.71</v>
       </c>
       <c r="D18" s="5">
-        <v>-1.71</v>
+        <v>-4.35</v>
       </c>
       <c r="E18" s="6">
-        <v>-2.51</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1614,13 +1611,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-9.609999999999999</v>
+        <v>-10.16</v>
       </c>
       <c r="D19" s="5">
-        <v>-10.16</v>
+        <v>-11.99</v>
       </c>
       <c r="E19" s="6">
-        <v>-0.55</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1631,13 +1628,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-7.24</v>
+        <v>-7.9</v>
       </c>
       <c r="D20" s="5">
-        <v>-7.9</v>
+        <v>-11.56</v>
       </c>
       <c r="E20" s="6">
-        <v>-0.66</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1648,13 +1645,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-27.26</v>
+        <v>-28.13</v>
       </c>
       <c r="D21" s="5">
-        <v>-28.13</v>
+        <v>-28.68</v>
       </c>
       <c r="E21" s="6">
-        <v>-0.87</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1665,13 +1662,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>3955</v>
+        <v>3930.7</v>
       </c>
       <c r="D22" s="5">
-        <v>3930.7</v>
+        <v>3850.7</v>
       </c>
       <c r="E22" s="6">
-        <v>-24.3</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1682,13 +1679,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>311.3</v>
+        <v>309.1</v>
       </c>
       <c r="D23" s="5">
-        <v>309.1</v>
+        <v>296.8</v>
       </c>
       <c r="E23" s="6">
-        <v>-2.2</v>
+        <v>-12.3</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1699,13 +1696,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3377.9</v>
+        <v>3337.4</v>
       </c>
       <c r="D24" s="5">
-        <v>3337.4</v>
+        <v>3312.2</v>
       </c>
       <c r="E24" s="6">
-        <v>-40.5</v>
+        <v>-25.2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1716,13 +1713,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>43.97</v>
+        <v>41.22</v>
       </c>
       <c r="D25" s="5">
-        <v>41.22</v>
+        <v>33.75</v>
       </c>
       <c r="E25" s="6">
-        <v>-2.75</v>
+        <v>-7.47</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1733,13 +1730,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>47.8</v>
+        <v>45.86</v>
       </c>
       <c r="D26" s="5">
-        <v>45.86</v>
+        <v>36.86</v>
       </c>
       <c r="E26" s="6">
-        <v>-1.94</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1750,13 +1747,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>37.58</v>
+        <v>34.5</v>
       </c>
       <c r="D27" s="5">
-        <v>34.5</v>
+        <v>32.71</v>
       </c>
       <c r="E27" s="6">
-        <v>-3.08</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1767,13 +1764,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-0.28</v>
+        <v>-10.76</v>
       </c>
       <c r="D28" s="5">
-        <v>-10.76</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-10.48</v>
+        <v>43.61</v>
+      </c>
+      <c r="E28" s="7">
+        <v>54.37</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1784,13 +1781,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>1.02</v>
+        <v>-11.1</v>
       </c>
       <c r="D29" s="5">
-        <v>-11.1</v>
+        <v>-15.84</v>
       </c>
       <c r="E29" s="6">
-        <v>-12.12</v>
+        <v>-4.74</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1801,13 +1798,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-50.18</v>
+        <v>-66.23</v>
       </c>
       <c r="D30" s="5">
-        <v>-66.23</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-16.05</v>
+        <v>-35.78</v>
+      </c>
+      <c r="E30" s="7">
+        <v>30.45</v>
       </c>
     </row>
   </sheetData>
@@ -1837,28 +1834,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1872,7 +1869,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>40.5</v>
+        <v>34.4</v>
       </c>
       <c r="E2" s="10">
         <v>30</v>
@@ -1881,7 +1878,7 @@
         <v>-4.3</v>
       </c>
       <c r="G2" s="10">
-        <v>-0.7</v>
+        <v>-3.8</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -2000,13 +1997,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.3108</v>
+        <v>0.2954</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1989</v>
+        <v>0.1874</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0413</v>
+        <v>-0.05139999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,7 +157,28 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -359,14 +380,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -881,10 +903,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3850.7</v>
+        <v>3807.7</v>
       </c>
       <c r="D2">
-        <v>-2.04</v>
+        <v>-1.12</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -893,46 +915,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-11.99</v>
+        <v>-12.97</v>
       </c>
       <c r="H2">
-        <v>16.33</v>
+        <v>15.03</v>
       </c>
       <c r="I2">
-        <v>-3.71</v>
+        <v>-3.51</v>
       </c>
       <c r="J2">
-        <v>-5.09</v>
+        <v>-6.83</v>
       </c>
       <c r="K2">
-        <v>-8.02</v>
+        <v>-9.51</v>
       </c>
       <c r="L2">
-        <v>9.529999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M2">
-        <v>18.74</v>
+        <v>18.41</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P2">
-        <v>3921.02</v>
+        <v>3893.34</v>
       </c>
       <c r="Q2">
-        <v>4007.44</v>
+        <v>3994.61</v>
       </c>
       <c r="R2">
-        <v>3961.68</v>
+        <v>3958</v>
       </c>
       <c r="S2">
-        <v>3957.71</v>
+        <v>3956.54</v>
       </c>
       <c r="T2">
-        <v>-2.7</v>
+        <v>-3.76</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,43 +969,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>33.75</v>
+        <v>30.55</v>
       </c>
       <c r="Z2">
-        <v>-26.45</v>
+        <v>-36.39</v>
       </c>
       <c r="AA2">
-        <v>-7.89</v>
+        <v>-13.59</v>
       </c>
       <c r="AB2">
-        <v>-18.56</v>
+        <v>-22.8</v>
       </c>
       <c r="AC2">
-        <v>10.2</v>
+        <v>3.19</v>
       </c>
       <c r="AD2">
-        <v>9.140000000000001</v>
+        <v>7.87</v>
       </c>
       <c r="AE2">
-        <v>62.26</v>
+        <v>62.67</v>
       </c>
       <c r="AF2">
-        <v>43.61</v>
+        <v>53.13</v>
       </c>
       <c r="AG2">
-        <v>4144.46</v>
+        <v>4155.23</v>
       </c>
       <c r="AH2">
-        <v>3870.41</v>
+        <v>3833.98</v>
       </c>
       <c r="AI2">
-        <v>4084.12</v>
+        <v>4021.9</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>23.41</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,109 +1016,109 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>296.8</v>
+        <v>295.5</v>
       </c>
       <c r="D3">
-        <v>-3.98</v>
+        <v>-0.44</v>
       </c>
       <c r="E3">
         <v>335.6</v>
       </c>
       <c r="F3">
-        <v>231.13</v>
+        <v>232.57</v>
       </c>
       <c r="G3">
-        <v>-11.56</v>
+        <v>-11.95</v>
       </c>
       <c r="H3">
-        <v>28.41</v>
+        <v>27.06</v>
       </c>
       <c r="I3">
-        <v>-5.02</v>
+        <v>-4.15</v>
       </c>
       <c r="J3">
-        <v>-3.1</v>
+        <v>-6.19</v>
       </c>
       <c r="K3">
-        <v>0.87</v>
+        <v>0.46</v>
       </c>
       <c r="L3">
-        <v>28.85</v>
+        <v>27.85</v>
       </c>
       <c r="M3">
-        <v>29.54</v>
+        <v>29.12</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P3">
-        <v>307.18</v>
+        <v>304.62</v>
       </c>
       <c r="Q3">
-        <v>314.41</v>
+        <v>312.93</v>
       </c>
       <c r="R3">
-        <v>313.76</v>
+        <v>312.99</v>
       </c>
       <c r="S3">
-        <v>292.26</v>
+        <v>292.22</v>
       </c>
       <c r="T3">
-        <v>1.55</v>
+        <v>1.12</v>
       </c>
       <c r="U3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V3" t="s">
         <v>41</v>
       </c>
       <c r="W3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="X3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y3">
-        <v>36.86</v>
+        <v>36.05</v>
       </c>
       <c r="Z3">
-        <v>-1.93</v>
+        <v>-2.96</v>
       </c>
       <c r="AA3">
-        <v>-0.08</v>
+        <v>-0.66</v>
       </c>
       <c r="AB3">
-        <v>-1.85</v>
+        <v>-2.3</v>
       </c>
       <c r="AC3">
-        <v>9.81</v>
+        <v>2.3</v>
       </c>
       <c r="AD3">
-        <v>12.52</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AE3">
-        <v>8.65</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AF3">
-        <v>-15.84</v>
+        <v>-60.86</v>
       </c>
       <c r="AG3">
-        <v>327.01</v>
+        <v>327.1</v>
       </c>
       <c r="AH3">
-        <v>301.82</v>
+        <v>298.77</v>
       </c>
       <c r="AI3">
-        <v>329.06</v>
+        <v>323.01</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>19.58</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1129,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3312.2</v>
+        <v>3351.5</v>
       </c>
       <c r="D4">
-        <v>-0.76</v>
+        <v>1.19</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1119,46 +1141,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-28.68</v>
+        <v>-27.83</v>
       </c>
       <c r="H4">
-        <v>8.91</v>
+        <v>10.2</v>
       </c>
       <c r="I4">
-        <v>-2.99</v>
+        <v>-1.11</v>
       </c>
       <c r="J4">
-        <v>-4.73</v>
+        <v>-3.6</v>
       </c>
       <c r="K4">
-        <v>-4.35</v>
+        <v>-2.96</v>
       </c>
       <c r="L4">
-        <v>-20.02</v>
+        <v>-19.07</v>
       </c>
       <c r="M4">
-        <v>-5.14</v>
+        <v>-4.92</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P4">
-        <v>3356.12</v>
+        <v>3348.6</v>
       </c>
       <c r="Q4">
-        <v>3496.38</v>
+        <v>3488.46</v>
       </c>
       <c r="R4">
-        <v>3470.59</v>
+        <v>3473.19</v>
       </c>
       <c r="S4">
-        <v>3621.55</v>
+        <v>3616.63</v>
       </c>
       <c r="T4">
-        <v>-8.539999999999999</v>
+        <v>-7.33</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,43 +1195,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>32.71</v>
+        <v>38.12</v>
       </c>
       <c r="Z4">
-        <v>-42.68</v>
+        <v>-45.32</v>
       </c>
       <c r="AA4">
-        <v>-13.29</v>
+        <v>-19.7</v>
       </c>
       <c r="AB4">
-        <v>-29.38</v>
+        <v>-25.62</v>
       </c>
       <c r="AC4">
-        <v>2.74</v>
+        <v>7.13</v>
       </c>
       <c r="AD4">
-        <v>2.74</v>
+        <v>4.2</v>
       </c>
       <c r="AE4">
-        <v>91.13</v>
+        <v>89.83</v>
       </c>
       <c r="AF4">
-        <v>-35.78</v>
+        <v>-48.19</v>
       </c>
       <c r="AG4">
-        <v>3687.14</v>
+        <v>3689.72</v>
       </c>
       <c r="AH4">
-        <v>3305.62</v>
+        <v>3287.2</v>
       </c>
       <c r="AI4">
-        <v>3608.08</v>
+        <v>3598.99</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>23.7</v>
+        <v>21.05</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1372,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1370,447 +1392,502 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-3.44</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-5.09</v>
       </c>
-      <c r="E7" s="6">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-6.83</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-1.98</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-3.1</v>
       </c>
-      <c r="E8" s="6">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-6.19</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-7.42</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-4.73</v>
       </c>
-      <c r="E9" s="7">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-3.6</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-0.84</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>-3.71</v>
       </c>
-      <c r="E10" s="6">
-        <v>-2.87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-3.51</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-1.56</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>-5.02</v>
       </c>
-      <c r="E11" s="6">
-        <v>-3.46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-4.15</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-4.46</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>-2.99</v>
       </c>
-      <c r="E12" s="7">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-1.11</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>12.6</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>9.529999999999999</v>
       </c>
-      <c r="E13" s="6">
-        <v>-3.07</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>33.47</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="6">
         <v>28.85</v>
       </c>
-      <c r="E14" s="6">
-        <v>-4.62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="6">
+        <v>27.85</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-17.28</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="6">
         <v>-20.02</v>
       </c>
-      <c r="E15" s="6">
-        <v>-2.74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-19.07</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-5.73</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="6">
         <v>-8.02</v>
       </c>
-      <c r="E16" s="6">
-        <v>-2.29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="6">
+        <v>-9.51</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>5.4</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="6">
         <v>0.87</v>
       </c>
-      <c r="E17" s="6">
-        <v>-4.53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="6">
+        <v>0.46</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>-1.71</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="6">
         <v>-4.35</v>
       </c>
-      <c r="E18" s="6">
-        <v>-2.64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="6">
+        <v>-2.96</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-10.16</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="6">
         <v>-11.99</v>
       </c>
-      <c r="E19" s="6">
-        <v>-1.83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="6">
+        <v>-12.97</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-7.9</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C21" s="6">
         <v>-11.56</v>
       </c>
-      <c r="E20" s="6">
-        <v>-3.66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="6">
+        <v>-11.95</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-28.13</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="6">
         <v>-28.68</v>
       </c>
-      <c r="E21" s="6">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="6">
+        <v>-27.83</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>3930.7</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C23" s="6">
         <v>3850.7</v>
       </c>
-      <c r="E22" s="6">
-        <v>-80</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="6">
+        <v>3807.7</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>309.1</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C24" s="6">
         <v>296.8</v>
       </c>
-      <c r="E23" s="6">
-        <v>-12.3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D24" s="6">
+        <v>295.5</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>3337.4</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C25" s="6">
         <v>3312.2</v>
       </c>
-      <c r="E24" s="6">
-        <v>-25.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D25" s="6">
+        <v>3351.5</v>
+      </c>
+      <c r="E25" s="8">
+        <v>39.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="5">
-        <v>41.22</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C26" s="6">
         <v>33.75</v>
       </c>
-      <c r="E25" s="6">
-        <v>-7.47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D26" s="6">
+        <v>30.55</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="5">
-        <v>45.86</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C27" s="6">
         <v>36.86</v>
       </c>
-      <c r="E26" s="6">
-        <v>-9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D27" s="6">
+        <v>36.05</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="5">
-        <v>34.5</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C28" s="6">
         <v>32.71</v>
       </c>
-      <c r="E27" s="6">
-        <v>-1.79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D28" s="6">
+        <v>38.12</v>
+      </c>
+      <c r="E28" s="8">
+        <v>5.41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>-10.76</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C29" s="6">
         <v>43.61</v>
       </c>
-      <c r="E28" s="7">
-        <v>54.37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D29" s="6">
+        <v>53.13</v>
+      </c>
+      <c r="E29" s="8">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5">
-        <v>-11.1</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C30" s="6">
         <v>-15.84</v>
       </c>
-      <c r="E29" s="6">
-        <v>-4.74</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="D30" s="6">
+        <v>-60.86</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-45.02</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>-66.23</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C31" s="6">
         <v>-35.78</v>
       </c>
-      <c r="E30" s="7">
-        <v>30.45</v>
+      <c r="D31" s="6">
+        <v>-48.19</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-12.41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1830,61 +1907,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>58</v>
       </c>
+      <c r="C1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>48.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>34.4</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>34.9</v>
+      </c>
+      <c r="E2" s="11">
         <v>30</v>
       </c>
-      <c r="F2" s="10">
-        <v>-4.3</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-3.8</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-5.5</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-4</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
-        <v>70</v>
+      <c r="I2" s="11">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1985,25 +2062,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.2954</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1874</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.05139999999999999</v>
+      <c r="A2" s="14">
+        <v>0.2912</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1841</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0492</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,28 +157,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -264,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -304,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,15 +359,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -903,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3807.7</v>
+        <v>3836.2</v>
       </c>
       <c r="D2">
-        <v>-1.12</v>
+        <v>0.75</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -915,25 +893,25 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-12.97</v>
+        <v>-12.32</v>
       </c>
       <c r="H2">
-        <v>15.03</v>
+        <v>15.89</v>
       </c>
       <c r="I2">
-        <v>-3.51</v>
+        <v>-2.2</v>
       </c>
       <c r="J2">
-        <v>-6.83</v>
+        <v>-5.61</v>
       </c>
       <c r="K2">
-        <v>-9.51</v>
+        <v>-8.44</v>
       </c>
       <c r="L2">
-        <v>8.619999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M2">
-        <v>18.41</v>
+        <v>18.66</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -942,19 +920,19 @@
         <v>58</v>
       </c>
       <c r="P2">
-        <v>3893.34</v>
+        <v>3876.06</v>
       </c>
       <c r="Q2">
-        <v>3994.61</v>
+        <v>3984.35</v>
       </c>
       <c r="R2">
-        <v>3958</v>
+        <v>3956.88</v>
       </c>
       <c r="S2">
-        <v>3956.54</v>
+        <v>3955.57</v>
       </c>
       <c r="T2">
-        <v>-3.76</v>
+        <v>-3.02</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -969,34 +947,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>30.55</v>
+        <v>34.96</v>
       </c>
       <c r="Z2">
-        <v>-36.39</v>
+        <v>-41.49</v>
       </c>
       <c r="AA2">
-        <v>-13.59</v>
+        <v>-19.17</v>
       </c>
       <c r="AB2">
-        <v>-22.8</v>
+        <v>-22.31</v>
       </c>
       <c r="AC2">
-        <v>3.19</v>
+        <v>6.71</v>
       </c>
       <c r="AD2">
-        <v>7.87</v>
+        <v>6.7</v>
       </c>
       <c r="AE2">
-        <v>62.67</v>
+        <v>63</v>
       </c>
       <c r="AF2">
-        <v>53.13</v>
+        <v>-4.57</v>
       </c>
       <c r="AG2">
-        <v>4155.23</v>
+        <v>4158.08</v>
       </c>
       <c r="AH2">
-        <v>3833.98</v>
+        <v>3810.62</v>
       </c>
       <c r="AI2">
         <v>4021.9</v>
@@ -1005,7 +983,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>27.7</v>
+        <v>30.54</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1016,58 +994,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>295.5</v>
+        <v>302.3</v>
       </c>
       <c r="D3">
-        <v>-0.44</v>
+        <v>2.3</v>
       </c>
       <c r="E3">
         <v>335.6</v>
       </c>
       <c r="F3">
-        <v>232.57</v>
+        <v>233.88</v>
       </c>
       <c r="G3">
-        <v>-11.95</v>
+        <v>-9.92</v>
       </c>
       <c r="H3">
-        <v>27.06</v>
+        <v>29.25</v>
       </c>
       <c r="I3">
-        <v>-4.15</v>
+        <v>-2.61</v>
       </c>
       <c r="J3">
-        <v>-6.19</v>
+        <v>-7.01</v>
       </c>
       <c r="K3">
-        <v>0.46</v>
+        <v>5.37</v>
       </c>
       <c r="L3">
-        <v>27.85</v>
+        <v>29.98</v>
       </c>
       <c r="M3">
-        <v>29.12</v>
+        <v>30.36</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P3">
-        <v>304.62</v>
+        <v>303</v>
       </c>
       <c r="Q3">
-        <v>312.93</v>
+        <v>312.28</v>
       </c>
       <c r="R3">
-        <v>312.99</v>
+        <v>312.75</v>
       </c>
       <c r="S3">
-        <v>292.22</v>
+        <v>292.18</v>
       </c>
       <c r="T3">
-        <v>1.12</v>
+        <v>3.46</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1082,34 +1060,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>36.05</v>
+        <v>43.06</v>
       </c>
       <c r="Z3">
-        <v>-2.96</v>
+        <v>-3.19</v>
       </c>
       <c r="AA3">
-        <v>-0.66</v>
+        <v>-1.16</v>
       </c>
       <c r="AB3">
-        <v>-2.3</v>
+        <v>-2.03</v>
       </c>
       <c r="AC3">
-        <v>2.3</v>
+        <v>12.19</v>
       </c>
       <c r="AD3">
-        <v>9.039999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="AE3">
-        <v>8.539999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="AF3">
-        <v>-60.86</v>
+        <v>-22.76</v>
       </c>
       <c r="AG3">
-        <v>327.1</v>
+        <v>327.16</v>
       </c>
       <c r="AH3">
-        <v>298.77</v>
+        <v>297.4</v>
       </c>
       <c r="AI3">
         <v>323.01</v>
@@ -1118,7 +1096,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>23.46</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1129,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3351.5</v>
+        <v>3324.3</v>
       </c>
       <c r="D4">
-        <v>1.19</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1141,46 +1119,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-27.83</v>
+        <v>-28.41</v>
       </c>
       <c r="H4">
-        <v>10.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I4">
-        <v>-1.11</v>
+        <v>-1.18</v>
       </c>
       <c r="J4">
-        <v>-3.6</v>
+        <v>-5.29</v>
       </c>
       <c r="K4">
-        <v>-2.96</v>
+        <v>-2.45</v>
       </c>
       <c r="L4">
-        <v>-19.07</v>
+        <v>-19.93</v>
       </c>
       <c r="M4">
-        <v>-4.92</v>
+        <v>-5</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P4">
-        <v>3348.6</v>
+        <v>3340.66</v>
       </c>
       <c r="Q4">
-        <v>3488.46</v>
+        <v>3477.63</v>
       </c>
       <c r="R4">
-        <v>3473.19</v>
+        <v>3476.85</v>
       </c>
       <c r="S4">
-        <v>3616.63</v>
+        <v>3611.29</v>
       </c>
       <c r="T4">
-        <v>-7.33</v>
+        <v>-7.95</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1195,34 +1173,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>38.12</v>
+        <v>35.96</v>
       </c>
       <c r="Z4">
-        <v>-45.32</v>
+        <v>-49.04</v>
       </c>
       <c r="AA4">
-        <v>-19.7</v>
+        <v>-25.57</v>
       </c>
       <c r="AB4">
-        <v>-25.62</v>
+        <v>-23.47</v>
       </c>
       <c r="AC4">
-        <v>7.13</v>
+        <v>11.42</v>
       </c>
       <c r="AD4">
-        <v>4.2</v>
+        <v>7.09</v>
       </c>
       <c r="AE4">
-        <v>89.83</v>
+        <v>88.39</v>
       </c>
       <c r="AF4">
-        <v>-48.19</v>
+        <v>-41.13</v>
       </c>
       <c r="AG4">
-        <v>3689.72</v>
+        <v>3690.01</v>
       </c>
       <c r="AH4">
-        <v>3287.2</v>
+        <v>3265.25</v>
       </c>
       <c r="AI4">
         <v>3598.99</v>
@@ -1231,7 +1209,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>21.05</v>
+        <v>18.38</v>
       </c>
     </row>
   </sheetData>
@@ -1372,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1392,502 +1370,447 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>57</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-6.83</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-5.61</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.22</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-6.19</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-7.01</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-3.6</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-5.29</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-5.09</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-6.83</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-3.51</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-2.2</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-3.1</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-6.19</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-3.09</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-4.15</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-2.61</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-4.73</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-3.6</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-1.11</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-1.18</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-3.71</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-3.51</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="D13" s="5">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-5.02</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-4.15</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>27.85</v>
+      </c>
+      <c r="D14" s="5">
+        <v>29.98</v>
+      </c>
+      <c r="E14" s="6">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-2.99</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-1.11</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-19.07</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-19.93</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="D14" s="6">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-9.51</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-8.44</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>28.85</v>
-      </c>
-      <c r="D15" s="6">
-        <v>27.85</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.46</v>
+      </c>
+      <c r="D17" s="5">
+        <v>5.37</v>
+      </c>
+      <c r="E17" s="6">
+        <v>4.91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-20.02</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-19.07</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-2.96</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-2.45</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-8.02</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-9.51</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-12.97</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-12.32</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.87</v>
-      </c>
-      <c r="D18" s="6">
-        <v>0.46</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-11.95</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-9.92</v>
+      </c>
+      <c r="E20" s="6">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-4.35</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-2.96</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-27.83</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-28.41</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-11.99</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-12.97</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>3807.7</v>
+      </c>
+      <c r="D22" s="5">
+        <v>3836.2</v>
+      </c>
+      <c r="E22" s="6">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-11.56</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-11.95</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>295.5</v>
+      </c>
+      <c r="D23" s="5">
+        <v>302.3</v>
+      </c>
+      <c r="E23" s="6">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-28.68</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-27.83</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>3351.5</v>
+      </c>
+      <c r="D24" s="5">
+        <v>3324.3</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-27.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>3850.7</v>
-      </c>
-      <c r="D23" s="6">
-        <v>3807.7</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>30.55</v>
+      </c>
+      <c r="D25" s="5">
+        <v>34.96</v>
+      </c>
+      <c r="E25" s="6">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>296.8</v>
-      </c>
-      <c r="D24" s="6">
-        <v>295.5</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>36.05</v>
+      </c>
+      <c r="D26" s="5">
+        <v>43.06</v>
+      </c>
+      <c r="E26" s="6">
+        <v>7.01</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="6">
-        <v>3312.2</v>
-      </c>
-      <c r="D25" s="6">
-        <v>3351.5</v>
-      </c>
-      <c r="E25" s="8">
-        <v>39.3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>38.12</v>
+      </c>
+      <c r="D27" s="5">
+        <v>35.96</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>33.75</v>
-      </c>
-      <c r="D26" s="6">
-        <v>30.55</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>53.13</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-4.57</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-57.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>36.86</v>
-      </c>
-      <c r="D27" s="6">
-        <v>36.05</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-60.86</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-22.76</v>
+      </c>
+      <c r="E29" s="6">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="6">
-        <v>32.71</v>
-      </c>
-      <c r="D28" s="6">
-        <v>38.12</v>
-      </c>
-      <c r="E28" s="8">
-        <v>5.41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>43.61</v>
-      </c>
-      <c r="D29" s="6">
-        <v>53.13</v>
-      </c>
-      <c r="E29" s="8">
-        <v>9.52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-15.84</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-60.86</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-45.02</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-35.78</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C30" s="5">
         <v>-48.19</v>
       </c>
-      <c r="E31" s="7">
-        <v>-12.41</v>
+      <c r="D30" s="5">
+        <v>-41.13</v>
+      </c>
+      <c r="E30" s="6">
+        <v>7.06</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1907,60 +1830,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>65</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>48.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>34.9</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>38</v>
+      </c>
+      <c r="E2" s="10">
         <v>30</v>
       </c>
-      <c r="F2" s="11">
-        <v>-5.5</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-1.8</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>30</v>
       </c>
     </row>
@@ -2062,25 +1985,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.2912</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1841</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0492</v>
+      <c r="A2" s="13">
+        <v>0.3036</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1866</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,7 +157,43 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>43.1 → 51.8</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>43.1</t>
+  </si>
+  <si>
+    <t>51.8</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -359,14 +395,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -881,10 +919,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3836.2</v>
+        <v>3885</v>
       </c>
       <c r="D2">
-        <v>0.75</v>
+        <v>1.27</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -893,46 +931,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-12.32</v>
+        <v>-11.21</v>
       </c>
       <c r="H2">
-        <v>15.89</v>
+        <v>17.37</v>
       </c>
       <c r="I2">
-        <v>-2.2</v>
+        <v>-1.77</v>
       </c>
       <c r="J2">
-        <v>-5.61</v>
+        <v>-3.87</v>
       </c>
       <c r="K2">
-        <v>-8.44</v>
+        <v>-7.71</v>
       </c>
       <c r="L2">
-        <v>8.210000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="M2">
-        <v>18.66</v>
+        <v>19.15</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P2">
-        <v>3876.06</v>
+        <v>3862.06</v>
       </c>
       <c r="Q2">
-        <v>3984.35</v>
+        <v>3974.55</v>
       </c>
       <c r="R2">
-        <v>3956.88</v>
+        <v>3956.86</v>
       </c>
       <c r="S2">
-        <v>3955.57</v>
+        <v>3954.83</v>
       </c>
       <c r="T2">
-        <v>-3.02</v>
+        <v>-1.77</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,34 +985,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>34.96</v>
+        <v>41.77</v>
       </c>
       <c r="Z2">
-        <v>-41.49</v>
+        <v>-41.11</v>
       </c>
       <c r="AA2">
-        <v>-19.17</v>
+        <v>-23.56</v>
       </c>
       <c r="AB2">
-        <v>-22.31</v>
+        <v>-17.55</v>
       </c>
       <c r="AC2">
-        <v>6.71</v>
+        <v>23.9</v>
       </c>
       <c r="AD2">
-        <v>6.7</v>
+        <v>11.27</v>
       </c>
       <c r="AE2">
-        <v>63</v>
+        <v>62.91</v>
       </c>
       <c r="AF2">
-        <v>-4.57</v>
+        <v>12.51</v>
       </c>
       <c r="AG2">
-        <v>4158.08</v>
+        <v>4147.43</v>
       </c>
       <c r="AH2">
-        <v>3810.62</v>
+        <v>3801.67</v>
       </c>
       <c r="AI2">
         <v>4021.9</v>
@@ -983,7 +1021,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>30.54</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +1032,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>302.3</v>
+        <v>312.8</v>
       </c>
       <c r="D3">
-        <v>2.3</v>
+        <v>3.47</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1006,46 +1044,46 @@
         <v>233.88</v>
       </c>
       <c r="G3">
-        <v>-9.92</v>
+        <v>-6.79</v>
       </c>
       <c r="H3">
-        <v>29.25</v>
+        <v>33.74</v>
       </c>
       <c r="I3">
-        <v>-2.61</v>
+        <v>0.48</v>
       </c>
       <c r="J3">
-        <v>-7.01</v>
+        <v>-0.82</v>
       </c>
       <c r="K3">
-        <v>5.37</v>
+        <v>9.18</v>
       </c>
       <c r="L3">
-        <v>29.98</v>
+        <v>33.29</v>
       </c>
       <c r="M3">
-        <v>30.36</v>
+        <v>31.83</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="P3">
-        <v>303</v>
+        <v>303.3</v>
       </c>
       <c r="Q3">
-        <v>312.28</v>
+        <v>312.18</v>
       </c>
       <c r="R3">
-        <v>312.75</v>
+        <v>312.58</v>
       </c>
       <c r="S3">
-        <v>292.18</v>
+        <v>292.22</v>
       </c>
       <c r="T3">
-        <v>3.46</v>
+        <v>7.04</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1060,34 +1098,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>43.06</v>
+        <v>51.84</v>
       </c>
       <c r="Z3">
-        <v>-3.19</v>
+        <v>-2.49</v>
       </c>
       <c r="AA3">
-        <v>-1.16</v>
+        <v>-1.43</v>
       </c>
       <c r="AB3">
-        <v>-2.03</v>
+        <v>-1.06</v>
       </c>
       <c r="AC3">
-        <v>12.19</v>
+        <v>39.64</v>
       </c>
       <c r="AD3">
-        <v>8.1</v>
+        <v>18.04</v>
       </c>
       <c r="AE3">
-        <v>8.69</v>
+        <v>8.92</v>
       </c>
       <c r="AF3">
-        <v>-22.76</v>
+        <v>10.31</v>
       </c>
       <c r="AG3">
-        <v>327.16</v>
+        <v>327.02</v>
       </c>
       <c r="AH3">
-        <v>297.4</v>
+        <v>297.34</v>
       </c>
       <c r="AI3">
         <v>323.01</v>
@@ -1096,7 +1134,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>24.3</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1145,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3324.3</v>
+        <v>3347.5</v>
       </c>
       <c r="D4">
-        <v>-0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1119,49 +1157,49 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-28.41</v>
+        <v>-27.92</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>10.07</v>
       </c>
       <c r="I4">
-        <v>-1.18</v>
+        <v>-0.9</v>
       </c>
       <c r="J4">
-        <v>-5.29</v>
+        <v>-5.46</v>
       </c>
       <c r="K4">
-        <v>-2.45</v>
+        <v>0.49</v>
       </c>
       <c r="L4">
-        <v>-19.93</v>
+        <v>-18.88</v>
       </c>
       <c r="M4">
-        <v>-5</v>
+        <v>-4.42</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P4">
-        <v>3340.66</v>
+        <v>3334.58</v>
       </c>
       <c r="Q4">
-        <v>3477.63</v>
+        <v>3466.05</v>
       </c>
       <c r="R4">
-        <v>3476.85</v>
+        <v>3479.45</v>
       </c>
       <c r="S4">
-        <v>3611.29</v>
+        <v>3606.06</v>
       </c>
       <c r="T4">
-        <v>-7.95</v>
+        <v>-7.17</v>
       </c>
       <c r="U4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V4" t="s">
         <v>42</v>
@@ -1170,46 +1208,46 @@
         <v>42</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>35.96</v>
+        <v>39.12</v>
       </c>
       <c r="Z4">
-        <v>-49.04</v>
+        <v>-49.54</v>
       </c>
       <c r="AA4">
-        <v>-25.57</v>
+        <v>-30.36</v>
       </c>
       <c r="AB4">
-        <v>-23.47</v>
+        <v>-19.18</v>
       </c>
       <c r="AC4">
-        <v>11.42</v>
+        <v>19.87</v>
       </c>
       <c r="AD4">
-        <v>7.09</v>
+        <v>12.8</v>
       </c>
       <c r="AE4">
-        <v>88.39</v>
+        <v>87.87</v>
       </c>
       <c r="AF4">
-        <v>-41.13</v>
+        <v>17.26</v>
       </c>
       <c r="AG4">
-        <v>3690.01</v>
+        <v>3680.38</v>
       </c>
       <c r="AH4">
-        <v>3265.25</v>
+        <v>3251.72</v>
       </c>
       <c r="AI4">
-        <v>3598.99</v>
+        <v>3590.97</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>18.38</v>
+        <v>17.03</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1370,447 +1408,502 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-6.83</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="7">
         <v>-5.61</v>
       </c>
-      <c r="E7" s="6">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="7">
+        <v>-3.87</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-6.19</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="7">
         <v>-7.01</v>
       </c>
-      <c r="E8" s="7">
+      <c r="D9" s="7">
         <v>-0.82</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="E9" s="8">
+        <v>6.19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-3.6</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="7">
         <v>-5.29</v>
       </c>
-      <c r="E9" s="7">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="7">
+        <v>-5.46</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-3.51</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="7">
         <v>-2.2</v>
       </c>
-      <c r="E10" s="6">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="7">
+        <v>-1.77</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-4.15</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="7">
         <v>-2.61</v>
       </c>
-      <c r="E11" s="6">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="7">
+        <v>0.48</v>
+      </c>
+      <c r="E12" s="8">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-1.11</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="7">
         <v>-1.18</v>
       </c>
-      <c r="E12" s="7">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="7">
+        <v>-0.9</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="7">
         <v>8.210000000000001</v>
       </c>
-      <c r="E13" s="7">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="7">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>27.85</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="7">
         <v>29.98</v>
       </c>
-      <c r="E14" s="6">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="7">
+        <v>33.29</v>
+      </c>
+      <c r="E15" s="8">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-19.07</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="7">
         <v>-19.93</v>
       </c>
-      <c r="E15" s="7">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="7">
+        <v>-18.88</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-9.51</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="7">
         <v>-8.44</v>
       </c>
-      <c r="E16" s="6">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="7">
+        <v>-7.71</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>0.46</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="7">
         <v>5.37</v>
       </c>
-      <c r="E17" s="6">
-        <v>4.91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="7">
+        <v>9.18</v>
+      </c>
+      <c r="E18" s="8">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>-2.96</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="7">
         <v>-2.45</v>
       </c>
-      <c r="E18" s="6">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="7">
+        <v>0.49</v>
+      </c>
+      <c r="E19" s="8">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-12.97</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="7">
         <v>-12.32</v>
       </c>
-      <c r="E19" s="6">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="7">
+        <v>-11.21</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-11.95</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C21" s="7">
         <v>-9.92</v>
       </c>
-      <c r="E20" s="6">
-        <v>2.03</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="7">
+        <v>-6.79</v>
+      </c>
+      <c r="E21" s="8">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-27.83</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="7">
         <v>-28.41</v>
       </c>
-      <c r="E21" s="7">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="7">
+        <v>-27.92</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>3807.7</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C23" s="7">
         <v>3836.2</v>
       </c>
-      <c r="E22" s="6">
-        <v>28.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="7">
+        <v>3885</v>
+      </c>
+      <c r="E23" s="8">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>295.5</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C24" s="7">
         <v>302.3</v>
       </c>
-      <c r="E23" s="6">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D24" s="7">
+        <v>312.8</v>
+      </c>
+      <c r="E24" s="8">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>3351.5</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C25" s="7">
         <v>3324.3</v>
       </c>
-      <c r="E24" s="7">
-        <v>-27.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D25" s="7">
+        <v>3347.5</v>
+      </c>
+      <c r="E25" s="8">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="5">
-        <v>30.55</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C26" s="7">
         <v>34.96</v>
       </c>
-      <c r="E25" s="6">
-        <v>4.41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D26" s="7">
+        <v>41.77</v>
+      </c>
+      <c r="E26" s="8">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="5">
-        <v>36.05</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C27" s="7">
         <v>43.06</v>
       </c>
-      <c r="E26" s="6">
-        <v>7.01</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D27" s="7">
+        <v>51.84</v>
+      </c>
+      <c r="E27" s="8">
+        <v>8.779999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="5">
-        <v>38.12</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C28" s="7">
         <v>35.96</v>
       </c>
-      <c r="E27" s="7">
-        <v>-2.16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D28" s="7">
+        <v>39.12</v>
+      </c>
+      <c r="E28" s="8">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>53.13</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C29" s="7">
         <v>-4.57</v>
       </c>
-      <c r="E28" s="7">
-        <v>-57.7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D29" s="7">
+        <v>12.51</v>
+      </c>
+      <c r="E29" s="8">
+        <v>17.08</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5">
-        <v>-60.86</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C30" s="7">
         <v>-22.76</v>
       </c>
-      <c r="E29" s="6">
-        <v>38.1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="D30" s="7">
+        <v>10.31</v>
+      </c>
+      <c r="E30" s="8">
+        <v>33.07</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B31" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>-48.19</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C31" s="7">
         <v>-41.13</v>
       </c>
-      <c r="E30" s="6">
-        <v>7.06</v>
+      <c r="D31" s="7">
+        <v>17.26</v>
+      </c>
+      <c r="E31" s="8">
+        <v>58.39</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1830,60 +1923,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>58</v>
+      <c r="B1" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="12">
         <v>48.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="13">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>38</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="12">
+        <v>44.2</v>
+      </c>
+      <c r="E2" s="12">
         <v>30</v>
       </c>
-      <c r="F2" s="10">
-        <v>-6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-1.8</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="12">
+        <v>-3.4</v>
+      </c>
+      <c r="G2" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="H2" s="12">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>30</v>
       </c>
     </row>
@@ -1985,25 +2078,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.3036</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1866</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.05</v>
+      <c r="A2" s="15">
+        <v>0.3183</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1915</v>
+      </c>
+      <c r="C2" s="15">
+        <v>-0.0442</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,25 +175,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>43.1 → 51.8</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>43.1</t>
+    <t>51.8 → 48.0</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>51.8</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
+    <t>48.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -279,14 +270,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -319,13 +310,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -403,7 +394,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -919,10 +909,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3885</v>
+        <v>3904.8</v>
       </c>
       <c r="D2">
-        <v>1.27</v>
+        <v>0.51</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -931,46 +921,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-11.21</v>
+        <v>-10.75</v>
       </c>
       <c r="H2">
-        <v>17.37</v>
+        <v>17.97</v>
       </c>
       <c r="I2">
-        <v>-1.77</v>
+        <v>-0.66</v>
       </c>
       <c r="J2">
-        <v>-3.87</v>
+        <v>-4.32</v>
       </c>
       <c r="K2">
-        <v>-7.71</v>
+        <v>-7.06</v>
       </c>
       <c r="L2">
-        <v>9.390000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="M2">
-        <v>19.15</v>
+        <v>19.01</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P2">
-        <v>3862.06</v>
+        <v>3856.88</v>
       </c>
       <c r="Q2">
-        <v>3974.55</v>
+        <v>3965.14</v>
       </c>
       <c r="R2">
-        <v>3956.86</v>
+        <v>3956.04</v>
       </c>
       <c r="S2">
-        <v>3954.83</v>
+        <v>3954.4</v>
       </c>
       <c r="T2">
-        <v>-1.77</v>
+        <v>-1.25</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -985,34 +975,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>41.77</v>
+        <v>44.32</v>
       </c>
       <c r="Z2">
-        <v>-41.11</v>
+        <v>-38.78</v>
       </c>
       <c r="AA2">
-        <v>-23.56</v>
+        <v>-26.6</v>
       </c>
       <c r="AB2">
-        <v>-17.55</v>
+        <v>-12.17</v>
       </c>
       <c r="AC2">
-        <v>23.9</v>
+        <v>50.38</v>
       </c>
       <c r="AD2">
-        <v>11.27</v>
+        <v>27</v>
       </c>
       <c r="AE2">
-        <v>62.91</v>
+        <v>60.25</v>
       </c>
       <c r="AF2">
-        <v>12.51</v>
+        <v>-31.93</v>
       </c>
       <c r="AG2">
-        <v>4147.43</v>
+        <v>4131.23</v>
       </c>
       <c r="AH2">
-        <v>3801.67</v>
+        <v>3799.05</v>
       </c>
       <c r="AI2">
         <v>4021.9</v>
@@ -1021,7 +1011,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>30.26</v>
+        <v>28.84</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1032,10 +1022,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>312.8</v>
+        <v>307.8</v>
       </c>
       <c r="D3">
-        <v>3.47</v>
+        <v>-1.6</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1044,46 +1034,46 @@
         <v>233.88</v>
       </c>
       <c r="G3">
-        <v>-6.79</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="H3">
-        <v>33.74</v>
+        <v>31.61</v>
       </c>
       <c r="I3">
-        <v>0.48</v>
+        <v>-0.42</v>
       </c>
       <c r="J3">
-        <v>-0.82</v>
+        <v>-2.21</v>
       </c>
       <c r="K3">
-        <v>9.18</v>
+        <v>6.62</v>
       </c>
       <c r="L3">
-        <v>33.29</v>
+        <v>29.02</v>
       </c>
       <c r="M3">
-        <v>31.83</v>
+        <v>31.33</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P3">
-        <v>303.3</v>
+        <v>303.04</v>
       </c>
       <c r="Q3">
-        <v>312.18</v>
+        <v>311.71</v>
       </c>
       <c r="R3">
-        <v>312.58</v>
+        <v>312.31</v>
       </c>
       <c r="S3">
-        <v>292.22</v>
+        <v>292.24</v>
       </c>
       <c r="T3">
-        <v>7.04</v>
+        <v>5.32</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1098,34 +1088,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>51.84</v>
+        <v>48.04</v>
       </c>
       <c r="Z3">
-        <v>-2.49</v>
+        <v>-2.32</v>
       </c>
       <c r="AA3">
-        <v>-1.43</v>
+        <v>-1.61</v>
       </c>
       <c r="AB3">
-        <v>-1.06</v>
+        <v>-0.71</v>
       </c>
       <c r="AC3">
-        <v>39.64</v>
+        <v>64.95</v>
       </c>
       <c r="AD3">
-        <v>18.04</v>
+        <v>38.92</v>
       </c>
       <c r="AE3">
-        <v>8.92</v>
+        <v>8.75</v>
       </c>
       <c r="AF3">
-        <v>10.31</v>
+        <v>-30.06</v>
       </c>
       <c r="AG3">
-        <v>327.02</v>
+        <v>326.48</v>
       </c>
       <c r="AH3">
-        <v>297.34</v>
+        <v>296.95</v>
       </c>
       <c r="AI3">
         <v>323.01</v>
@@ -1134,7 +1124,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>22.76</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1145,10 +1135,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3347.5</v>
+        <v>3307</v>
       </c>
       <c r="D4">
-        <v>0.7</v>
+        <v>-1.21</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1157,46 +1147,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-27.92</v>
+        <v>-28.79</v>
       </c>
       <c r="H4">
-        <v>10.07</v>
+        <v>8.74</v>
       </c>
       <c r="I4">
-        <v>-0.9</v>
+        <v>-0.91</v>
       </c>
       <c r="J4">
-        <v>-5.46</v>
+        <v>-7.6</v>
       </c>
       <c r="K4">
-        <v>0.49</v>
+        <v>-0.93</v>
       </c>
       <c r="L4">
-        <v>-18.88</v>
+        <v>-21.19</v>
       </c>
       <c r="M4">
-        <v>-4.42</v>
+        <v>-5.16</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P4">
-        <v>3334.58</v>
+        <v>3328.5</v>
       </c>
       <c r="Q4">
-        <v>3466.05</v>
+        <v>3451.17</v>
       </c>
       <c r="R4">
-        <v>3479.45</v>
+        <v>3480.03</v>
       </c>
       <c r="S4">
-        <v>3606.06</v>
+        <v>3600.32</v>
       </c>
       <c r="T4">
-        <v>-7.17</v>
+        <v>-8.15</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1211,43 +1201,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.12</v>
+        <v>35.8</v>
       </c>
       <c r="Z4">
-        <v>-49.54</v>
+        <v>-52.61</v>
       </c>
       <c r="AA4">
-        <v>-30.36</v>
+        <v>-34.81</v>
       </c>
       <c r="AB4">
-        <v>-19.18</v>
+        <v>-17.8</v>
       </c>
       <c r="AC4">
-        <v>19.87</v>
+        <v>17.23</v>
       </c>
       <c r="AD4">
-        <v>12.8</v>
+        <v>16.17</v>
       </c>
       <c r="AE4">
-        <v>87.87</v>
+        <v>85.45</v>
       </c>
       <c r="AF4">
-        <v>17.26</v>
+        <v>-48.73</v>
       </c>
       <c r="AG4">
-        <v>3680.38</v>
+        <v>3666.32</v>
       </c>
       <c r="AH4">
-        <v>3251.72</v>
+        <v>3236.02</v>
       </c>
       <c r="AI4">
-        <v>3590.97</v>
+        <v>3577.56</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>17.03</v>
+        <v>15.85</v>
       </c>
     </row>
   </sheetData>
@@ -1388,7 +1378,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1446,464 +1436,444 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-3.87</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-4.32</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-0.82</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-2.21</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-5.46</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-7.6</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-5.61</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-3.87</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-1.77</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-0.66</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-7.01</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-0.82</v>
-      </c>
-      <c r="E9" s="8">
-        <v>6.19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.48</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-0.42</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-5.29</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-5.46</v>
-      </c>
-      <c r="E10" s="9">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-0.9</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-0.91</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-2.2</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-1.77</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="6">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="D13" s="6">
+        <v>7.5</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-2.61</v>
-      </c>
-      <c r="D12" s="7">
-        <v>0.48</v>
-      </c>
-      <c r="E12" s="8">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6">
+        <v>33.29</v>
+      </c>
+      <c r="D14" s="6">
+        <v>29.02</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-4.27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-1.18</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-0.9</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-18.88</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-21.19</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="7">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="D14" s="7">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="E14" s="8">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-7.71</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-7.06</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="7">
-        <v>29.98</v>
-      </c>
-      <c r="D15" s="7">
-        <v>33.29</v>
-      </c>
-      <c r="E15" s="8">
-        <v>3.31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6">
+        <v>9.18</v>
+      </c>
+      <c r="D17" s="6">
+        <v>6.62</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-19.93</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-18.88</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.49</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.93</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-8.44</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-7.71</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-11.21</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-10.75</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="7">
-        <v>5.37</v>
-      </c>
-      <c r="D18" s="7">
-        <v>9.18</v>
-      </c>
-      <c r="E18" s="8">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-6.79</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-2.45</v>
-      </c>
-      <c r="D19" s="7">
-        <v>0.49</v>
-      </c>
-      <c r="E19" s="8">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-27.92</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-28.79</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-12.32</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-11.21</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6">
+        <v>3885</v>
+      </c>
+      <c r="D22" s="6">
+        <v>3904.8</v>
+      </c>
+      <c r="E22" s="8">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-9.92</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-6.79</v>
-      </c>
-      <c r="E21" s="8">
-        <v>3.13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6">
+        <v>312.8</v>
+      </c>
+      <c r="D23" s="6">
+        <v>307.8</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-28.41</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-27.92</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <v>3347.5</v>
+      </c>
+      <c r="D24" s="6">
+        <v>3307</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-40.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="7">
-        <v>3836.2</v>
-      </c>
-      <c r="D23" s="7">
-        <v>3885</v>
-      </c>
-      <c r="E23" s="8">
-        <v>48.8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="6">
+        <v>41.77</v>
+      </c>
+      <c r="D25" s="6">
+        <v>44.32</v>
+      </c>
+      <c r="E25" s="8">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="7">
-        <v>302.3</v>
-      </c>
-      <c r="D24" s="7">
-        <v>312.8</v>
-      </c>
-      <c r="E24" s="8">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="6">
+        <v>51.84</v>
+      </c>
+      <c r="D26" s="6">
+        <v>48.04</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-3.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="7">
-        <v>3324.3</v>
-      </c>
-      <c r="D25" s="7">
-        <v>3347.5</v>
-      </c>
-      <c r="E25" s="8">
-        <v>23.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>39.12</v>
+      </c>
+      <c r="D27" s="6">
+        <v>35.8</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-3.32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="7">
-        <v>34.96</v>
-      </c>
-      <c r="D26" s="7">
-        <v>41.77</v>
-      </c>
-      <c r="E26" s="8">
-        <v>6.81</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6">
+        <v>12.51</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-31.93</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-44.44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="7">
-        <v>43.06</v>
-      </c>
-      <c r="D27" s="7">
-        <v>51.84</v>
-      </c>
-      <c r="E27" s="8">
-        <v>8.779999999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="6">
+        <v>10.31</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-30.06</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-40.37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="7">
-        <v>35.96</v>
-      </c>
-      <c r="D28" s="7">
-        <v>39.12</v>
-      </c>
-      <c r="E28" s="8">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="7">
-        <v>-4.57</v>
-      </c>
-      <c r="D29" s="7">
-        <v>12.51</v>
-      </c>
-      <c r="E29" s="8">
-        <v>17.08</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-22.76</v>
-      </c>
-      <c r="D30" s="7">
-        <v>10.31</v>
-      </c>
-      <c r="E30" s="8">
-        <v>33.07</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-41.13</v>
-      </c>
-      <c r="D31" s="7">
+      <c r="C30" s="6">
         <v>17.26</v>
       </c>
-      <c r="E31" s="8">
-        <v>58.39</v>
+      <c r="D30" s="6">
+        <v>-48.73</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-65.98999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1923,60 +1893,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>70</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>48.52</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="12">
-        <v>44.2</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>42.7</v>
+      </c>
+      <c r="E2" s="11">
         <v>30</v>
       </c>
-      <c r="F2" s="12">
-        <v>-3.4</v>
-      </c>
-      <c r="G2" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-4.7</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-0.5</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>30</v>
       </c>
     </row>
@@ -2078,25 +2048,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="15">
-        <v>0.3183</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.1915</v>
-      </c>
-      <c r="C2" s="15">
-        <v>-0.0442</v>
+      <c r="A2" s="14">
+        <v>0.3133</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1901</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0516</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -145,12 +145,12 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>DOWN</t>
   </si>
   <si>
@@ -172,19 +172,13 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>51.8 → 48.0</t>
+    <t>Yes → No</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>51.8</t>
-  </si>
-  <si>
-    <t>48.0</t>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -909,10 +903,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3904.8</v>
+        <v>3866.4</v>
       </c>
       <c r="D2">
-        <v>0.51</v>
+        <v>-0.98</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -921,88 +915,88 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-10.75</v>
+        <v>-11.63</v>
       </c>
       <c r="H2">
-        <v>17.97</v>
+        <v>16.81</v>
       </c>
       <c r="I2">
-        <v>-0.66</v>
+        <v>0.41</v>
       </c>
       <c r="J2">
-        <v>-4.32</v>
+        <v>-5.54</v>
       </c>
       <c r="K2">
-        <v>-7.06</v>
+        <v>-7.49</v>
       </c>
       <c r="L2">
-        <v>7.5</v>
+        <v>5.93</v>
       </c>
       <c r="M2">
-        <v>19.01</v>
+        <v>18.92</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P2">
-        <v>3856.88</v>
+        <v>3860.02</v>
       </c>
       <c r="Q2">
-        <v>3965.14</v>
+        <v>3953.96</v>
       </c>
       <c r="R2">
-        <v>3956.04</v>
+        <v>3954.8</v>
       </c>
       <c r="S2">
-        <v>3954.4</v>
+        <v>3953.98</v>
       </c>
       <c r="T2">
-        <v>-1.25</v>
+        <v>-2.21</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
       </c>
       <c r="V2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W2" t="s">
         <v>41</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>44.32</v>
+        <v>40.61</v>
       </c>
       <c r="Z2">
-        <v>-38.78</v>
+        <v>-39.56</v>
       </c>
       <c r="AA2">
-        <v>-26.6</v>
+        <v>-29.2</v>
       </c>
       <c r="AB2">
-        <v>-12.17</v>
+        <v>-10.37</v>
       </c>
       <c r="AC2">
-        <v>50.38</v>
+        <v>63</v>
       </c>
       <c r="AD2">
-        <v>27</v>
+        <v>45.76</v>
       </c>
       <c r="AE2">
-        <v>60.25</v>
+        <v>60.56</v>
       </c>
       <c r="AF2">
-        <v>-31.93</v>
+        <v>-2.27</v>
       </c>
       <c r="AG2">
-        <v>4131.23</v>
+        <v>4114.68</v>
       </c>
       <c r="AH2">
-        <v>3799.05</v>
+        <v>3793.24</v>
       </c>
       <c r="AI2">
         <v>4021.9</v>
@@ -1011,7 +1005,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>28.84</v>
+        <v>25.39</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1022,10 +1016,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>307.8</v>
+        <v>304.9</v>
       </c>
       <c r="D3">
-        <v>-1.6</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1034,88 +1028,88 @@
         <v>233.88</v>
       </c>
       <c r="G3">
-        <v>-8.279999999999999</v>
+        <v>-9.15</v>
       </c>
       <c r="H3">
-        <v>31.61</v>
+        <v>30.37</v>
       </c>
       <c r="I3">
-        <v>-0.42</v>
+        <v>2.73</v>
       </c>
       <c r="J3">
-        <v>-2.21</v>
+        <v>-3.86</v>
       </c>
       <c r="K3">
-        <v>6.62</v>
+        <v>6.48</v>
       </c>
       <c r="L3">
-        <v>29.02</v>
+        <v>26.83</v>
       </c>
       <c r="M3">
-        <v>31.33</v>
+        <v>30.35</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="P3">
-        <v>303.04</v>
+        <v>304.66</v>
       </c>
       <c r="Q3">
-        <v>311.71</v>
+        <v>311.17</v>
       </c>
       <c r="R3">
-        <v>312.31</v>
+        <v>311.92</v>
       </c>
       <c r="S3">
-        <v>292.24</v>
+        <v>292.27</v>
       </c>
       <c r="T3">
-        <v>5.32</v>
+        <v>4.32</v>
       </c>
       <c r="U3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V3" t="s">
         <v>42</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>41</v>
-      </c>
-      <c r="W3" t="s">
-        <v>42</v>
       </c>
       <c r="X3">
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>48.04</v>
+        <v>45.94</v>
       </c>
       <c r="Z3">
-        <v>-2.32</v>
+        <v>-2.39</v>
       </c>
       <c r="AA3">
-        <v>-1.61</v>
+        <v>-1.76</v>
       </c>
       <c r="AB3">
-        <v>-0.71</v>
+        <v>-0.62</v>
       </c>
       <c r="AC3">
-        <v>64.95</v>
+        <v>73.64</v>
       </c>
       <c r="AD3">
-        <v>38.92</v>
+        <v>59.41</v>
       </c>
       <c r="AE3">
-        <v>8.75</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AF3">
-        <v>-30.06</v>
+        <v>-30.71</v>
       </c>
       <c r="AG3">
-        <v>326.48</v>
+        <v>326.1</v>
       </c>
       <c r="AH3">
-        <v>296.95</v>
+        <v>296.23</v>
       </c>
       <c r="AI3">
         <v>323.01</v>
@@ -1124,7 +1118,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>21.43</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1135,10 +1129,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3307</v>
+        <v>3293.6</v>
       </c>
       <c r="D4">
-        <v>-1.21</v>
+        <v>-0.41</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1147,97 +1141,97 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-28.79</v>
+        <v>-29.08</v>
       </c>
       <c r="H4">
-        <v>8.74</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
-        <v>-0.91</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J4">
-        <v>-7.6</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="K4">
         <v>-0.93</v>
       </c>
       <c r="L4">
-        <v>-21.19</v>
+        <v>-21.99</v>
       </c>
       <c r="M4">
-        <v>-5.16</v>
+        <v>-5.68</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="P4">
-        <v>3328.5</v>
+        <v>3324.78</v>
       </c>
       <c r="Q4">
-        <v>3451.17</v>
+        <v>3436.62</v>
       </c>
       <c r="R4">
-        <v>3480.03</v>
+        <v>3479.95</v>
       </c>
       <c r="S4">
-        <v>3600.32</v>
+        <v>3594.48</v>
       </c>
       <c r="T4">
-        <v>-8.15</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="U4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X4">
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>35.8</v>
+        <v>34.75</v>
       </c>
       <c r="Z4">
-        <v>-52.61</v>
+        <v>-55.47</v>
       </c>
       <c r="AA4">
-        <v>-34.81</v>
+        <v>-38.94</v>
       </c>
       <c r="AB4">
-        <v>-17.8</v>
+        <v>-16.53</v>
       </c>
       <c r="AC4">
-        <v>17.23</v>
+        <v>17.57</v>
       </c>
       <c r="AD4">
-        <v>16.17</v>
+        <v>18.22</v>
       </c>
       <c r="AE4">
-        <v>85.45</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="AF4">
-        <v>-48.73</v>
+        <v>-49.33</v>
       </c>
       <c r="AG4">
-        <v>3666.32</v>
+        <v>3653.13</v>
       </c>
       <c r="AH4">
-        <v>3236.02</v>
+        <v>3220.11</v>
       </c>
       <c r="AI4">
-        <v>3577.56</v>
+        <v>3551.55</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>15.85</v>
+        <v>16.32</v>
       </c>
     </row>
   </sheetData>
@@ -1418,252 +1412,255 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-3.87</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-4.32</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.45</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-0.82</v>
+        <v>-4.32</v>
       </c>
       <c r="D8" s="6">
-        <v>-2.21</v>
+        <v>-5.54</v>
       </c>
       <c r="E8" s="7">
-        <v>-1.39</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-5.46</v>
+        <v>-2.21</v>
       </c>
       <c r="D9" s="6">
-        <v>-7.6</v>
+        <v>-3.86</v>
       </c>
       <c r="E9" s="7">
-        <v>-2.14</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-1.77</v>
+        <v>-7.6</v>
       </c>
       <c r="D10" s="6">
-        <v>-0.66</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1.11</v>
+        <v>-8.630000000000001</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>0.48</v>
+        <v>-0.66</v>
       </c>
       <c r="D11" s="6">
-        <v>-0.42</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.9</v>
+        <v>0.41</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.07</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-0.9</v>
+        <v>-0.42</v>
       </c>
       <c r="D12" s="6">
-        <v>-0.91</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.01</v>
+        <v>2.73</v>
+      </c>
+      <c r="E12" s="8">
+        <v>3.15</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>9.390000000000001</v>
+        <v>-0.91</v>
       </c>
       <c r="D13" s="6">
-        <v>7.5</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.89</v>
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.35</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>33.29</v>
+        <v>7.5</v>
       </c>
       <c r="D14" s="6">
-        <v>29.02</v>
+        <v>5.93</v>
       </c>
       <c r="E14" s="7">
-        <v>-4.27</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-18.88</v>
+        <v>29.02</v>
       </c>
       <c r="D15" s="6">
-        <v>-21.19</v>
+        <v>26.83</v>
       </c>
       <c r="E15" s="7">
-        <v>-2.31</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="6">
-        <v>-7.71</v>
+        <v>-21.19</v>
       </c>
       <c r="D16" s="6">
-        <v>-7.06</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.65</v>
+        <v>-21.99</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>9.18</v>
+        <v>-7.06</v>
       </c>
       <c r="D17" s="6">
-        <v>6.62</v>
+        <v>-7.49</v>
       </c>
       <c r="E17" s="7">
-        <v>-2.56</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>0.49</v>
+        <v>6.62</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.93</v>
+        <v>6.48</v>
       </c>
       <c r="E18" s="7">
-        <v>-1.42</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1674,13 +1671,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>-11.21</v>
+        <v>-10.75</v>
       </c>
       <c r="D19" s="6">
-        <v>-10.75</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.46</v>
+        <v>-11.63</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1691,13 +1688,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-6.79</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="D20" s="6">
-        <v>-8.279999999999999</v>
+        <v>-9.15</v>
       </c>
       <c r="E20" s="7">
-        <v>-1.49</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1708,13 +1705,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-27.92</v>
+        <v>-28.79</v>
       </c>
       <c r="D21" s="6">
-        <v>-28.79</v>
+        <v>-29.08</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.87</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1725,13 +1722,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>3885</v>
+        <v>3904.8</v>
       </c>
       <c r="D22" s="6">
-        <v>3904.8</v>
-      </c>
-      <c r="E22" s="8">
-        <v>19.8</v>
+        <v>3866.4</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-38.4</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1742,13 +1739,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>312.8</v>
+        <v>307.8</v>
       </c>
       <c r="D23" s="6">
-        <v>307.8</v>
+        <v>304.9</v>
       </c>
       <c r="E23" s="7">
-        <v>-5</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1759,13 +1756,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>3347.5</v>
+        <v>3307</v>
       </c>
       <c r="D24" s="6">
-        <v>3307</v>
+        <v>3293.6</v>
       </c>
       <c r="E24" s="7">
-        <v>-40.5</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1776,13 +1773,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="6">
-        <v>41.77</v>
+        <v>44.32</v>
       </c>
       <c r="D25" s="6">
-        <v>44.32</v>
-      </c>
-      <c r="E25" s="8">
-        <v>2.55</v>
+        <v>40.61</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-3.71</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1793,13 +1790,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>51.84</v>
+        <v>48.04</v>
       </c>
       <c r="D26" s="6">
-        <v>48.04</v>
+        <v>45.94</v>
       </c>
       <c r="E26" s="7">
-        <v>-3.8</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1810,13 +1807,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>39.12</v>
+        <v>35.8</v>
       </c>
       <c r="D27" s="6">
-        <v>35.8</v>
+        <v>34.75</v>
       </c>
       <c r="E27" s="7">
-        <v>-3.32</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1827,13 +1824,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="6">
-        <v>12.51</v>
+        <v>-31.93</v>
       </c>
       <c r="D28" s="6">
-        <v>-31.93</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-44.44</v>
+        <v>-2.27</v>
+      </c>
+      <c r="E28" s="8">
+        <v>29.66</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1844,13 +1841,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>10.31</v>
+        <v>-30.06</v>
       </c>
       <c r="D29" s="6">
-        <v>-30.06</v>
+        <v>-30.71</v>
       </c>
       <c r="E29" s="7">
-        <v>-40.37</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1861,19 +1858,19 @@
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>17.26</v>
+        <v>-48.73</v>
       </c>
       <c r="D30" s="6">
-        <v>-48.73</v>
+        <v>-49.33</v>
       </c>
       <c r="E30" s="7">
-        <v>-65.98999999999999</v>
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1897,28 +1894,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>65</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1932,22 +1929,22 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>42.7</v>
+        <v>40.4</v>
       </c>
       <c r="E2" s="11">
         <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.7</v>
+        <v>-6</v>
       </c>
       <c r="G2" s="11">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
       </c>
       <c r="I2" s="11">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2060,13 +2057,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.3133</v>
+        <v>0.3035</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1901</v>
+        <v>0.1892</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0516</v>
+        <v>-0.0568</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,13 +172,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>45.9 → 50.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>45.9</t>
+  </si>
+  <si>
+    <t>50.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -264,14 +270,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -304,13 +310,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -903,10 +909,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3866.4</v>
+        <v>3929.9</v>
       </c>
       <c r="D2">
-        <v>-0.98</v>
+        <v>1.64</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -915,46 +921,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-11.63</v>
+        <v>-10.18</v>
       </c>
       <c r="H2">
-        <v>16.81</v>
+        <v>18.73</v>
       </c>
       <c r="I2">
-        <v>0.41</v>
+        <v>3.21</v>
       </c>
       <c r="J2">
-        <v>-5.54</v>
+        <v>-3.91</v>
       </c>
       <c r="K2">
-        <v>-7.49</v>
+        <v>-6.02</v>
       </c>
       <c r="L2">
-        <v>5.93</v>
+        <v>7.66</v>
       </c>
       <c r="M2">
-        <v>18.92</v>
+        <v>18.5</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P2">
-        <v>3860.02</v>
+        <v>3884.46</v>
       </c>
       <c r="Q2">
-        <v>3953.96</v>
+        <v>3944.51</v>
       </c>
       <c r="R2">
-        <v>3954.8</v>
+        <v>3956.42</v>
       </c>
       <c r="S2">
-        <v>3953.98</v>
+        <v>3953.9</v>
       </c>
       <c r="T2">
-        <v>-2.21</v>
+        <v>-0.61</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -969,34 +975,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>40.61</v>
+        <v>48.32</v>
       </c>
       <c r="Z2">
-        <v>-39.56</v>
+        <v>-34.67</v>
       </c>
       <c r="AA2">
-        <v>-29.2</v>
+        <v>-30.29</v>
       </c>
       <c r="AB2">
-        <v>-10.37</v>
+        <v>-4.38</v>
       </c>
       <c r="AC2">
-        <v>63</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="AD2">
-        <v>45.76</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="AE2">
-        <v>60.56</v>
+        <v>61.85</v>
       </c>
       <c r="AF2">
-        <v>-2.27</v>
+        <v>-32.05</v>
       </c>
       <c r="AG2">
-        <v>4114.68</v>
+        <v>4085.36</v>
       </c>
       <c r="AH2">
-        <v>3793.24</v>
+        <v>3803.65</v>
       </c>
       <c r="AI2">
         <v>4021.9</v>
@@ -1005,7 +1011,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>25.39</v>
+        <v>22.93</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1016,10 +1022,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>304.9</v>
+        <v>310</v>
       </c>
       <c r="D3">
-        <v>-0.9399999999999999</v>
+        <v>1.67</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1028,46 +1034,46 @@
         <v>233.88</v>
       </c>
       <c r="G3">
-        <v>-9.15</v>
+        <v>-7.63</v>
       </c>
       <c r="H3">
-        <v>30.37</v>
+        <v>32.55</v>
       </c>
       <c r="I3">
-        <v>2.73</v>
+        <v>4.91</v>
       </c>
       <c r="J3">
-        <v>-3.86</v>
+        <v>-1.85</v>
       </c>
       <c r="K3">
-        <v>6.48</v>
+        <v>4.54</v>
       </c>
       <c r="L3">
-        <v>26.83</v>
+        <v>26.61</v>
       </c>
       <c r="M3">
-        <v>30.35</v>
+        <v>30.33</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P3">
-        <v>304.66</v>
+        <v>307.56</v>
       </c>
       <c r="Q3">
-        <v>311.17</v>
+        <v>310.69</v>
       </c>
       <c r="R3">
-        <v>311.92</v>
+        <v>311.81</v>
       </c>
       <c r="S3">
-        <v>292.27</v>
+        <v>292.33</v>
       </c>
       <c r="T3">
-        <v>4.32</v>
+        <v>6.04</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1082,34 +1088,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>45.94</v>
+        <v>50.08</v>
       </c>
       <c r="Z3">
-        <v>-2.39</v>
+        <v>-2.01</v>
       </c>
       <c r="AA3">
-        <v>-1.76</v>
+        <v>-1.81</v>
       </c>
       <c r="AB3">
-        <v>-0.62</v>
+        <v>-0.2</v>
       </c>
       <c r="AC3">
-        <v>73.64</v>
+        <v>75.8</v>
       </c>
       <c r="AD3">
-        <v>59.41</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="AE3">
-        <v>8.640000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="AF3">
-        <v>-30.71</v>
+        <v>61.04</v>
       </c>
       <c r="AG3">
-        <v>326.1</v>
+        <v>325.11</v>
       </c>
       <c r="AH3">
-        <v>296.23</v>
+        <v>296.28</v>
       </c>
       <c r="AI3">
         <v>323.01</v>
@@ -1118,7 +1124,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>19.17</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1129,10 +1135,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3293.6</v>
+        <v>3231.3</v>
       </c>
       <c r="D4">
-        <v>-0.41</v>
+        <v>-1.89</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1141,46 +1147,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-29.08</v>
+        <v>-30.42</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="I4">
-        <v>-0.5600000000000001</v>
+        <v>-3.59</v>
       </c>
       <c r="J4">
-        <v>-8.630000000000001</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="K4">
-        <v>-0.93</v>
+        <v>-2.74</v>
       </c>
       <c r="L4">
-        <v>-21.99</v>
+        <v>-25.28</v>
       </c>
       <c r="M4">
-        <v>-5.68</v>
+        <v>-6.39</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="P4">
-        <v>3324.78</v>
+        <v>3300.74</v>
       </c>
       <c r="Q4">
-        <v>3436.62</v>
+        <v>3419.77</v>
       </c>
       <c r="R4">
-        <v>3479.95</v>
+        <v>3478.71</v>
       </c>
       <c r="S4">
-        <v>3594.48</v>
+        <v>3587.47</v>
       </c>
       <c r="T4">
-        <v>-8.369999999999999</v>
+        <v>-9.93</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1195,43 +1201,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.75</v>
+        <v>30.29</v>
       </c>
       <c r="Z4">
-        <v>-55.47</v>
+        <v>-62.06</v>
       </c>
       <c r="AA4">
-        <v>-38.94</v>
+        <v>-43.57</v>
       </c>
       <c r="AB4">
-        <v>-16.53</v>
+        <v>-18.49</v>
       </c>
       <c r="AC4">
-        <v>17.57</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AD4">
-        <v>18.22</v>
+        <v>14.64</v>
       </c>
       <c r="AE4">
-        <v>83.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="AF4">
-        <v>-49.33</v>
+        <v>-39.85</v>
       </c>
       <c r="AG4">
-        <v>3653.13</v>
+        <v>3645.41</v>
       </c>
       <c r="AH4">
-        <v>3220.11</v>
+        <v>3194.14</v>
       </c>
       <c r="AI4">
-        <v>3551.55</v>
+        <v>3503.8</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>16.32</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1412,255 +1418,252 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>57</v>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-5.54</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-3.91</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.63</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-4.32</v>
+        <v>-3.86</v>
       </c>
       <c r="D8" s="6">
-        <v>-5.54</v>
+        <v>-1.85</v>
       </c>
       <c r="E8" s="7">
-        <v>-1.22</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-2.21</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="D9" s="6">
-        <v>-3.86</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.65</v>
+        <v>-9.859999999999999</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>-7.6</v>
+        <v>0.41</v>
       </c>
       <c r="D10" s="6">
-        <v>-8.630000000000001</v>
+        <v>3.21</v>
       </c>
       <c r="E10" s="7">
-        <v>-1.03</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>-0.66</v>
+        <v>2.73</v>
       </c>
       <c r="D11" s="6">
-        <v>0.41</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.07</v>
+        <v>4.91</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.18</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-0.42</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D12" s="6">
-        <v>2.73</v>
+        <v>-3.59</v>
       </c>
       <c r="E12" s="8">
-        <v>3.15</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>-0.91</v>
+        <v>5.93</v>
       </c>
       <c r="D13" s="6">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.35</v>
+        <v>7.66</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.73</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>7.5</v>
+        <v>26.83</v>
       </c>
       <c r="D14" s="6">
-        <v>5.93</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.57</v>
+        <v>26.61</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>29.02</v>
+        <v>-21.99</v>
       </c>
       <c r="D15" s="6">
-        <v>26.83</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.19</v>
+        <v>-25.28</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-3.29</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-21.19</v>
+        <v>-7.49</v>
       </c>
       <c r="D16" s="6">
-        <v>-21.99</v>
+        <v>-6.02</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.8</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-7.06</v>
+        <v>6.48</v>
       </c>
       <c r="D17" s="6">
-        <v>-7.49</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.43</v>
+        <v>4.54</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.94</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>6.62</v>
+        <v>-0.93</v>
       </c>
       <c r="D18" s="6">
-        <v>6.48</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.14</v>
+        <v>-2.74</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.81</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1671,13 +1674,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>-10.75</v>
+        <v>-11.63</v>
       </c>
       <c r="D19" s="6">
-        <v>-11.63</v>
+        <v>-10.18</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.88</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1688,13 +1691,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-8.279999999999999</v>
+        <v>-9.15</v>
       </c>
       <c r="D20" s="6">
-        <v>-9.15</v>
+        <v>-7.63</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.87</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1705,13 +1708,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-28.79</v>
+        <v>-29.08</v>
       </c>
       <c r="D21" s="6">
-        <v>-29.08</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.29</v>
+        <v>-30.42</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.34</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1722,13 +1725,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>3904.8</v>
+        <v>3866.4</v>
       </c>
       <c r="D22" s="6">
-        <v>3866.4</v>
+        <v>3929.9</v>
       </c>
       <c r="E22" s="7">
-        <v>-38.4</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1739,13 +1742,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>307.8</v>
+        <v>304.9</v>
       </c>
       <c r="D23" s="6">
-        <v>304.9</v>
+        <v>310</v>
       </c>
       <c r="E23" s="7">
-        <v>-2.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1756,13 +1759,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>3307</v>
+        <v>3293.6</v>
       </c>
       <c r="D24" s="6">
-        <v>3293.6</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-13.4</v>
+        <v>3231.3</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-62.3</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1773,13 +1776,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="6">
-        <v>44.32</v>
+        <v>40.61</v>
       </c>
       <c r="D25" s="6">
-        <v>40.61</v>
+        <v>48.32</v>
       </c>
       <c r="E25" s="7">
-        <v>-3.71</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1790,13 +1793,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>48.04</v>
+        <v>45.94</v>
       </c>
       <c r="D26" s="6">
-        <v>45.94</v>
+        <v>50.08</v>
       </c>
       <c r="E26" s="7">
-        <v>-2.1</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1807,13 +1810,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>35.8</v>
+        <v>34.75</v>
       </c>
       <c r="D27" s="6">
-        <v>34.75</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.05</v>
+        <v>30.29</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-4.46</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1824,13 +1827,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="6">
-        <v>-31.93</v>
+        <v>-2.27</v>
       </c>
       <c r="D28" s="6">
-        <v>-2.27</v>
+        <v>-32.05</v>
       </c>
       <c r="E28" s="8">
-        <v>29.66</v>
+        <v>-29.78</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1841,13 +1844,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>-30.06</v>
+        <v>-30.71</v>
       </c>
       <c r="D29" s="6">
-        <v>-30.71</v>
+        <v>61.04</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.65</v>
+        <v>91.75</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1858,19 +1861,19 @@
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>-48.73</v>
+        <v>-49.33</v>
       </c>
       <c r="D30" s="6">
-        <v>-49.33</v>
+        <v>-39.85</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.6</v>
+        <v>9.48</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1894,28 +1897,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1929,16 +1932,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>40.4</v>
+        <v>42.9</v>
       </c>
       <c r="E2" s="11">
         <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>-6</v>
+        <v>-5.2</v>
       </c>
       <c r="G2" s="11">
-        <v>-0.6</v>
+        <v>-1.4</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2057,13 +2060,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.3035</v>
+        <v>0.3033</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1892</v>
+        <v>0.185</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0568</v>
+        <v>-0.0639</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -175,16 +175,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>45.9 → 50.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.9</t>
+    <t>50.1 → 34.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.1</t>
+  </si>
+  <si>
+    <t>34.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -270,14 +270,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -310,13 +310,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -769,7 +769,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -909,10 +910,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3929.9</v>
+        <v>3858.4</v>
       </c>
       <c r="D2">
-        <v>1.64</v>
+        <v>-1.82</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -921,46 +922,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-10.18</v>
+        <v>-11.82</v>
       </c>
       <c r="H2">
-        <v>18.73</v>
+        <v>16.57</v>
       </c>
       <c r="I2">
-        <v>3.21</v>
+        <v>0.58</v>
       </c>
       <c r="J2">
-        <v>-3.91</v>
+        <v>-6.33</v>
       </c>
       <c r="K2">
-        <v>-6.02</v>
+        <v>-8.49</v>
       </c>
       <c r="L2">
-        <v>7.66</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>18.5</v>
+        <v>18.08</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P2">
-        <v>3884.46</v>
+        <v>3888.9</v>
       </c>
       <c r="Q2">
-        <v>3944.51</v>
+        <v>3935.52</v>
       </c>
       <c r="R2">
-        <v>3956.42</v>
+        <v>3957.91</v>
       </c>
       <c r="S2">
-        <v>3953.9</v>
+        <v>3953.2</v>
       </c>
       <c r="T2">
-        <v>-0.61</v>
+        <v>-2.4</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -975,34 +976,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>48.32</v>
+        <v>41.75</v>
       </c>
       <c r="Z2">
-        <v>-34.67</v>
+        <v>-36.14</v>
       </c>
       <c r="AA2">
-        <v>-30.29</v>
+        <v>-31.46</v>
       </c>
       <c r="AB2">
-        <v>-4.38</v>
+        <v>-4.68</v>
       </c>
       <c r="AC2">
-        <v>79.15000000000001</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="AD2">
-        <v>64.18000000000001</v>
+        <v>71.94</v>
       </c>
       <c r="AE2">
-        <v>61.85</v>
+        <v>63.21</v>
       </c>
       <c r="AF2">
-        <v>-32.05</v>
+        <v>19.57</v>
       </c>
       <c r="AG2">
-        <v>4085.36</v>
+        <v>4074.15</v>
       </c>
       <c r="AH2">
-        <v>3803.65</v>
+        <v>3796.89</v>
       </c>
       <c r="AI2">
         <v>4021.9</v>
@@ -1011,7 +1012,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>22.93</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1022,10 +1023,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>310</v>
+        <v>282</v>
       </c>
       <c r="D3">
-        <v>1.67</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1034,46 +1035,46 @@
         <v>233.88</v>
       </c>
       <c r="G3">
-        <v>-7.63</v>
+        <v>-15.97</v>
       </c>
       <c r="H3">
-        <v>32.55</v>
+        <v>20.57</v>
       </c>
       <c r="I3">
-        <v>4.91</v>
+        <v>-6.72</v>
       </c>
       <c r="J3">
-        <v>-1.85</v>
+        <v>-11.74</v>
       </c>
       <c r="K3">
-        <v>4.54</v>
+        <v>-5.69</v>
       </c>
       <c r="L3">
-        <v>26.61</v>
+        <v>15.48</v>
       </c>
       <c r="M3">
-        <v>30.33</v>
+        <v>28.58</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="P3">
-        <v>307.56</v>
+        <v>303.5</v>
       </c>
       <c r="Q3">
-        <v>310.69</v>
+        <v>308.68</v>
       </c>
       <c r="R3">
-        <v>311.81</v>
+        <v>311.2</v>
       </c>
       <c r="S3">
-        <v>292.33</v>
+        <v>292.21</v>
       </c>
       <c r="T3">
-        <v>6.04</v>
+        <v>-3.49</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1085,46 +1086,46 @@
         <v>41</v>
       </c>
       <c r="X3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>50.08</v>
+        <v>34.48</v>
       </c>
       <c r="Z3">
-        <v>-2.01</v>
+        <v>-3.92</v>
       </c>
       <c r="AA3">
-        <v>-1.81</v>
+        <v>-2.23</v>
       </c>
       <c r="AB3">
-        <v>-0.2</v>
+        <v>-1.69</v>
       </c>
       <c r="AC3">
-        <v>75.8</v>
+        <v>50.49</v>
       </c>
       <c r="AD3">
-        <v>71.45999999999999</v>
+        <v>66.64</v>
       </c>
       <c r="AE3">
-        <v>8.58</v>
+        <v>10.18</v>
       </c>
       <c r="AF3">
-        <v>61.04</v>
+        <v>848.3</v>
       </c>
       <c r="AG3">
-        <v>325.11</v>
+        <v>327.02</v>
       </c>
       <c r="AH3">
-        <v>296.28</v>
+        <v>290.35</v>
       </c>
       <c r="AI3">
-        <v>323.01</v>
+        <v>315.34</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>17.76</v>
+        <v>22.17</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1135,10 +1136,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3231.3</v>
+        <v>3209.1</v>
       </c>
       <c r="D4">
-        <v>-1.89</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1147,46 +1148,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-30.42</v>
+        <v>-30.9</v>
       </c>
       <c r="H4">
-        <v>6.25</v>
+        <v>5.52</v>
       </c>
       <c r="I4">
-        <v>-3.59</v>
+        <v>-3.47</v>
       </c>
       <c r="J4">
-        <v>-9.859999999999999</v>
+        <v>-10.06</v>
       </c>
       <c r="K4">
-        <v>-2.74</v>
+        <v>-3.41</v>
       </c>
       <c r="L4">
-        <v>-25.28</v>
+        <v>-24.99</v>
       </c>
       <c r="M4">
-        <v>-6.39</v>
+        <v>-6.82</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P4">
-        <v>3300.74</v>
+        <v>3277.7</v>
       </c>
       <c r="Q4">
-        <v>3419.77</v>
+        <v>3403.07</v>
       </c>
       <c r="R4">
-        <v>3478.71</v>
+        <v>3472.73</v>
       </c>
       <c r="S4">
-        <v>3587.47</v>
+        <v>3581.04</v>
       </c>
       <c r="T4">
-        <v>-9.93</v>
+        <v>-10.39</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1201,43 +1202,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>30.29</v>
+        <v>28.87</v>
       </c>
       <c r="Z4">
-        <v>-62.06</v>
+        <v>-68.28</v>
       </c>
       <c r="AA4">
-        <v>-43.57</v>
+        <v>-48.51</v>
       </c>
       <c r="AB4">
-        <v>-18.49</v>
+        <v>-19.77</v>
       </c>
       <c r="AC4">
-        <v>9.119999999999999</v>
+        <v>4.63</v>
       </c>
       <c r="AD4">
-        <v>14.64</v>
+        <v>10.44</v>
       </c>
       <c r="AE4">
-        <v>84.90000000000001</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="AF4">
-        <v>-39.85</v>
+        <v>-65.45999999999999</v>
       </c>
       <c r="AG4">
-        <v>3645.41</v>
+        <v>3639.45</v>
       </c>
       <c r="AH4">
-        <v>3194.14</v>
+        <v>3166.69</v>
       </c>
       <c r="AI4">
-        <v>3503.8</v>
+        <v>3461.36</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>20</v>
+        <v>23.48</v>
       </c>
     </row>
   </sheetData>
@@ -1470,13 +1471,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-5.54</v>
+        <v>-3.91</v>
       </c>
       <c r="D7" s="6">
-        <v>-3.91</v>
+        <v>-6.33</v>
       </c>
       <c r="E7" s="7">
-        <v>1.63</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1487,13 +1488,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-3.86</v>
+        <v>-1.85</v>
       </c>
       <c r="D8" s="6">
-        <v>-1.85</v>
+        <v>-11.74</v>
       </c>
       <c r="E8" s="7">
-        <v>2.01</v>
+        <v>-9.890000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1504,13 +1505,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-8.630000000000001</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="D9" s="6">
-        <v>-9.859999999999999</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-1.23</v>
+        <v>-10.06</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1521,13 +1522,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>0.41</v>
+        <v>3.21</v>
       </c>
       <c r="D10" s="6">
-        <v>3.21</v>
+        <v>0.58</v>
       </c>
       <c r="E10" s="7">
-        <v>2.8</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1538,13 +1539,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>2.73</v>
+        <v>4.91</v>
       </c>
       <c r="D11" s="6">
-        <v>4.91</v>
+        <v>-6.72</v>
       </c>
       <c r="E11" s="7">
-        <v>2.18</v>
+        <v>-11.63</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1555,13 +1556,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-0.5600000000000001</v>
+        <v>-3.59</v>
       </c>
       <c r="D12" s="6">
-        <v>-3.59</v>
+        <v>-3.47</v>
       </c>
       <c r="E12" s="8">
-        <v>-3.03</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1572,13 +1573,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>5.93</v>
+        <v>7.66</v>
       </c>
       <c r="D13" s="6">
-        <v>7.66</v>
+        <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>1.73</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1589,13 +1590,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>26.83</v>
+        <v>26.61</v>
       </c>
       <c r="D14" s="6">
-        <v>26.61</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.22</v>
+        <v>15.48</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-11.13</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1606,13 +1607,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-21.99</v>
+        <v>-25.28</v>
       </c>
       <c r="D15" s="6">
-        <v>-25.28</v>
+        <v>-24.99</v>
       </c>
       <c r="E15" s="8">
-        <v>-3.29</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1623,13 +1624,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-7.49</v>
+        <v>-6.02</v>
       </c>
       <c r="D16" s="6">
-        <v>-6.02</v>
+        <v>-8.49</v>
       </c>
       <c r="E16" s="7">
-        <v>1.47</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1640,13 +1641,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>6.48</v>
+        <v>4.54</v>
       </c>
       <c r="D17" s="6">
-        <v>4.54</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-1.94</v>
+        <v>-5.69</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-10.23</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1657,13 +1658,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-0.93</v>
+        <v>-2.74</v>
       </c>
       <c r="D18" s="6">
-        <v>-2.74</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.81</v>
+        <v>-3.41</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1674,13 +1675,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>-11.63</v>
+        <v>-10.18</v>
       </c>
       <c r="D19" s="6">
-        <v>-10.18</v>
+        <v>-11.82</v>
       </c>
       <c r="E19" s="7">
-        <v>1.45</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1691,13 +1692,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-9.15</v>
+        <v>-7.63</v>
       </c>
       <c r="D20" s="6">
-        <v>-7.63</v>
+        <v>-15.97</v>
       </c>
       <c r="E20" s="7">
-        <v>1.52</v>
+        <v>-8.34</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1708,13 +1709,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-29.08</v>
+        <v>-30.42</v>
       </c>
       <c r="D21" s="6">
-        <v>-30.42</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-1.34</v>
+        <v>-30.9</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1725,13 +1726,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>3866.4</v>
+        <v>3929.9</v>
       </c>
       <c r="D22" s="6">
-        <v>3929.9</v>
+        <v>3858.4</v>
       </c>
       <c r="E22" s="7">
-        <v>63.5</v>
+        <v>-71.5</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1742,13 +1743,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>304.9</v>
+        <v>310</v>
       </c>
       <c r="D23" s="6">
-        <v>310</v>
+        <v>282</v>
       </c>
       <c r="E23" s="7">
-        <v>5.1</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1759,13 +1760,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>3293.6</v>
+        <v>3231.3</v>
       </c>
       <c r="D24" s="6">
-        <v>3231.3</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-62.3</v>
+        <v>3209.1</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-22.2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1776,13 +1777,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="6">
-        <v>40.61</v>
+        <v>48.32</v>
       </c>
       <c r="D25" s="6">
-        <v>48.32</v>
+        <v>41.75</v>
       </c>
       <c r="E25" s="7">
-        <v>7.71</v>
+        <v>-6.57</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1793,13 +1794,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>45.94</v>
+        <v>50.08</v>
       </c>
       <c r="D26" s="6">
-        <v>50.08</v>
+        <v>34.48</v>
       </c>
       <c r="E26" s="7">
-        <v>4.14</v>
+        <v>-15.6</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1810,13 +1811,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>34.75</v>
+        <v>30.29</v>
       </c>
       <c r="D27" s="6">
-        <v>30.29</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-4.46</v>
+        <v>28.87</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1827,13 +1828,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="6">
-        <v>-2.27</v>
+        <v>-32.05</v>
       </c>
       <c r="D28" s="6">
-        <v>-32.05</v>
+        <v>19.57</v>
       </c>
       <c r="E28" s="8">
-        <v>-29.78</v>
+        <v>51.62</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1844,13 +1845,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>-30.71</v>
+        <v>61.04</v>
       </c>
       <c r="D29" s="6">
-        <v>61.04</v>
-      </c>
-      <c r="E29" s="7">
-        <v>91.75</v>
+        <v>848.3</v>
+      </c>
+      <c r="E29" s="8">
+        <v>787.26</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1861,13 +1862,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>-49.33</v>
+        <v>-39.85</v>
       </c>
       <c r="D30" s="6">
-        <v>-39.85</v>
+        <v>-65.45999999999999</v>
       </c>
       <c r="E30" s="7">
-        <v>9.48</v>
+        <v>-25.61</v>
       </c>
     </row>
   </sheetData>
@@ -1926,22 +1927,22 @@
         <v>40</v>
       </c>
       <c r="B2" s="11">
-        <v>48.52</v>
+        <v>36.52</v>
       </c>
       <c r="C2" s="12">
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>42.9</v>
+        <v>35</v>
       </c>
       <c r="E2" s="11">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F2" s="11">
-        <v>-5.2</v>
+        <v>-9.4</v>
       </c>
       <c r="G2" s="11">
-        <v>-1.4</v>
+        <v>-5.9</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2060,13 +2061,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.3033</v>
+        <v>0.2858</v>
       </c>
       <c r="B2" s="14">
-        <v>0.185</v>
+        <v>0.1808</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0639</v>
+        <v>-0.0682</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,34 +157,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.1 → 34.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.1</t>
-  </si>
-  <si>
-    <t>34.5</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -270,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -310,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,15 +359,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -769,8 +741,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -910,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3858.4</v>
+        <v>3876.2</v>
       </c>
       <c r="D2">
-        <v>-1.82</v>
+        <v>0.46</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -922,46 +893,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-11.82</v>
+        <v>-11.41</v>
       </c>
       <c r="H2">
-        <v>16.57</v>
+        <v>17.1</v>
       </c>
       <c r="I2">
-        <v>0.58</v>
+        <v>-0.23</v>
       </c>
       <c r="J2">
-        <v>-6.33</v>
+        <v>-4.01</v>
       </c>
       <c r="K2">
-        <v>-8.49</v>
+        <v>-6.94</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="M2">
-        <v>18.08</v>
+        <v>18.6</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P2">
-        <v>3888.9</v>
+        <v>3887.14</v>
       </c>
       <c r="Q2">
-        <v>3935.52</v>
+        <v>3927.98</v>
       </c>
       <c r="R2">
-        <v>3957.91</v>
+        <v>3959.92</v>
       </c>
       <c r="S2">
-        <v>3953.2</v>
+        <v>3952.79</v>
       </c>
       <c r="T2">
-        <v>-2.4</v>
+        <v>-1.94</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -976,34 +947,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>41.75</v>
+        <v>43.79</v>
       </c>
       <c r="Z2">
-        <v>-36.14</v>
+        <v>-35.46</v>
       </c>
       <c r="AA2">
-        <v>-31.46</v>
+        <v>-32.26</v>
       </c>
       <c r="AB2">
-        <v>-4.68</v>
+        <v>-3.2</v>
       </c>
       <c r="AC2">
-        <v>73.68000000000001</v>
+        <v>79.19</v>
       </c>
       <c r="AD2">
-        <v>71.94</v>
+        <v>77.34</v>
       </c>
       <c r="AE2">
-        <v>63.21</v>
+        <v>61.91</v>
       </c>
       <c r="AF2">
-        <v>19.57</v>
+        <v>-11.25</v>
       </c>
       <c r="AG2">
-        <v>4074.15</v>
+        <v>4061.99</v>
       </c>
       <c r="AH2">
-        <v>3796.89</v>
+        <v>3793.97</v>
       </c>
       <c r="AI2">
         <v>4021.9</v>
@@ -1012,7 +983,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>20.93</v>
+        <v>19.78</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1023,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D3">
-        <v>-9.029999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1035,46 +1006,46 @@
         <v>233.88</v>
       </c>
       <c r="G3">
-        <v>-15.97</v>
+        <v>-15.38</v>
       </c>
       <c r="H3">
-        <v>20.57</v>
+        <v>21.43</v>
       </c>
       <c r="I3">
-        <v>-6.72</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="J3">
-        <v>-11.74</v>
+        <v>-11.86</v>
       </c>
       <c r="K3">
-        <v>-5.69</v>
+        <v>-5.03</v>
       </c>
       <c r="L3">
-        <v>15.48</v>
+        <v>15.65</v>
       </c>
       <c r="M3">
-        <v>28.58</v>
+        <v>28.32</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P3">
-        <v>303.5</v>
+        <v>297.74</v>
       </c>
       <c r="Q3">
-        <v>308.68</v>
+        <v>306.79</v>
       </c>
       <c r="R3">
-        <v>311.2</v>
+        <v>310.69</v>
       </c>
       <c r="S3">
-        <v>292.21</v>
+        <v>292.15</v>
       </c>
       <c r="T3">
-        <v>-3.49</v>
+        <v>-2.79</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1089,43 +1060,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>34.48</v>
+        <v>36.01</v>
       </c>
       <c r="Z3">
-        <v>-3.92</v>
+        <v>-5.21</v>
       </c>
       <c r="AA3">
-        <v>-2.23</v>
+        <v>-2.83</v>
       </c>
       <c r="AB3">
-        <v>-1.69</v>
+        <v>-2.38</v>
       </c>
       <c r="AC3">
-        <v>50.49</v>
+        <v>32.56</v>
       </c>
       <c r="AD3">
-        <v>66.64</v>
+        <v>52.95</v>
       </c>
       <c r="AE3">
-        <v>10.18</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AF3">
-        <v>848.3</v>
+        <v>15.74</v>
       </c>
       <c r="AG3">
-        <v>327.02</v>
+        <v>327.1</v>
       </c>
       <c r="AH3">
-        <v>290.35</v>
+        <v>286.48</v>
       </c>
       <c r="AI3">
-        <v>315.34</v>
+        <v>312.48</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>22.17</v>
+        <v>25.98</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1136,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3209.1</v>
+        <v>3206.1</v>
       </c>
       <c r="D4">
-        <v>-0.6899999999999999</v>
+        <v>-0.09</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1148,46 +1119,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-30.9</v>
+        <v>-30.96</v>
       </c>
       <c r="H4">
-        <v>5.52</v>
+        <v>5.42</v>
       </c>
       <c r="I4">
-        <v>-3.47</v>
+        <v>-4.22</v>
       </c>
       <c r="J4">
-        <v>-10.06</v>
+        <v>-9.51</v>
       </c>
       <c r="K4">
-        <v>-3.41</v>
+        <v>2.44</v>
       </c>
       <c r="L4">
-        <v>-24.99</v>
+        <v>-22.32</v>
       </c>
       <c r="M4">
-        <v>-6.82</v>
+        <v>-6.43</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="P4">
-        <v>3277.7</v>
+        <v>3249.42</v>
       </c>
       <c r="Q4">
-        <v>3403.07</v>
+        <v>3386.48</v>
       </c>
       <c r="R4">
-        <v>3472.73</v>
+        <v>3467.24</v>
       </c>
       <c r="S4">
-        <v>3581.04</v>
+        <v>3574.62</v>
       </c>
       <c r="T4">
-        <v>-10.39</v>
+        <v>-10.31</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1202,43 +1173,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>28.87</v>
+        <v>28.68</v>
       </c>
       <c r="Z4">
-        <v>-68.28</v>
+        <v>-72.62</v>
       </c>
       <c r="AA4">
-        <v>-48.51</v>
+        <v>-53.33</v>
       </c>
       <c r="AB4">
-        <v>-19.77</v>
+        <v>-19.29</v>
       </c>
       <c r="AC4">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>10.44</v>
+        <v>4.58</v>
       </c>
       <c r="AE4">
-        <v>82.31999999999999</v>
+        <v>80.08</v>
       </c>
       <c r="AF4">
-        <v>-65.45999999999999</v>
+        <v>-70.22</v>
       </c>
       <c r="AG4">
-        <v>3639.45</v>
+        <v>3629.49</v>
       </c>
       <c r="AH4">
-        <v>3166.69</v>
+        <v>3143.47</v>
       </c>
       <c r="AI4">
-        <v>3461.36</v>
+        <v>3443.75</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>23.48</v>
+        <v>26.93</v>
       </c>
     </row>
   </sheetData>
@@ -1399,47 +1370,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1447,428 +1383,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>59</v>
+      <c r="B6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-3.91</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-6.33</v>
       </c>
-      <c r="E7" s="7">
-        <v>-2.42</v>
+      <c r="D7" s="5">
+        <v>-4.01</v>
+      </c>
+      <c r="E7" s="6">
+        <v>2.32</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-1.85</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-11.74</v>
       </c>
+      <c r="D8" s="5">
+        <v>-11.86</v>
+      </c>
       <c r="E8" s="7">
-        <v>-9.890000000000001</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-9.859999999999999</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-10.06</v>
       </c>
-      <c r="E9" s="7">
-        <v>-0.2</v>
+      <c r="D9" s="5">
+        <v>-9.51</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.55</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>3.21</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>0.58</v>
       </c>
+      <c r="D10" s="5">
+        <v>-0.23</v>
+      </c>
       <c r="E10" s="7">
-        <v>-2.63</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>4.91</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-6.72</v>
       </c>
+      <c r="D11" s="5">
+        <v>-9.210000000000001</v>
+      </c>
       <c r="E11" s="7">
-        <v>-11.63</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-3.59</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-3.47</v>
       </c>
-      <c r="E12" s="8">
-        <v>0.12</v>
+      <c r="D12" s="5">
+        <v>-4.22</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>7.66</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>6</v>
       </c>
-      <c r="E13" s="7">
-        <v>-1.66</v>
+      <c r="D13" s="5">
+        <v>7.4</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1.4</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>26.61</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>15.48</v>
       </c>
-      <c r="E14" s="7">
-        <v>-11.13</v>
+      <c r="D14" s="5">
+        <v>15.65</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.17</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-25.28</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-24.99</v>
       </c>
-      <c r="E15" s="8">
-        <v>0.29</v>
+      <c r="D15" s="5">
+        <v>-22.32</v>
+      </c>
+      <c r="E15" s="6">
+        <v>2.67</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>-6.02</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-8.49</v>
       </c>
-      <c r="E16" s="7">
-        <v>-2.47</v>
+      <c r="D16" s="5">
+        <v>-6.94</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1.55</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>4.54</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-5.69</v>
       </c>
-      <c r="E17" s="7">
-        <v>-10.23</v>
+      <c r="D17" s="5">
+        <v>-5.03</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.66</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>-2.74</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-3.41</v>
       </c>
-      <c r="E18" s="7">
-        <v>-0.67</v>
+      <c r="D18" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="E18" s="6">
+        <v>5.85</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-10.18</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-11.82</v>
       </c>
-      <c r="E19" s="7">
-        <v>-1.64</v>
+      <c r="D19" s="5">
+        <v>-11.41</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.41</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-7.63</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-15.97</v>
       </c>
-      <c r="E20" s="7">
-        <v>-8.34</v>
+      <c r="D20" s="5">
+        <v>-15.38</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.59</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-30.42</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>-30.9</v>
       </c>
+      <c r="D21" s="5">
+        <v>-30.96</v>
+      </c>
       <c r="E21" s="7">
-        <v>-0.48</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>3929.9</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>3858.4</v>
       </c>
-      <c r="E22" s="7">
-        <v>-71.5</v>
+      <c r="D22" s="5">
+        <v>3876.2</v>
+      </c>
+      <c r="E22" s="6">
+        <v>17.8</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>310</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>282</v>
       </c>
-      <c r="E23" s="7">
-        <v>-28</v>
+      <c r="D23" s="5">
+        <v>284</v>
+      </c>
+      <c r="E23" s="6">
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>3231.3</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>3209.1</v>
       </c>
+      <c r="D24" s="5">
+        <v>3206.1</v>
+      </c>
       <c r="E24" s="7">
-        <v>-22.2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="6">
-        <v>48.32</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="5">
         <v>41.75</v>
       </c>
-      <c r="E25" s="7">
-        <v>-6.57</v>
+      <c r="D25" s="5">
+        <v>43.79</v>
+      </c>
+      <c r="E25" s="6">
+        <v>2.04</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="6">
-        <v>50.08</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="5">
         <v>34.48</v>
       </c>
-      <c r="E26" s="7">
-        <v>-15.6</v>
+      <c r="D26" s="5">
+        <v>36.01</v>
+      </c>
+      <c r="E26" s="6">
+        <v>1.53</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="6">
-        <v>30.29</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C27" s="5">
         <v>28.87</v>
       </c>
+      <c r="D27" s="5">
+        <v>28.68</v>
+      </c>
       <c r="E27" s="7">
-        <v>-1.42</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>-32.05</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" s="5">
         <v>19.57</v>
       </c>
-      <c r="E28" s="8">
-        <v>51.62</v>
+      <c r="D28" s="5">
+        <v>-11.25</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-30.82</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>61.04</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="5">
         <v>848.3</v>
       </c>
-      <c r="E29" s="8">
-        <v>787.26</v>
+      <c r="D29" s="5">
+        <v>15.74</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-832.5599999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>-39.85</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>-65.45999999999999</v>
       </c>
+      <c r="D30" s="5">
+        <v>-70.22</v>
+      </c>
       <c r="E30" s="7">
-        <v>-25.61</v>
+        <v>-4.76</v>
       </c>
     </row>
   </sheetData>
@@ -1894,60 +1830,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>67</v>
+      <c r="B1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>35</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>36.2</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-9.4</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-5.9</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-8.5</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-3.2</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2049,25 +1985,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.2858</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1808</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0682</v>
+      <c r="A2" s="13">
+        <v>0.2832</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.186</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0643</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -243,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -881,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3876.2</v>
+        <v>3766.4</v>
       </c>
       <c r="D2">
-        <v>0.46</v>
+        <v>-2.83</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -893,46 +893,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-11.41</v>
+        <v>-13.92</v>
       </c>
       <c r="H2">
-        <v>17.1</v>
+        <v>13.79</v>
       </c>
       <c r="I2">
-        <v>-0.23</v>
+        <v>-3.54</v>
       </c>
       <c r="J2">
-        <v>-4.01</v>
+        <v>-6.47</v>
       </c>
       <c r="K2">
-        <v>-6.94</v>
+        <v>-9.1</v>
       </c>
       <c r="L2">
-        <v>7.4</v>
+        <v>3.98</v>
       </c>
       <c r="M2">
-        <v>18.6</v>
+        <v>17.94</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="P2">
-        <v>3887.14</v>
+        <v>3859.46</v>
       </c>
       <c r="Q2">
-        <v>3927.98</v>
+        <v>3914.01</v>
       </c>
       <c r="R2">
-        <v>3959.92</v>
+        <v>3958.96</v>
       </c>
       <c r="S2">
-        <v>3952.79</v>
+        <v>3951.83</v>
       </c>
       <c r="T2">
-        <v>-1.94</v>
+        <v>-4.69</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,43 +947,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>43.79</v>
+        <v>35.5</v>
       </c>
       <c r="Z2">
-        <v>-35.46</v>
+        <v>-43.28</v>
       </c>
       <c r="AA2">
-        <v>-32.26</v>
+        <v>-34.46</v>
       </c>
       <c r="AB2">
-        <v>-3.2</v>
+        <v>-8.82</v>
       </c>
       <c r="AC2">
-        <v>79.19</v>
+        <v>55.14</v>
       </c>
       <c r="AD2">
-        <v>77.34</v>
+        <v>69.34</v>
       </c>
       <c r="AE2">
-        <v>61.91</v>
+        <v>65.33</v>
       </c>
       <c r="AF2">
-        <v>-11.25</v>
+        <v>-1.31</v>
       </c>
       <c r="AG2">
-        <v>4061.99</v>
+        <v>4054.4</v>
       </c>
       <c r="AH2">
-        <v>3793.97</v>
+        <v>3773.62</v>
       </c>
       <c r="AI2">
-        <v>4021.9</v>
+        <v>4008.3</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>19.78</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>284</v>
+        <v>280.85</v>
       </c>
       <c r="D3">
-        <v>0.71</v>
+        <v>-1.11</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1006,46 +1006,46 @@
         <v>233.88</v>
       </c>
       <c r="G3">
-        <v>-15.38</v>
+        <v>-16.31</v>
       </c>
       <c r="H3">
-        <v>21.43</v>
+        <v>20.08</v>
       </c>
       <c r="I3">
-        <v>-9.210000000000001</v>
+        <v>-8.76</v>
       </c>
       <c r="J3">
-        <v>-11.86</v>
+        <v>-12.75</v>
       </c>
       <c r="K3">
-        <v>-5.03</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="L3">
-        <v>15.65</v>
+        <v>15.15</v>
       </c>
       <c r="M3">
-        <v>28.32</v>
+        <v>27.53</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P3">
-        <v>297.74</v>
+        <v>292.35</v>
       </c>
       <c r="Q3">
-        <v>306.79</v>
+        <v>305.11</v>
       </c>
       <c r="R3">
-        <v>310.69</v>
+        <v>310.11</v>
       </c>
       <c r="S3">
-        <v>292.15</v>
+        <v>292.03</v>
       </c>
       <c r="T3">
-        <v>-2.79</v>
+        <v>-3.83</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,43 +1060,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>36.01</v>
+        <v>34.63</v>
       </c>
       <c r="Z3">
-        <v>-5.21</v>
+        <v>-6.42</v>
       </c>
       <c r="AA3">
-        <v>-2.83</v>
+        <v>-3.55</v>
       </c>
       <c r="AB3">
-        <v>-2.38</v>
+        <v>-2.87</v>
       </c>
       <c r="AC3">
-        <v>32.56</v>
+        <v>3.25</v>
       </c>
       <c r="AD3">
-        <v>52.95</v>
+        <v>28.76</v>
       </c>
       <c r="AE3">
-        <v>9.859999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AF3">
-        <v>15.74</v>
+        <v>3.29</v>
       </c>
       <c r="AG3">
-        <v>327.1</v>
+        <v>328.15</v>
       </c>
       <c r="AH3">
-        <v>286.48</v>
+        <v>282.08</v>
       </c>
       <c r="AI3">
-        <v>312.48</v>
+        <v>309.42</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>25.98</v>
+        <v>29.64</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3206.1</v>
+        <v>3211.6</v>
       </c>
       <c r="D4">
-        <v>-0.09</v>
+        <v>0.17</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1119,46 +1119,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-30.96</v>
+        <v>-30.84</v>
       </c>
       <c r="H4">
-        <v>5.42</v>
+        <v>5.6</v>
       </c>
       <c r="I4">
-        <v>-4.22</v>
+        <v>-2.88</v>
       </c>
       <c r="J4">
-        <v>-9.51</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="K4">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="L4">
-        <v>-22.32</v>
+        <v>-22.15</v>
       </c>
       <c r="M4">
-        <v>-6.43</v>
+        <v>-5.85</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P4">
-        <v>3249.42</v>
+        <v>3230.34</v>
       </c>
       <c r="Q4">
-        <v>3386.48</v>
+        <v>3368.63</v>
       </c>
       <c r="R4">
-        <v>3467.24</v>
+        <v>3463.17</v>
       </c>
       <c r="S4">
-        <v>3574.62</v>
+        <v>3568.19</v>
       </c>
       <c r="T4">
-        <v>-10.31</v>
+        <v>-9.99</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,34 +1173,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>28.68</v>
+        <v>29.62</v>
       </c>
       <c r="Z4">
-        <v>-72.62</v>
+        <v>-74.75</v>
       </c>
       <c r="AA4">
-        <v>-53.33</v>
+        <v>-57.62</v>
       </c>
       <c r="AB4">
-        <v>-19.29</v>
+        <v>-17.14</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AD4">
-        <v>4.58</v>
+        <v>2.54</v>
       </c>
       <c r="AE4">
-        <v>80.08</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="AF4">
-        <v>-70.22</v>
+        <v>-54.26</v>
       </c>
       <c r="AG4">
-        <v>3629.49</v>
+        <v>3607.71</v>
       </c>
       <c r="AH4">
-        <v>3143.47</v>
+        <v>3129.54</v>
       </c>
       <c r="AI4">
         <v>3443.75</v>
@@ -1209,7 +1209,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>26.93</v>
+        <v>25.36</v>
       </c>
     </row>
   </sheetData>
@@ -1407,13 +1407,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-6.33</v>
+        <v>-4.01</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.01</v>
+        <v>-6.47</v>
       </c>
       <c r="E7" s="6">
-        <v>2.32</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1424,13 +1424,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-11.74</v>
+        <v>-11.86</v>
       </c>
       <c r="D8" s="5">
-        <v>-11.86</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.12</v>
+        <v>-12.75</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1441,13 +1441,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-10.06</v>
+        <v>-9.51</v>
       </c>
       <c r="D9" s="5">
-        <v>-9.51</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.55</v>
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.29</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1458,13 +1458,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>0.58</v>
+        <v>-0.23</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.23</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.8100000000000001</v>
+        <v>-3.54</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-3.31</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1475,13 +1475,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-6.72</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="D11" s="5">
-        <v>-9.210000000000001</v>
+        <v>-8.76</v>
       </c>
       <c r="E11" s="7">
-        <v>-2.49</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1492,13 +1492,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-3.47</v>
+        <v>-4.22</v>
       </c>
       <c r="D12" s="5">
-        <v>-4.22</v>
+        <v>-2.88</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.75</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1509,13 +1509,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="D13" s="5">
-        <v>7.4</v>
+        <v>3.98</v>
       </c>
       <c r="E13" s="6">
-        <v>1.4</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1526,13 +1526,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>15.48</v>
+        <v>15.65</v>
       </c>
       <c r="D14" s="5">
-        <v>15.65</v>
+        <v>15.15</v>
       </c>
       <c r="E14" s="6">
-        <v>0.17</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1543,13 +1543,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-24.99</v>
+        <v>-22.32</v>
       </c>
       <c r="D15" s="5">
-        <v>-22.32</v>
-      </c>
-      <c r="E15" s="6">
-        <v>2.67</v>
+        <v>-22.15</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.17</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1560,13 +1560,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-8.49</v>
+        <v>-6.94</v>
       </c>
       <c r="D16" s="5">
-        <v>-6.94</v>
+        <v>-9.1</v>
       </c>
       <c r="E16" s="6">
-        <v>1.55</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1577,13 +1577,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-5.69</v>
+        <v>-5.03</v>
       </c>
       <c r="D17" s="5">
-        <v>-5.03</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="E17" s="6">
-        <v>0.66</v>
+        <v>-4.59</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1594,13 +1594,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-3.41</v>
+        <v>2.44</v>
       </c>
       <c r="D18" s="5">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="E18" s="6">
-        <v>5.85</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1611,13 +1611,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-11.82</v>
+        <v>-11.41</v>
       </c>
       <c r="D19" s="5">
-        <v>-11.41</v>
+        <v>-13.92</v>
       </c>
       <c r="E19" s="6">
-        <v>0.41</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1628,13 +1628,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-15.97</v>
+        <v>-15.38</v>
       </c>
       <c r="D20" s="5">
-        <v>-15.38</v>
+        <v>-16.31</v>
       </c>
       <c r="E20" s="6">
-        <v>0.59</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1645,13 +1645,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-30.9</v>
+        <v>-30.96</v>
       </c>
       <c r="D21" s="5">
-        <v>-30.96</v>
+        <v>-30.84</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.06</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1662,13 +1662,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>3858.4</v>
+        <v>3876.2</v>
       </c>
       <c r="D22" s="5">
-        <v>3876.2</v>
+        <v>3766.4</v>
       </c>
       <c r="E22" s="6">
-        <v>17.8</v>
+        <v>-109.8</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1679,13 +1679,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D23" s="5">
-        <v>284</v>
+        <v>280.85</v>
       </c>
       <c r="E23" s="6">
-        <v>2</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1696,13 +1696,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3209.1</v>
+        <v>3206.1</v>
       </c>
       <c r="D24" s="5">
-        <v>3206.1</v>
+        <v>3211.6</v>
       </c>
       <c r="E24" s="7">
-        <v>-3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1713,13 +1713,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>41.75</v>
+        <v>43.79</v>
       </c>
       <c r="D25" s="5">
-        <v>43.79</v>
+        <v>35.5</v>
       </c>
       <c r="E25" s="6">
-        <v>2.04</v>
+        <v>-8.289999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1730,13 +1730,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>34.48</v>
+        <v>36.01</v>
       </c>
       <c r="D26" s="5">
-        <v>36.01</v>
+        <v>34.63</v>
       </c>
       <c r="E26" s="6">
-        <v>1.53</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1747,13 +1747,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>28.87</v>
+        <v>28.68</v>
       </c>
       <c r="D27" s="5">
-        <v>28.68</v>
+        <v>29.62</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.19</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1764,13 +1764,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>19.57</v>
+        <v>-11.25</v>
       </c>
       <c r="D28" s="5">
-        <v>-11.25</v>
+        <v>-1.31</v>
       </c>
       <c r="E28" s="7">
-        <v>-30.82</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1781,13 +1781,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>848.3</v>
+        <v>15.74</v>
       </c>
       <c r="D29" s="5">
-        <v>15.74</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-832.5599999999999</v>
+        <v>3.29</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-12.45</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1798,13 +1798,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-65.45999999999999</v>
+        <v>-70.22</v>
       </c>
       <c r="D30" s="5">
-        <v>-70.22</v>
+        <v>-54.26</v>
       </c>
       <c r="E30" s="7">
-        <v>-4.76</v>
+        <v>15.96</v>
       </c>
     </row>
   </sheetData>
@@ -1869,16 +1869,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>36.2</v>
+        <v>33.2</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-8.5</v>
+        <v>-9.5</v>
       </c>
       <c r="G2" s="10">
-        <v>-3.2</v>
+        <v>-5.5</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1997,13 +1997,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.2832</v>
+        <v>0.2753</v>
       </c>
       <c r="B2" s="13">
-        <v>0.186</v>
+        <v>0.1794</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0643</v>
+        <v>-0.0585</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -881,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3766.4</v>
+        <v>3749.1</v>
       </c>
       <c r="D2">
-        <v>-2.83</v>
+        <v>-0.46</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -893,46 +893,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-13.92</v>
+        <v>-14.31</v>
       </c>
       <c r="H2">
-        <v>13.79</v>
+        <v>13.26</v>
       </c>
       <c r="I2">
-        <v>-3.54</v>
+        <v>-3.03</v>
       </c>
       <c r="J2">
-        <v>-6.47</v>
+        <v>-7.33</v>
       </c>
       <c r="K2">
-        <v>-9.1</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="L2">
-        <v>3.98</v>
+        <v>3.05</v>
       </c>
       <c r="M2">
-        <v>17.94</v>
+        <v>18.05</v>
       </c>
       <c r="N2">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="O2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P2">
-        <v>3859.46</v>
+        <v>3836</v>
       </c>
       <c r="Q2">
-        <v>3914.01</v>
+        <v>3899.22</v>
       </c>
       <c r="R2">
-        <v>3958.96</v>
+        <v>3957.17</v>
       </c>
       <c r="S2">
-        <v>3951.83</v>
+        <v>3950.81</v>
       </c>
       <c r="T2">
-        <v>-4.69</v>
+        <v>-5.11</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,43 +947,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>35.5</v>
+        <v>34.39</v>
       </c>
       <c r="Z2">
-        <v>-43.28</v>
+        <v>-50.3</v>
       </c>
       <c r="AA2">
-        <v>-34.46</v>
+        <v>-37.63</v>
       </c>
       <c r="AB2">
-        <v>-8.82</v>
+        <v>-12.67</v>
       </c>
       <c r="AC2">
-        <v>55.14</v>
+        <v>41.35</v>
       </c>
       <c r="AD2">
-        <v>69.34</v>
+        <v>58.56</v>
       </c>
       <c r="AE2">
-        <v>65.33</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="AF2">
-        <v>-1.31</v>
+        <v>83.36</v>
       </c>
       <c r="AG2">
-        <v>4054.4</v>
+        <v>4043.81</v>
       </c>
       <c r="AH2">
-        <v>3773.62</v>
+        <v>3754.63</v>
       </c>
       <c r="AI2">
-        <v>4008.3</v>
+        <v>3959.06</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>23.33</v>
+        <v>27.37</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>280.85</v>
+        <v>271.05</v>
       </c>
       <c r="D3">
-        <v>-1.11</v>
+        <v>-3.49</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1006,46 +1006,46 @@
         <v>233.88</v>
       </c>
       <c r="G3">
-        <v>-16.31</v>
+        <v>-19.23</v>
       </c>
       <c r="H3">
-        <v>20.08</v>
+        <v>15.89</v>
       </c>
       <c r="I3">
-        <v>-8.76</v>
+        <v>-11.1</v>
       </c>
       <c r="J3">
-        <v>-12.75</v>
+        <v>-13.76</v>
       </c>
       <c r="K3">
-        <v>-9.619999999999999</v>
+        <v>-13.32</v>
       </c>
       <c r="L3">
-        <v>15.15</v>
+        <v>10.95</v>
       </c>
       <c r="M3">
-        <v>27.53</v>
+        <v>26.28</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="O3">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="P3">
-        <v>292.35</v>
+        <v>285.58</v>
       </c>
       <c r="Q3">
-        <v>305.11</v>
+        <v>302.62</v>
       </c>
       <c r="R3">
-        <v>310.11</v>
+        <v>309.41</v>
       </c>
       <c r="S3">
-        <v>292.03</v>
+        <v>291.88</v>
       </c>
       <c r="T3">
-        <v>-3.83</v>
+        <v>-7.14</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,43 +1060,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>34.63</v>
+        <v>30.71</v>
       </c>
       <c r="Z3">
-        <v>-6.42</v>
+        <v>-8.07</v>
       </c>
       <c r="AA3">
-        <v>-3.55</v>
+        <v>-4.45</v>
       </c>
       <c r="AB3">
-        <v>-2.87</v>
+        <v>-3.62</v>
       </c>
       <c r="AC3">
         <v>3.25</v>
       </c>
       <c r="AD3">
-        <v>28.76</v>
+        <v>13.02</v>
       </c>
       <c r="AE3">
-        <v>9.6</v>
+        <v>9.76</v>
       </c>
       <c r="AF3">
-        <v>3.29</v>
+        <v>150.16</v>
       </c>
       <c r="AG3">
-        <v>328.15</v>
+        <v>328.99</v>
       </c>
       <c r="AH3">
-        <v>282.08</v>
+        <v>276.25</v>
       </c>
       <c r="AI3">
-        <v>309.42</v>
+        <v>304.66</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>29.64</v>
+        <v>33.98</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3211.6</v>
+        <v>3081.6</v>
       </c>
       <c r="D4">
-        <v>0.17</v>
+        <v>-4.05</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1119,46 +1119,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-30.84</v>
+        <v>-33.64</v>
       </c>
       <c r="H4">
-        <v>5.6</v>
+        <v>1.32</v>
       </c>
       <c r="I4">
-        <v>-2.88</v>
+        <v>-6.44</v>
       </c>
       <c r="J4">
-        <v>-9.220000000000001</v>
+        <v>-13.65</v>
       </c>
       <c r="K4">
-        <v>2.29</v>
+        <v>1.11</v>
       </c>
       <c r="L4">
-        <v>-22.15</v>
+        <v>-25.18</v>
       </c>
       <c r="M4">
-        <v>-5.85</v>
+        <v>-7.33</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P4">
-        <v>3230.34</v>
+        <v>3187.94</v>
       </c>
       <c r="Q4">
-        <v>3368.63</v>
+        <v>3342.29</v>
       </c>
       <c r="R4">
-        <v>3463.17</v>
+        <v>3457.81</v>
       </c>
       <c r="S4">
-        <v>3568.19</v>
+        <v>3560.89</v>
       </c>
       <c r="T4">
-        <v>-9.99</v>
+        <v>-13.46</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,43 +1173,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>29.62</v>
+        <v>22.17</v>
       </c>
       <c r="Z4">
-        <v>-74.75</v>
+        <v>-85.94</v>
       </c>
       <c r="AA4">
-        <v>-57.62</v>
+        <v>-63.28</v>
       </c>
       <c r="AB4">
-        <v>-17.14</v>
+        <v>-22.66</v>
       </c>
       <c r="AC4">
         <v>3.01</v>
       </c>
       <c r="AD4">
-        <v>2.54</v>
+        <v>2</v>
       </c>
       <c r="AE4">
-        <v>83.15000000000001</v>
+        <v>89.75</v>
       </c>
       <c r="AF4">
-        <v>-54.26</v>
+        <v>46.8</v>
       </c>
       <c r="AG4">
-        <v>3607.71</v>
+        <v>3586.17</v>
       </c>
       <c r="AH4">
-        <v>3129.54</v>
+        <v>3098.4</v>
       </c>
       <c r="AI4">
-        <v>3443.75</v>
+        <v>3408.79</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>25.36</v>
+        <v>27.99</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1407,13 +1407,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.01</v>
+        <v>-6.47</v>
       </c>
       <c r="D7" s="5">
-        <v>-6.47</v>
+        <v>-7.33</v>
       </c>
       <c r="E7" s="6">
-        <v>-2.46</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1424,13 +1424,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-11.86</v>
+        <v>-12.75</v>
       </c>
       <c r="D8" s="5">
-        <v>-12.75</v>
+        <v>-13.76</v>
       </c>
       <c r="E8" s="6">
-        <v>-0.89</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1441,13 +1441,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-9.51</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="D9" s="5">
-        <v>-9.220000000000001</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.29</v>
+        <v>-13.65</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-4.43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1458,13 +1458,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-0.23</v>
+        <v>-3.54</v>
       </c>
       <c r="D10" s="5">
-        <v>-3.54</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-3.31</v>
+        <v>-3.03</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.51</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1475,13 +1475,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-9.210000000000001</v>
+        <v>-8.76</v>
       </c>
       <c r="D11" s="5">
-        <v>-8.76</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.45</v>
+        <v>-11.1</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-2.34</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1492,13 +1492,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-4.22</v>
+        <v>-2.88</v>
       </c>
       <c r="D12" s="5">
-        <v>-2.88</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.34</v>
+        <v>-6.44</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-3.56</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1509,13 +1509,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>7.4</v>
+        <v>3.98</v>
       </c>
       <c r="D13" s="5">
-        <v>3.98</v>
+        <v>3.05</v>
       </c>
       <c r="E13" s="6">
-        <v>-3.42</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1526,13 +1526,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>15.65</v>
+        <v>15.15</v>
       </c>
       <c r="D14" s="5">
-        <v>15.15</v>
+        <v>10.95</v>
       </c>
       <c r="E14" s="6">
-        <v>-0.5</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1543,13 +1543,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-22.32</v>
+        <v>-22.15</v>
       </c>
       <c r="D15" s="5">
-        <v>-22.15</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.17</v>
+        <v>-25.18</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-3.03</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1560,13 +1560,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-6.94</v>
+        <v>-9.1</v>
       </c>
       <c r="D16" s="5">
-        <v>-9.1</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-2.16</v>
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.71</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1577,13 +1577,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-5.03</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="D17" s="5">
-        <v>-9.619999999999999</v>
+        <v>-13.32</v>
       </c>
       <c r="E17" s="6">
-        <v>-4.59</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1594,13 +1594,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="D18" s="5">
-        <v>2.29</v>
+        <v>1.11</v>
       </c>
       <c r="E18" s="6">
-        <v>-0.15</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1611,13 +1611,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-11.41</v>
+        <v>-13.92</v>
       </c>
       <c r="D19" s="5">
-        <v>-13.92</v>
+        <v>-14.31</v>
       </c>
       <c r="E19" s="6">
-        <v>-2.51</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1628,13 +1628,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-15.38</v>
+        <v>-16.31</v>
       </c>
       <c r="D20" s="5">
-        <v>-16.31</v>
+        <v>-19.23</v>
       </c>
       <c r="E20" s="6">
-        <v>-0.93</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1645,13 +1645,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-30.96</v>
+        <v>-30.84</v>
       </c>
       <c r="D21" s="5">
-        <v>-30.84</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.12</v>
+        <v>-33.64</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-2.8</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1662,13 +1662,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>3876.2</v>
+        <v>3766.4</v>
       </c>
       <c r="D22" s="5">
-        <v>3766.4</v>
+        <v>3749.1</v>
       </c>
       <c r="E22" s="6">
-        <v>-109.8</v>
+        <v>-17.3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1679,13 +1679,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>284</v>
+        <v>280.85</v>
       </c>
       <c r="D23" s="5">
-        <v>280.85</v>
+        <v>271.05</v>
       </c>
       <c r="E23" s="6">
-        <v>-3.15</v>
+        <v>-9.800000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1696,13 +1696,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3206.1</v>
+        <v>3211.6</v>
       </c>
       <c r="D24" s="5">
-        <v>3211.6</v>
-      </c>
-      <c r="E24" s="7">
-        <v>5.5</v>
+        <v>3081.6</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-130</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1710,16 +1710,16 @@
         <v>37</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C25" s="5">
-        <v>43.79</v>
+        <v>66</v>
       </c>
       <c r="D25" s="5">
-        <v>35.5</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-8.289999999999999</v>
+        <v>99</v>
+      </c>
+      <c r="E25" s="7">
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1727,84 +1727,118 @@
         <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C26" s="5">
-        <v>36.01</v>
+        <v>99</v>
       </c>
       <c r="D26" s="5">
-        <v>34.63</v>
+        <v>66</v>
       </c>
       <c r="E26" s="6">
-        <v>-1.38</v>
+        <v>-33</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>28.68</v>
+        <v>35.5</v>
       </c>
       <c r="D27" s="5">
-        <v>29.62</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.9399999999999999</v>
+        <v>34.39</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C28" s="5">
-        <v>-11.25</v>
+        <v>34.63</v>
       </c>
       <c r="D28" s="5">
-        <v>-1.31</v>
-      </c>
-      <c r="E28" s="7">
-        <v>9.94</v>
+        <v>30.71</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-3.92</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C29" s="5">
-        <v>15.74</v>
+        <v>29.62</v>
       </c>
       <c r="D29" s="5">
-        <v>3.29</v>
+        <v>22.17</v>
       </c>
       <c r="E29" s="6">
-        <v>-12.45</v>
+        <v>-7.45</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-70.22</v>
+        <v>-1.31</v>
       </c>
       <c r="D30" s="5">
+        <v>83.36</v>
+      </c>
+      <c r="E30" s="7">
+        <v>84.67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="5">
+        <v>3.29</v>
+      </c>
+      <c r="D31" s="5">
+        <v>150.16</v>
+      </c>
+      <c r="E31" s="7">
+        <v>146.87</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="5">
         <v>-54.26</v>
       </c>
-      <c r="E30" s="7">
-        <v>15.96</v>
+      <c r="D32" s="5">
+        <v>46.8</v>
+      </c>
+      <c r="E32" s="7">
+        <v>101.06</v>
       </c>
     </row>
   </sheetData>
@@ -1869,16 +1903,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>33.2</v>
+        <v>29.1</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-9.5</v>
+        <v>-11.6</v>
       </c>
       <c r="G2" s="10">
-        <v>-5.5</v>
+        <v>-6.9</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1997,13 +2031,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.2753</v>
+        <v>0.2628</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1794</v>
+        <v>0.1805</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0585</v>
+        <v>-0.0733</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,7 +157,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>22.2 → 40.4</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>22.2</t>
+  </si>
+  <si>
+    <t>40.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -243,14 +270,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +310,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -359,14 +386,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -881,10 +909,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3749.1</v>
+        <v>3760</v>
       </c>
       <c r="D2">
-        <v>-0.46</v>
+        <v>0.29</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -893,46 +921,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-14.31</v>
+        <v>-14.06</v>
       </c>
       <c r="H2">
-        <v>13.26</v>
+        <v>13.59</v>
       </c>
       <c r="I2">
-        <v>-3.03</v>
+        <v>-4.32</v>
       </c>
       <c r="J2">
-        <v>-7.33</v>
+        <v>-7.04</v>
       </c>
       <c r="K2">
-        <v>-8.390000000000001</v>
+        <v>-7.38</v>
       </c>
       <c r="L2">
-        <v>3.05</v>
+        <v>4.18</v>
       </c>
       <c r="M2">
-        <v>18.05</v>
+        <v>18.37</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P2">
-        <v>3836</v>
+        <v>3802.02</v>
       </c>
       <c r="Q2">
-        <v>3899.22</v>
+        <v>3888.21</v>
       </c>
       <c r="R2">
-        <v>3957.17</v>
+        <v>3955.44</v>
       </c>
       <c r="S2">
-        <v>3950.81</v>
+        <v>3949.79</v>
       </c>
       <c r="T2">
-        <v>-5.11</v>
+        <v>-4.8</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,43 +975,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>34.39</v>
+        <v>35.75</v>
       </c>
       <c r="Z2">
-        <v>-50.3</v>
+        <v>-54.35</v>
       </c>
       <c r="AA2">
-        <v>-37.63</v>
+        <v>-40.97</v>
       </c>
       <c r="AB2">
-        <v>-12.67</v>
+        <v>-13.38</v>
       </c>
       <c r="AC2">
-        <v>41.35</v>
+        <v>26.26</v>
       </c>
       <c r="AD2">
-        <v>58.56</v>
+        <v>40.92</v>
       </c>
       <c r="AE2">
-        <v>64.34999999999999</v>
+        <v>63.79</v>
       </c>
       <c r="AF2">
-        <v>83.36</v>
+        <v>63.24</v>
       </c>
       <c r="AG2">
-        <v>4043.81</v>
+        <v>4040.21</v>
       </c>
       <c r="AH2">
-        <v>3754.63</v>
+        <v>3736.22</v>
       </c>
       <c r="AI2">
-        <v>3959.06</v>
+        <v>3949.63</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>27.37</v>
+        <v>31.22</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +1022,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>271.05</v>
+        <v>265</v>
       </c>
       <c r="D3">
-        <v>-3.49</v>
+        <v>-2.23</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1006,46 +1034,46 @@
         <v>233.88</v>
       </c>
       <c r="G3">
-        <v>-19.23</v>
+        <v>-21.04</v>
       </c>
       <c r="H3">
-        <v>15.89</v>
+        <v>13.31</v>
       </c>
       <c r="I3">
-        <v>-11.1</v>
+        <v>-14.52</v>
       </c>
       <c r="J3">
-        <v>-13.76</v>
+        <v>-17.45</v>
       </c>
       <c r="K3">
-        <v>-13.32</v>
+        <v>-15.94</v>
       </c>
       <c r="L3">
-        <v>10.95</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M3">
-        <v>26.28</v>
+        <v>25.42</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="P3">
-        <v>285.58</v>
+        <v>276.58</v>
       </c>
       <c r="Q3">
-        <v>302.62</v>
+        <v>300.41</v>
       </c>
       <c r="R3">
-        <v>309.41</v>
+        <v>308.58</v>
       </c>
       <c r="S3">
-        <v>291.88</v>
+        <v>291.71</v>
       </c>
       <c r="T3">
-        <v>-7.14</v>
+        <v>-9.16</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,43 +1088,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>30.71</v>
+        <v>28.55</v>
       </c>
       <c r="Z3">
-        <v>-8.07</v>
+        <v>-9.76</v>
       </c>
       <c r="AA3">
-        <v>-4.45</v>
+        <v>-5.51</v>
       </c>
       <c r="AB3">
-        <v>-3.62</v>
+        <v>-4.25</v>
       </c>
       <c r="AC3">
-        <v>3.25</v>
+        <v>0.3</v>
       </c>
       <c r="AD3">
-        <v>13.02</v>
+        <v>2.27</v>
       </c>
       <c r="AE3">
-        <v>9.76</v>
+        <v>9.66</v>
       </c>
       <c r="AF3">
-        <v>150.16</v>
+        <v>5.01</v>
       </c>
       <c r="AG3">
-        <v>328.99</v>
+        <v>331.47</v>
       </c>
       <c r="AH3">
-        <v>276.25</v>
+        <v>269.36</v>
       </c>
       <c r="AI3">
-        <v>304.66</v>
+        <v>298.05</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>33.98</v>
+        <v>38.27</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1135,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3081.6</v>
+        <v>3228.6</v>
       </c>
       <c r="D4">
-        <v>-4.05</v>
+        <v>4.77</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1119,46 +1147,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-33.64</v>
+        <v>-30.48</v>
       </c>
       <c r="H4">
-        <v>1.32</v>
+        <v>6.16</v>
       </c>
       <c r="I4">
-        <v>-6.44</v>
+        <v>-0.08</v>
       </c>
       <c r="J4">
-        <v>-13.65</v>
+        <v>-10.53</v>
       </c>
       <c r="K4">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="L4">
-        <v>-25.18</v>
+        <v>-20.42</v>
       </c>
       <c r="M4">
-        <v>-7.33</v>
+        <v>-6.11</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P4">
-        <v>3187.94</v>
+        <v>3187.4</v>
       </c>
       <c r="Q4">
-        <v>3342.29</v>
+        <v>3324.33</v>
       </c>
       <c r="R4">
-        <v>3457.81</v>
+        <v>3456.26</v>
       </c>
       <c r="S4">
-        <v>3560.89</v>
+        <v>3553.96</v>
       </c>
       <c r="T4">
-        <v>-13.46</v>
+        <v>-9.15</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,34 +1201,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>22.17</v>
+        <v>40.42</v>
       </c>
       <c r="Z4">
-        <v>-85.94</v>
+        <v>-82</v>
       </c>
       <c r="AA4">
-        <v>-63.28</v>
+        <v>-67.02</v>
       </c>
       <c r="AB4">
-        <v>-22.66</v>
+        <v>-14.98</v>
       </c>
       <c r="AC4">
-        <v>3.01</v>
+        <v>36.34</v>
       </c>
       <c r="AD4">
-        <v>2</v>
+        <v>14.12</v>
       </c>
       <c r="AE4">
-        <v>89.75</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="AF4">
-        <v>46.8</v>
+        <v>79.62</v>
       </c>
       <c r="AG4">
-        <v>3586.17</v>
+        <v>3543.76</v>
       </c>
       <c r="AH4">
-        <v>3098.4</v>
+        <v>3104.89</v>
       </c>
       <c r="AI4">
         <v>3408.79</v>
@@ -1209,7 +1237,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>27.99</v>
+        <v>28.4</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1378,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1370,12 +1398,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>45</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1383,462 +1446,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-6.47</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-7.33</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.86</v>
+      <c r="D7" s="6">
+        <v>-7.04</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.29</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-12.75</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-13.76</v>
       </c>
-      <c r="E8" s="6">
-        <v>-1.01</v>
+      <c r="D8" s="6">
+        <v>-17.45</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-3.69</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-9.220000000000001</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-13.65</v>
       </c>
-      <c r="E9" s="6">
-        <v>-4.43</v>
+      <c r="D9" s="6">
+        <v>-10.53</v>
+      </c>
+      <c r="E9" s="7">
+        <v>3.12</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-3.54</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-3.03</v>
       </c>
-      <c r="E10" s="7">
-        <v>0.51</v>
+      <c r="D10" s="6">
+        <v>-4.32</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-8.76</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-11.1</v>
       </c>
-      <c r="E11" s="6">
-        <v>-2.34</v>
+      <c r="D11" s="6">
+        <v>-14.52</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-3.42</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-2.88</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-6.44</v>
       </c>
-      <c r="E12" s="6">
-        <v>-3.56</v>
+      <c r="D12" s="6">
+        <v>-0.08</v>
+      </c>
+      <c r="E12" s="7">
+        <v>6.36</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>3.98</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>3.05</v>
       </c>
-      <c r="E13" s="6">
-        <v>-0.93</v>
+      <c r="D13" s="6">
+        <v>4.18</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.13</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>15.15</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>10.95</v>
       </c>
-      <c r="E14" s="6">
-        <v>-4.2</v>
+      <c r="D14" s="6">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-22.15</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-25.18</v>
       </c>
-      <c r="E15" s="6">
-        <v>-3.03</v>
+      <c r="D15" s="6">
+        <v>-20.42</v>
+      </c>
+      <c r="E15" s="7">
+        <v>4.76</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-9.1</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-8.390000000000001</v>
       </c>
+      <c r="D16" s="6">
+        <v>-7.38</v>
+      </c>
       <c r="E16" s="7">
-        <v>0.71</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-9.619999999999999</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-13.32</v>
       </c>
-      <c r="E17" s="6">
-        <v>-3.7</v>
+      <c r="D17" s="6">
+        <v>-15.94</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-2.62</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>2.29</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>1.11</v>
       </c>
-      <c r="E18" s="6">
-        <v>-1.18</v>
+      <c r="D18" s="6">
+        <v>1.95</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.84</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-13.92</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-14.31</v>
       </c>
-      <c r="E19" s="6">
-        <v>-0.39</v>
+      <c r="D19" s="6">
+        <v>-14.06</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.25</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-16.31</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-19.23</v>
       </c>
-      <c r="E20" s="6">
-        <v>-2.92</v>
+      <c r="D20" s="6">
+        <v>-21.04</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.81</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-30.84</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-33.64</v>
       </c>
-      <c r="E21" s="6">
-        <v>-2.8</v>
+      <c r="D21" s="6">
+        <v>-30.48</v>
+      </c>
+      <c r="E21" s="7">
+        <v>3.16</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>3766.4</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>3749.1</v>
       </c>
-      <c r="E22" s="6">
-        <v>-17.3</v>
+      <c r="D22" s="6">
+        <v>3760</v>
+      </c>
+      <c r="E22" s="7">
+        <v>10.9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>280.85</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>271.05</v>
       </c>
-      <c r="E23" s="6">
-        <v>-9.800000000000001</v>
+      <c r="D23" s="6">
+        <v>265</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-6.05</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>3211.6</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>3081.6</v>
       </c>
-      <c r="E24" s="6">
-        <v>-130</v>
+      <c r="D24" s="6">
+        <v>3228.6</v>
+      </c>
+      <c r="E24" s="7">
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="5">
-        <v>66</v>
-      </c>
-      <c r="D25" s="5">
-        <v>99</v>
+      <c r="B25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="6">
+        <v>34.39</v>
+      </c>
+      <c r="D25" s="6">
+        <v>35.75</v>
       </c>
       <c r="E25" s="7">
-        <v>33</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="5">
-        <v>99</v>
-      </c>
-      <c r="D26" s="5">
-        <v>66</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-33</v>
+      <c r="B26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="6">
+        <v>30.71</v>
+      </c>
+      <c r="D26" s="6">
+        <v>28.55</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>22.17</v>
+      </c>
+      <c r="D27" s="6">
+        <v>40.42</v>
+      </c>
+      <c r="E27" s="7">
+        <v>18.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>35.5</v>
-      </c>
-      <c r="D27" s="5">
-        <v>34.39</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6">
+        <v>83.36</v>
+      </c>
+      <c r="D28" s="6">
+        <v>63.24</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-20.12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="5">
-        <v>34.63</v>
-      </c>
-      <c r="D28" s="5">
-        <v>30.71</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-3.92</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="6">
+        <v>150.16</v>
+      </c>
+      <c r="D29" s="6">
+        <v>5.01</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-145.15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="5">
-        <v>29.62</v>
-      </c>
-      <c r="D29" s="5">
-        <v>22.17</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-7.45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>-1.31</v>
-      </c>
-      <c r="D30" s="5">
-        <v>83.36</v>
+      <c r="C30" s="6">
+        <v>46.8</v>
+      </c>
+      <c r="D30" s="6">
+        <v>79.62</v>
       </c>
       <c r="E30" s="7">
-        <v>84.67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="5">
-        <v>3.29</v>
-      </c>
-      <c r="D31" s="5">
-        <v>150.16</v>
-      </c>
-      <c r="E31" s="7">
-        <v>146.87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-54.26</v>
-      </c>
-      <c r="D32" s="5">
-        <v>46.8</v>
-      </c>
-      <c r="E32" s="7">
-        <v>101.06</v>
+        <v>32.82</v>
       </c>
     </row>
   </sheetData>
@@ -1864,60 +1893,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>58</v>
+      <c r="B1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>36.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>29.1</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>34.9</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-11.6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-6.9</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-11.7</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-7.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2019,25 +2048,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.2628</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1805</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0733</v>
+      <c r="A2" s="14">
+        <v>0.2542</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1837</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0611</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,34 +157,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>22.2 → 40.4</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>22.2</t>
-  </si>
-  <si>
-    <t>40.4</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -270,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -310,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,15 +359,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -909,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3760</v>
+        <v>3693.4</v>
       </c>
       <c r="D2">
-        <v>0.29</v>
+        <v>-1.77</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -921,46 +893,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-14.06</v>
+        <v>-15.59</v>
       </c>
       <c r="H2">
-        <v>13.59</v>
+        <v>11.58</v>
       </c>
       <c r="I2">
-        <v>-4.32</v>
+        <v>-4.28</v>
       </c>
       <c r="J2">
-        <v>-7.04</v>
+        <v>-7.2</v>
       </c>
       <c r="K2">
-        <v>-7.38</v>
+        <v>-8.27</v>
       </c>
       <c r="L2">
-        <v>4.18</v>
+        <v>-0</v>
       </c>
       <c r="M2">
-        <v>18.37</v>
+        <v>18.03</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P2">
-        <v>3802.02</v>
+        <v>3769.02</v>
       </c>
       <c r="Q2">
-        <v>3888.21</v>
+        <v>3873.83</v>
       </c>
       <c r="R2">
-        <v>3955.44</v>
+        <v>3952.96</v>
       </c>
       <c r="S2">
-        <v>3949.79</v>
+        <v>3948.08</v>
       </c>
       <c r="T2">
-        <v>-4.8</v>
+        <v>-6.45</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -975,43 +947,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>35.75</v>
+        <v>31.47</v>
       </c>
       <c r="Z2">
-        <v>-54.35</v>
+        <v>-62.22</v>
       </c>
       <c r="AA2">
-        <v>-40.97</v>
+        <v>-45.22</v>
       </c>
       <c r="AB2">
-        <v>-13.38</v>
+        <v>-17</v>
       </c>
       <c r="AC2">
-        <v>26.26</v>
+        <v>18.69</v>
       </c>
       <c r="AD2">
-        <v>40.92</v>
+        <v>28.77</v>
       </c>
       <c r="AE2">
-        <v>63.79</v>
+        <v>66.67</v>
       </c>
       <c r="AF2">
-        <v>63.24</v>
+        <v>47.18</v>
       </c>
       <c r="AG2">
-        <v>4040.21</v>
+        <v>4042.38</v>
       </c>
       <c r="AH2">
-        <v>3736.22</v>
+        <v>3705.29</v>
       </c>
       <c r="AI2">
-        <v>3949.63</v>
+        <v>3896.62</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>31.22</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1022,58 +994,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>265</v>
+        <v>264.35</v>
       </c>
       <c r="D3">
-        <v>-2.23</v>
+        <v>-0.25</v>
       </c>
       <c r="E3">
         <v>335.6</v>
       </c>
       <c r="F3">
-        <v>233.88</v>
+        <v>237.75</v>
       </c>
       <c r="G3">
-        <v>-21.04</v>
+        <v>-21.23</v>
       </c>
       <c r="H3">
-        <v>13.31</v>
+        <v>11.19</v>
       </c>
       <c r="I3">
-        <v>-14.52</v>
+        <v>-6.26</v>
       </c>
       <c r="J3">
-        <v>-17.45</v>
+        <v>-14.46</v>
       </c>
       <c r="K3">
-        <v>-15.94</v>
+        <v>-19.16</v>
       </c>
       <c r="L3">
-        <v>9.699999999999999</v>
+        <v>13.03</v>
       </c>
       <c r="M3">
-        <v>25.42</v>
+        <v>25.72</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P3">
-        <v>276.58</v>
+        <v>273.05</v>
       </c>
       <c r="Q3">
-        <v>300.41</v>
+        <v>297.99</v>
       </c>
       <c r="R3">
-        <v>308.58</v>
+        <v>307.74</v>
       </c>
       <c r="S3">
-        <v>291.71</v>
+        <v>291.51</v>
       </c>
       <c r="T3">
-        <v>-9.16</v>
+        <v>-9.32</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1088,43 +1060,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>28.55</v>
+        <v>28.32</v>
       </c>
       <c r="Z3">
-        <v>-9.76</v>
+        <v>-11.02</v>
       </c>
       <c r="AA3">
-        <v>-5.51</v>
+        <v>-6.61</v>
       </c>
       <c r="AB3">
-        <v>-4.25</v>
+        <v>-4.41</v>
       </c>
       <c r="AC3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>2.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE3">
-        <v>9.66</v>
+        <v>9.69</v>
       </c>
       <c r="AF3">
-        <v>5.01</v>
+        <v>14.42</v>
       </c>
       <c r="AG3">
-        <v>331.47</v>
+        <v>332.36</v>
       </c>
       <c r="AH3">
-        <v>269.36</v>
+        <v>263.63</v>
       </c>
       <c r="AI3">
-        <v>298.05</v>
+        <v>295.84</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>38.27</v>
+        <v>42.33</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1135,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3228.6</v>
+        <v>3267.8</v>
       </c>
       <c r="D4">
-        <v>4.77</v>
+        <v>1.21</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1147,46 +1119,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-30.48</v>
+        <v>-29.63</v>
       </c>
       <c r="H4">
-        <v>6.16</v>
+        <v>7.45</v>
       </c>
       <c r="I4">
-        <v>-0.08</v>
+        <v>1.83</v>
       </c>
       <c r="J4">
-        <v>-10.53</v>
+        <v>-8.92</v>
       </c>
       <c r="K4">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="L4">
-        <v>-20.42</v>
+        <v>-18.23</v>
       </c>
       <c r="M4">
-        <v>-6.11</v>
+        <v>-5.67</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="P4">
-        <v>3187.4</v>
+        <v>3199.14</v>
       </c>
       <c r="Q4">
-        <v>3324.33</v>
+        <v>3312.47</v>
       </c>
       <c r="R4">
-        <v>3456.26</v>
+        <v>3454.95</v>
       </c>
       <c r="S4">
-        <v>3553.96</v>
+        <v>3547.18</v>
       </c>
       <c r="T4">
-        <v>-9.15</v>
+        <v>-7.88</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1201,34 +1173,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>40.42</v>
+        <v>44.18</v>
       </c>
       <c r="Z4">
-        <v>-82</v>
+        <v>-74.84999999999999</v>
       </c>
       <c r="AA4">
-        <v>-67.02</v>
+        <v>-68.59</v>
       </c>
       <c r="AB4">
-        <v>-14.98</v>
+        <v>-6.26</v>
       </c>
       <c r="AC4">
-        <v>36.34</v>
+        <v>66.67</v>
       </c>
       <c r="AD4">
-        <v>14.12</v>
+        <v>35.34</v>
       </c>
       <c r="AE4">
-        <v>95.70999999999999</v>
+        <v>97.09</v>
       </c>
       <c r="AF4">
-        <v>79.62</v>
+        <v>44</v>
       </c>
       <c r="AG4">
-        <v>3543.76</v>
+        <v>3515.84</v>
       </c>
       <c r="AH4">
-        <v>3104.89</v>
+        <v>3109.09</v>
       </c>
       <c r="AI4">
         <v>3408.79</v>
@@ -1237,7 +1209,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>28.4</v>
+        <v>27.16</v>
       </c>
     </row>
   </sheetData>
@@ -1398,47 +1370,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1446,428 +1383,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>59</v>
+      <c r="B6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-7.33</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-7.04</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.29</v>
+      <c r="D7" s="5">
+        <v>-7.2</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-13.76</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-17.45</v>
       </c>
-      <c r="E8" s="8">
-        <v>-3.69</v>
+      <c r="D8" s="5">
+        <v>-14.46</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.99</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-13.65</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-10.53</v>
       </c>
+      <c r="D9" s="5">
+        <v>-8.92</v>
+      </c>
       <c r="E9" s="7">
-        <v>3.12</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-3.03</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-4.32</v>
       </c>
-      <c r="E10" s="8">
-        <v>-1.29</v>
+      <c r="D10" s="5">
+        <v>-4.28</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.04</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-11.1</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-14.52</v>
       </c>
-      <c r="E11" s="8">
-        <v>-3.42</v>
+      <c r="D11" s="5">
+        <v>-6.26</v>
+      </c>
+      <c r="E11" s="7">
+        <v>8.26</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-6.44</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-0.08</v>
       </c>
+      <c r="D12" s="5">
+        <v>1.83</v>
+      </c>
       <c r="E12" s="7">
-        <v>6.36</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>3.05</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>4.18</v>
       </c>
-      <c r="E13" s="7">
-        <v>1.13</v>
+      <c r="D13" s="5">
+        <v>-0</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-4.18</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>10.95</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>9.699999999999999</v>
       </c>
-      <c r="E14" s="8">
-        <v>-1.25</v>
+      <c r="D14" s="5">
+        <v>13.03</v>
+      </c>
+      <c r="E14" s="7">
+        <v>3.33</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-25.18</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-20.42</v>
       </c>
+      <c r="D15" s="5">
+        <v>-18.23</v>
+      </c>
       <c r="E15" s="7">
-        <v>4.76</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>-8.390000000000001</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-7.38</v>
       </c>
-      <c r="E16" s="7">
-        <v>1.01</v>
+      <c r="D16" s="5">
+        <v>-8.27</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-13.32</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-15.94</v>
       </c>
-      <c r="E17" s="8">
-        <v>-2.62</v>
+      <c r="D17" s="5">
+        <v>-19.16</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-3.22</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>1.11</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>1.95</v>
       </c>
-      <c r="E18" s="7">
-        <v>0.84</v>
+      <c r="D18" s="5">
+        <v>1.92</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-14.31</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-14.06</v>
       </c>
-      <c r="E19" s="7">
-        <v>0.25</v>
+      <c r="D19" s="5">
+        <v>-15.59</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-1.53</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-19.23</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-21.04</v>
       </c>
-      <c r="E20" s="8">
-        <v>-1.81</v>
+      <c r="D20" s="5">
+        <v>-21.23</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-33.64</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>-30.48</v>
       </c>
+      <c r="D21" s="5">
+        <v>-29.63</v>
+      </c>
       <c r="E21" s="7">
-        <v>3.16</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>3749.1</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>3760</v>
       </c>
-      <c r="E22" s="7">
-        <v>10.9</v>
+      <c r="D22" s="5">
+        <v>3693.4</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-66.59999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>271.05</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>265</v>
       </c>
-      <c r="E23" s="8">
-        <v>-6.05</v>
+      <c r="D23" s="5">
+        <v>264.35</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>3081.6</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>3228.6</v>
       </c>
+      <c r="D24" s="5">
+        <v>3267.8</v>
+      </c>
       <c r="E24" s="7">
-        <v>147</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="6">
-        <v>34.39</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="5">
         <v>35.75</v>
       </c>
-      <c r="E25" s="7">
-        <v>1.36</v>
+      <c r="D25" s="5">
+        <v>31.47</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-4.28</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="6">
-        <v>30.71</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="5">
         <v>28.55</v>
       </c>
-      <c r="E26" s="8">
-        <v>-2.16</v>
+      <c r="D26" s="5">
+        <v>28.32</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="6">
-        <v>22.17</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C27" s="5">
         <v>40.42</v>
       </c>
+      <c r="D27" s="5">
+        <v>44.18</v>
+      </c>
       <c r="E27" s="7">
-        <v>18.25</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>83.36</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" s="5">
         <v>63.24</v>
       </c>
-      <c r="E28" s="8">
-        <v>-20.12</v>
+      <c r="D28" s="5">
+        <v>47.18</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-16.06</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>150.16</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="5">
         <v>5.01</v>
       </c>
-      <c r="E29" s="8">
-        <v>-145.15</v>
+      <c r="D29" s="5">
+        <v>14.42</v>
+      </c>
+      <c r="E29" s="7">
+        <v>9.41</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>46.8</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>79.62</v>
       </c>
-      <c r="E30" s="7">
-        <v>32.82</v>
+      <c r="D30" s="5">
+        <v>44</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-35.62</v>
       </c>
     </row>
   </sheetData>
@@ -1893,60 +1830,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>67</v>
+      <c r="B1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>34.9</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>34.7</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-11.7</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-7.1</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-10.2</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-8.5</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2048,25 +1985,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.2542</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1837</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0611</v>
+      <c r="A2" s="13">
+        <v>0.2572</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1803</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0567</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -243,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -881,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3693.4</v>
+        <v>3750</v>
       </c>
       <c r="D2">
-        <v>-1.77</v>
+        <v>1.53</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -893,46 +893,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-15.59</v>
+        <v>-14.29</v>
       </c>
       <c r="H2">
-        <v>11.58</v>
+        <v>13.29</v>
       </c>
       <c r="I2">
-        <v>-4.28</v>
+        <v>-3.26</v>
       </c>
       <c r="J2">
+        <v>-5.8</v>
+      </c>
+      <c r="K2">
         <v>-7.2</v>
       </c>
-      <c r="K2">
-        <v>-8.27</v>
-      </c>
       <c r="L2">
-        <v>-0</v>
+        <v>2.66</v>
       </c>
       <c r="M2">
-        <v>18.03</v>
+        <v>18.11</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="P2">
-        <v>3769.02</v>
+        <v>3743.78</v>
       </c>
       <c r="Q2">
-        <v>3873.83</v>
+        <v>3862.58</v>
       </c>
       <c r="R2">
-        <v>3952.96</v>
+        <v>3952.11</v>
       </c>
       <c r="S2">
-        <v>3948.08</v>
+        <v>3946.57</v>
       </c>
       <c r="T2">
-        <v>-6.45</v>
+        <v>-4.98</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,34 +947,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>31.47</v>
+        <v>38.24</v>
       </c>
       <c r="Z2">
-        <v>-62.22</v>
+        <v>-63.16</v>
       </c>
       <c r="AA2">
-        <v>-45.22</v>
+        <v>-48.81</v>
       </c>
       <c r="AB2">
-        <v>-17</v>
+        <v>-14.35</v>
       </c>
       <c r="AC2">
-        <v>18.69</v>
+        <v>25.91</v>
       </c>
       <c r="AD2">
-        <v>28.77</v>
+        <v>23.62</v>
       </c>
       <c r="AE2">
-        <v>66.67</v>
+        <v>65.95</v>
       </c>
       <c r="AF2">
-        <v>47.18</v>
+        <v>48.14</v>
       </c>
       <c r="AG2">
-        <v>4042.38</v>
+        <v>4032.73</v>
       </c>
       <c r="AH2">
-        <v>3705.29</v>
+        <v>3692.44</v>
       </c>
       <c r="AI2">
         <v>3896.62</v>
@@ -983,7 +983,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>36.44</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>264.35</v>
+        <v>263.75</v>
       </c>
       <c r="D3">
-        <v>-0.25</v>
+        <v>-0.23</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1006,46 +1006,46 @@
         <v>237.75</v>
       </c>
       <c r="G3">
-        <v>-21.23</v>
+        <v>-21.41</v>
       </c>
       <c r="H3">
-        <v>11.19</v>
+        <v>10.94</v>
       </c>
       <c r="I3">
-        <v>-6.26</v>
+        <v>-7.13</v>
       </c>
       <c r="J3">
-        <v>-14.46</v>
+        <v>-15.68</v>
       </c>
       <c r="K3">
-        <v>-19.16</v>
+        <v>-21.41</v>
       </c>
       <c r="L3">
-        <v>13.03</v>
+        <v>8.83</v>
       </c>
       <c r="M3">
-        <v>25.72</v>
+        <v>25.26</v>
       </c>
       <c r="N3">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="O3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P3">
-        <v>273.05</v>
+        <v>269</v>
       </c>
       <c r="Q3">
-        <v>297.99</v>
+        <v>295.33</v>
       </c>
       <c r="R3">
-        <v>307.74</v>
+        <v>306.92</v>
       </c>
       <c r="S3">
-        <v>291.51</v>
+        <v>291.32</v>
       </c>
       <c r="T3">
-        <v>-9.32</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,43 +1060,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>28.32</v>
+        <v>28.1</v>
       </c>
       <c r="Z3">
-        <v>-11.02</v>
+        <v>-11.93</v>
       </c>
       <c r="AA3">
-        <v>-6.61</v>
+        <v>-7.68</v>
       </c>
       <c r="AB3">
-        <v>-4.41</v>
+        <v>-4.25</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>1.18</v>
+        <v>0.1</v>
       </c>
       <c r="AE3">
-        <v>9.69</v>
+        <v>9.33</v>
       </c>
       <c r="AF3">
-        <v>14.42</v>
+        <v>-32.84</v>
       </c>
       <c r="AG3">
-        <v>332.36</v>
+        <v>331.71</v>
       </c>
       <c r="AH3">
-        <v>263.63</v>
+        <v>258.96</v>
       </c>
       <c r="AI3">
-        <v>295.84</v>
+        <v>293.34</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>42.33</v>
+        <v>45.86</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3267.8</v>
+        <v>3219.5</v>
       </c>
       <c r="D4">
-        <v>1.21</v>
+        <v>-1.48</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1119,46 +1119,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-29.63</v>
+        <v>-30.67</v>
       </c>
       <c r="H4">
-        <v>7.45</v>
+        <v>5.86</v>
       </c>
       <c r="I4">
+        <v>0.42</v>
+      </c>
+      <c r="J4">
+        <v>-8.15</v>
+      </c>
+      <c r="K4">
         <v>1.83</v>
       </c>
-      <c r="J4">
-        <v>-8.92</v>
-      </c>
-      <c r="K4">
-        <v>1.92</v>
-      </c>
       <c r="L4">
-        <v>-18.23</v>
+        <v>-17.99</v>
       </c>
       <c r="M4">
-        <v>-5.67</v>
+        <v>-6.05</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="O4">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P4">
-        <v>3199.14</v>
+        <v>3201.82</v>
       </c>
       <c r="Q4">
-        <v>3312.47</v>
+        <v>3298.38</v>
       </c>
       <c r="R4">
-        <v>3454.95</v>
+        <v>3451.83</v>
       </c>
       <c r="S4">
-        <v>3547.18</v>
+        <v>3540.48</v>
       </c>
       <c r="T4">
-        <v>-7.88</v>
+        <v>-9.07</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,34 +1173,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>44.18</v>
+        <v>40.77</v>
       </c>
       <c r="Z4">
-        <v>-74.84999999999999</v>
+        <v>-72.25</v>
       </c>
       <c r="AA4">
-        <v>-68.59</v>
+        <v>-69.31999999999999</v>
       </c>
       <c r="AB4">
-        <v>-6.26</v>
+        <v>-2.93</v>
       </c>
       <c r="AC4">
-        <v>66.67</v>
+        <v>94.83</v>
       </c>
       <c r="AD4">
-        <v>35.34</v>
+        <v>65.95</v>
       </c>
       <c r="AE4">
-        <v>97.09</v>
+        <v>97.64</v>
       </c>
       <c r="AF4">
-        <v>44</v>
+        <v>8.25</v>
       </c>
       <c r="AG4">
-        <v>3515.84</v>
+        <v>3485.05</v>
       </c>
       <c r="AH4">
-        <v>3109.09</v>
+        <v>3111.71</v>
       </c>
       <c r="AI4">
         <v>3408.79</v>
@@ -1209,7 +1209,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>27.16</v>
+        <v>24.51</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1407,13 +1407,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-7.04</v>
+        <v>-7.2</v>
       </c>
       <c r="D7" s="5">
-        <v>-7.2</v>
+        <v>-5.8</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.16</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1424,13 +1424,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-17.45</v>
+        <v>-14.46</v>
       </c>
       <c r="D8" s="5">
-        <v>-14.46</v>
+        <v>-15.68</v>
       </c>
       <c r="E8" s="7">
-        <v>2.99</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1441,13 +1441,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-10.53</v>
+        <v>-8.92</v>
       </c>
       <c r="D9" s="5">
-        <v>-8.92</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1.61</v>
+        <v>-8.15</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.77</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1458,13 +1458,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-4.32</v>
+        <v>-4.28</v>
       </c>
       <c r="D10" s="5">
-        <v>-4.28</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.04</v>
+        <v>-3.26</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1.02</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1475,13 +1475,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-14.52</v>
+        <v>-6.26</v>
       </c>
       <c r="D11" s="5">
-        <v>-6.26</v>
+        <v>-7.13</v>
       </c>
       <c r="E11" s="7">
-        <v>8.26</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1492,13 +1492,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-0.08</v>
+        <v>1.83</v>
       </c>
       <c r="D12" s="5">
-        <v>1.83</v>
+        <v>0.42</v>
       </c>
       <c r="E12" s="7">
-        <v>1.91</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1509,13 +1509,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>4.18</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="5">
-        <v>-0</v>
+        <v>2.66</v>
       </c>
       <c r="E13" s="6">
-        <v>-4.18</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1526,13 +1526,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>9.699999999999999</v>
+        <v>13.03</v>
       </c>
       <c r="D14" s="5">
-        <v>13.03</v>
+        <v>8.83</v>
       </c>
       <c r="E14" s="7">
-        <v>3.33</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1543,13 +1543,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-20.42</v>
+        <v>-18.23</v>
       </c>
       <c r="D15" s="5">
-        <v>-18.23</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.19</v>
+        <v>-17.99</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.24</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1560,13 +1560,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-7.38</v>
+        <v>-8.27</v>
       </c>
       <c r="D16" s="5">
-        <v>-8.27</v>
+        <v>-7.2</v>
       </c>
       <c r="E16" s="6">
-        <v>-0.89</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1577,13 +1577,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-15.94</v>
+        <v>-19.16</v>
       </c>
       <c r="D17" s="5">
-        <v>-19.16</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-3.22</v>
+        <v>-21.41</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1594,13 +1594,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="D18" s="5">
-        <v>1.92</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-0.03</v>
+        <v>1.83</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1611,13 +1611,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-14.06</v>
+        <v>-15.59</v>
       </c>
       <c r="D19" s="5">
-        <v>-15.59</v>
+        <v>-14.29</v>
       </c>
       <c r="E19" s="6">
-        <v>-1.53</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1628,13 +1628,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-21.04</v>
+        <v>-21.23</v>
       </c>
       <c r="D20" s="5">
-        <v>-21.23</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-0.19</v>
+        <v>-21.41</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1645,13 +1645,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-30.48</v>
+        <v>-29.63</v>
       </c>
       <c r="D21" s="5">
-        <v>-29.63</v>
+        <v>-30.67</v>
       </c>
       <c r="E21" s="7">
-        <v>0.85</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1662,13 +1662,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>3760</v>
+        <v>3693.4</v>
       </c>
       <c r="D22" s="5">
-        <v>3693.4</v>
+        <v>3750</v>
       </c>
       <c r="E22" s="6">
-        <v>-66.59999999999999</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1679,13 +1679,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>265</v>
+        <v>264.35</v>
       </c>
       <c r="D23" s="5">
-        <v>264.35</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-0.65</v>
+        <v>263.75</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1696,115 +1696,149 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3228.6</v>
+        <v>3267.8</v>
       </c>
       <c r="D24" s="5">
-        <v>3267.8</v>
+        <v>3219.5</v>
       </c>
       <c r="E24" s="7">
-        <v>39.2</v>
+        <v>-48.3</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C25" s="5">
-        <v>35.75</v>
+        <v>66</v>
       </c>
       <c r="D25" s="5">
-        <v>31.47</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-4.28</v>
+        <v>34</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-32</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C26" s="5">
-        <v>28.55</v>
+        <v>34</v>
       </c>
       <c r="D26" s="5">
-        <v>28.32</v>
+        <v>66</v>
       </c>
       <c r="E26" s="6">
-        <v>-0.23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>40.42</v>
+        <v>31.47</v>
       </c>
       <c r="D27" s="5">
-        <v>44.18</v>
-      </c>
-      <c r="E27" s="7">
-        <v>3.76</v>
+        <v>38.24</v>
+      </c>
+      <c r="E27" s="6">
+        <v>6.77</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C28" s="5">
-        <v>63.24</v>
+        <v>28.32</v>
       </c>
       <c r="D28" s="5">
-        <v>47.18</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-16.06</v>
+        <v>28.1</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C29" s="5">
-        <v>5.01</v>
+        <v>44.18</v>
       </c>
       <c r="D29" s="5">
-        <v>14.42</v>
+        <v>40.77</v>
       </c>
       <c r="E29" s="7">
-        <v>9.41</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>79.62</v>
+        <v>47.18</v>
       </c>
       <c r="D30" s="5">
+        <v>48.14</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="5">
+        <v>14.42</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-32.84</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-47.26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="5">
         <v>44</v>
       </c>
-      <c r="E30" s="6">
-        <v>-35.62</v>
+      <c r="D32" s="5">
+        <v>8.25</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-35.75</v>
       </c>
     </row>
   </sheetData>
@@ -1869,16 +1903,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>34.7</v>
+        <v>35.7</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-10.2</v>
+        <v>-9.9</v>
       </c>
       <c r="G2" s="10">
-        <v>-8.5</v>
+        <v>-8.9</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1997,13 +2031,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.2572</v>
+        <v>0.2526</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1803</v>
+        <v>0.1811</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0567</v>
+        <v>-0.0605</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -741,7 +741,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -881,10 +882,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3750</v>
+        <v>3770</v>
       </c>
       <c r="D2">
-        <v>1.53</v>
+        <v>0.53</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -893,25 +894,25 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-14.29</v>
+        <v>-13.84</v>
       </c>
       <c r="H2">
-        <v>13.29</v>
+        <v>13.89</v>
       </c>
       <c r="I2">
-        <v>-3.26</v>
+        <v>0.1</v>
       </c>
       <c r="J2">
-        <v>-5.8</v>
+        <v>-5.16</v>
       </c>
       <c r="K2">
-        <v>-7.2</v>
+        <v>-5.56</v>
       </c>
       <c r="L2">
-        <v>2.66</v>
+        <v>4.04</v>
       </c>
       <c r="M2">
-        <v>18.11</v>
+        <v>18.54</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -920,19 +921,19 @@
         <v>59</v>
       </c>
       <c r="P2">
-        <v>3743.78</v>
+        <v>3744.5</v>
       </c>
       <c r="Q2">
-        <v>3862.58</v>
+        <v>3852.88</v>
       </c>
       <c r="R2">
-        <v>3952.11</v>
+        <v>3951.8</v>
       </c>
       <c r="S2">
-        <v>3946.57</v>
+        <v>3945.29</v>
       </c>
       <c r="T2">
-        <v>-4.98</v>
+        <v>-4.44</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,34 +948,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>38.24</v>
+        <v>40.48</v>
       </c>
       <c r="Z2">
-        <v>-63.16</v>
+        <v>-61.58</v>
       </c>
       <c r="AA2">
-        <v>-48.81</v>
+        <v>-51.36</v>
       </c>
       <c r="AB2">
-        <v>-14.35</v>
+        <v>-10.22</v>
       </c>
       <c r="AC2">
-        <v>25.91</v>
+        <v>34.78</v>
       </c>
       <c r="AD2">
-        <v>23.62</v>
+        <v>26.46</v>
       </c>
       <c r="AE2">
-        <v>65.95</v>
+        <v>64.39</v>
       </c>
       <c r="AF2">
-        <v>48.14</v>
+        <v>23.34</v>
       </c>
       <c r="AG2">
-        <v>4032.73</v>
+        <v>4020.77</v>
       </c>
       <c r="AH2">
-        <v>3692.44</v>
+        <v>3684.99</v>
       </c>
       <c r="AI2">
         <v>3896.62</v>
@@ -983,7 +984,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>39.6</v>
+        <v>39.86</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +995,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>263.75</v>
+        <v>264.4</v>
       </c>
       <c r="D3">
-        <v>-0.23</v>
+        <v>0.25</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1006,46 +1007,46 @@
         <v>237.75</v>
       </c>
       <c r="G3">
-        <v>-21.41</v>
+        <v>-21.22</v>
       </c>
       <c r="H3">
-        <v>10.94</v>
+        <v>11.21</v>
       </c>
       <c r="I3">
-        <v>-7.13</v>
+        <v>-5.86</v>
       </c>
       <c r="J3">
-        <v>-15.68</v>
+        <v>-16.57</v>
       </c>
       <c r="K3">
-        <v>-21.41</v>
+        <v>-20.89</v>
       </c>
       <c r="L3">
-        <v>8.83</v>
+        <v>7.16</v>
       </c>
       <c r="M3">
-        <v>25.26</v>
+        <v>25.91</v>
       </c>
       <c r="N3">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="O3">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P3">
-        <v>269</v>
+        <v>265.71</v>
       </c>
       <c r="Q3">
-        <v>295.33</v>
+        <v>292.85</v>
       </c>
       <c r="R3">
-        <v>306.92</v>
+        <v>306.16</v>
       </c>
       <c r="S3">
-        <v>291.32</v>
+        <v>291.15</v>
       </c>
       <c r="T3">
-        <v>-9.460000000000001</v>
+        <v>-9.19</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,43 +1061,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>28.1</v>
+        <v>28.76</v>
       </c>
       <c r="Z3">
-        <v>-11.93</v>
+        <v>-12.46</v>
       </c>
       <c r="AA3">
-        <v>-7.68</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="AB3">
-        <v>-4.25</v>
+        <v>-3.82</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AD3">
-        <v>0.1</v>
+        <v>0.31</v>
       </c>
       <c r="AE3">
-        <v>9.33</v>
+        <v>8.94</v>
       </c>
       <c r="AF3">
-        <v>-32.84</v>
+        <v>-47.49</v>
       </c>
       <c r="AG3">
-        <v>331.71</v>
+        <v>330.61</v>
       </c>
       <c r="AH3">
-        <v>258.96</v>
+        <v>255.1</v>
       </c>
       <c r="AI3">
-        <v>293.34</v>
+        <v>290.18</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>45.86</v>
+        <v>49.12</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1108,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3219.5</v>
+        <v>3246</v>
       </c>
       <c r="D4">
-        <v>-1.48</v>
+        <v>0.82</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1119,46 +1120,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-30.67</v>
+        <v>-30.1</v>
       </c>
       <c r="H4">
-        <v>5.86</v>
+        <v>6.73</v>
       </c>
       <c r="I4">
-        <v>0.42</v>
+        <v>1.07</v>
       </c>
       <c r="J4">
+        <v>-7.29</v>
+      </c>
+      <c r="K4">
+        <v>0.77</v>
+      </c>
+      <c r="L4">
+        <v>-19.86</v>
+      </c>
+      <c r="M4">
+        <v>-5.6</v>
+      </c>
+      <c r="N4">
+        <v>34</v>
+      </c>
+      <c r="O4">
+        <v>43</v>
+      </c>
+      <c r="P4">
+        <v>3208.7</v>
+      </c>
+      <c r="Q4">
+        <v>3286.02</v>
+      </c>
+      <c r="R4">
+        <v>3448.39</v>
+      </c>
+      <c r="S4">
+        <v>3534.02</v>
+      </c>
+      <c r="T4">
         <v>-8.15</v>
-      </c>
-      <c r="K4">
-        <v>1.83</v>
-      </c>
-      <c r="L4">
-        <v>-17.99</v>
-      </c>
-      <c r="M4">
-        <v>-6.05</v>
-      </c>
-      <c r="N4">
-        <v>66</v>
-      </c>
-      <c r="O4">
-        <v>46</v>
-      </c>
-      <c r="P4">
-        <v>3201.82</v>
-      </c>
-      <c r="Q4">
-        <v>3298.38</v>
-      </c>
-      <c r="R4">
-        <v>3451.83</v>
-      </c>
-      <c r="S4">
-        <v>3540.48</v>
-      </c>
-      <c r="T4">
-        <v>-9.07</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,34 +1174,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>40.77</v>
+        <v>43.35</v>
       </c>
       <c r="Z4">
-        <v>-72.25</v>
+        <v>-67.28</v>
       </c>
       <c r="AA4">
-        <v>-69.31999999999999</v>
+        <v>-68.91</v>
       </c>
       <c r="AB4">
-        <v>-2.93</v>
+        <v>1.64</v>
       </c>
       <c r="AC4">
-        <v>94.83</v>
+        <v>93.58</v>
       </c>
       <c r="AD4">
-        <v>65.95</v>
+        <v>85.03</v>
       </c>
       <c r="AE4">
-        <v>97.64</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AF4">
-        <v>8.25</v>
+        <v>-31.58</v>
       </c>
       <c r="AG4">
-        <v>3485.05</v>
+        <v>3449.67</v>
       </c>
       <c r="AH4">
-        <v>3111.71</v>
+        <v>3122.36</v>
       </c>
       <c r="AI4">
         <v>3408.79</v>
@@ -1209,7 +1210,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>24.51</v>
+        <v>23.04</v>
       </c>
     </row>
   </sheetData>
@@ -1407,13 +1408,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-7.2</v>
+        <v>-5.8</v>
       </c>
       <c r="D7" s="5">
-        <v>-5.8</v>
+        <v>-5.16</v>
       </c>
       <c r="E7" s="6">
-        <v>1.4</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1424,13 +1425,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-14.46</v>
+        <v>-15.68</v>
       </c>
       <c r="D8" s="5">
-        <v>-15.68</v>
+        <v>-16.57</v>
       </c>
       <c r="E8" s="7">
-        <v>-1.22</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1441,13 +1442,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-8.92</v>
+        <v>-8.15</v>
       </c>
       <c r="D9" s="5">
-        <v>-8.15</v>
+        <v>-7.29</v>
       </c>
       <c r="E9" s="6">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1458,13 +1459,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-4.28</v>
+        <v>-3.26</v>
       </c>
       <c r="D10" s="5">
-        <v>-3.26</v>
+        <v>0.1</v>
       </c>
       <c r="E10" s="6">
-        <v>1.02</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1475,13 +1476,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-6.26</v>
+        <v>-7.13</v>
       </c>
       <c r="D11" s="5">
-        <v>-7.13</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.87</v>
+        <v>-5.86</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1.27</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1492,13 +1493,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>1.83</v>
+        <v>0.42</v>
       </c>
       <c r="D12" s="5">
-        <v>0.42</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-1.41</v>
+        <v>1.07</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.65</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1509,13 +1510,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-0</v>
+        <v>2.66</v>
       </c>
       <c r="D13" s="5">
-        <v>2.66</v>
+        <v>4.04</v>
       </c>
       <c r="E13" s="6">
-        <v>2.66</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1526,13 +1527,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>13.03</v>
+        <v>8.83</v>
       </c>
       <c r="D14" s="5">
-        <v>8.83</v>
+        <v>7.16</v>
       </c>
       <c r="E14" s="7">
-        <v>-4.2</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1543,13 +1544,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-18.23</v>
+        <v>-17.99</v>
       </c>
       <c r="D15" s="5">
-        <v>-17.99</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.24</v>
+        <v>-19.86</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.87</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1560,13 +1561,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-8.27</v>
+        <v>-7.2</v>
       </c>
       <c r="D16" s="5">
-        <v>-7.2</v>
+        <v>-5.56</v>
       </c>
       <c r="E16" s="6">
-        <v>1.07</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1577,13 +1578,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-19.16</v>
+        <v>-21.41</v>
       </c>
       <c r="D17" s="5">
-        <v>-21.41</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.25</v>
+        <v>-20.89</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.52</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1594,13 +1595,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="D18" s="5">
-        <v>1.83</v>
+        <v>0.77</v>
       </c>
       <c r="E18" s="7">
-        <v>-0.09</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1611,13 +1612,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-15.59</v>
+        <v>-14.29</v>
       </c>
       <c r="D19" s="5">
-        <v>-14.29</v>
+        <v>-13.84</v>
       </c>
       <c r="E19" s="6">
-        <v>1.3</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1628,13 +1629,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-21.23</v>
+        <v>-21.41</v>
       </c>
       <c r="D20" s="5">
-        <v>-21.41</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.18</v>
+        <v>-21.22</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.19</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1645,13 +1646,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-29.63</v>
+        <v>-30.67</v>
       </c>
       <c r="D21" s="5">
-        <v>-30.67</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1.04</v>
+        <v>-30.1</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.57</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1662,13 +1663,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>3693.4</v>
+        <v>3750</v>
       </c>
       <c r="D22" s="5">
-        <v>3750</v>
+        <v>3770</v>
       </c>
       <c r="E22" s="6">
-        <v>56.6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1679,13 +1680,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>264.35</v>
+        <v>263.75</v>
       </c>
       <c r="D23" s="5">
-        <v>263.75</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.6</v>
+        <v>264.4</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.65</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1696,13 +1697,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3267.8</v>
+        <v>3219.5</v>
       </c>
       <c r="D24" s="5">
-        <v>3219.5</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-48.3</v>
+        <v>3246</v>
+      </c>
+      <c r="E24" s="6">
+        <v>26.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1713,13 +1714,13 @@
         <v>13</v>
       </c>
       <c r="C25" s="5">
+        <v>34</v>
+      </c>
+      <c r="D25" s="5">
         <v>66</v>
       </c>
-      <c r="D25" s="5">
-        <v>34</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-32</v>
+      <c r="E25" s="6">
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1730,13 +1731,13 @@
         <v>13</v>
       </c>
       <c r="C26" s="5">
+        <v>66</v>
+      </c>
+      <c r="D26" s="5">
         <v>34</v>
       </c>
-      <c r="D26" s="5">
-        <v>66</v>
-      </c>
-      <c r="E26" s="6">
-        <v>32</v>
+      <c r="E26" s="7">
+        <v>-32</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1747,13 +1748,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>31.47</v>
+        <v>38.24</v>
       </c>
       <c r="D27" s="5">
-        <v>38.24</v>
+        <v>40.48</v>
       </c>
       <c r="E27" s="6">
-        <v>6.77</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1764,13 +1765,13 @@
         <v>24</v>
       </c>
       <c r="C28" s="5">
-        <v>28.32</v>
+        <v>28.1</v>
       </c>
       <c r="D28" s="5">
-        <v>28.1</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.22</v>
+        <v>28.76</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.66</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1781,13 +1782,13 @@
         <v>24</v>
       </c>
       <c r="C29" s="5">
-        <v>44.18</v>
+        <v>40.77</v>
       </c>
       <c r="D29" s="5">
-        <v>40.77</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-3.41</v>
+        <v>43.35</v>
+      </c>
+      <c r="E29" s="6">
+        <v>2.58</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1798,13 +1799,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>47.18</v>
+        <v>48.14</v>
       </c>
       <c r="D30" s="5">
-        <v>48.14</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0.96</v>
+        <v>23.34</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-24.8</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1815,13 +1816,13 @@
         <v>31</v>
       </c>
       <c r="C31" s="5">
-        <v>14.42</v>
+        <v>-32.84</v>
       </c>
       <c r="D31" s="5">
-        <v>-32.84</v>
+        <v>-47.49</v>
       </c>
       <c r="E31" s="7">
-        <v>-47.26</v>
+        <v>-14.65</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1832,13 +1833,13 @@
         <v>31</v>
       </c>
       <c r="C32" s="5">
-        <v>44</v>
+        <v>8.25</v>
       </c>
       <c r="D32" s="5">
-        <v>8.25</v>
+        <v>-31.58</v>
       </c>
       <c r="E32" s="7">
-        <v>-35.75</v>
+        <v>-39.83</v>
       </c>
     </row>
   </sheetData>
@@ -1903,16 +1904,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>35.7</v>
+        <v>37.5</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-9.9</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G2" s="10">
-        <v>-8.9</v>
+        <v>-8.6</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -2031,13 +2032,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.2526</v>
+        <v>0.2591</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1811</v>
+        <v>0.1854</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0605</v>
+        <v>-0.05599999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -243,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -741,8 +741,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -882,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3770</v>
+        <v>3701.5</v>
       </c>
       <c r="D2">
-        <v>0.53</v>
+        <v>-1.82</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -894,46 +893,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-13.84</v>
+        <v>-15.4</v>
       </c>
       <c r="H2">
-        <v>13.89</v>
+        <v>11.83</v>
       </c>
       <c r="I2">
-        <v>0.1</v>
+        <v>-1.27</v>
       </c>
       <c r="J2">
-        <v>-5.16</v>
+        <v>-6.62</v>
       </c>
       <c r="K2">
-        <v>-5.56</v>
+        <v>-4.9</v>
       </c>
       <c r="L2">
-        <v>4.04</v>
+        <v>1.84</v>
       </c>
       <c r="M2">
-        <v>18.54</v>
+        <v>17.86</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="P2">
-        <v>3744.5</v>
+        <v>3734.98</v>
       </c>
       <c r="Q2">
-        <v>3852.88</v>
+        <v>3838</v>
       </c>
       <c r="R2">
-        <v>3951.8</v>
+        <v>3949.71</v>
       </c>
       <c r="S2">
-        <v>3945.29</v>
+        <v>3943.68</v>
       </c>
       <c r="T2">
-        <v>-4.44</v>
+        <v>-6.14</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -948,34 +947,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>40.48</v>
+        <v>35.71</v>
       </c>
       <c r="Z2">
-        <v>-61.58</v>
+        <v>-65.11</v>
       </c>
       <c r="AA2">
-        <v>-51.36</v>
+        <v>-54.11</v>
       </c>
       <c r="AB2">
-        <v>-10.22</v>
+        <v>-11</v>
       </c>
       <c r="AC2">
-        <v>34.78</v>
+        <v>41.45</v>
       </c>
       <c r="AD2">
-        <v>26.46</v>
+        <v>34.05</v>
       </c>
       <c r="AE2">
-        <v>64.39</v>
+        <v>65.89</v>
       </c>
       <c r="AF2">
-        <v>23.34</v>
+        <v>-3.44</v>
       </c>
       <c r="AG2">
-        <v>4020.77</v>
+        <v>4004.09</v>
       </c>
       <c r="AH2">
-        <v>3684.99</v>
+        <v>3671.92</v>
       </c>
       <c r="AI2">
         <v>3896.62</v>
@@ -984,7 +983,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>39.86</v>
+        <v>41.66</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -995,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>264.4</v>
+        <v>260.25</v>
       </c>
       <c r="D3">
-        <v>0.25</v>
+        <v>-1.57</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1007,46 +1006,46 @@
         <v>237.75</v>
       </c>
       <c r="G3">
-        <v>-21.22</v>
+        <v>-22.45</v>
       </c>
       <c r="H3">
-        <v>11.21</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I3">
-        <v>-5.86</v>
+        <v>-3.98</v>
       </c>
       <c r="J3">
-        <v>-16.57</v>
+        <v>-17.12</v>
       </c>
       <c r="K3">
-        <v>-20.89</v>
+        <v>-17.2</v>
       </c>
       <c r="L3">
-        <v>7.16</v>
+        <v>1.68</v>
       </c>
       <c r="M3">
-        <v>25.91</v>
+        <v>25.17</v>
       </c>
       <c r="N3">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="O3">
         <v>42</v>
       </c>
       <c r="P3">
-        <v>265.71</v>
+        <v>263.55</v>
       </c>
       <c r="Q3">
-        <v>292.85</v>
+        <v>290.24</v>
       </c>
       <c r="R3">
-        <v>306.16</v>
+        <v>305.12</v>
       </c>
       <c r="S3">
-        <v>291.15</v>
+        <v>290.96</v>
       </c>
       <c r="T3">
-        <v>-9.19</v>
+        <v>-10.55</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1061,43 +1060,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>28.76</v>
+        <v>27.05</v>
       </c>
       <c r="Z3">
-        <v>-12.46</v>
+        <v>-13.06</v>
       </c>
       <c r="AA3">
-        <v>-8.630000000000001</v>
+        <v>-9.52</v>
       </c>
       <c r="AB3">
-        <v>-3.82</v>
+        <v>-3.54</v>
       </c>
       <c r="AC3">
         <v>0.93</v>
       </c>
       <c r="AD3">
-        <v>0.31</v>
+        <v>0.62</v>
       </c>
       <c r="AE3">
-        <v>8.94</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="AF3">
-        <v>-47.49</v>
+        <v>16.93</v>
       </c>
       <c r="AG3">
-        <v>330.61</v>
+        <v>329.47</v>
       </c>
       <c r="AH3">
-        <v>255.1</v>
+        <v>251.01</v>
       </c>
       <c r="AI3">
-        <v>290.18</v>
+        <v>289.41</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>49.12</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1108,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3246</v>
+        <v>3252.1</v>
       </c>
       <c r="D4">
-        <v>0.82</v>
+        <v>0.19</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1120,46 +1119,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-30.1</v>
+        <v>-29.97</v>
       </c>
       <c r="H4">
-        <v>6.73</v>
+        <v>6.93</v>
       </c>
       <c r="I4">
-        <v>1.07</v>
+        <v>5.53</v>
       </c>
       <c r="J4">
-        <v>-7.29</v>
+        <v>-6.9</v>
       </c>
       <c r="K4">
-        <v>0.77</v>
+        <v>3.53</v>
       </c>
       <c r="L4">
-        <v>-19.86</v>
+        <v>-21.11</v>
       </c>
       <c r="M4">
-        <v>-5.6</v>
+        <v>-5.94</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="O4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P4">
-        <v>3208.7</v>
+        <v>3242.8</v>
       </c>
       <c r="Q4">
-        <v>3286.02</v>
+        <v>3277.91</v>
       </c>
       <c r="R4">
-        <v>3448.39</v>
+        <v>3443.47</v>
       </c>
       <c r="S4">
-        <v>3534.02</v>
+        <v>3528.12</v>
       </c>
       <c r="T4">
-        <v>-8.15</v>
+        <v>-7.82</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1174,34 +1173,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>43.35</v>
+        <v>43.96</v>
       </c>
       <c r="Z4">
-        <v>-67.28</v>
+        <v>-62.13</v>
       </c>
       <c r="AA4">
-        <v>-68.91</v>
+        <v>-67.56</v>
       </c>
       <c r="AB4">
-        <v>1.64</v>
+        <v>5.43</v>
       </c>
       <c r="AC4">
-        <v>93.58</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="AD4">
-        <v>85.03</v>
+        <v>93.88</v>
       </c>
       <c r="AE4">
-        <v>95.90000000000001</v>
+        <v>94.37</v>
       </c>
       <c r="AF4">
-        <v>-31.58</v>
+        <v>-21.06</v>
       </c>
       <c r="AG4">
-        <v>3449.67</v>
+        <v>3430.51</v>
       </c>
       <c r="AH4">
-        <v>3122.36</v>
+        <v>3125.31</v>
       </c>
       <c r="AI4">
         <v>3408.79</v>
@@ -1210,7 +1209,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>23.04</v>
+        <v>20.2</v>
       </c>
     </row>
   </sheetData>
@@ -1408,13 +1407,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-5.8</v>
+        <v>-5.16</v>
       </c>
       <c r="D7" s="5">
-        <v>-5.16</v>
+        <v>-6.62</v>
       </c>
       <c r="E7" s="6">
-        <v>0.64</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1425,13 +1424,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-15.68</v>
+        <v>-16.57</v>
       </c>
       <c r="D8" s="5">
-        <v>-16.57</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.89</v>
+        <v>-17.12</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1442,13 +1441,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-8.15</v>
+        <v>-7.29</v>
       </c>
       <c r="D9" s="5">
-        <v>-7.29</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.86</v>
+        <v>-6.9</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.39</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1459,13 +1458,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-3.26</v>
+        <v>0.1</v>
       </c>
       <c r="D10" s="5">
-        <v>0.1</v>
+        <v>-1.27</v>
       </c>
       <c r="E10" s="6">
-        <v>3.36</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1476,13 +1475,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-7.13</v>
+        <v>-5.86</v>
       </c>
       <c r="D11" s="5">
-        <v>-5.86</v>
-      </c>
-      <c r="E11" s="6">
-        <v>1.27</v>
+        <v>-3.98</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.88</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1493,13 +1492,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>0.42</v>
+        <v>1.07</v>
       </c>
       <c r="D12" s="5">
-        <v>1.07</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0.65</v>
+        <v>5.53</v>
+      </c>
+      <c r="E12" s="7">
+        <v>4.46</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1510,13 +1509,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>2.66</v>
+        <v>4.04</v>
       </c>
       <c r="D13" s="5">
-        <v>4.04</v>
+        <v>1.84</v>
       </c>
       <c r="E13" s="6">
-        <v>1.38</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1527,13 +1526,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>8.83</v>
+        <v>7.16</v>
       </c>
       <c r="D14" s="5">
-        <v>7.16</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.67</v>
+        <v>1.68</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-5.48</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1544,13 +1543,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-17.99</v>
+        <v>-19.86</v>
       </c>
       <c r="D15" s="5">
-        <v>-19.86</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.87</v>
+        <v>-21.11</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1561,13 +1560,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-7.2</v>
+        <v>-5.56</v>
       </c>
       <c r="D16" s="5">
-        <v>-5.56</v>
-      </c>
-      <c r="E16" s="6">
-        <v>1.64</v>
+        <v>-4.9</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.66</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1578,13 +1577,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-21.41</v>
+        <v>-20.89</v>
       </c>
       <c r="D17" s="5">
-        <v>-20.89</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.52</v>
+        <v>-17.2</v>
+      </c>
+      <c r="E17" s="7">
+        <v>3.69</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1595,13 +1594,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>1.83</v>
+        <v>0.77</v>
       </c>
       <c r="D18" s="5">
-        <v>0.77</v>
+        <v>3.53</v>
       </c>
       <c r="E18" s="7">
-        <v>-1.06</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1612,13 +1611,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-14.29</v>
+        <v>-13.84</v>
       </c>
       <c r="D19" s="5">
-        <v>-13.84</v>
+        <v>-15.4</v>
       </c>
       <c r="E19" s="6">
-        <v>0.45</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1629,13 +1628,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-21.41</v>
+        <v>-21.22</v>
       </c>
       <c r="D20" s="5">
-        <v>-21.22</v>
+        <v>-22.45</v>
       </c>
       <c r="E20" s="6">
-        <v>0.19</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1646,13 +1645,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-30.67</v>
+        <v>-30.1</v>
       </c>
       <c r="D21" s="5">
-        <v>-30.1</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.57</v>
+        <v>-29.97</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.13</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1663,13 +1662,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>3750</v>
+        <v>3770</v>
       </c>
       <c r="D22" s="5">
-        <v>3770</v>
+        <v>3701.5</v>
       </c>
       <c r="E22" s="6">
-        <v>20</v>
+        <v>-68.5</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1680,13 +1679,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>263.75</v>
+        <v>264.4</v>
       </c>
       <c r="D23" s="5">
-        <v>264.4</v>
+        <v>260.25</v>
       </c>
       <c r="E23" s="6">
-        <v>0.65</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1697,13 +1696,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3219.5</v>
+        <v>3246</v>
       </c>
       <c r="D24" s="5">
-        <v>3246</v>
-      </c>
-      <c r="E24" s="6">
-        <v>26.5</v>
+        <v>3252.1</v>
+      </c>
+      <c r="E24" s="7">
+        <v>6.1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1714,13 +1713,13 @@
         <v>13</v>
       </c>
       <c r="C25" s="5">
+        <v>66</v>
+      </c>
+      <c r="D25" s="5">
         <v>34</v>
       </c>
-      <c r="D25" s="5">
-        <v>66</v>
-      </c>
       <c r="E25" s="6">
-        <v>32</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1731,13 +1730,13 @@
         <v>13</v>
       </c>
       <c r="C26" s="5">
+        <v>34</v>
+      </c>
+      <c r="D26" s="5">
         <v>66</v>
       </c>
-      <c r="D26" s="5">
-        <v>34</v>
-      </c>
       <c r="E26" s="7">
-        <v>-32</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1748,13 +1747,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>38.24</v>
+        <v>40.48</v>
       </c>
       <c r="D27" s="5">
-        <v>40.48</v>
+        <v>35.71</v>
       </c>
       <c r="E27" s="6">
-        <v>2.24</v>
+        <v>-4.77</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1765,13 +1764,13 @@
         <v>24</v>
       </c>
       <c r="C28" s="5">
-        <v>28.1</v>
+        <v>28.76</v>
       </c>
       <c r="D28" s="5">
-        <v>28.76</v>
+        <v>27.05</v>
       </c>
       <c r="E28" s="6">
-        <v>0.66</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1782,13 +1781,13 @@
         <v>24</v>
       </c>
       <c r="C29" s="5">
-        <v>40.77</v>
+        <v>43.35</v>
       </c>
       <c r="D29" s="5">
-        <v>43.35</v>
-      </c>
-      <c r="E29" s="6">
-        <v>2.58</v>
+        <v>43.96</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.61</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1799,13 +1798,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>48.14</v>
+        <v>23.34</v>
       </c>
       <c r="D30" s="5">
-        <v>23.34</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-24.8</v>
+        <v>-3.44</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-26.78</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1816,13 +1815,13 @@
         <v>31</v>
       </c>
       <c r="C31" s="5">
-        <v>-32.84</v>
+        <v>-47.49</v>
       </c>
       <c r="D31" s="5">
-        <v>-47.49</v>
+        <v>16.93</v>
       </c>
       <c r="E31" s="7">
-        <v>-14.65</v>
+        <v>64.42</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1833,13 +1832,13 @@
         <v>31</v>
       </c>
       <c r="C32" s="5">
-        <v>8.25</v>
+        <v>-31.58</v>
       </c>
       <c r="D32" s="5">
-        <v>-31.58</v>
+        <v>-21.06</v>
       </c>
       <c r="E32" s="7">
-        <v>-39.83</v>
+        <v>10.52</v>
       </c>
     </row>
   </sheetData>
@@ -1904,16 +1903,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>37.5</v>
+        <v>35.6</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-9.699999999999999</v>
+        <v>-10.2</v>
       </c>
       <c r="G2" s="10">
-        <v>-8.6</v>
+        <v>-6.2</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -2032,13 +2031,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.2591</v>
+        <v>0.2517</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1854</v>
+        <v>0.1786</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.05599999999999999</v>
+        <v>-0.0594</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -741,7 +741,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -881,10 +882,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3701.5</v>
+        <v>3625.1</v>
       </c>
       <c r="D2">
-        <v>-1.82</v>
+        <v>-2.06</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -893,46 +894,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-15.4</v>
+        <v>-17.15</v>
       </c>
       <c r="H2">
-        <v>11.83</v>
+        <v>9.52</v>
       </c>
       <c r="I2">
-        <v>-1.27</v>
+        <v>-3.59</v>
       </c>
       <c r="J2">
-        <v>-6.62</v>
+        <v>-9.35</v>
       </c>
       <c r="K2">
-        <v>-4.9</v>
+        <v>-6.71</v>
       </c>
       <c r="L2">
-        <v>1.84</v>
+        <v>-1.94</v>
       </c>
       <c r="M2">
-        <v>17.86</v>
+        <v>17.18</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P2">
-        <v>3734.98</v>
+        <v>3708</v>
       </c>
       <c r="Q2">
-        <v>3838</v>
+        <v>3821.95</v>
       </c>
       <c r="R2">
-        <v>3949.71</v>
+        <v>3945.57</v>
       </c>
       <c r="S2">
-        <v>3943.68</v>
+        <v>3941.85</v>
       </c>
       <c r="T2">
-        <v>-6.14</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,43 +948,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>35.71</v>
+        <v>31.28</v>
       </c>
       <c r="Z2">
-        <v>-65.11</v>
+        <v>-73.23</v>
       </c>
       <c r="AA2">
-        <v>-54.11</v>
+        <v>-57.94</v>
       </c>
       <c r="AB2">
-        <v>-11</v>
+        <v>-15.29</v>
       </c>
       <c r="AC2">
-        <v>41.45</v>
+        <v>27.02</v>
       </c>
       <c r="AD2">
-        <v>34.05</v>
+        <v>34.41</v>
       </c>
       <c r="AE2">
-        <v>65.89</v>
+        <v>67.97</v>
       </c>
       <c r="AF2">
-        <v>-3.44</v>
+        <v>0.58</v>
       </c>
       <c r="AG2">
-        <v>4004.09</v>
+        <v>4005.21</v>
       </c>
       <c r="AH2">
-        <v>3671.92</v>
+        <v>3638.7</v>
       </c>
       <c r="AI2">
-        <v>3896.62</v>
+        <v>3858.41</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>41.66</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +995,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>260.25</v>
+        <v>257.4</v>
       </c>
       <c r="D3">
-        <v>-1.57</v>
+        <v>-1.1</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1006,46 +1007,46 @@
         <v>237.75</v>
       </c>
       <c r="G3">
-        <v>-22.45</v>
+        <v>-23.3</v>
       </c>
       <c r="H3">
-        <v>9.460000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="I3">
-        <v>-3.98</v>
+        <v>-2.87</v>
       </c>
       <c r="J3">
-        <v>-17.12</v>
+        <v>-17.63</v>
       </c>
       <c r="K3">
-        <v>-17.2</v>
+        <v>-19.84</v>
       </c>
       <c r="L3">
-        <v>1.68</v>
+        <v>-0.87</v>
       </c>
       <c r="M3">
-        <v>25.17</v>
+        <v>24.69</v>
       </c>
       <c r="N3">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="O3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P3">
-        <v>263.55</v>
+        <v>262.03</v>
       </c>
       <c r="Q3">
-        <v>290.24</v>
+        <v>287.7</v>
       </c>
       <c r="R3">
-        <v>305.12</v>
+        <v>304.05</v>
       </c>
       <c r="S3">
-        <v>290.96</v>
+        <v>290.76</v>
       </c>
       <c r="T3">
-        <v>-10.55</v>
+        <v>-11.47</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,43 +1061,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>27.05</v>
+        <v>25.92</v>
       </c>
       <c r="Z3">
-        <v>-13.06</v>
+        <v>-13.61</v>
       </c>
       <c r="AA3">
-        <v>-9.52</v>
+        <v>-10.34</v>
       </c>
       <c r="AB3">
-        <v>-3.54</v>
+        <v>-3.27</v>
       </c>
       <c r="AC3">
         <v>0.93</v>
       </c>
       <c r="AD3">
-        <v>0.62</v>
+        <v>0.93</v>
       </c>
       <c r="AE3">
-        <v>8.869999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="AF3">
-        <v>16.93</v>
+        <v>-2.88</v>
       </c>
       <c r="AG3">
-        <v>329.47</v>
+        <v>328.56</v>
       </c>
       <c r="AH3">
-        <v>251.01</v>
+        <v>246.83</v>
       </c>
       <c r="AI3">
-        <v>289.41</v>
+        <v>284.18</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>52.29</v>
+        <v>55.48</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1108,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3252.1</v>
+        <v>3176.6</v>
       </c>
       <c r="D4">
-        <v>0.19</v>
+        <v>-2.32</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1119,46 +1120,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-29.97</v>
+        <v>-31.6</v>
       </c>
       <c r="H4">
-        <v>6.93</v>
+        <v>4.45</v>
       </c>
       <c r="I4">
-        <v>5.53</v>
+        <v>-1.61</v>
       </c>
       <c r="J4">
-        <v>-6.9</v>
+        <v>-6.96</v>
       </c>
       <c r="K4">
-        <v>3.53</v>
+        <v>-1.27</v>
       </c>
       <c r="L4">
-        <v>-21.11</v>
+        <v>-24.79</v>
       </c>
       <c r="M4">
-        <v>-5.94</v>
+        <v>-6.76</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="O4">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P4">
-        <v>3242.8</v>
+        <v>3232.4</v>
       </c>
       <c r="Q4">
-        <v>3277.91</v>
+        <v>3267.29</v>
       </c>
       <c r="R4">
-        <v>3443.47</v>
+        <v>3435.02</v>
       </c>
       <c r="S4">
-        <v>3528.12</v>
+        <v>3521.5</v>
       </c>
       <c r="T4">
-        <v>-7.82</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,34 +1174,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>43.96</v>
+        <v>38.47</v>
       </c>
       <c r="Z4">
-        <v>-62.13</v>
+        <v>-63.4</v>
       </c>
       <c r="AA4">
-        <v>-67.56</v>
+        <v>-66.73</v>
       </c>
       <c r="AB4">
-        <v>5.43</v>
+        <v>3.32</v>
       </c>
       <c r="AC4">
-        <v>93.23999999999999</v>
+        <v>89.77</v>
       </c>
       <c r="AD4">
-        <v>93.88</v>
+        <v>92.2</v>
       </c>
       <c r="AE4">
-        <v>94.37</v>
+        <v>101.01</v>
       </c>
       <c r="AF4">
-        <v>-21.06</v>
+        <v>-8.51</v>
       </c>
       <c r="AG4">
-        <v>3430.51</v>
+        <v>3416.85</v>
       </c>
       <c r="AH4">
-        <v>3125.31</v>
+        <v>3117.72</v>
       </c>
       <c r="AI4">
         <v>3408.79</v>
@@ -1209,7 +1210,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>20.2</v>
+        <v>20.84</v>
       </c>
     </row>
   </sheetData>
@@ -1407,13 +1408,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-5.16</v>
+        <v>-6.62</v>
       </c>
       <c r="D7" s="5">
-        <v>-6.62</v>
+        <v>-9.35</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.46</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1424,13 +1425,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-16.57</v>
+        <v>-17.12</v>
       </c>
       <c r="D8" s="5">
-        <v>-17.12</v>
+        <v>-17.63</v>
       </c>
       <c r="E8" s="6">
-        <v>-0.55</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1441,13 +1442,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-7.29</v>
+        <v>-6.9</v>
       </c>
       <c r="D9" s="5">
-        <v>-6.9</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.39</v>
+        <v>-6.96</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1458,13 +1459,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>0.1</v>
+        <v>-1.27</v>
       </c>
       <c r="D10" s="5">
-        <v>-1.27</v>
+        <v>-3.59</v>
       </c>
       <c r="E10" s="6">
-        <v>-1.37</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1475,13 +1476,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-5.86</v>
+        <v>-3.98</v>
       </c>
       <c r="D11" s="5">
-        <v>-3.98</v>
+        <v>-2.87</v>
       </c>
       <c r="E11" s="7">
-        <v>1.88</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1492,13 +1493,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>1.07</v>
+        <v>5.53</v>
       </c>
       <c r="D12" s="5">
-        <v>5.53</v>
-      </c>
-      <c r="E12" s="7">
-        <v>4.46</v>
+        <v>-1.61</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-7.14</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1509,13 +1510,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>4.04</v>
+        <v>1.84</v>
       </c>
       <c r="D13" s="5">
-        <v>1.84</v>
+        <v>-1.94</v>
       </c>
       <c r="E13" s="6">
-        <v>-2.2</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1526,13 +1527,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>7.16</v>
+        <v>1.68</v>
       </c>
       <c r="D14" s="5">
-        <v>1.68</v>
+        <v>-0.87</v>
       </c>
       <c r="E14" s="6">
-        <v>-5.48</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1543,13 +1544,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-19.86</v>
+        <v>-21.11</v>
       </c>
       <c r="D15" s="5">
-        <v>-21.11</v>
+        <v>-24.79</v>
       </c>
       <c r="E15" s="6">
-        <v>-1.25</v>
+        <v>-3.68</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1560,13 +1561,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-5.56</v>
+        <v>-4.9</v>
       </c>
       <c r="D16" s="5">
-        <v>-4.9</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.66</v>
+        <v>-6.71</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-1.81</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1577,13 +1578,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-20.89</v>
+        <v>-17.2</v>
       </c>
       <c r="D17" s="5">
-        <v>-17.2</v>
-      </c>
-      <c r="E17" s="7">
-        <v>3.69</v>
+        <v>-19.84</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-2.64</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1594,13 +1595,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>0.77</v>
+        <v>3.53</v>
       </c>
       <c r="D18" s="5">
-        <v>3.53</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.76</v>
+        <v>-1.27</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-4.8</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1611,13 +1612,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-13.84</v>
+        <v>-15.4</v>
       </c>
       <c r="D19" s="5">
-        <v>-15.4</v>
+        <v>-17.15</v>
       </c>
       <c r="E19" s="6">
-        <v>-1.56</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1628,13 +1629,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-21.22</v>
+        <v>-22.45</v>
       </c>
       <c r="D20" s="5">
-        <v>-22.45</v>
+        <v>-23.3</v>
       </c>
       <c r="E20" s="6">
-        <v>-1.23</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1645,13 +1646,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-30.1</v>
+        <v>-29.97</v>
       </c>
       <c r="D21" s="5">
-        <v>-29.97</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.13</v>
+        <v>-31.6</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-1.63</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1662,13 +1663,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>3770</v>
+        <v>3701.5</v>
       </c>
       <c r="D22" s="5">
-        <v>3701.5</v>
+        <v>3625.1</v>
       </c>
       <c r="E22" s="6">
-        <v>-68.5</v>
+        <v>-76.40000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1679,13 +1680,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>264.4</v>
+        <v>260.25</v>
       </c>
       <c r="D23" s="5">
-        <v>260.25</v>
+        <v>257.4</v>
       </c>
       <c r="E23" s="6">
-        <v>-4.15</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1696,13 +1697,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3246</v>
+        <v>3252.1</v>
       </c>
       <c r="D24" s="5">
-        <v>3252.1</v>
-      </c>
-      <c r="E24" s="7">
-        <v>6.1</v>
+        <v>3176.6</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-75.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1713,13 +1714,13 @@
         <v>13</v>
       </c>
       <c r="C25" s="5">
+        <v>34</v>
+      </c>
+      <c r="D25" s="5">
         <v>66</v>
       </c>
-      <c r="D25" s="5">
-        <v>34</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-32</v>
+      <c r="E25" s="7">
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1730,13 +1731,13 @@
         <v>13</v>
       </c>
       <c r="C26" s="5">
+        <v>66</v>
+      </c>
+      <c r="D26" s="5">
         <v>34</v>
       </c>
-      <c r="D26" s="5">
-        <v>66</v>
-      </c>
-      <c r="E26" s="7">
-        <v>32</v>
+      <c r="E26" s="6">
+        <v>-32</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1747,13 +1748,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>40.48</v>
+        <v>35.71</v>
       </c>
       <c r="D27" s="5">
-        <v>35.71</v>
+        <v>31.28</v>
       </c>
       <c r="E27" s="6">
-        <v>-4.77</v>
+        <v>-4.43</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1764,13 +1765,13 @@
         <v>24</v>
       </c>
       <c r="C28" s="5">
-        <v>28.76</v>
+        <v>27.05</v>
       </c>
       <c r="D28" s="5">
-        <v>27.05</v>
+        <v>25.92</v>
       </c>
       <c r="E28" s="6">
-        <v>-1.71</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1781,13 +1782,13 @@
         <v>24</v>
       </c>
       <c r="C29" s="5">
-        <v>43.35</v>
+        <v>43.96</v>
       </c>
       <c r="D29" s="5">
-        <v>43.96</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.61</v>
+        <v>38.47</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-5.49</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1798,13 +1799,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>23.34</v>
+        <v>-3.44</v>
       </c>
       <c r="D30" s="5">
-        <v>-3.44</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-26.78</v>
+        <v>0.58</v>
+      </c>
+      <c r="E30" s="7">
+        <v>4.02</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1815,13 +1816,13 @@
         <v>31</v>
       </c>
       <c r="C31" s="5">
-        <v>-47.49</v>
+        <v>16.93</v>
       </c>
       <c r="D31" s="5">
-        <v>16.93</v>
-      </c>
-      <c r="E31" s="7">
-        <v>64.42</v>
+        <v>-2.88</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-19.81</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1832,13 +1833,13 @@
         <v>31</v>
       </c>
       <c r="C32" s="5">
-        <v>-31.58</v>
+        <v>-21.06</v>
       </c>
       <c r="D32" s="5">
-        <v>-21.06</v>
+        <v>-8.51</v>
       </c>
       <c r="E32" s="7">
-        <v>10.52</v>
+        <v>12.55</v>
       </c>
     </row>
   </sheetData>
@@ -1903,16 +1904,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>35.6</v>
+        <v>31.9</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-10.2</v>
+        <v>-11.3</v>
       </c>
       <c r="G2" s="10">
-        <v>-6.2</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -2031,13 +2032,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.2517</v>
+        <v>0.2469</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1786</v>
+        <v>0.1718</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0594</v>
+        <v>-0.06759999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="56">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,16 +163,7 @@
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Previous</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Delta</t>
+    <t>No numeric changes detected since last run.</t>
   </si>
   <si>
     <t>Rank</t>
@@ -203,13 +194,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.00"/>
-    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,22 +230,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -272,24 +247,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -359,33 +316,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1351,7 +1302,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1384,462 +1335,8 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-6.62</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-9.35</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-2.73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-17.12</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-17.63</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-6.9</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-6.96</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-1.27</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-3.59</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-2.32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-3.98</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-2.87</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5">
-        <v>5.53</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-1.61</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-7.14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5">
-        <v>1.84</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-1.94</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-3.78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5">
-        <v>1.68</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-0.87</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-2.55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-21.11</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-24.79</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-3.68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-4.9</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-6.71</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-1.81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-17.2</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-19.84</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-2.64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5">
-        <v>3.53</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-1.27</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-4.8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-15.4</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-17.15</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-1.75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-22.45</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-23.3</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-29.97</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-31.6</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-1.63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5">
-        <v>3701.5</v>
-      </c>
-      <c r="D22" s="5">
-        <v>3625.1</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-76.40000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="5">
-        <v>260.25</v>
-      </c>
-      <c r="D23" s="5">
-        <v>257.4</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-2.85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="5">
-        <v>3252.1</v>
-      </c>
-      <c r="D24" s="5">
-        <v>3176.6</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-75.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="5">
-        <v>34</v>
-      </c>
-      <c r="D25" s="5">
-        <v>66</v>
-      </c>
-      <c r="E25" s="7">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="5">
-        <v>66</v>
-      </c>
-      <c r="D26" s="5">
-        <v>34</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>35.71</v>
-      </c>
-      <c r="D27" s="5">
-        <v>31.28</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-4.43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="5">
-        <v>27.05</v>
-      </c>
-      <c r="D28" s="5">
-        <v>25.92</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-1.13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="5">
-        <v>43.96</v>
-      </c>
-      <c r="D29" s="5">
-        <v>38.47</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-5.49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-3.44</v>
-      </c>
-      <c r="D30" s="5">
-        <v>0.58</v>
-      </c>
-      <c r="E30" s="7">
-        <v>4.02</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="5">
-        <v>16.93</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-2.88</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-19.81</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-21.06</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-8.51</v>
-      </c>
-      <c r="E32" s="7">
-        <v>12.55</v>
       </c>
     </row>
   </sheetData>
@@ -1865,60 +1362,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="F1" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="G1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="H1" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="I1" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="6">
         <v>36.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="7">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="6">
         <v>31.9</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="6">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="6">
         <v>-11.3</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="6">
         <v>-9.300000000000001</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="6">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2020,24 +1517,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
+      <c r="A2" s="9">
         <v>0.2469</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="9">
         <v>0.1718</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="9">
         <v>-0.06759999999999999</v>
       </c>
     </row>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="68">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,13 +157,49 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>25.9 → 30.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>25.9</t>
+  </si>
+  <si>
+    <t>30.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>No numeric changes detected since last run.</t>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
   <si>
     <t>Rank</t>
@@ -194,11 +230,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,8 +268,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -247,6 +299,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -316,27 +386,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -692,8 +769,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -833,10 +909,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3625.1</v>
+        <v>3703.3</v>
       </c>
       <c r="D2">
-        <v>-2.06</v>
+        <v>2.16</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -845,46 +921,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-17.15</v>
+        <v>-15.36</v>
       </c>
       <c r="H2">
-        <v>9.52</v>
+        <v>11.88</v>
       </c>
       <c r="I2">
-        <v>-3.59</v>
+        <v>0.27</v>
       </c>
       <c r="J2">
-        <v>-9.35</v>
+        <v>-6.15</v>
       </c>
       <c r="K2">
-        <v>-6.71</v>
+        <v>-6.15</v>
       </c>
       <c r="L2">
-        <v>-1.94</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M2">
-        <v>17.18</v>
+        <v>17.84</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="P2">
-        <v>3708</v>
+        <v>3709.98</v>
       </c>
       <c r="Q2">
-        <v>3821.95</v>
+        <v>3810.99</v>
       </c>
       <c r="R2">
-        <v>3945.57</v>
+        <v>3941.01</v>
       </c>
       <c r="S2">
-        <v>3941.85</v>
+        <v>3940.2</v>
       </c>
       <c r="T2">
-        <v>-8.039999999999999</v>
+        <v>-6.01</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -899,34 +975,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>31.28</v>
+        <v>39.54</v>
       </c>
       <c r="Z2">
-        <v>-73.23</v>
+        <v>-72.51000000000001</v>
       </c>
       <c r="AA2">
-        <v>-57.94</v>
+        <v>-60.85</v>
       </c>
       <c r="AB2">
-        <v>-15.29</v>
+        <v>-11.66</v>
       </c>
       <c r="AC2">
-        <v>27.02</v>
+        <v>24.56</v>
       </c>
       <c r="AD2">
-        <v>34.41</v>
+        <v>31.01</v>
       </c>
       <c r="AE2">
-        <v>67.97</v>
+        <v>69.12</v>
       </c>
       <c r="AF2">
-        <v>0.58</v>
+        <v>-21.31</v>
       </c>
       <c r="AG2">
-        <v>4005.21</v>
+        <v>3995.13</v>
       </c>
       <c r="AH2">
-        <v>3638.7</v>
+        <v>3626.85</v>
       </c>
       <c r="AI2">
         <v>3858.41</v>
@@ -935,7 +1011,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>44.98</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -946,10 +1022,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>257.4</v>
+        <v>261.2</v>
       </c>
       <c r="D3">
-        <v>-1.1</v>
+        <v>1.48</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -958,46 +1034,46 @@
         <v>237.75</v>
       </c>
       <c r="G3">
-        <v>-23.3</v>
+        <v>-22.17</v>
       </c>
       <c r="H3">
-        <v>8.26</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="I3">
-        <v>-2.87</v>
+        <v>-1.19</v>
       </c>
       <c r="J3">
-        <v>-17.63</v>
+        <v>-15.28</v>
       </c>
       <c r="K3">
-        <v>-19.84</v>
+        <v>-18.69</v>
       </c>
       <c r="L3">
-        <v>-0.87</v>
+        <v>1.55</v>
       </c>
       <c r="M3">
-        <v>24.69</v>
+        <v>25.11</v>
       </c>
       <c r="N3">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="O3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="P3">
-        <v>262.03</v>
+        <v>261.4</v>
       </c>
       <c r="Q3">
-        <v>287.7</v>
+        <v>285.24</v>
       </c>
       <c r="R3">
-        <v>304.05</v>
+        <v>303.09</v>
       </c>
       <c r="S3">
-        <v>290.76</v>
+        <v>290.58</v>
       </c>
       <c r="T3">
-        <v>-11.47</v>
+        <v>-10.11</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1012,34 +1088,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>25.92</v>
+        <v>30.13</v>
       </c>
       <c r="Z3">
-        <v>-13.61</v>
+        <v>-13.58</v>
       </c>
       <c r="AA3">
-        <v>-10.34</v>
+        <v>-10.99</v>
       </c>
       <c r="AB3">
-        <v>-3.27</v>
+        <v>-2.59</v>
       </c>
       <c r="AC3">
-        <v>0.93</v>
+        <v>5.82</v>
       </c>
       <c r="AD3">
-        <v>0.93</v>
+        <v>2.56</v>
       </c>
       <c r="AE3">
-        <v>8.68</v>
+        <v>8.6</v>
       </c>
       <c r="AF3">
-        <v>-2.88</v>
+        <v>-59.1</v>
       </c>
       <c r="AG3">
-        <v>328.56</v>
+        <v>326.27</v>
       </c>
       <c r="AH3">
-        <v>246.83</v>
+        <v>244.2</v>
       </c>
       <c r="AI3">
         <v>284.18</v>
@@ -1048,7 +1124,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>55.48</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1059,10 +1135,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3176.6</v>
+        <v>3270.1</v>
       </c>
       <c r="D4">
-        <v>-2.32</v>
+        <v>2.94</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1071,46 +1147,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-31.6</v>
+        <v>-29.58</v>
       </c>
       <c r="H4">
-        <v>4.45</v>
+        <v>7.52</v>
       </c>
       <c r="I4">
-        <v>-1.61</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J4">
-        <v>-6.96</v>
+        <v>-3.51</v>
       </c>
       <c r="K4">
-        <v>-1.27</v>
+        <v>-0.25</v>
       </c>
       <c r="L4">
-        <v>-24.79</v>
+        <v>-22.77</v>
       </c>
       <c r="M4">
-        <v>-6.76</v>
+        <v>-5.84</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="O4">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="P4">
-        <v>3232.4</v>
+        <v>3232.86</v>
       </c>
       <c r="Q4">
-        <v>3267.29</v>
+        <v>3262.59</v>
       </c>
       <c r="R4">
-        <v>3435.02</v>
+        <v>3428.72</v>
       </c>
       <c r="S4">
-        <v>3521.5</v>
+        <v>3515.52</v>
       </c>
       <c r="T4">
-        <v>-9.789999999999999</v>
+        <v>-6.98</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1125,34 +1201,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>38.47</v>
+        <v>47.25</v>
       </c>
       <c r="Z4">
-        <v>-63.4</v>
+        <v>-56.23</v>
       </c>
       <c r="AA4">
-        <v>-66.73</v>
+        <v>-64.63</v>
       </c>
       <c r="AB4">
-        <v>3.32</v>
+        <v>8.4</v>
       </c>
       <c r="AC4">
-        <v>89.77</v>
+        <v>91.02</v>
       </c>
       <c r="AD4">
-        <v>92.2</v>
+        <v>91.34</v>
       </c>
       <c r="AE4">
-        <v>101.01</v>
+        <v>103.75</v>
       </c>
       <c r="AF4">
-        <v>-8.51</v>
+        <v>4.72</v>
       </c>
       <c r="AG4">
-        <v>3416.85</v>
+        <v>3405.1</v>
       </c>
       <c r="AH4">
-        <v>3117.72</v>
+        <v>3120.08</v>
       </c>
       <c r="AI4">
         <v>3408.79</v>
@@ -1161,7 +1237,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>20.84</v>
+        <v>21.38</v>
       </c>
     </row>
   </sheetData>
@@ -1302,7 +1378,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1322,12 +1398,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>45</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1336,7 +1447,461 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>47</v>
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-9.35</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-6.15</v>
+      </c>
+      <c r="E7" s="7">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-17.63</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-15.28</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-6.96</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-3.51</v>
+      </c>
+      <c r="E9" s="7">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-3.59</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.27</v>
+      </c>
+      <c r="E10" s="7">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-2.87</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-1.19</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-1.61</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-1.94</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-0.87</v>
+      </c>
+      <c r="D14" s="6">
+        <v>1.55</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-24.79</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-22.77</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-6.71</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-6.15</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-19.84</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-18.69</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-1.27</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.25</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-17.15</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-15.36</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-23.3</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-22.17</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-31.6</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-29.58</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6">
+        <v>3625.1</v>
+      </c>
+      <c r="D22" s="6">
+        <v>3703.3</v>
+      </c>
+      <c r="E22" s="7">
+        <v>78.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6">
+        <v>257.4</v>
+      </c>
+      <c r="D23" s="6">
+        <v>261.2</v>
+      </c>
+      <c r="E23" s="7">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <v>3176.6</v>
+      </c>
+      <c r="D24" s="6">
+        <v>3270.1</v>
+      </c>
+      <c r="E24" s="7">
+        <v>93.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="6">
+        <v>66</v>
+      </c>
+      <c r="D25" s="6">
+        <v>34</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="6">
+        <v>34</v>
+      </c>
+      <c r="D26" s="6">
+        <v>66</v>
+      </c>
+      <c r="E26" s="7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>31.28</v>
+      </c>
+      <c r="D27" s="6">
+        <v>39.54</v>
+      </c>
+      <c r="E27" s="7">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="6">
+        <v>25.92</v>
+      </c>
+      <c r="D28" s="6">
+        <v>30.13</v>
+      </c>
+      <c r="E28" s="7">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="6">
+        <v>38.47</v>
+      </c>
+      <c r="D29" s="6">
+        <v>47.25</v>
+      </c>
+      <c r="E29" s="7">
+        <v>8.779999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.58</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-21.31</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-21.89</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-2.88</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-59.1</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-56.22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-8.51</v>
+      </c>
+      <c r="D32" s="6">
+        <v>4.72</v>
+      </c>
+      <c r="E32" s="7">
+        <v>13.23</v>
       </c>
     </row>
   </sheetData>
@@ -1362,60 +1927,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>55</v>
+      <c r="B1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="11">
         <v>36.52</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="6">
-        <v>31.9</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="D2" s="11">
+        <v>39</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="6">
-        <v>-11.3</v>
-      </c>
-      <c r="G2" s="6">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="F2" s="11">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-8.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1517,25 +2082,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="9">
-        <v>0.2469</v>
-      </c>
-      <c r="B2" s="9">
-        <v>0.1718</v>
-      </c>
-      <c r="C2" s="9">
-        <v>-0.06759999999999999</v>
+      <c r="A2" s="14">
+        <v>0.2511</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1784</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0584</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,19 +172,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>25.9 → 30.1</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>47.2 → 50.4</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>25.9</t>
-  </si>
-  <si>
-    <t>30.1</t>
+    <t>47.2</t>
+  </si>
+  <si>
+    <t>50.4</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 DEATH CROSS</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -386,7 +395,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -394,10 +403,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -909,10 +919,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3703.3</v>
+        <v>3627.5</v>
       </c>
       <c r="D2">
-        <v>2.16</v>
+        <v>-2.05</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -921,88 +931,88 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-15.36</v>
+        <v>-17.09</v>
       </c>
       <c r="H2">
-        <v>11.88</v>
+        <v>9.59</v>
       </c>
       <c r="I2">
-        <v>0.27</v>
+        <v>-3.27</v>
       </c>
       <c r="J2">
-        <v>-6.15</v>
+        <v>-7.52</v>
       </c>
       <c r="K2">
-        <v>-6.15</v>
+        <v>-7.66</v>
       </c>
       <c r="L2">
-        <v>0.07000000000000001</v>
+        <v>-1.79</v>
       </c>
       <c r="M2">
-        <v>17.84</v>
+        <v>17.31</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="P2">
-        <v>3709.98</v>
+        <v>3685.48</v>
       </c>
       <c r="Q2">
-        <v>3810.99</v>
+        <v>3794.61</v>
       </c>
       <c r="R2">
-        <v>3941.01</v>
+        <v>3934.8</v>
       </c>
       <c r="S2">
-        <v>3940.2</v>
+        <v>3938.17</v>
       </c>
       <c r="T2">
-        <v>-6.01</v>
+        <v>-7.89</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
       </c>
       <c r="V2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W2" t="s">
         <v>41</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.54</v>
+        <v>35.13</v>
       </c>
       <c r="Z2">
-        <v>-72.51000000000001</v>
+        <v>-77.17</v>
       </c>
       <c r="AA2">
-        <v>-60.85</v>
+        <v>-64.12</v>
       </c>
       <c r="AB2">
-        <v>-11.66</v>
+        <v>-13.06</v>
       </c>
       <c r="AC2">
-        <v>24.56</v>
+        <v>23.72</v>
       </c>
       <c r="AD2">
-        <v>31.01</v>
+        <v>25.1</v>
       </c>
       <c r="AE2">
-        <v>69.12</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="AF2">
-        <v>-21.31</v>
+        <v>-31.15</v>
       </c>
       <c r="AG2">
-        <v>3995.13</v>
+        <v>3983.03</v>
       </c>
       <c r="AH2">
-        <v>3626.85</v>
+        <v>3606.2</v>
       </c>
       <c r="AI2">
         <v>3858.41</v>
@@ -1011,7 +1021,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>47.21</v>
+        <v>46.52</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1022,10 +1032,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>261.2</v>
+        <v>262.7</v>
       </c>
       <c r="D3">
-        <v>1.48</v>
+        <v>0.57</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1034,46 +1044,46 @@
         <v>237.75</v>
       </c>
       <c r="G3">
-        <v>-22.17</v>
+        <v>-21.72</v>
       </c>
       <c r="H3">
-        <v>9.859999999999999</v>
+        <v>10.49</v>
       </c>
       <c r="I3">
-        <v>-1.19</v>
+        <v>-0.4</v>
       </c>
       <c r="J3">
-        <v>-15.28</v>
+        <v>-15.37</v>
       </c>
       <c r="K3">
-        <v>-18.69</v>
+        <v>-19.09</v>
       </c>
       <c r="L3">
-        <v>1.55</v>
+        <v>2.36</v>
       </c>
       <c r="M3">
-        <v>25.11</v>
+        <v>25.23</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P3">
-        <v>261.4</v>
+        <v>261.19</v>
       </c>
       <c r="Q3">
-        <v>285.24</v>
+        <v>282.81</v>
       </c>
       <c r="R3">
-        <v>303.09</v>
+        <v>302.22</v>
       </c>
       <c r="S3">
-        <v>290.58</v>
+        <v>290.39</v>
       </c>
       <c r="T3">
-        <v>-10.11</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1088,34 +1098,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>30.13</v>
+        <v>31.78</v>
       </c>
       <c r="Z3">
-        <v>-13.58</v>
+        <v>-13.28</v>
       </c>
       <c r="AA3">
-        <v>-10.99</v>
+        <v>-11.44</v>
       </c>
       <c r="AB3">
-        <v>-2.59</v>
+        <v>-1.84</v>
       </c>
       <c r="AC3">
-        <v>5.82</v>
+        <v>13.91</v>
       </c>
       <c r="AD3">
-        <v>2.56</v>
+        <v>6.89</v>
       </c>
       <c r="AE3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AF3">
-        <v>-59.1</v>
+        <v>-66.83</v>
       </c>
       <c r="AG3">
-        <v>326.27</v>
+        <v>323.09</v>
       </c>
       <c r="AH3">
-        <v>244.2</v>
+        <v>242.52</v>
       </c>
       <c r="AI3">
         <v>284.18</v>
@@ -1124,7 +1134,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>56.7</v>
+        <v>54.84</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1135,10 +1145,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3270.1</v>
+        <v>3309</v>
       </c>
       <c r="D4">
-        <v>2.94</v>
+        <v>1.19</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1147,46 +1157,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-29.58</v>
+        <v>-28.74</v>
       </c>
       <c r="H4">
-        <v>7.52</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4">
-        <v>0.07000000000000001</v>
+        <v>2.78</v>
       </c>
       <c r="J4">
-        <v>-3.51</v>
+        <v>-1.63</v>
       </c>
       <c r="K4">
-        <v>-0.25</v>
+        <v>0.34</v>
       </c>
       <c r="L4">
-        <v>-22.77</v>
+        <v>-21.88</v>
       </c>
       <c r="M4">
-        <v>-5.84</v>
+        <v>-5.32</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P4">
-        <v>3232.86</v>
+        <v>3250.76</v>
       </c>
       <c r="Q4">
-        <v>3262.59</v>
+        <v>3259.15</v>
       </c>
       <c r="R4">
-        <v>3428.72</v>
+        <v>3423.72</v>
       </c>
       <c r="S4">
-        <v>3515.52</v>
+        <v>3509.17</v>
       </c>
       <c r="T4">
-        <v>-6.98</v>
+        <v>-5.7</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1201,34 +1211,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>47.25</v>
+        <v>50.43</v>
       </c>
       <c r="Z4">
-        <v>-56.23</v>
+        <v>-46.86</v>
       </c>
       <c r="AA4">
-        <v>-64.63</v>
+        <v>-61.07</v>
       </c>
       <c r="AB4">
-        <v>8.4</v>
+        <v>14.21</v>
       </c>
       <c r="AC4">
-        <v>91.02</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="AD4">
-        <v>91.34</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="AE4">
-        <v>103.75</v>
+        <v>100.62</v>
       </c>
       <c r="AF4">
-        <v>4.72</v>
+        <v>-17.68</v>
       </c>
       <c r="AG4">
-        <v>3405.1</v>
+        <v>3392.99</v>
       </c>
       <c r="AH4">
-        <v>3120.08</v>
+        <v>3125.3</v>
       </c>
       <c r="AI4">
         <v>3408.79</v>
@@ -1237,7 +1247,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>21.38</v>
+        <v>22.49</v>
       </c>
     </row>
   </sheetData>
@@ -1378,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1418,7 +1428,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>50</v>
@@ -1436,478 +1446,464 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="C7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-9.35</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C8" s="7">
         <v>-6.15</v>
       </c>
-      <c r="E7" s="7">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D8" s="7">
+        <v>-7.52</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-17.63</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C9" s="7">
         <v>-15.28</v>
       </c>
-      <c r="E8" s="7">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D9" s="7">
+        <v>-15.37</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-6.96</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C10" s="7">
         <v>-3.51</v>
       </c>
-      <c r="E9" s="7">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D10" s="7">
+        <v>-1.63</v>
+      </c>
+      <c r="E10" s="9">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-3.59</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C11" s="7">
         <v>0.27</v>
       </c>
-      <c r="E10" s="7">
-        <v>3.86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D11" s="7">
+        <v>-3.27</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-3.54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-2.87</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C12" s="7">
         <v>-1.19</v>
       </c>
-      <c r="E11" s="7">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D12" s="7">
+        <v>-0.4</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-1.61</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C13" s="7">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E12" s="7">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="D13" s="7">
+        <v>2.78</v>
+      </c>
+      <c r="E13" s="9">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-1.94</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C14" s="7">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E13" s="7">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="D14" s="7">
+        <v>-1.79</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-0.87</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C15" s="7">
         <v>1.55</v>
       </c>
-      <c r="E14" s="7">
-        <v>2.42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="D15" s="7">
+        <v>2.36</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-24.79</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C16" s="7">
         <v>-22.77</v>
       </c>
-      <c r="E15" s="7">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="D16" s="7">
+        <v>-21.88</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>-6.71</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C17" s="7">
         <v>-6.15</v>
       </c>
-      <c r="E16" s="7">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="D17" s="7">
+        <v>-7.66</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-19.84</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C18" s="7">
         <v>-18.69</v>
       </c>
-      <c r="E17" s="7">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="D18" s="7">
+        <v>-19.09</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>-1.27</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C19" s="7">
         <v>-0.25</v>
       </c>
-      <c r="E18" s="7">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="D19" s="7">
+        <v>0.34</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-17.15</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C20" s="7">
         <v>-15.36</v>
       </c>
-      <c r="E19" s="7">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="D20" s="7">
+        <v>-17.09</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-23.3</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C21" s="7">
         <v>-22.17</v>
       </c>
-      <c r="E20" s="7">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="D21" s="7">
+        <v>-21.72</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-31.6</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C22" s="7">
         <v>-29.58</v>
       </c>
-      <c r="E21" s="7">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="D22" s="7">
+        <v>-28.74</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>3625.1</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C23" s="7">
         <v>3703.3</v>
       </c>
-      <c r="E22" s="7">
-        <v>78.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="D23" s="7">
+        <v>3627.5</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-75.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>257.4</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C24" s="7">
         <v>261.2</v>
       </c>
-      <c r="E23" s="7">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="D24" s="7">
+        <v>262.7</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>3176.6</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C25" s="7">
         <v>3270.1</v>
       </c>
-      <c r="E24" s="7">
-        <v>93.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="D25" s="7">
+        <v>3309</v>
+      </c>
+      <c r="E25" s="9">
+        <v>38.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="7">
+        <v>39.54</v>
+      </c>
+      <c r="D26" s="7">
+        <v>35.13</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-4.41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="6">
-        <v>66</v>
-      </c>
-      <c r="D25" s="6">
-        <v>34</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B27" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="7">
+        <v>30.13</v>
+      </c>
+      <c r="D27" s="7">
+        <v>31.78</v>
+      </c>
+      <c r="E27" s="9">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="6">
-        <v>34</v>
-      </c>
-      <c r="D26" s="6">
-        <v>66</v>
-      </c>
-      <c r="E26" s="7">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="7">
+        <v>47.25</v>
+      </c>
+      <c r="D28" s="7">
+        <v>50.43</v>
+      </c>
+      <c r="E28" s="9">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>31.28</v>
-      </c>
-      <c r="D27" s="6">
-        <v>39.54</v>
-      </c>
-      <c r="E27" s="7">
-        <v>8.26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B29" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-21.31</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-31.15</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-9.84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="6">
-        <v>25.92</v>
-      </c>
-      <c r="D28" s="6">
-        <v>30.13</v>
-      </c>
-      <c r="E28" s="7">
-        <v>4.21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B30" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-59.1</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-66.83</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-7.73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="6">
-        <v>38.47</v>
-      </c>
-      <c r="D29" s="6">
-        <v>47.25</v>
-      </c>
-      <c r="E29" s="7">
-        <v>8.779999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>0.58</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-21.31</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-21.89</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-2.88</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-59.1</v>
+      <c r="C31" s="7">
+        <v>4.72</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-17.68</v>
       </c>
       <c r="E31" s="8">
-        <v>-56.22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-8.51</v>
-      </c>
-      <c r="D32" s="6">
-        <v>4.72</v>
-      </c>
-      <c r="E32" s="7">
-        <v>13.23</v>
+        <v>-22.4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1927,60 +1923,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>67</v>
       </c>
+      <c r="G1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>39</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>39.1</v>
+      </c>
+      <c r="E2" s="12">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-8.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="H2" s="12">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2082,25 +2078,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.2511</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1784</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0584</v>
+      <c r="A2" s="15">
+        <v>0.2523</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1731</v>
+      </c>
+      <c r="C2" s="15">
+        <v>-0.0532</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -154,46 +154,13 @@
     <t>DOWN</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>47.2 → 50.4</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>47.2</t>
-  </si>
-  <si>
-    <t>50.4</t>
-  </si>
-  <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 DEATH CROSS</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -245,7 +212,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,15 +251,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -320,12 +280,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,23 +349,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -420,7 +371,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -919,10 +870,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3627.5</v>
+        <v>3675</v>
       </c>
       <c r="D2">
-        <v>-2.05</v>
+        <v>1.31</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -931,46 +882,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-17.09</v>
+        <v>-16.01</v>
       </c>
       <c r="H2">
-        <v>9.59</v>
+        <v>11.02</v>
       </c>
       <c r="I2">
-        <v>-3.27</v>
+        <v>-2.52</v>
       </c>
       <c r="J2">
-        <v>-7.52</v>
+        <v>-7.08</v>
       </c>
       <c r="K2">
-        <v>-7.66</v>
+        <v>-4.51</v>
       </c>
       <c r="L2">
-        <v>-1.79</v>
+        <v>-0.51</v>
       </c>
       <c r="M2">
-        <v>17.31</v>
+        <v>17.16</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P2">
-        <v>3685.48</v>
+        <v>3666.48</v>
       </c>
       <c r="Q2">
-        <v>3794.61</v>
+        <v>3781.83</v>
       </c>
       <c r="R2">
-        <v>3934.8</v>
+        <v>3929.52</v>
       </c>
       <c r="S2">
-        <v>3938.17</v>
+        <v>3936.45</v>
       </c>
       <c r="T2">
-        <v>-7.89</v>
+        <v>-6.64</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -985,43 +936,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>35.13</v>
+        <v>39.67</v>
       </c>
       <c r="Z2">
-        <v>-77.17</v>
+        <v>-76.15000000000001</v>
       </c>
       <c r="AA2">
-        <v>-64.12</v>
+        <v>-66.52</v>
       </c>
       <c r="AB2">
-        <v>-13.06</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="AC2">
-        <v>23.72</v>
+        <v>40.15</v>
       </c>
       <c r="AD2">
-        <v>25.1</v>
+        <v>29.47</v>
       </c>
       <c r="AE2">
-        <v>73.29000000000001</v>
+        <v>74.13</v>
       </c>
       <c r="AF2">
-        <v>-31.15</v>
+        <v>38.88</v>
       </c>
       <c r="AG2">
-        <v>3983.03</v>
+        <v>3966.02</v>
       </c>
       <c r="AH2">
-        <v>3606.2</v>
+        <v>3597.64</v>
       </c>
       <c r="AI2">
-        <v>3858.41</v>
+        <v>3857.84</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>46.52</v>
+        <v>46.54</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1032,10 +983,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>262.7</v>
+        <v>267.6</v>
       </c>
       <c r="D3">
-        <v>0.57</v>
+        <v>1.87</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1044,46 +995,46 @@
         <v>237.75</v>
       </c>
       <c r="G3">
-        <v>-21.72</v>
+        <v>-20.26</v>
       </c>
       <c r="H3">
-        <v>10.49</v>
+        <v>12.56</v>
       </c>
       <c r="I3">
-        <v>-0.4</v>
+        <v>1.21</v>
       </c>
       <c r="J3">
-        <v>-15.37</v>
+        <v>-14.04</v>
       </c>
       <c r="K3">
-        <v>-19.09</v>
+        <v>-15.13</v>
       </c>
       <c r="L3">
-        <v>2.36</v>
+        <v>5.79</v>
       </c>
       <c r="M3">
-        <v>25.23</v>
+        <v>25.26</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="P3">
-        <v>261.19</v>
+        <v>261.83</v>
       </c>
       <c r="Q3">
-        <v>282.81</v>
+        <v>280.73</v>
       </c>
       <c r="R3">
-        <v>302.22</v>
+        <v>301.34</v>
       </c>
       <c r="S3">
-        <v>290.39</v>
+        <v>290.23</v>
       </c>
       <c r="T3">
-        <v>-9.539999999999999</v>
+        <v>-7.8</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1098,34 +1049,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>31.78</v>
+        <v>37.02</v>
       </c>
       <c r="Z3">
-        <v>-13.28</v>
+        <v>-12.51</v>
       </c>
       <c r="AA3">
-        <v>-11.44</v>
+        <v>-11.66</v>
       </c>
       <c r="AB3">
-        <v>-1.84</v>
+        <v>-0.85</v>
       </c>
       <c r="AC3">
-        <v>13.91</v>
+        <v>29.23</v>
       </c>
       <c r="AD3">
-        <v>6.89</v>
+        <v>16.32</v>
       </c>
       <c r="AE3">
-        <v>8.4</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AF3">
-        <v>-66.83</v>
+        <v>-63.54</v>
       </c>
       <c r="AG3">
-        <v>323.09</v>
+        <v>319.57</v>
       </c>
       <c r="AH3">
-        <v>242.52</v>
+        <v>241.9</v>
       </c>
       <c r="AI3">
         <v>284.18</v>
@@ -1134,7 +1085,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>54.84</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1145,10 +1096,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3309</v>
+        <v>3429.2</v>
       </c>
       <c r="D4">
-        <v>1.19</v>
+        <v>3.63</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1157,46 +1108,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-28.74</v>
+        <v>-26.16</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>12.75</v>
       </c>
       <c r="I4">
-        <v>2.78</v>
+        <v>5.64</v>
       </c>
       <c r="J4">
-        <v>-1.63</v>
+        <v>1.52</v>
       </c>
       <c r="K4">
-        <v>0.34</v>
+        <v>4.13</v>
       </c>
       <c r="L4">
-        <v>-21.88</v>
+        <v>-17.69</v>
       </c>
       <c r="M4">
-        <v>-5.32</v>
+        <v>-4.96</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="P4">
-        <v>3250.76</v>
+        <v>3287.4</v>
       </c>
       <c r="Q4">
-        <v>3259.15</v>
+        <v>3263.74</v>
       </c>
       <c r="R4">
-        <v>3423.72</v>
+        <v>3421.19</v>
       </c>
       <c r="S4">
-        <v>3509.17</v>
+        <v>3503.1</v>
       </c>
       <c r="T4">
-        <v>-5.7</v>
+        <v>-2.11</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1211,43 +1162,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>50.43</v>
+        <v>58.69</v>
       </c>
       <c r="Z4">
-        <v>-46.86</v>
+        <v>-29.39</v>
       </c>
       <c r="AA4">
-        <v>-61.07</v>
+        <v>-54.74</v>
       </c>
       <c r="AB4">
-        <v>14.21</v>
+        <v>25.34</v>
       </c>
       <c r="AC4">
-        <v>91.34999999999999</v>
+        <v>100</v>
       </c>
       <c r="AD4">
-        <v>90.70999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="AE4">
-        <v>100.62</v>
+        <v>103.96</v>
       </c>
       <c r="AF4">
-        <v>-17.68</v>
+        <v>49.47</v>
       </c>
       <c r="AG4">
-        <v>3392.99</v>
+        <v>3414.15</v>
       </c>
       <c r="AH4">
-        <v>3125.3</v>
+        <v>3113.32</v>
       </c>
       <c r="AI4">
-        <v>3408.79</v>
+        <v>3076.97</v>
       </c>
       <c r="AJ4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AK4">
-        <v>22.49</v>
+        <v>27.17</v>
       </c>
     </row>
   </sheetData>
@@ -1388,7 +1339,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1398,7 +1349,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1408,502 +1359,447 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>62</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-7.52</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-7.08</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.44</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-15.37</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-14.04</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-1.63</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1.52</v>
+      </c>
+      <c r="E9" s="6">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-6.15</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-7.52</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-3.27</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-2.52</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-15.28</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-15.37</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-0.4</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1.21</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-3.51</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-1.63</v>
-      </c>
-      <c r="E10" s="9">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2.78</v>
+      </c>
+      <c r="D12" s="5">
+        <v>5.64</v>
+      </c>
+      <c r="E12" s="6">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="7">
-        <v>0.27</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-3.27</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-3.54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-1.79</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-0.51</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-1.19</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-0.4</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2.36</v>
+      </c>
+      <c r="D14" s="5">
+        <v>5.79</v>
+      </c>
+      <c r="E14" s="6">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="7">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D13" s="7">
-        <v>2.78</v>
-      </c>
-      <c r="E13" s="9">
-        <v>2.71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-21.88</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-17.69</v>
+      </c>
+      <c r="E15" s="6">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="7">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-1.79</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-7.66</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-4.51</v>
+      </c>
+      <c r="E16" s="6">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="7">
-        <v>1.55</v>
-      </c>
-      <c r="D15" s="7">
-        <v>2.36</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-19.09</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-15.13</v>
+      </c>
+      <c r="E17" s="6">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-22.77</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-21.88</v>
-      </c>
-      <c r="E16" s="9">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.34</v>
+      </c>
+      <c r="D18" s="5">
+        <v>4.13</v>
+      </c>
+      <c r="E18" s="6">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-6.15</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-7.66</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-17.09</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-16.01</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-18.69</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-19.09</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-21.72</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-20.26</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-0.25</v>
-      </c>
-      <c r="D19" s="7">
-        <v>0.34</v>
-      </c>
-      <c r="E19" s="9">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-28.74</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-26.16</v>
+      </c>
+      <c r="E21" s="6">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-15.36</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-17.09</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>3627.5</v>
+      </c>
+      <c r="D22" s="5">
+        <v>3675</v>
+      </c>
+      <c r="E22" s="6">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-22.17</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-21.72</v>
-      </c>
-      <c r="E21" s="9">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>262.7</v>
+      </c>
+      <c r="D23" s="5">
+        <v>267.6</v>
+      </c>
+      <c r="E23" s="6">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-29.58</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-28.74</v>
-      </c>
-      <c r="E22" s="9">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>3309</v>
+      </c>
+      <c r="D24" s="5">
+        <v>3429.2</v>
+      </c>
+      <c r="E24" s="6">
+        <v>120.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="7">
-        <v>3703.3</v>
-      </c>
-      <c r="D23" s="7">
-        <v>3627.5</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-75.8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>35.13</v>
+      </c>
+      <c r="D25" s="5">
+        <v>39.67</v>
+      </c>
+      <c r="E25" s="6">
+        <v>4.54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="7">
-        <v>261.2</v>
-      </c>
-      <c r="D24" s="7">
-        <v>262.7</v>
-      </c>
-      <c r="E24" s="9">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>31.78</v>
+      </c>
+      <c r="D26" s="5">
+        <v>37.02</v>
+      </c>
+      <c r="E26" s="6">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="7">
-        <v>3270.1</v>
-      </c>
-      <c r="D25" s="7">
-        <v>3309</v>
-      </c>
-      <c r="E25" s="9">
-        <v>38.9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>50.43</v>
+      </c>
+      <c r="D27" s="5">
+        <v>58.69</v>
+      </c>
+      <c r="E27" s="6">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="7">
-        <v>39.54</v>
-      </c>
-      <c r="D26" s="7">
-        <v>35.13</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-4.41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-31.15</v>
+      </c>
+      <c r="D28" s="5">
+        <v>38.88</v>
+      </c>
+      <c r="E28" s="6">
+        <v>70.03</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="7">
-        <v>30.13</v>
-      </c>
-      <c r="D27" s="7">
-        <v>31.78</v>
-      </c>
-      <c r="E27" s="9">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-66.83</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-63.54</v>
+      </c>
+      <c r="E29" s="6">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="7">
-        <v>47.25</v>
-      </c>
-      <c r="D28" s="7">
-        <v>50.43</v>
-      </c>
-      <c r="E28" s="9">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="6" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="7">
-        <v>-21.31</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-31.15</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-9.84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-59.1</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-66.83</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-7.73</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="7">
-        <v>4.72</v>
-      </c>
-      <c r="D31" s="7">
+      <c r="C30" s="5">
         <v>-17.68</v>
       </c>
-      <c r="E31" s="8">
-        <v>-22.4</v>
+      <c r="D30" s="5">
+        <v>49.47</v>
+      </c>
+      <c r="E30" s="6">
+        <v>67.15000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1923,60 +1819,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>70</v>
+      <c r="B1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="9">
         <v>36.52</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="10">
         <v>3</v>
       </c>
-      <c r="D2" s="12">
-        <v>39.1</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="9">
+        <v>45.1</v>
+      </c>
+      <c r="E2" s="9">
         <v>0</v>
       </c>
-      <c r="F2" s="12">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="9">
+        <v>-6.5</v>
+      </c>
+      <c r="G2" s="9">
+        <v>-5.2</v>
+      </c>
+      <c r="H2" s="9">
         <v>66.3</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2078,25 +1974,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="15">
-        <v>0.2523</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.1731</v>
-      </c>
-      <c r="C2" s="15">
-        <v>-0.0532</v>
+      <c r="A2" s="12">
+        <v>0.2526</v>
+      </c>
+      <c r="B2" s="12">
+        <v>0.1716</v>
+      </c>
+      <c r="C2" s="12">
+        <v>-0.0496</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -212,7 +212,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,13 +246,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -274,6 +281,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -349,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -359,10 +372,11 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -371,7 +385,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -870,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3675</v>
+        <v>3642</v>
       </c>
       <c r="D2">
-        <v>1.31</v>
+        <v>-0.9</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -882,46 +896,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-16.01</v>
+        <v>-16.76</v>
       </c>
       <c r="H2">
-        <v>11.02</v>
+        <v>10.03</v>
       </c>
       <c r="I2">
-        <v>-2.52</v>
+        <v>-1.61</v>
       </c>
       <c r="J2">
-        <v>-7.08</v>
+        <v>-7.34</v>
       </c>
       <c r="K2">
-        <v>-4.51</v>
+        <v>-3.75</v>
       </c>
       <c r="L2">
-        <v>-0.51</v>
+        <v>-2.43</v>
       </c>
       <c r="M2">
-        <v>17.16</v>
+        <v>16.46</v>
       </c>
       <c r="N2">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="O2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P2">
-        <v>3666.48</v>
+        <v>3654.58</v>
       </c>
       <c r="Q2">
-        <v>3781.83</v>
+        <v>3771.39</v>
       </c>
       <c r="R2">
-        <v>3929.52</v>
+        <v>3921.86</v>
       </c>
       <c r="S2">
-        <v>3936.45</v>
+        <v>3934.58</v>
       </c>
       <c r="T2">
-        <v>-6.64</v>
+        <v>-7.44</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -936,34 +950,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.67</v>
+        <v>37.7</v>
       </c>
       <c r="Z2">
-        <v>-76.15000000000001</v>
+        <v>-77.12</v>
       </c>
       <c r="AA2">
-        <v>-66.52</v>
+        <v>-68.64</v>
       </c>
       <c r="AB2">
-        <v>-9.630000000000001</v>
+        <v>-8.48</v>
       </c>
       <c r="AC2">
-        <v>40.15</v>
+        <v>41.08</v>
       </c>
       <c r="AD2">
-        <v>29.47</v>
+        <v>34.98</v>
       </c>
       <c r="AE2">
-        <v>74.13</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="AF2">
-        <v>38.88</v>
+        <v>9.65</v>
       </c>
       <c r="AG2">
-        <v>3966.02</v>
+        <v>3962.67</v>
       </c>
       <c r="AH2">
-        <v>3597.64</v>
+        <v>3580.12</v>
       </c>
       <c r="AI2">
         <v>3857.84</v>
@@ -972,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>46.54</v>
+        <v>46.56</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -983,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>267.6</v>
+        <v>258.8</v>
       </c>
       <c r="D3">
-        <v>1.87</v>
+        <v>-3.29</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -995,46 +1009,46 @@
         <v>237.75</v>
       </c>
       <c r="G3">
-        <v>-20.26</v>
+        <v>-22.88</v>
       </c>
       <c r="H3">
-        <v>12.56</v>
+        <v>8.85</v>
       </c>
       <c r="I3">
-        <v>1.21</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J3">
-        <v>-14.04</v>
+        <v>-16.27</v>
       </c>
       <c r="K3">
-        <v>-15.13</v>
+        <v>-17.16</v>
       </c>
       <c r="L3">
-        <v>5.79</v>
+        <v>0.47</v>
       </c>
       <c r="M3">
-        <v>25.26</v>
+        <v>23.91</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="P3">
-        <v>261.83</v>
+        <v>261.54</v>
       </c>
       <c r="Q3">
-        <v>280.73</v>
+        <v>278.83</v>
       </c>
       <c r="R3">
-        <v>301.34</v>
+        <v>300.16</v>
       </c>
       <c r="S3">
-        <v>290.23</v>
+        <v>290.02</v>
       </c>
       <c r="T3">
-        <v>-7.8</v>
+        <v>-10.77</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1049,34 +1063,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>37.02</v>
+        <v>32.23</v>
       </c>
       <c r="Z3">
-        <v>-12.51</v>
+        <v>-12.46</v>
       </c>
       <c r="AA3">
-        <v>-11.66</v>
+        <v>-11.82</v>
       </c>
       <c r="AB3">
-        <v>-0.85</v>
+        <v>-0.64</v>
       </c>
       <c r="AC3">
-        <v>29.23</v>
+        <v>42.38</v>
       </c>
       <c r="AD3">
-        <v>16.32</v>
+        <v>28.51</v>
       </c>
       <c r="AE3">
-        <v>8.220000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AF3">
-        <v>-63.54</v>
+        <v>-17.23</v>
       </c>
       <c r="AG3">
-        <v>319.57</v>
+        <v>318.07</v>
       </c>
       <c r="AH3">
-        <v>241.9</v>
+        <v>239.59</v>
       </c>
       <c r="AI3">
         <v>284.18</v>
@@ -1085,7 +1099,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>52.62</v>
+        <v>52.03</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1096,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3429.2</v>
+        <v>3613.4</v>
       </c>
       <c r="D4">
-        <v>3.63</v>
+        <v>5.37</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1108,46 +1122,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-26.16</v>
+        <v>-22.19</v>
       </c>
       <c r="H4">
-        <v>12.75</v>
+        <v>18.81</v>
       </c>
       <c r="I4">
-        <v>5.64</v>
+        <v>11.11</v>
       </c>
       <c r="J4">
-        <v>1.52</v>
+        <v>8.27</v>
       </c>
       <c r="K4">
-        <v>4.13</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>-17.69</v>
+        <v>-14.14</v>
       </c>
       <c r="M4">
-        <v>-4.96</v>
+        <v>-4.46</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="O4">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="P4">
-        <v>3287.4</v>
+        <v>3359.66</v>
       </c>
       <c r="Q4">
-        <v>3263.74</v>
+        <v>3278.8</v>
       </c>
       <c r="R4">
-        <v>3421.19</v>
+        <v>3422.16</v>
       </c>
       <c r="S4">
-        <v>3503.1</v>
+        <v>3498.38</v>
       </c>
       <c r="T4">
-        <v>-2.11</v>
+        <v>3.29</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1159,46 +1173,46 @@
         <v>41</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>58.69</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="Z4">
-        <v>-29.39</v>
+        <v>-0.68</v>
       </c>
       <c r="AA4">
-        <v>-54.74</v>
+        <v>-43.93</v>
       </c>
       <c r="AB4">
-        <v>25.34</v>
+        <v>43.24</v>
       </c>
       <c r="AC4">
         <v>100</v>
       </c>
       <c r="AD4">
-        <v>94.12</v>
+        <v>97.12</v>
       </c>
       <c r="AE4">
-        <v>103.96</v>
+        <v>113.11</v>
       </c>
       <c r="AF4">
-        <v>49.47</v>
+        <v>205.79</v>
       </c>
       <c r="AG4">
-        <v>3414.15</v>
+        <v>3495.39</v>
       </c>
       <c r="AH4">
-        <v>3113.32</v>
+        <v>3062.2</v>
       </c>
       <c r="AI4">
-        <v>3076.97</v>
+        <v>3174.67</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>27.17</v>
+        <v>33.41</v>
       </c>
     </row>
   </sheetData>
@@ -1339,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1396,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-7.52</v>
+        <v>-7.08</v>
       </c>
       <c r="D7" s="5">
-        <v>-7.08</v>
+        <v>-7.34</v>
       </c>
       <c r="E7" s="6">
-        <v>0.44</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1413,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-15.37</v>
+        <v>-14.04</v>
       </c>
       <c r="D8" s="5">
-        <v>-14.04</v>
+        <v>-16.27</v>
       </c>
       <c r="E8" s="6">
-        <v>1.33</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1430,13 +1444,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-1.63</v>
+        <v>1.52</v>
       </c>
       <c r="D9" s="5">
-        <v>1.52</v>
-      </c>
-      <c r="E9" s="6">
-        <v>3.15</v>
+        <v>8.27</v>
+      </c>
+      <c r="E9" s="7">
+        <v>6.75</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1447,13 +1461,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-3.27</v>
+        <v>-2.52</v>
       </c>
       <c r="D10" s="5">
-        <v>-2.52</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0.75</v>
+        <v>-1.61</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.91</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1464,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-0.4</v>
+        <v>1.21</v>
       </c>
       <c r="D11" s="5">
-        <v>1.21</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E11" s="6">
-        <v>1.61</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1481,13 +1495,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>2.78</v>
+        <v>5.64</v>
       </c>
       <c r="D12" s="5">
-        <v>5.64</v>
-      </c>
-      <c r="E12" s="6">
-        <v>2.86</v>
+        <v>11.11</v>
+      </c>
+      <c r="E12" s="7">
+        <v>5.47</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1498,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-1.79</v>
+        <v>-0.51</v>
       </c>
       <c r="D13" s="5">
-        <v>-0.51</v>
+        <v>-2.43</v>
       </c>
       <c r="E13" s="6">
-        <v>1.28</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1515,13 +1529,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>2.36</v>
+        <v>5.79</v>
       </c>
       <c r="D14" s="5">
-        <v>5.79</v>
+        <v>0.47</v>
       </c>
       <c r="E14" s="6">
-        <v>3.43</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1532,13 +1546,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-21.88</v>
+        <v>-17.69</v>
       </c>
       <c r="D15" s="5">
-        <v>-17.69</v>
-      </c>
-      <c r="E15" s="6">
-        <v>4.19</v>
+        <v>-14.14</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3.55</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1549,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-7.66</v>
+        <v>-4.51</v>
       </c>
       <c r="D16" s="5">
-        <v>-4.51</v>
-      </c>
-      <c r="E16" s="6">
-        <v>3.15</v>
+        <v>-3.75</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.76</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1566,13 +1580,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-19.09</v>
+        <v>-15.13</v>
       </c>
       <c r="D17" s="5">
-        <v>-15.13</v>
+        <v>-17.16</v>
       </c>
       <c r="E17" s="6">
-        <v>3.96</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1583,13 +1597,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>0.34</v>
+        <v>4.13</v>
       </c>
       <c r="D18" s="5">
-        <v>4.13</v>
+        <v>3</v>
       </c>
       <c r="E18" s="6">
-        <v>3.79</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1600,13 +1614,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-17.09</v>
+        <v>-16.01</v>
       </c>
       <c r="D19" s="5">
-        <v>-16.01</v>
+        <v>-16.76</v>
       </c>
       <c r="E19" s="6">
-        <v>1.08</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1617,13 +1631,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-21.72</v>
+        <v>-20.26</v>
       </c>
       <c r="D20" s="5">
-        <v>-20.26</v>
+        <v>-22.88</v>
       </c>
       <c r="E20" s="6">
-        <v>1.46</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1634,13 +1648,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-28.74</v>
+        <v>-26.16</v>
       </c>
       <c r="D21" s="5">
-        <v>-26.16</v>
-      </c>
-      <c r="E21" s="6">
-        <v>2.58</v>
+        <v>-22.19</v>
+      </c>
+      <c r="E21" s="7">
+        <v>3.97</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1651,13 +1665,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>3627.5</v>
+        <v>3675</v>
       </c>
       <c r="D22" s="5">
-        <v>3675</v>
+        <v>3642</v>
       </c>
       <c r="E22" s="6">
-        <v>47.5</v>
+        <v>-33</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1668,13 +1682,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>262.7</v>
+        <v>267.6</v>
       </c>
       <c r="D23" s="5">
-        <v>267.6</v>
+        <v>258.8</v>
       </c>
       <c r="E23" s="6">
-        <v>4.9</v>
+        <v>-8.800000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1685,13 +1699,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3309</v>
+        <v>3429.2</v>
       </c>
       <c r="D24" s="5">
-        <v>3429.2</v>
-      </c>
-      <c r="E24" s="6">
-        <v>120.2</v>
+        <v>3613.4</v>
+      </c>
+      <c r="E24" s="7">
+        <v>184.2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1699,101 +1713,135 @@
         <v>37</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C25" s="5">
-        <v>35.13</v>
+        <v>99</v>
       </c>
       <c r="D25" s="5">
-        <v>39.67</v>
+        <v>66</v>
       </c>
       <c r="E25" s="6">
-        <v>4.54</v>
+        <v>-33</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C26" s="5">
-        <v>31.78</v>
+        <v>66</v>
       </c>
       <c r="D26" s="5">
-        <v>37.02</v>
-      </c>
-      <c r="E26" s="6">
-        <v>5.24</v>
+        <v>99</v>
+      </c>
+      <c r="E26" s="7">
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>50.43</v>
+        <v>39.67</v>
       </c>
       <c r="D27" s="5">
-        <v>58.69</v>
+        <v>37.7</v>
       </c>
       <c r="E27" s="6">
-        <v>8.26</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C28" s="5">
-        <v>-31.15</v>
+        <v>37.02</v>
       </c>
       <c r="D28" s="5">
-        <v>38.88</v>
+        <v>32.23</v>
       </c>
       <c r="E28" s="6">
-        <v>70.03</v>
+        <v>-4.79</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C29" s="5">
-        <v>-66.83</v>
+        <v>58.69</v>
       </c>
       <c r="D29" s="5">
-        <v>-63.54</v>
-      </c>
-      <c r="E29" s="6">
-        <v>3.29</v>
+        <v>67.59999999999999</v>
+      </c>
+      <c r="E29" s="7">
+        <v>8.91</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-17.68</v>
+        <v>38.88</v>
       </c>
       <c r="D30" s="5">
+        <v>9.65</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-29.23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-63.54</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-17.23</v>
+      </c>
+      <c r="E31" s="7">
+        <v>46.31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="5">
         <v>49.47</v>
       </c>
-      <c r="E30" s="6">
-        <v>67.15000000000001</v>
+      <c r="D32" s="5">
+        <v>205.79</v>
+      </c>
+      <c r="E32" s="7">
+        <v>156.32</v>
       </c>
     </row>
   </sheetData>
@@ -1819,60 +1867,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="9">
-        <v>36.52</v>
-      </c>
-      <c r="C2" s="10">
+      <c r="B2" s="10">
+        <v>48.52</v>
+      </c>
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="9">
-        <v>45.1</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0</v>
-      </c>
-      <c r="F2" s="9">
-        <v>-6.5</v>
-      </c>
-      <c r="G2" s="9">
-        <v>-5.2</v>
-      </c>
-      <c r="H2" s="9">
+      <c r="D2" s="10">
+        <v>45.8</v>
+      </c>
+      <c r="E2" s="10">
+        <v>30</v>
+      </c>
+      <c r="F2" s="10">
+        <v>-5.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-6</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1974,25 +2022,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="12">
-        <v>0.2526</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0.1716</v>
-      </c>
-      <c r="C2" s="12">
-        <v>-0.0496</v>
+      <c r="A2" s="13">
+        <v>0.2391</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1646</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0446</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,7 +160,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>67.6 → 70.3</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>67.6</t>
+  </si>
+  <si>
+    <t>70.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -212,7 +239,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,7 +273,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -258,8 +285,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -286,13 +320,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -362,21 +402,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -385,7 +426,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -884,10 +925,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3642</v>
+        <v>3632</v>
       </c>
       <c r="D2">
-        <v>-0.9</v>
+        <v>-0.27</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -896,25 +937,25 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-16.76</v>
+        <v>-16.99</v>
       </c>
       <c r="H2">
-        <v>10.03</v>
+        <v>9.73</v>
       </c>
       <c r="I2">
-        <v>-1.61</v>
+        <v>0.19</v>
       </c>
       <c r="J2">
-        <v>-7.34</v>
+        <v>-5.68</v>
       </c>
       <c r="K2">
-        <v>-3.75</v>
+        <v>-3.8</v>
       </c>
       <c r="L2">
-        <v>-2.43</v>
+        <v>-3.08</v>
       </c>
       <c r="M2">
-        <v>16.46</v>
+        <v>16.43</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -923,19 +964,19 @@
         <v>57</v>
       </c>
       <c r="P2">
-        <v>3654.58</v>
+        <v>3655.96</v>
       </c>
       <c r="Q2">
-        <v>3771.39</v>
+        <v>3762.61</v>
       </c>
       <c r="R2">
-        <v>3921.86</v>
+        <v>3914.7</v>
       </c>
       <c r="S2">
-        <v>3934.58</v>
+        <v>3932.7</v>
       </c>
       <c r="T2">
-        <v>-7.44</v>
+        <v>-7.65</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,34 +991,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>37.7</v>
+        <v>37.1</v>
       </c>
       <c r="Z2">
-        <v>-77.12</v>
+        <v>-77.8</v>
       </c>
       <c r="AA2">
-        <v>-68.64</v>
+        <v>-70.47</v>
       </c>
       <c r="AB2">
-        <v>-8.48</v>
+        <v>-7.33</v>
       </c>
       <c r="AC2">
-        <v>41.08</v>
+        <v>49.03</v>
       </c>
       <c r="AD2">
-        <v>34.98</v>
+        <v>43.42</v>
       </c>
       <c r="AE2">
-        <v>73.76000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="AF2">
-        <v>9.65</v>
+        <v>43.81</v>
       </c>
       <c r="AG2">
-        <v>3962.67</v>
+        <v>3962.8</v>
       </c>
       <c r="AH2">
-        <v>3580.12</v>
+        <v>3562.42</v>
       </c>
       <c r="AI2">
         <v>3857.84</v>
@@ -986,7 +1027,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>46.56</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +1038,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>258.8</v>
+        <v>262</v>
       </c>
       <c r="D3">
-        <v>-3.29</v>
+        <v>1.24</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1009,46 +1050,46 @@
         <v>237.75</v>
       </c>
       <c r="G3">
-        <v>-22.88</v>
+        <v>-21.93</v>
       </c>
       <c r="H3">
-        <v>8.85</v>
+        <v>10.2</v>
       </c>
       <c r="I3">
-        <v>-0.5600000000000001</v>
+        <v>1.79</v>
       </c>
       <c r="J3">
-        <v>-16.27</v>
+        <v>-11.73</v>
       </c>
       <c r="K3">
-        <v>-17.16</v>
+        <v>-15.36</v>
       </c>
       <c r="L3">
-        <v>0.47</v>
+        <v>3.38</v>
       </c>
       <c r="M3">
-        <v>23.91</v>
+        <v>24.63</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P3">
-        <v>261.54</v>
+        <v>262.46</v>
       </c>
       <c r="Q3">
-        <v>278.83</v>
+        <v>277.16</v>
       </c>
       <c r="R3">
-        <v>300.16</v>
+        <v>299.04</v>
       </c>
       <c r="S3">
-        <v>290.02</v>
+        <v>289.84</v>
       </c>
       <c r="T3">
-        <v>-10.77</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,34 +1104,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>32.23</v>
+        <v>35.5</v>
       </c>
       <c r="Z3">
-        <v>-12.46</v>
+        <v>-12.03</v>
       </c>
       <c r="AA3">
-        <v>-11.82</v>
+        <v>-11.86</v>
       </c>
       <c r="AB3">
-        <v>-0.64</v>
+        <v>-0.17</v>
       </c>
       <c r="AC3">
-        <v>42.38</v>
+        <v>63.06</v>
       </c>
       <c r="AD3">
-        <v>28.51</v>
+        <v>44.89</v>
       </c>
       <c r="AE3">
-        <v>8.359999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="AF3">
-        <v>-17.23</v>
+        <v>50.73</v>
       </c>
       <c r="AG3">
-        <v>318.07</v>
+        <v>316.26</v>
       </c>
       <c r="AH3">
-        <v>239.59</v>
+        <v>238.05</v>
       </c>
       <c r="AI3">
         <v>284.18</v>
@@ -1099,7 +1140,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>52.03</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1151,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3613.4</v>
+        <v>3686.8</v>
       </c>
       <c r="D4">
-        <v>5.37</v>
+        <v>2.03</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1122,46 +1163,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-22.19</v>
+        <v>-20.61</v>
       </c>
       <c r="H4">
-        <v>18.81</v>
+        <v>21.22</v>
       </c>
       <c r="I4">
-        <v>11.11</v>
+        <v>16.06</v>
       </c>
       <c r="J4">
-        <v>8.27</v>
+        <v>11.31</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>5.94</v>
       </c>
       <c r="L4">
-        <v>-14.14</v>
+        <v>-13.26</v>
       </c>
       <c r="M4">
-        <v>-4.46</v>
+        <v>-4.22</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="P4">
-        <v>3359.66</v>
+        <v>3461.7</v>
       </c>
       <c r="Q4">
-        <v>3278.8</v>
+        <v>3295.56</v>
       </c>
       <c r="R4">
-        <v>3422.16</v>
+        <v>3425.86</v>
       </c>
       <c r="S4">
-        <v>3498.38</v>
+        <v>3494.48</v>
       </c>
       <c r="T4">
-        <v>3.29</v>
+        <v>5.5</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,43 +1217,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>67.59999999999999</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="Z4">
-        <v>-0.68</v>
+        <v>27.67</v>
       </c>
       <c r="AA4">
-        <v>-43.93</v>
+        <v>-29.61</v>
       </c>
       <c r="AB4">
-        <v>43.24</v>
+        <v>57.28</v>
       </c>
       <c r="AC4">
         <v>100</v>
       </c>
       <c r="AD4">
-        <v>97.12</v>
+        <v>100</v>
       </c>
       <c r="AE4">
-        <v>113.11</v>
+        <v>118.04</v>
       </c>
       <c r="AF4">
-        <v>205.79</v>
+        <v>170.98</v>
       </c>
       <c r="AG4">
-        <v>3495.39</v>
+        <v>3577.81</v>
       </c>
       <c r="AH4">
-        <v>3062.2</v>
+        <v>3013.31</v>
       </c>
       <c r="AI4">
-        <v>3174.67</v>
+        <v>3299.77</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>33.41</v>
+        <v>39.61</v>
       </c>
     </row>
   </sheetData>
@@ -1353,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1373,12 +1414,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1386,462 +1462,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-7.08</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-7.34</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.26</v>
+      <c r="D7" s="6">
+        <v>-5.68</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.66</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-14.04</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-16.27</v>
       </c>
-      <c r="E8" s="6">
-        <v>-2.23</v>
+      <c r="D8" s="6">
+        <v>-11.73</v>
+      </c>
+      <c r="E8" s="7">
+        <v>4.54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>1.52</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>8.27</v>
       </c>
+      <c r="D9" s="6">
+        <v>11.31</v>
+      </c>
       <c r="E9" s="7">
-        <v>6.75</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-2.52</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-1.61</v>
       </c>
+      <c r="D10" s="6">
+        <v>0.19</v>
+      </c>
       <c r="E10" s="7">
-        <v>0.91</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>1.21</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="E11" s="6">
-        <v>-1.77</v>
+      <c r="D11" s="6">
+        <v>1.79</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.35</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>5.64</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>11.11</v>
       </c>
+      <c r="D12" s="6">
+        <v>16.06</v>
+      </c>
       <c r="E12" s="7">
-        <v>5.47</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-0.51</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-2.43</v>
       </c>
-      <c r="E13" s="6">
-        <v>-1.92</v>
+      <c r="D13" s="6">
+        <v>-3.08</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>5.79</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>0.47</v>
       </c>
-      <c r="E14" s="6">
-        <v>-5.32</v>
+      <c r="D14" s="6">
+        <v>3.38</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2.91</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-17.69</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-14.14</v>
       </c>
+      <c r="D15" s="6">
+        <v>-13.26</v>
+      </c>
       <c r="E15" s="7">
-        <v>3.55</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-4.51</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-3.75</v>
       </c>
-      <c r="E16" s="7">
-        <v>0.76</v>
+      <c r="D16" s="6">
+        <v>-3.8</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-15.13</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-17.16</v>
       </c>
-      <c r="E17" s="6">
-        <v>-2.03</v>
+      <c r="D17" s="6">
+        <v>-15.36</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.8</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>4.13</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>3</v>
       </c>
-      <c r="E18" s="6">
-        <v>-1.13</v>
+      <c r="D18" s="6">
+        <v>5.94</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.94</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-16.01</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-16.76</v>
       </c>
-      <c r="E19" s="6">
-        <v>-0.75</v>
+      <c r="D19" s="6">
+        <v>-16.99</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-20.26</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-22.88</v>
       </c>
-      <c r="E20" s="6">
-        <v>-2.62</v>
+      <c r="D20" s="6">
+        <v>-21.93</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.95</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-26.16</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-22.19</v>
       </c>
+      <c r="D21" s="6">
+        <v>-20.61</v>
+      </c>
       <c r="E21" s="7">
-        <v>3.97</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>3675</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>3642</v>
       </c>
-      <c r="E22" s="6">
-        <v>-33</v>
+      <c r="D22" s="6">
+        <v>3632</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-10</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>267.6</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>258.8</v>
       </c>
-      <c r="E23" s="6">
-        <v>-8.800000000000001</v>
+      <c r="D23" s="6">
+        <v>262</v>
+      </c>
+      <c r="E23" s="7">
+        <v>3.2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>3429.2</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>3613.4</v>
       </c>
+      <c r="D24" s="6">
+        <v>3686.8</v>
+      </c>
       <c r="E24" s="7">
-        <v>184.2</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="5">
-        <v>99</v>
-      </c>
-      <c r="D25" s="5">
-        <v>66</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-33</v>
+      <c r="B25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="6">
+        <v>37.7</v>
+      </c>
+      <c r="D25" s="6">
+        <v>37.1</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="6">
+        <v>32.23</v>
+      </c>
+      <c r="D26" s="6">
+        <v>35.5</v>
+      </c>
+      <c r="E26" s="7">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="5">
-        <v>66</v>
-      </c>
-      <c r="D26" s="5">
-        <v>99</v>
-      </c>
-      <c r="E26" s="7">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="D27" s="6">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>39.67</v>
-      </c>
-      <c r="D27" s="5">
-        <v>37.7</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-1.97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6">
+        <v>9.65</v>
+      </c>
+      <c r="D28" s="6">
+        <v>43.81</v>
+      </c>
+      <c r="E28" s="7">
+        <v>34.16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="5">
-        <v>37.02</v>
-      </c>
-      <c r="D28" s="5">
-        <v>32.23</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-4.79</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-17.23</v>
+      </c>
+      <c r="D29" s="6">
+        <v>50.73</v>
+      </c>
+      <c r="E29" s="7">
+        <v>67.95999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="5">
-        <v>58.69</v>
-      </c>
-      <c r="D29" s="5">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="E29" s="7">
-        <v>8.91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>38.88</v>
-      </c>
-      <c r="D30" s="5">
-        <v>9.65</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-29.23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-63.54</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-17.23</v>
-      </c>
-      <c r="E31" s="7">
-        <v>46.31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="5">
-        <v>49.47</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C30" s="6">
         <v>205.79</v>
       </c>
-      <c r="E32" s="7">
-        <v>156.32</v>
+      <c r="D30" s="6">
+        <v>170.98</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-34.81</v>
       </c>
     </row>
   </sheetData>
@@ -1867,60 +1909,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>48.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>45.8</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>47.6</v>
+      </c>
+      <c r="E2" s="11">
         <v>30</v>
       </c>
-      <c r="F2" s="10">
-        <v>-5.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-6</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-4.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2022,25 +2064,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.2391</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1646</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0446</v>
+      <c r="A2" s="14">
+        <v>0.2463</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1643</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.04219999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,34 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>67.6 → 70.3</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>67.6</t>
-  </si>
-  <si>
-    <t>70.3</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -239,7 +212,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -273,13 +246,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -293,7 +259,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -315,12 +281,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -402,22 +362,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -426,7 +385,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -925,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3632</v>
+        <v>3627.1</v>
       </c>
       <c r="D2">
-        <v>-0.27</v>
+        <v>-0.13</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -937,46 +896,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-16.99</v>
+        <v>-17.1</v>
       </c>
       <c r="H2">
-        <v>9.73</v>
+        <v>9.58</v>
       </c>
       <c r="I2">
-        <v>0.19</v>
+        <v>-2.06</v>
       </c>
       <c r="J2">
-        <v>-5.68</v>
+        <v>-4.74</v>
       </c>
       <c r="K2">
-        <v>-3.8</v>
+        <v>-4.91</v>
       </c>
       <c r="L2">
-        <v>-3.08</v>
+        <v>-2.84</v>
       </c>
       <c r="M2">
-        <v>16.43</v>
+        <v>16.39</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="P2">
-        <v>3655.96</v>
+        <v>3640.72</v>
       </c>
       <c r="Q2">
-        <v>3762.61</v>
+        <v>3752.15</v>
       </c>
       <c r="R2">
-        <v>3914.7</v>
+        <v>3906.11</v>
       </c>
       <c r="S2">
-        <v>3932.7</v>
+        <v>3930.84</v>
       </c>
       <c r="T2">
-        <v>-7.65</v>
+        <v>-7.73</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -991,34 +950,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>37.1</v>
+        <v>36.79</v>
       </c>
       <c r="Z2">
-        <v>-77.8</v>
+        <v>-77.83</v>
       </c>
       <c r="AA2">
-        <v>-70.47</v>
+        <v>-71.95</v>
       </c>
       <c r="AB2">
-        <v>-7.33</v>
+        <v>-5.89</v>
       </c>
       <c r="AC2">
-        <v>49.03</v>
+        <v>52.56</v>
       </c>
       <c r="AD2">
-        <v>43.42</v>
+        <v>47.56</v>
       </c>
       <c r="AE2">
-        <v>73.94</v>
+        <v>73.08</v>
       </c>
       <c r="AF2">
-        <v>43.81</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AG2">
-        <v>3962.8</v>
+        <v>3957.92</v>
       </c>
       <c r="AH2">
-        <v>3562.42</v>
+        <v>3546.39</v>
       </c>
       <c r="AI2">
         <v>3857.84</v>
@@ -1027,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>45.71</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1038,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>262</v>
+        <v>253.85</v>
       </c>
       <c r="D3">
-        <v>1.24</v>
+        <v>-3.11</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1050,46 +1009,46 @@
         <v>237.75</v>
       </c>
       <c r="G3">
-        <v>-21.93</v>
+        <v>-24.36</v>
       </c>
       <c r="H3">
-        <v>10.2</v>
+        <v>6.77</v>
       </c>
       <c r="I3">
-        <v>1.79</v>
+        <v>-2.81</v>
       </c>
       <c r="J3">
-        <v>-11.73</v>
+        <v>-14.09</v>
       </c>
       <c r="K3">
-        <v>-15.36</v>
+        <v>-18.13</v>
       </c>
       <c r="L3">
-        <v>3.38</v>
+        <v>-3.79</v>
       </c>
       <c r="M3">
-        <v>24.63</v>
+        <v>23.83</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="P3">
-        <v>262.46</v>
+        <v>260.99</v>
       </c>
       <c r="Q3">
-        <v>277.16</v>
+        <v>274.73</v>
       </c>
       <c r="R3">
-        <v>299.04</v>
+        <v>297.75</v>
       </c>
       <c r="S3">
-        <v>289.84</v>
+        <v>289.63</v>
       </c>
       <c r="T3">
-        <v>-9.609999999999999</v>
+        <v>-12.35</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1104,43 +1063,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>35.5</v>
+        <v>31.36</v>
       </c>
       <c r="Z3">
-        <v>-12.03</v>
+        <v>-12.2</v>
       </c>
       <c r="AA3">
-        <v>-11.86</v>
+        <v>-11.93</v>
       </c>
       <c r="AB3">
-        <v>-0.17</v>
+        <v>-0.27</v>
       </c>
       <c r="AC3">
-        <v>63.06</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="AD3">
-        <v>44.89</v>
+        <v>56.51</v>
       </c>
       <c r="AE3">
-        <v>8.31</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AF3">
-        <v>50.73</v>
+        <v>263.31</v>
       </c>
       <c r="AG3">
-        <v>316.26</v>
+        <v>313.28</v>
       </c>
       <c r="AH3">
-        <v>238.05</v>
+        <v>236.19</v>
       </c>
       <c r="AI3">
-        <v>284.18</v>
+        <v>282.15</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>51.48</v>
+        <v>53.72</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1151,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3686.8</v>
+        <v>3714.6</v>
       </c>
       <c r="D4">
-        <v>2.03</v>
+        <v>0.75</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1163,46 +1122,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-20.61</v>
+        <v>-20.01</v>
       </c>
       <c r="H4">
-        <v>21.22</v>
+        <v>22.14</v>
       </c>
       <c r="I4">
-        <v>16.06</v>
+        <v>13.59</v>
       </c>
       <c r="J4">
-        <v>11.31</v>
+        <v>10.83</v>
       </c>
       <c r="K4">
-        <v>5.94</v>
+        <v>8.76</v>
       </c>
       <c r="L4">
-        <v>-13.26</v>
+        <v>-10.04</v>
       </c>
       <c r="M4">
-        <v>-4.22</v>
+        <v>-4.07</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P4">
-        <v>3461.7</v>
+        <v>3550.6</v>
       </c>
       <c r="Q4">
-        <v>3295.56</v>
+        <v>3315.08</v>
       </c>
       <c r="R4">
-        <v>3425.86</v>
+        <v>3428.65</v>
       </c>
       <c r="S4">
-        <v>3494.48</v>
+        <v>3490.69</v>
       </c>
       <c r="T4">
-        <v>5.5</v>
+        <v>6.41</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1217,16 +1176,16 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>70.34999999999999</v>
+        <v>71.34</v>
       </c>
       <c r="Z4">
-        <v>27.67</v>
+        <v>51.79</v>
       </c>
       <c r="AA4">
-        <v>-29.61</v>
+        <v>-13.33</v>
       </c>
       <c r="AB4">
-        <v>57.28</v>
+        <v>65.12</v>
       </c>
       <c r="AC4">
         <v>100</v>
@@ -1235,25 +1194,25 @@
         <v>100</v>
       </c>
       <c r="AE4">
-        <v>118.04</v>
+        <v>119.25</v>
       </c>
       <c r="AF4">
-        <v>170.98</v>
+        <v>20.03</v>
       </c>
       <c r="AG4">
-        <v>3577.81</v>
+        <v>3653.98</v>
       </c>
       <c r="AH4">
-        <v>3013.31</v>
+        <v>2976.17</v>
       </c>
       <c r="AI4">
-        <v>3299.77</v>
+        <v>3359.74</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>39.61</v>
+        <v>45.2</v>
       </c>
     </row>
   </sheetData>
@@ -1414,47 +1373,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1462,428 +1386,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-7.34</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-5.68</v>
       </c>
-      <c r="E7" s="7">
-        <v>1.66</v>
+      <c r="D7" s="5">
+        <v>-4.74</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-16.27</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-11.73</v>
       </c>
+      <c r="D8" s="5">
+        <v>-14.09</v>
+      </c>
       <c r="E8" s="7">
-        <v>4.54</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>8.27</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>11.31</v>
       </c>
+      <c r="D9" s="5">
+        <v>10.83</v>
+      </c>
       <c r="E9" s="7">
-        <v>3.04</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-1.61</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>0.19</v>
       </c>
+      <c r="D10" s="5">
+        <v>-2.06</v>
+      </c>
       <c r="E10" s="7">
-        <v>1.8</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>1.79</v>
       </c>
+      <c r="D11" s="5">
+        <v>-2.81</v>
+      </c>
       <c r="E11" s="7">
-        <v>2.35</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>11.11</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>16.06</v>
       </c>
+      <c r="D12" s="5">
+        <v>13.59</v>
+      </c>
       <c r="E12" s="7">
-        <v>4.95</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
+        <v>-3.08</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-2.84</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>3.38</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-3.79</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-7.17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-13.26</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-10.04</v>
+      </c>
+      <c r="E15" s="6">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-3.8</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-4.91</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-15.36</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-18.13</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>5.94</v>
+      </c>
+      <c r="D18" s="5">
+        <v>8.76</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-16.99</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-17.1</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-21.93</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-24.36</v>
+      </c>
+      <c r="E20" s="7">
         <v>-2.43</v>
       </c>
-      <c r="D13" s="6">
-        <v>-3.08</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-20.61</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-20.01</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>3632</v>
+      </c>
+      <c r="D22" s="5">
+        <v>3627.1</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-4.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.47</v>
-      </c>
-      <c r="D14" s="6">
-        <v>3.38</v>
-      </c>
-      <c r="E14" s="7">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>262</v>
+      </c>
+      <c r="D23" s="5">
+        <v>253.85</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-8.15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-14.14</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-13.26</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>3686.8</v>
+      </c>
+      <c r="D24" s="5">
+        <v>3714.6</v>
+      </c>
+      <c r="E24" s="6">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-3.75</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-3.8</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>37.1</v>
+      </c>
+      <c r="D25" s="5">
+        <v>36.79</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-17.16</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-15.36</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>35.5</v>
+      </c>
+      <c r="D26" s="5">
+        <v>31.36</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-4.14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>3</v>
-      </c>
-      <c r="D18" s="6">
-        <v>5.94</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="D27" s="5">
+        <v>71.34</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-16.76</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-16.99</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>43.81</v>
+      </c>
+      <c r="D28" s="5">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-35.09</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-22.88</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-21.93</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>50.73</v>
+      </c>
+      <c r="D29" s="5">
+        <v>263.31</v>
+      </c>
+      <c r="E29" s="6">
+        <v>212.58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-22.19</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-20.61</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6">
-        <v>3642</v>
-      </c>
-      <c r="D22" s="6">
-        <v>3632</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>258.8</v>
-      </c>
-      <c r="D23" s="6">
-        <v>262</v>
-      </c>
-      <c r="E23" s="7">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>3613.4</v>
-      </c>
-      <c r="D24" s="6">
-        <v>3686.8</v>
-      </c>
-      <c r="E24" s="7">
-        <v>73.40000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="6">
-        <v>37.7</v>
-      </c>
-      <c r="D25" s="6">
-        <v>37.1</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>32.23</v>
-      </c>
-      <c r="D26" s="6">
-        <v>35.5</v>
-      </c>
-      <c r="E26" s="7">
-        <v>3.27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="D27" s="6">
-        <v>70.34999999999999</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>9.65</v>
-      </c>
-      <c r="D28" s="6">
-        <v>43.81</v>
-      </c>
-      <c r="E28" s="7">
-        <v>34.16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-17.23</v>
-      </c>
-      <c r="D29" s="6">
-        <v>50.73</v>
-      </c>
-      <c r="E29" s="7">
-        <v>67.95999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>205.79</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>170.98</v>
       </c>
-      <c r="E30" s="8">
-        <v>-34.81</v>
+      <c r="D30" s="5">
+        <v>20.03</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-150.95</v>
       </c>
     </row>
   </sheetData>
@@ -1909,60 +1833,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>68</v>
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>48.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>47.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>46.5</v>
+      </c>
+      <c r="E2" s="10">
         <v>30</v>
       </c>
-      <c r="F2" s="11">
-        <v>-2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-4.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-2.7</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-4.8</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2064,25 +1988,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.2463</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1643</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.04219999999999999</v>
+      <c r="A2" s="13">
+        <v>0.2383</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1639</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0407</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,7 +160,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>71.3 → 62.9</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>71.3</t>
+  </si>
+  <si>
+    <t>62.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -212,7 +239,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,6 +273,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -259,7 +293,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -281,6 +315,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -362,21 +402,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -385,7 +426,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -884,10 +925,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3627.1</v>
+        <v>3661.9</v>
       </c>
       <c r="D2">
-        <v>-0.13</v>
+        <v>0.96</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -896,46 +937,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-17.1</v>
+        <v>-16.31</v>
       </c>
       <c r="H2">
-        <v>9.58</v>
+        <v>10.63</v>
       </c>
       <c r="I2">
-        <v>-2.06</v>
+        <v>0.95</v>
       </c>
       <c r="J2">
-        <v>-4.74</v>
+        <v>-4.54</v>
       </c>
       <c r="K2">
-        <v>-4.91</v>
+        <v>-4.61</v>
       </c>
       <c r="L2">
-        <v>-2.84</v>
+        <v>-1.25</v>
       </c>
       <c r="M2">
-        <v>16.39</v>
+        <v>15.86</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P2">
-        <v>3640.72</v>
+        <v>3647.6</v>
       </c>
       <c r="Q2">
-        <v>3752.15</v>
+        <v>3741</v>
       </c>
       <c r="R2">
-        <v>3906.11</v>
+        <v>3898.11</v>
       </c>
       <c r="S2">
-        <v>3930.84</v>
+        <v>3929.09</v>
       </c>
       <c r="T2">
-        <v>-7.73</v>
+        <v>-6.8</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,34 +991,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>36.79</v>
+        <v>40.59</v>
       </c>
       <c r="Z2">
-        <v>-77.83</v>
+        <v>-74.2</v>
       </c>
       <c r="AA2">
-        <v>-71.95</v>
+        <v>-72.40000000000001</v>
       </c>
       <c r="AB2">
-        <v>-5.89</v>
+        <v>-1.8</v>
       </c>
       <c r="AC2">
-        <v>52.56</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="AD2">
-        <v>47.56</v>
+        <v>56.79</v>
       </c>
       <c r="AE2">
-        <v>73.08</v>
+        <v>72.19</v>
       </c>
       <c r="AF2">
-        <v>8.720000000000001</v>
+        <v>35.89</v>
       </c>
       <c r="AG2">
-        <v>3957.92</v>
+        <v>3940.54</v>
       </c>
       <c r="AH2">
-        <v>3546.39</v>
+        <v>3541.46</v>
       </c>
       <c r="AI2">
         <v>3857.84</v>
@@ -986,7 +1027,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>44.97</v>
+        <v>42.14</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +1038,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>253.85</v>
+        <v>253</v>
       </c>
       <c r="D3">
-        <v>-3.11</v>
+        <v>-0.33</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1009,46 +1050,46 @@
         <v>237.75</v>
       </c>
       <c r="G3">
-        <v>-24.36</v>
+        <v>-24.61</v>
       </c>
       <c r="H3">
-        <v>6.77</v>
+        <v>6.41</v>
       </c>
       <c r="I3">
-        <v>-2.81</v>
+        <v>-3.69</v>
       </c>
       <c r="J3">
-        <v>-14.09</v>
+        <v>-16.31</v>
       </c>
       <c r="K3">
-        <v>-18.13</v>
+        <v>-17.28</v>
       </c>
       <c r="L3">
-        <v>-3.79</v>
+        <v>-2.79</v>
       </c>
       <c r="M3">
-        <v>23.83</v>
+        <v>23.91</v>
       </c>
       <c r="N3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O3">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="P3">
-        <v>260.99</v>
+        <v>259.05</v>
       </c>
       <c r="Q3">
-        <v>274.73</v>
+        <v>271.74</v>
       </c>
       <c r="R3">
-        <v>297.75</v>
+        <v>296.48</v>
       </c>
       <c r="S3">
-        <v>289.63</v>
+        <v>289.38</v>
       </c>
       <c r="T3">
-        <v>-12.35</v>
+        <v>-12.57</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,43 +1104,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>31.36</v>
+        <v>30.95</v>
       </c>
       <c r="Z3">
-        <v>-12.2</v>
+        <v>-12.26</v>
       </c>
       <c r="AA3">
-        <v>-11.93</v>
+        <v>-12</v>
       </c>
       <c r="AB3">
         <v>-0.27</v>
       </c>
       <c r="AC3">
-        <v>64.06999999999999</v>
+        <v>60.22</v>
       </c>
       <c r="AD3">
-        <v>56.51</v>
+        <v>62.45</v>
       </c>
       <c r="AE3">
-        <v>8.970000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="AF3">
-        <v>263.31</v>
+        <v>-34.19</v>
       </c>
       <c r="AG3">
-        <v>313.28</v>
+        <v>306.99</v>
       </c>
       <c r="AH3">
-        <v>236.19</v>
+        <v>236.5</v>
       </c>
       <c r="AI3">
-        <v>282.15</v>
+        <v>278.16</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>53.72</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1151,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3714.6</v>
+        <v>3611.3</v>
       </c>
       <c r="D4">
-        <v>0.75</v>
+        <v>-2.78</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1122,25 +1163,25 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-20.01</v>
+        <v>-22.23</v>
       </c>
       <c r="H4">
-        <v>22.14</v>
+        <v>18.74</v>
       </c>
       <c r="I4">
-        <v>13.59</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="J4">
-        <v>10.83</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="K4">
-        <v>8.76</v>
+        <v>7.82</v>
       </c>
       <c r="L4">
-        <v>-10.04</v>
+        <v>-11.68</v>
       </c>
       <c r="M4">
-        <v>-4.07</v>
+        <v>-5.67</v>
       </c>
       <c r="N4">
         <v>99</v>
@@ -1149,19 +1190,19 @@
         <v>66</v>
       </c>
       <c r="P4">
-        <v>3550.6</v>
+        <v>3611.06</v>
       </c>
       <c r="Q4">
-        <v>3315.08</v>
+        <v>3328.27</v>
       </c>
       <c r="R4">
-        <v>3428.65</v>
+        <v>3429.76</v>
       </c>
       <c r="S4">
-        <v>3490.69</v>
+        <v>3486.8</v>
       </c>
       <c r="T4">
-        <v>6.41</v>
+        <v>3.57</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,34 +1217,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>71.34</v>
+        <v>62.93</v>
       </c>
       <c r="Z4">
-        <v>51.79</v>
+        <v>61.86</v>
       </c>
       <c r="AA4">
-        <v>-13.33</v>
+        <v>1.71</v>
       </c>
       <c r="AB4">
-        <v>65.12</v>
+        <v>60.15</v>
       </c>
       <c r="AC4">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="AD4">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AE4">
-        <v>119.25</v>
+        <v>121.85</v>
       </c>
       <c r="AF4">
-        <v>20.03</v>
+        <v>40.63</v>
       </c>
       <c r="AG4">
-        <v>3653.98</v>
+        <v>3692.1</v>
       </c>
       <c r="AH4">
-        <v>2976.17</v>
+        <v>2964.43</v>
       </c>
       <c r="AI4">
         <v>3359.74</v>
@@ -1212,12 +1253,72 @@
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>45.2</v>
+        <v>46.55</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AK4"/>
   <conditionalFormatting sqref="AF2:AF4">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D4">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I4">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J4">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K4">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L4">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -1229,8 +1330,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="N2:N4">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="greaterThanOrEqual">
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -1241,72 +1348,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J4">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K4">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L4">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N4">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="18" operator="greaterThanOrEqual">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="19" operator="lessThanOrEqual">
-      <formula>20</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="T2:T4">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
       <formula>0</formula>
@@ -1316,26 +1357,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U4">
-    <cfRule type="containsText" dxfId="1" priority="12" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="13" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V4">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W4">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1353,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1373,12 +1414,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1386,428 +1462,445 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-5.68</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-4.74</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.9399999999999999</v>
+      <c r="D7" s="6">
+        <v>-4.54</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-11.73</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-14.09</v>
       </c>
-      <c r="E8" s="7">
-        <v>-2.36</v>
+      <c r="D8" s="6">
+        <v>-16.31</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-2.22</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>11.31</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>10.83</v>
       </c>
-      <c r="E9" s="7">
-        <v>-0.48</v>
+      <c r="D9" s="6">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-2.2</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>0.19</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-2.06</v>
       </c>
+      <c r="D10" s="6">
+        <v>0.95</v>
+      </c>
       <c r="E10" s="7">
-        <v>-2.25</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-2.81</v>
       </c>
-      <c r="E11" s="7">
-        <v>-4.6</v>
+      <c r="D11" s="6">
+        <v>-3.69</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>16.06</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>13.59</v>
       </c>
-      <c r="E12" s="7">
-        <v>-2.47</v>
+      <c r="D12" s="6">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-4.45</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-3.08</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-2.84</v>
       </c>
-      <c r="E13" s="6">
-        <v>0.24</v>
+      <c r="D13" s="6">
+        <v>-1.25</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.59</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>3.38</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-3.79</v>
       </c>
+      <c r="D14" s="6">
+        <v>-2.79</v>
+      </c>
       <c r="E14" s="7">
-        <v>-7.17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-13.26</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-10.04</v>
       </c>
-      <c r="E15" s="6">
-        <v>3.22</v>
+      <c r="D15" s="6">
+        <v>-11.68</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-3.8</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-4.91</v>
       </c>
+      <c r="D16" s="6">
+        <v>-4.61</v>
+      </c>
       <c r="E16" s="7">
-        <v>-1.11</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-15.36</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-18.13</v>
       </c>
+      <c r="D17" s="6">
+        <v>-17.28</v>
+      </c>
       <c r="E17" s="7">
-        <v>-2.77</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>5.94</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>8.76</v>
       </c>
-      <c r="E18" s="6">
-        <v>2.82</v>
+      <c r="D18" s="6">
+        <v>7.82</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-16.99</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-17.1</v>
       </c>
+      <c r="D19" s="6">
+        <v>-16.31</v>
+      </c>
       <c r="E19" s="7">
-        <v>-0.11</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-21.93</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-24.36</v>
       </c>
-      <c r="E20" s="7">
-        <v>-2.43</v>
+      <c r="D20" s="6">
+        <v>-24.61</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-20.61</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-20.01</v>
       </c>
-      <c r="E21" s="6">
-        <v>0.6</v>
+      <c r="D21" s="6">
+        <v>-22.23</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-2.22</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>3632</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>3627.1</v>
       </c>
+      <c r="D22" s="6">
+        <v>3661.9</v>
+      </c>
       <c r="E22" s="7">
-        <v>-4.9</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>262</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>253.85</v>
       </c>
-      <c r="E23" s="7">
-        <v>-8.15</v>
+      <c r="D23" s="6">
+        <v>253</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>3686.8</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>3714.6</v>
       </c>
-      <c r="E24" s="6">
-        <v>27.8</v>
+      <c r="D24" s="6">
+        <v>3611.3</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-103.3</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="6">
+        <v>34</v>
+      </c>
+      <c r="D25" s="6">
+        <v>33</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="5">
-        <v>37.1</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C26" s="6">
         <v>36.79</v>
       </c>
-      <c r="E25" s="7">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D26" s="6">
+        <v>40.59</v>
+      </c>
+      <c r="E26" s="7">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="5">
-        <v>35.5</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C27" s="6">
         <v>31.36</v>
       </c>
-      <c r="E26" s="7">
-        <v>-4.14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D27" s="6">
+        <v>30.95</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="5">
-        <v>70.34999999999999</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C28" s="6">
         <v>71.34</v>
       </c>
-      <c r="E27" s="6">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D28" s="6">
+        <v>62.93</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-8.41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>43.81</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C29" s="6">
         <v>8.720000000000001</v>
       </c>
-      <c r="E28" s="7">
-        <v>-35.09</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D29" s="6">
+        <v>35.89</v>
+      </c>
+      <c r="E29" s="7">
+        <v>27.17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5">
-        <v>50.73</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C30" s="6">
         <v>263.31</v>
       </c>
-      <c r="E29" s="6">
-        <v>212.58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="D30" s="6">
+        <v>-34.19</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-297.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>170.98</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C31" s="6">
         <v>20.03</v>
       </c>
-      <c r="E30" s="7">
-        <v>-150.95</v>
+      <c r="D31" s="6">
+        <v>40.63</v>
+      </c>
+      <c r="E31" s="7">
+        <v>20.6</v>
       </c>
     </row>
   </sheetData>
@@ -1833,60 +1926,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
-        <v>48.52</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="11">
+        <v>49.72</v>
+      </c>
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>46.5</v>
-      </c>
-      <c r="E2" s="10">
-        <v>30</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-2.7</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-4.8</v>
-      </c>
-      <c r="H2" s="10">
-        <v>66.3</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="D2" s="11">
+        <v>44.8</v>
+      </c>
+      <c r="E2" s="11">
+        <v>33.3</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-4.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-4.7</v>
+      </c>
+      <c r="H2" s="11">
+        <v>66</v>
+      </c>
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1988,25 +2081,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.2383</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1639</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0407</v>
+      <c r="A2" s="14">
+        <v>0.2391</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1586</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0567</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,19 +175,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>71.3 → 62.9</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>71.3</t>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>62.9 → 74.8</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
   </si>
   <si>
     <t>62.9</t>
+  </si>
+  <si>
+    <t>74.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,7 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -281,13 +288,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -320,19 +320,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -925,10 +925,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3661.9</v>
+        <v>3636</v>
       </c>
       <c r="D2">
-        <v>0.96</v>
+        <v>-0.71</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -937,46 +937,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-16.31</v>
+        <v>-16.9</v>
       </c>
       <c r="H2">
-        <v>10.63</v>
+        <v>9.85</v>
       </c>
       <c r="I2">
-        <v>0.95</v>
+        <v>-1.06</v>
       </c>
       <c r="J2">
-        <v>-4.54</v>
+        <v>-6.41</v>
       </c>
       <c r="K2">
-        <v>-4.61</v>
+        <v>-5.47</v>
       </c>
       <c r="L2">
-        <v>-1.25</v>
+        <v>-4.11</v>
       </c>
       <c r="M2">
-        <v>15.86</v>
+        <v>16.2</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P2">
-        <v>3647.6</v>
+        <v>3639.8</v>
       </c>
       <c r="Q2">
-        <v>3741</v>
+        <v>3727.56</v>
       </c>
       <c r="R2">
-        <v>3898.11</v>
+        <v>3889.71</v>
       </c>
       <c r="S2">
-        <v>3929.09</v>
+        <v>3927.05</v>
       </c>
       <c r="T2">
-        <v>-6.8</v>
+        <v>-7.41</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -991,34 +991,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>40.59</v>
+        <v>38.72</v>
       </c>
       <c r="Z2">
-        <v>-74.2</v>
+        <v>-72.56999999999999</v>
       </c>
       <c r="AA2">
-        <v>-72.40000000000001</v>
+        <v>-72.43000000000001</v>
       </c>
       <c r="AB2">
-        <v>-1.8</v>
+        <v>-0.14</v>
       </c>
       <c r="AC2">
-        <v>68.79000000000001</v>
+        <v>79.94</v>
       </c>
       <c r="AD2">
-        <v>56.79</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="AE2">
-        <v>72.19</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="AF2">
-        <v>35.89</v>
+        <v>7.75</v>
       </c>
       <c r="AG2">
-        <v>3940.54</v>
+        <v>3916.58</v>
       </c>
       <c r="AH2">
-        <v>3541.46</v>
+        <v>3538.54</v>
       </c>
       <c r="AI2">
         <v>3857.84</v>
@@ -1027,7 +1027,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>42.14</v>
+        <v>40.74</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1038,10 +1038,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>253</v>
+        <v>245.6</v>
       </c>
       <c r="D3">
-        <v>-0.33</v>
+        <v>-2.92</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1050,46 +1050,46 @@
         <v>237.75</v>
       </c>
       <c r="G3">
-        <v>-24.61</v>
+        <v>-26.82</v>
       </c>
       <c r="H3">
-        <v>6.41</v>
+        <v>3.3</v>
       </c>
       <c r="I3">
-        <v>-3.69</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="J3">
-        <v>-16.31</v>
+        <v>-21.48</v>
       </c>
       <c r="K3">
-        <v>-17.28</v>
+        <v>-19.93</v>
       </c>
       <c r="L3">
-        <v>-2.79</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="M3">
-        <v>23.91</v>
+        <v>25.15</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P3">
-        <v>259.05</v>
+        <v>254.65</v>
       </c>
       <c r="Q3">
-        <v>271.74</v>
+        <v>268.64</v>
       </c>
       <c r="R3">
-        <v>296.48</v>
+        <v>295.23</v>
       </c>
       <c r="S3">
-        <v>289.38</v>
+        <v>289.05</v>
       </c>
       <c r="T3">
-        <v>-12.57</v>
+        <v>-15.03</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1104,43 +1104,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>30.95</v>
+        <v>27.6</v>
       </c>
       <c r="Z3">
-        <v>-12.26</v>
+        <v>-12.77</v>
       </c>
       <c r="AA3">
-        <v>-12</v>
+        <v>-12.15</v>
       </c>
       <c r="AB3">
-        <v>-0.27</v>
+        <v>-0.62</v>
       </c>
       <c r="AC3">
-        <v>60.22</v>
+        <v>36.51</v>
       </c>
       <c r="AD3">
-        <v>62.45</v>
+        <v>53.6</v>
       </c>
       <c r="AE3">
-        <v>8.73</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="AF3">
-        <v>-34.19</v>
+        <v>-55.36</v>
       </c>
       <c r="AG3">
-        <v>306.99</v>
+        <v>301.38</v>
       </c>
       <c r="AH3">
-        <v>236.5</v>
+        <v>235.89</v>
       </c>
       <c r="AI3">
-        <v>278.16</v>
+        <v>275.46</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>55.66</v>
+        <v>58.15</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1151,10 +1151,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3611.3</v>
+        <v>3996.3</v>
       </c>
       <c r="D4">
-        <v>-2.78</v>
+        <v>10.66</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1163,46 +1163,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-22.23</v>
+        <v>-13.94</v>
       </c>
       <c r="H4">
-        <v>18.74</v>
+        <v>31.4</v>
       </c>
       <c r="I4">
-        <v>9.140000000000001</v>
+        <v>16.54</v>
       </c>
       <c r="J4">
-        <v>8.630000000000001</v>
+        <v>19.38</v>
       </c>
       <c r="K4">
-        <v>7.82</v>
+        <v>20.87</v>
       </c>
       <c r="L4">
-        <v>-11.68</v>
+        <v>-1.83</v>
       </c>
       <c r="M4">
-        <v>-5.67</v>
+        <v>-2.14</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="P4">
-        <v>3611.06</v>
+        <v>3724.48</v>
       </c>
       <c r="Q4">
-        <v>3328.27</v>
+        <v>3362.73</v>
       </c>
       <c r="R4">
-        <v>3429.76</v>
+        <v>3437.72</v>
       </c>
       <c r="S4">
-        <v>3486.8</v>
+        <v>3484.72</v>
       </c>
       <c r="T4">
-        <v>3.57</v>
+        <v>14.68</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1217,43 +1217,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>62.93</v>
+        <v>74.84</v>
       </c>
       <c r="Z4">
-        <v>61.86</v>
+        <v>99.75</v>
       </c>
       <c r="AA4">
-        <v>1.71</v>
+        <v>21.32</v>
       </c>
       <c r="AB4">
-        <v>60.15</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="AC4">
         <v>94.3</v>
       </c>
       <c r="AD4">
-        <v>98.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="AE4">
-        <v>121.85</v>
+        <v>151.13</v>
       </c>
       <c r="AF4">
-        <v>40.63</v>
+        <v>10562.28</v>
       </c>
       <c r="AG4">
-        <v>3692.1</v>
+        <v>3833.08</v>
       </c>
       <c r="AH4">
-        <v>2964.43</v>
+        <v>2892.38</v>
       </c>
       <c r="AI4">
-        <v>3359.74</v>
+        <v>3511.87</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>46.55</v>
+        <v>50.66</v>
       </c>
     </row>
   </sheetData>
@@ -1394,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1486,13 +1486,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-4.74</v>
+        <v>-4.54</v>
       </c>
       <c r="D7" s="6">
-        <v>-4.54</v>
+        <v>-6.41</v>
       </c>
       <c r="E7" s="7">
-        <v>0.2</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1503,13 +1503,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-14.09</v>
+        <v>-16.31</v>
       </c>
       <c r="D8" s="6">
-        <v>-16.31</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-2.22</v>
+        <v>-21.48</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-5.17</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1520,13 +1520,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>10.83</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="D9" s="6">
-        <v>8.630000000000001</v>
+        <v>19.38</v>
       </c>
       <c r="E9" s="8">
-        <v>-2.2</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1537,13 +1537,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>-2.06</v>
+        <v>0.95</v>
       </c>
       <c r="D10" s="6">
-        <v>0.95</v>
+        <v>-1.06</v>
       </c>
       <c r="E10" s="7">
-        <v>3.01</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1554,13 +1554,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>-2.81</v>
+        <v>-3.69</v>
       </c>
       <c r="D11" s="6">
-        <v>-3.69</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.88</v>
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-4.53</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1571,13 +1571,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>13.59</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="D12" s="6">
-        <v>9.140000000000001</v>
+        <v>16.54</v>
       </c>
       <c r="E12" s="8">
-        <v>-4.45</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1588,13 +1588,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>-2.84</v>
+        <v>-1.25</v>
       </c>
       <c r="D13" s="6">
-        <v>-1.25</v>
+        <v>-4.11</v>
       </c>
       <c r="E13" s="7">
-        <v>1.59</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1605,13 +1605,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>-3.79</v>
+        <v>-2.79</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.79</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="E14" s="7">
-        <v>1</v>
+        <v>-5.83</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1622,13 +1622,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-10.04</v>
+        <v>-11.68</v>
       </c>
       <c r="D15" s="6">
-        <v>-11.68</v>
+        <v>-1.83</v>
       </c>
       <c r="E15" s="8">
-        <v>-1.64</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1639,13 +1639,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-4.91</v>
+        <v>-4.61</v>
       </c>
       <c r="D16" s="6">
-        <v>-4.61</v>
+        <v>-5.47</v>
       </c>
       <c r="E16" s="7">
-        <v>0.3</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1656,13 +1656,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-18.13</v>
+        <v>-17.28</v>
       </c>
       <c r="D17" s="6">
-        <v>-17.28</v>
+        <v>-19.93</v>
       </c>
       <c r="E17" s="7">
-        <v>0.85</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1673,13 +1673,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>8.76</v>
+        <v>7.82</v>
       </c>
       <c r="D18" s="6">
-        <v>7.82</v>
+        <v>20.87</v>
       </c>
       <c r="E18" s="8">
-        <v>-0.9399999999999999</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1690,13 +1690,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>-17.1</v>
+        <v>-16.31</v>
       </c>
       <c r="D19" s="6">
-        <v>-16.31</v>
+        <v>-16.9</v>
       </c>
       <c r="E19" s="7">
-        <v>0.79</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1707,13 +1707,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-24.36</v>
+        <v>-24.61</v>
       </c>
       <c r="D20" s="6">
-        <v>-24.61</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.25</v>
+        <v>-26.82</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-2.21</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1724,13 +1724,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-20.01</v>
+        <v>-22.23</v>
       </c>
       <c r="D21" s="6">
-        <v>-22.23</v>
+        <v>-13.94</v>
       </c>
       <c r="E21" s="8">
-        <v>-2.22</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>3627.1</v>
+        <v>3661.9</v>
       </c>
       <c r="D22" s="6">
-        <v>3661.9</v>
+        <v>3636</v>
       </c>
       <c r="E22" s="7">
-        <v>34.8</v>
+        <v>-25.9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1758,13 +1758,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>253.85</v>
+        <v>253</v>
       </c>
       <c r="D23" s="6">
-        <v>253</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.85</v>
+        <v>245.6</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-7.4</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1775,132 +1775,115 @@
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>3714.6</v>
+        <v>3611.3</v>
       </c>
       <c r="D24" s="6">
-        <v>3611.3</v>
+        <v>3996.3</v>
       </c>
       <c r="E24" s="8">
-        <v>-103.3</v>
+        <v>385</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C25" s="6">
-        <v>34</v>
+        <v>40.59</v>
       </c>
       <c r="D25" s="6">
-        <v>33</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1</v>
+        <v>38.72</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.87</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>36.79</v>
+        <v>30.95</v>
       </c>
       <c r="D26" s="6">
-        <v>40.59</v>
+        <v>27.6</v>
       </c>
       <c r="E26" s="7">
-        <v>3.8</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>31.36</v>
+        <v>62.93</v>
       </c>
       <c r="D27" s="6">
-        <v>30.95</v>
+        <v>74.84</v>
       </c>
       <c r="E27" s="8">
-        <v>-0.41</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C28" s="6">
-        <v>71.34</v>
+        <v>35.89</v>
       </c>
       <c r="D28" s="6">
-        <v>62.93</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-8.41</v>
+        <v>7.75</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-28.14</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>8.720000000000001</v>
+        <v>-34.19</v>
       </c>
       <c r="D29" s="6">
-        <v>35.89</v>
+        <v>-55.36</v>
       </c>
       <c r="E29" s="7">
-        <v>27.17</v>
+        <v>-21.17</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>263.31</v>
+        <v>40.63</v>
       </c>
       <c r="D30" s="6">
-        <v>-34.19</v>
+        <v>10562.28</v>
       </c>
       <c r="E30" s="8">
-        <v>-297.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>20.03</v>
-      </c>
-      <c r="D31" s="6">
-        <v>40.63</v>
-      </c>
-      <c r="E31" s="7">
-        <v>20.6</v>
+        <v>10521.65</v>
       </c>
     </row>
   </sheetData>
@@ -1965,16 +1948,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>44.8</v>
+        <v>47.1</v>
       </c>
       <c r="E2" s="11">
         <v>33.3</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.1</v>
+        <v>-2.8</v>
       </c>
       <c r="G2" s="11">
-        <v>-4.7</v>
+        <v>-1.5</v>
       </c>
       <c r="H2" s="11">
         <v>66</v>
@@ -2093,13 +2076,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.2391</v>
+        <v>0.2515</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1586</v>
+        <v>0.162</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0567</v>
+        <v>-0.0214</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,34 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>62.9 → 74.8</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>62.9</t>
-  </si>
-  <si>
-    <t>74.8</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -239,7 +212,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -273,13 +246,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -293,7 +259,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -315,12 +281,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -402,22 +362,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -426,7 +385,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -925,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3636</v>
+        <v>3638.3</v>
       </c>
       <c r="D2">
-        <v>-0.71</v>
+        <v>0.06</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -937,46 +896,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-16.9</v>
+        <v>-16.85</v>
       </c>
       <c r="H2">
-        <v>9.85</v>
+        <v>9.92</v>
       </c>
       <c r="I2">
-        <v>-1.06</v>
+        <v>-0.1</v>
       </c>
       <c r="J2">
-        <v>-6.41</v>
+        <v>-6.82</v>
       </c>
       <c r="K2">
-        <v>-5.47</v>
+        <v>-4.69</v>
       </c>
       <c r="L2">
-        <v>-4.11</v>
+        <v>-4.87</v>
       </c>
       <c r="M2">
-        <v>16.2</v>
+        <v>16.39</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="P2">
-        <v>3639.8</v>
+        <v>3639.06</v>
       </c>
       <c r="Q2">
-        <v>3727.56</v>
+        <v>3716.15</v>
       </c>
       <c r="R2">
-        <v>3889.71</v>
+        <v>3880.87</v>
       </c>
       <c r="S2">
-        <v>3927.05</v>
+        <v>3924.74</v>
       </c>
       <c r="T2">
-        <v>-7.41</v>
+        <v>-7.3</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -991,34 +950,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.72</v>
+        <v>38.99</v>
       </c>
       <c r="Z2">
-        <v>-72.56999999999999</v>
+        <v>-70.28</v>
       </c>
       <c r="AA2">
-        <v>-72.43000000000001</v>
+        <v>-72</v>
       </c>
       <c r="AB2">
-        <v>-0.14</v>
+        <v>1.72</v>
       </c>
       <c r="AC2">
-        <v>79.94</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="AD2">
-        <v>67.09999999999999</v>
+        <v>78.78</v>
       </c>
       <c r="AE2">
-        <v>73.15000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="AF2">
-        <v>7.75</v>
+        <v>47.77</v>
       </c>
       <c r="AG2">
-        <v>3916.58</v>
+        <v>3897.26</v>
       </c>
       <c r="AH2">
-        <v>3538.54</v>
+        <v>3535.05</v>
       </c>
       <c r="AI2">
         <v>3857.84</v>
@@ -1027,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>40.74</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1038,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>245.6</v>
+        <v>244.1</v>
       </c>
       <c r="D3">
-        <v>-2.92</v>
+        <v>-0.61</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1050,46 +1009,46 @@
         <v>237.75</v>
       </c>
       <c r="G3">
-        <v>-26.82</v>
+        <v>-27.26</v>
       </c>
       <c r="H3">
-        <v>3.3</v>
+        <v>2.67</v>
       </c>
       <c r="I3">
-        <v>-8.220000000000001</v>
+        <v>-5.68</v>
       </c>
       <c r="J3">
-        <v>-21.48</v>
+        <v>-20.7</v>
       </c>
       <c r="K3">
-        <v>-19.93</v>
+        <v>-20.2</v>
       </c>
       <c r="L3">
-        <v>-8.619999999999999</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="M3">
-        <v>25.15</v>
+        <v>25.11</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P3">
-        <v>254.65</v>
+        <v>251.71</v>
       </c>
       <c r="Q3">
-        <v>268.64</v>
+        <v>265.6</v>
       </c>
       <c r="R3">
-        <v>295.23</v>
+        <v>293.85</v>
       </c>
       <c r="S3">
-        <v>289.05</v>
+        <v>288.7</v>
       </c>
       <c r="T3">
-        <v>-15.03</v>
+        <v>-15.45</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1104,43 +1063,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>27.6</v>
+        <v>26.96</v>
       </c>
       <c r="Z3">
-        <v>-12.77</v>
+        <v>-13.13</v>
       </c>
       <c r="AA3">
-        <v>-12.15</v>
+        <v>-12.35</v>
       </c>
       <c r="AB3">
-        <v>-0.62</v>
+        <v>-0.79</v>
       </c>
       <c r="AC3">
-        <v>36.51</v>
+        <v>23.33</v>
       </c>
       <c r="AD3">
-        <v>53.6</v>
+        <v>40.02</v>
       </c>
       <c r="AE3">
-        <v>8.869999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="AF3">
-        <v>-55.36</v>
+        <v>-56.95</v>
       </c>
       <c r="AG3">
-        <v>301.38</v>
+        <v>295.31</v>
       </c>
       <c r="AH3">
-        <v>235.89</v>
+        <v>235.88</v>
       </c>
       <c r="AI3">
-        <v>275.46</v>
+        <v>269.99</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>58.15</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1151,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3996.3</v>
+        <v>3954.8</v>
       </c>
       <c r="D4">
-        <v>10.66</v>
+        <v>-1.04</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1163,25 +1122,25 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-13.94</v>
+        <v>-14.84</v>
       </c>
       <c r="H4">
-        <v>31.4</v>
+        <v>30.04</v>
       </c>
       <c r="I4">
-        <v>16.54</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="J4">
-        <v>19.38</v>
+        <v>19.59</v>
       </c>
       <c r="K4">
-        <v>20.87</v>
+        <v>18.65</v>
       </c>
       <c r="L4">
-        <v>-1.83</v>
+        <v>-4.29</v>
       </c>
       <c r="M4">
-        <v>-2.14</v>
+        <v>-1.72</v>
       </c>
       <c r="N4">
         <v>99</v>
@@ -1190,19 +1149,19 @@
         <v>83</v>
       </c>
       <c r="P4">
-        <v>3724.48</v>
+        <v>3792.76</v>
       </c>
       <c r="Q4">
-        <v>3362.73</v>
+        <v>3395.79</v>
       </c>
       <c r="R4">
-        <v>3437.72</v>
+        <v>3445.14</v>
       </c>
       <c r="S4">
-        <v>3484.72</v>
+        <v>3482.84</v>
       </c>
       <c r="T4">
-        <v>14.68</v>
+        <v>13.55</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1217,34 +1176,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>74.84</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="Z4">
-        <v>99.75</v>
+        <v>124.99</v>
       </c>
       <c r="AA4">
-        <v>21.32</v>
+        <v>42.05</v>
       </c>
       <c r="AB4">
-        <v>78.43000000000001</v>
+        <v>82.94</v>
       </c>
       <c r="AC4">
-        <v>94.3</v>
+        <v>91.83</v>
       </c>
       <c r="AD4">
-        <v>96.2</v>
+        <v>93.47</v>
       </c>
       <c r="AE4">
-        <v>151.13</v>
+        <v>155.26</v>
       </c>
       <c r="AF4">
-        <v>10562.28</v>
+        <v>209.6</v>
       </c>
       <c r="AG4">
-        <v>3833.08</v>
+        <v>3933.77</v>
       </c>
       <c r="AH4">
-        <v>2892.38</v>
+        <v>2857.81</v>
       </c>
       <c r="AI4">
         <v>3511.87</v>
@@ -1253,7 +1212,7 @@
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>50.66</v>
+        <v>54.21</v>
       </c>
     </row>
   </sheetData>
@@ -1414,47 +1373,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1462,428 +1386,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-4.54</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-6.41</v>
       </c>
-      <c r="E7" s="7">
-        <v>-1.87</v>
+      <c r="D7" s="5">
+        <v>-6.82</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-16.31</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-21.48</v>
       </c>
+      <c r="D8" s="5">
+        <v>-20.7</v>
+      </c>
       <c r="E8" s="7">
-        <v>-5.17</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>19.38</v>
       </c>
-      <c r="E9" s="8">
-        <v>10.75</v>
+      <c r="D9" s="5">
+        <v>19.59</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.21</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>0.95</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-1.06</v>
       </c>
+      <c r="D10" s="5">
+        <v>-0.1</v>
+      </c>
       <c r="E10" s="7">
-        <v>-2.01</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-3.69</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-8.220000000000001</v>
       </c>
+      <c r="D11" s="5">
+        <v>-5.68</v>
+      </c>
       <c r="E11" s="7">
-        <v>-4.53</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>16.54</v>
       </c>
-      <c r="E12" s="8">
-        <v>7.4</v>
+      <c r="D12" s="5">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-7.09</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-1.25</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-4.11</v>
       </c>
-      <c r="E13" s="7">
-        <v>-2.86</v>
+      <c r="D13" s="5">
+        <v>-4.87</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-2.79</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-8.619999999999999</v>
       </c>
+      <c r="D14" s="5">
+        <v>-8.390000000000001</v>
+      </c>
       <c r="E14" s="7">
-        <v>-5.83</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-11.68</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-1.83</v>
       </c>
-      <c r="E15" s="8">
-        <v>9.85</v>
+      <c r="D15" s="5">
+        <v>-4.29</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>-4.61</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-5.47</v>
       </c>
+      <c r="D16" s="5">
+        <v>-4.69</v>
+      </c>
       <c r="E16" s="7">
-        <v>-0.86</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-17.28</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-19.93</v>
       </c>
-      <c r="E17" s="7">
-        <v>-2.65</v>
+      <c r="D17" s="5">
+        <v>-20.2</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>7.82</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>20.87</v>
       </c>
-      <c r="E18" s="8">
-        <v>13.05</v>
+      <c r="D18" s="5">
+        <v>18.65</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-2.22</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-16.31</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-16.9</v>
       </c>
+      <c r="D19" s="5">
+        <v>-16.85</v>
+      </c>
       <c r="E19" s="7">
-        <v>-0.59</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-24.61</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-26.82</v>
       </c>
-      <c r="E20" s="7">
-        <v>-2.21</v>
+      <c r="D20" s="5">
+        <v>-27.26</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-22.23</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>-13.94</v>
       </c>
-      <c r="E21" s="8">
-        <v>8.289999999999999</v>
+      <c r="D21" s="5">
+        <v>-14.84</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>3661.9</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>3636</v>
       </c>
+      <c r="D22" s="5">
+        <v>3638.3</v>
+      </c>
       <c r="E22" s="7">
-        <v>-25.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>253</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>245.6</v>
       </c>
-      <c r="E23" s="7">
-        <v>-7.4</v>
+      <c r="D23" s="5">
+        <v>244.1</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>3611.3</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>3996.3</v>
       </c>
-      <c r="E24" s="8">
-        <v>385</v>
+      <c r="D24" s="5">
+        <v>3954.8</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-41.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="6">
-        <v>40.59</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="5">
         <v>38.72</v>
       </c>
+      <c r="D25" s="5">
+        <v>38.99</v>
+      </c>
       <c r="E25" s="7">
-        <v>-1.87</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="6">
-        <v>30.95</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="5">
         <v>27.6</v>
       </c>
-      <c r="E26" s="7">
-        <v>-3.35</v>
+      <c r="D26" s="5">
+        <v>26.96</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="6">
-        <v>62.93</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C27" s="5">
         <v>74.84</v>
       </c>
-      <c r="E27" s="8">
-        <v>11.91</v>
+      <c r="D27" s="5">
+        <v>72.15000000000001</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-2.69</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>35.89</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" s="5">
         <v>7.75</v>
       </c>
+      <c r="D28" s="5">
+        <v>47.77</v>
+      </c>
       <c r="E28" s="7">
-        <v>-28.14</v>
+        <v>40.02</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>-34.19</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="5">
         <v>-55.36</v>
       </c>
-      <c r="E29" s="7">
-        <v>-21.17</v>
+      <c r="D29" s="5">
+        <v>-56.95</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>40.63</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>10562.28</v>
       </c>
-      <c r="E30" s="8">
-        <v>10521.65</v>
+      <c r="D30" s="5">
+        <v>209.6</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-10352.68</v>
       </c>
     </row>
   </sheetData>
@@ -1909,60 +1833,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="10">
+        <v>49.72</v>
+      </c>
+      <c r="C2" s="11">
+        <v>3</v>
+      </c>
+      <c r="D2" s="10">
+        <v>46</v>
+      </c>
+      <c r="E2" s="10">
+        <v>33.3</v>
+      </c>
+      <c r="F2" s="10">
+        <v>-2.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-2.1</v>
+      </c>
+      <c r="H2" s="10">
         <v>66</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="11">
-        <v>49.72</v>
-      </c>
-      <c r="C2" s="12">
-        <v>3</v>
-      </c>
-      <c r="D2" s="11">
-        <v>47.1</v>
-      </c>
-      <c r="E2" s="11">
-        <v>33.3</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-2.8</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-1.5</v>
-      </c>
-      <c r="H2" s="11">
-        <v>66</v>
-      </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2064,25 +1988,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.2515</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.162</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0214</v>
+      <c r="A2" s="13">
+        <v>0.2511</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1639</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0172</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,7 +160,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>72.2 → 69.3</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>72.2</t>
+  </si>
+  <si>
+    <t>69.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -212,7 +239,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,7 +273,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -258,8 +285,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -286,13 +320,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -362,21 +402,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -385,7 +426,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -750,8 +791,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -884,10 +924,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3638.3</v>
+        <v>3647</v>
       </c>
       <c r="D2">
-        <v>0.06</v>
+        <v>0.24</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -896,46 +936,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-16.85</v>
+        <v>-16.65</v>
       </c>
       <c r="H2">
-        <v>9.92</v>
+        <v>10.18</v>
       </c>
       <c r="I2">
-        <v>-0.1</v>
+        <v>0.41</v>
       </c>
       <c r="J2">
-        <v>-6.82</v>
+        <v>-5.67</v>
       </c>
       <c r="K2">
-        <v>-4.69</v>
+        <v>-3.83</v>
       </c>
       <c r="L2">
-        <v>-4.87</v>
+        <v>-4.08</v>
       </c>
       <c r="M2">
-        <v>16.39</v>
+        <v>16.57</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="P2">
-        <v>3639.06</v>
+        <v>3642.06</v>
       </c>
       <c r="Q2">
-        <v>3716.15</v>
+        <v>3702.01</v>
       </c>
       <c r="R2">
-        <v>3880.87</v>
+        <v>3873.07</v>
       </c>
       <c r="S2">
-        <v>3924.74</v>
+        <v>3922.35</v>
       </c>
       <c r="T2">
-        <v>-7.3</v>
+        <v>-7.02</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,43 +990,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.99</v>
+        <v>40.06</v>
       </c>
       <c r="Z2">
-        <v>-70.28</v>
+        <v>-67</v>
       </c>
       <c r="AA2">
-        <v>-72</v>
+        <v>-71</v>
       </c>
       <c r="AB2">
-        <v>1.72</v>
+        <v>4</v>
       </c>
       <c r="AC2">
-        <v>87.59999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="AD2">
-        <v>78.78</v>
+        <v>84.42</v>
       </c>
       <c r="AE2">
-        <v>74.7</v>
+        <v>74.16</v>
       </c>
       <c r="AF2">
-        <v>47.77</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AG2">
-        <v>3897.26</v>
+        <v>3854.8</v>
       </c>
       <c r="AH2">
-        <v>3535.05</v>
+        <v>3549.22</v>
       </c>
       <c r="AI2">
-        <v>3857.84</v>
+        <v>3852.83</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>40.87</v>
+        <v>40.98</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,37 +1037,37 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>244.1</v>
+        <v>237.5</v>
       </c>
       <c r="D3">
-        <v>-0.61</v>
+        <v>-2.7</v>
       </c>
       <c r="E3">
         <v>335.6</v>
       </c>
       <c r="F3">
-        <v>237.75</v>
+        <v>237.5</v>
       </c>
       <c r="G3">
-        <v>-27.26</v>
+        <v>-29.23</v>
       </c>
       <c r="H3">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-5.68</v>
+        <v>-9.35</v>
       </c>
       <c r="J3">
-        <v>-20.7</v>
+        <v>-22.11</v>
       </c>
       <c r="K3">
-        <v>-20.2</v>
+        <v>-22.14</v>
       </c>
       <c r="L3">
-        <v>-8.390000000000001</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="M3">
-        <v>25.11</v>
+        <v>25.54</v>
       </c>
       <c r="N3">
         <v>33</v>
@@ -1036,19 +1076,19 @@
         <v>37</v>
       </c>
       <c r="P3">
-        <v>251.71</v>
+        <v>246.81</v>
       </c>
       <c r="Q3">
-        <v>265.6</v>
+        <v>261.97</v>
       </c>
       <c r="R3">
-        <v>293.85</v>
+        <v>292.3</v>
       </c>
       <c r="S3">
-        <v>288.7</v>
+        <v>288.3</v>
       </c>
       <c r="T3">
-        <v>-15.45</v>
+        <v>-17.62</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,43 +1103,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>26.96</v>
+        <v>24.31</v>
       </c>
       <c r="Z3">
-        <v>-13.13</v>
+        <v>-13.8</v>
       </c>
       <c r="AA3">
-        <v>-12.35</v>
+        <v>-12.64</v>
       </c>
       <c r="AB3">
-        <v>-0.79</v>
+        <v>-1.16</v>
       </c>
       <c r="AC3">
-        <v>23.33</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="AD3">
-        <v>40.02</v>
+        <v>22.68</v>
       </c>
       <c r="AE3">
-        <v>8.73</v>
+        <v>8.83</v>
       </c>
       <c r="AF3">
-        <v>-56.95</v>
+        <v>-38.45</v>
       </c>
       <c r="AG3">
-        <v>295.31</v>
+        <v>286.02</v>
       </c>
       <c r="AH3">
-        <v>235.88</v>
+        <v>237.92</v>
       </c>
       <c r="AI3">
-        <v>269.99</v>
+        <v>265.9</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>60.68</v>
+        <v>63.47</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1150,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3954.8</v>
+        <v>3910.3</v>
       </c>
       <c r="D4">
-        <v>-1.04</v>
+        <v>-1.13</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1122,25 +1162,25 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-14.84</v>
+        <v>-15.8</v>
       </c>
       <c r="H4">
-        <v>30.04</v>
+        <v>28.57</v>
       </c>
       <c r="I4">
-        <v>9.449999999999999</v>
+        <v>6.06</v>
       </c>
       <c r="J4">
-        <v>19.59</v>
+        <v>18.72</v>
       </c>
       <c r="K4">
-        <v>18.65</v>
+        <v>15.85</v>
       </c>
       <c r="L4">
-        <v>-4.29</v>
+        <v>-4.41</v>
       </c>
       <c r="M4">
-        <v>-1.72</v>
+        <v>-1.71</v>
       </c>
       <c r="N4">
         <v>99</v>
@@ -1149,19 +1189,19 @@
         <v>83</v>
       </c>
       <c r="P4">
-        <v>3792.76</v>
+        <v>3837.46</v>
       </c>
       <c r="Q4">
-        <v>3395.79</v>
+        <v>3429.74</v>
       </c>
       <c r="R4">
-        <v>3445.14</v>
+        <v>3450.3</v>
       </c>
       <c r="S4">
-        <v>3482.84</v>
+        <v>3480.6</v>
       </c>
       <c r="T4">
-        <v>13.55</v>
+        <v>12.35</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,34 +1216,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>72.15000000000001</v>
+        <v>69.27</v>
       </c>
       <c r="Z4">
-        <v>124.99</v>
+        <v>139.8</v>
       </c>
       <c r="AA4">
-        <v>42.05</v>
+        <v>61.6</v>
       </c>
       <c r="AB4">
-        <v>82.94</v>
+        <v>78.19</v>
       </c>
       <c r="AC4">
-        <v>91.83</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="AD4">
-        <v>93.47</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="AE4">
-        <v>155.26</v>
+        <v>154.96</v>
       </c>
       <c r="AF4">
-        <v>209.6</v>
+        <v>13.22</v>
       </c>
       <c r="AG4">
-        <v>3933.77</v>
+        <v>4008.19</v>
       </c>
       <c r="AH4">
-        <v>2857.81</v>
+        <v>2851.29</v>
       </c>
       <c r="AI4">
         <v>3511.87</v>
@@ -1212,7 +1252,7 @@
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>54.21</v>
+        <v>57.3</v>
       </c>
     </row>
   </sheetData>
@@ -1373,12 +1413,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1386,428 +1461,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-6.41</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-6.82</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.41</v>
+      <c r="D7" s="6">
+        <v>-5.67</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.15</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-21.48</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-20.7</v>
       </c>
-      <c r="E8" s="7">
-        <v>0.78</v>
+      <c r="D8" s="6">
+        <v>-22.11</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>19.38</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>19.59</v>
       </c>
-      <c r="E9" s="7">
-        <v>0.21</v>
+      <c r="D9" s="6">
+        <v>18.72</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-1.06</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-0.1</v>
       </c>
+      <c r="D10" s="6">
+        <v>0.41</v>
+      </c>
       <c r="E10" s="7">
-        <v>0.96</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-5.68</v>
       </c>
-      <c r="E11" s="7">
-        <v>2.54</v>
+      <c r="D11" s="6">
+        <v>-9.35</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-3.67</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>16.54</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>9.449999999999999</v>
       </c>
-      <c r="E12" s="6">
-        <v>-7.09</v>
+      <c r="D12" s="6">
+        <v>6.06</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-3.39</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-4.11</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-4.87</v>
       </c>
-      <c r="E13" s="6">
-        <v>-0.76</v>
+      <c r="D13" s="6">
+        <v>-4.08</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.79</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>-8.619999999999999</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-8.390000000000001</v>
       </c>
-      <c r="E14" s="7">
-        <v>0.23</v>
+      <c r="D14" s="6">
+        <v>-9.880000000000001</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-1.83</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-4.29</v>
       </c>
-      <c r="E15" s="6">
-        <v>-2.46</v>
+      <c r="D15" s="6">
+        <v>-4.41</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-5.47</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-4.69</v>
       </c>
+      <c r="D16" s="6">
+        <v>-3.83</v>
+      </c>
       <c r="E16" s="7">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-19.93</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-20.2</v>
       </c>
-      <c r="E17" s="6">
-        <v>-0.27</v>
+      <c r="D17" s="6">
+        <v>-22.14</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.94</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>20.87</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>18.65</v>
       </c>
-      <c r="E18" s="6">
-        <v>-2.22</v>
+      <c r="D18" s="6">
+        <v>15.85</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-2.8</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-16.9</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-16.85</v>
       </c>
+      <c r="D19" s="6">
+        <v>-16.65</v>
+      </c>
       <c r="E19" s="7">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-26.82</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-27.26</v>
       </c>
-      <c r="E20" s="6">
-        <v>-0.44</v>
+      <c r="D20" s="6">
+        <v>-29.23</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.97</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-13.94</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-14.84</v>
       </c>
-      <c r="E21" s="6">
-        <v>-0.9</v>
+      <c r="D21" s="6">
+        <v>-15.8</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>3636</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>3638.3</v>
       </c>
+      <c r="D22" s="6">
+        <v>3647</v>
+      </c>
       <c r="E22" s="7">
-        <v>2.3</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>245.6</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>244.1</v>
       </c>
-      <c r="E23" s="6">
-        <v>-1.5</v>
+      <c r="D23" s="6">
+        <v>237.5</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-6.6</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>3996.3</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>3954.8</v>
       </c>
-      <c r="E24" s="6">
-        <v>-41.5</v>
+      <c r="D24" s="6">
+        <v>3910.3</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-44.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="5">
-        <v>38.72</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C25" s="6">
         <v>38.99</v>
       </c>
+      <c r="D25" s="6">
+        <v>40.06</v>
+      </c>
       <c r="E25" s="7">
-        <v>0.27</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="5">
-        <v>27.6</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C26" s="6">
         <v>26.96</v>
       </c>
-      <c r="E26" s="6">
-        <v>-0.64</v>
+      <c r="D26" s="6">
+        <v>24.31</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-2.65</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="5">
-        <v>74.84</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C27" s="6">
         <v>72.15000000000001</v>
       </c>
-      <c r="E27" s="6">
-        <v>-2.69</v>
+      <c r="D27" s="6">
+        <v>69.27</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.88</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>7.75</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C28" s="6">
         <v>47.77</v>
       </c>
-      <c r="E28" s="7">
-        <v>40.02</v>
+      <c r="D28" s="6">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-39.15</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5">
-        <v>-55.36</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C29" s="6">
         <v>-56.95</v>
       </c>
-      <c r="E29" s="6">
-        <v>-1.59</v>
+      <c r="D29" s="6">
+        <v>-38.45</v>
+      </c>
+      <c r="E29" s="7">
+        <v>18.5</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>10562.28</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>209.6</v>
       </c>
-      <c r="E30" s="6">
-        <v>-10352.68</v>
+      <c r="D30" s="6">
+        <v>13.22</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-196.38</v>
       </c>
     </row>
   </sheetData>
@@ -1833,60 +1908,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>49.72</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>46</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>44.5</v>
+      </c>
+      <c r="E2" s="11">
         <v>33.3</v>
       </c>
-      <c r="F2" s="10">
-        <v>-2.6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-2.1</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-3.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>66</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1988,25 +2063,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.2511</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1639</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0172</v>
+      <c r="A2" s="14">
+        <v>0.2554</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1657</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0171</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,19 +175,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>72.2 → 69.3</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>72.2</t>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>69.3 → 72.6</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
   </si>
   <si>
     <t>69.3</t>
+  </si>
+  <si>
+    <t>72.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +282,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -320,13 +329,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -402,7 +411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -410,10 +419,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -791,7 +801,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -924,10 +935,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3647</v>
+        <v>3680</v>
       </c>
       <c r="D2">
-        <v>0.24</v>
+        <v>0.9</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -936,46 +947,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-16.65</v>
+        <v>-15.89</v>
       </c>
       <c r="H2">
-        <v>10.18</v>
+        <v>11.18</v>
       </c>
       <c r="I2">
-        <v>0.41</v>
+        <v>1.46</v>
       </c>
       <c r="J2">
-        <v>-5.67</v>
+        <v>-6.36</v>
       </c>
       <c r="K2">
-        <v>-3.83</v>
+        <v>-2.79</v>
       </c>
       <c r="L2">
-        <v>-4.08</v>
+        <v>-4.05</v>
       </c>
       <c r="M2">
-        <v>16.57</v>
+        <v>16.61</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P2">
-        <v>3642.06</v>
+        <v>3652.64</v>
       </c>
       <c r="Q2">
-        <v>3702.01</v>
+        <v>3693.09</v>
       </c>
       <c r="R2">
-        <v>3873.07</v>
+        <v>3866.27</v>
       </c>
       <c r="S2">
-        <v>3922.35</v>
+        <v>3920.2</v>
       </c>
       <c r="T2">
-        <v>-7.02</v>
+        <v>-6.13</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -990,34 +1001,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>40.06</v>
+        <v>44.06</v>
       </c>
       <c r="Z2">
-        <v>-67</v>
+        <v>-61.03</v>
       </c>
       <c r="AA2">
-        <v>-71</v>
+        <v>-69.01000000000001</v>
       </c>
       <c r="AB2">
-        <v>4</v>
+        <v>7.98</v>
       </c>
       <c r="AC2">
-        <v>85.70999999999999</v>
+        <v>92.39</v>
       </c>
       <c r="AD2">
-        <v>84.42</v>
+        <v>88.56</v>
       </c>
       <c r="AE2">
-        <v>74.16</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="AF2">
-        <v>8.619999999999999</v>
+        <v>-39.54</v>
       </c>
       <c r="AG2">
-        <v>3854.8</v>
+        <v>3827.12</v>
       </c>
       <c r="AH2">
-        <v>3549.22</v>
+        <v>3559.06</v>
       </c>
       <c r="AI2">
         <v>3852.83</v>
@@ -1026,7 +1037,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>40.98</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1048,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>237.5</v>
+        <v>241.1</v>
       </c>
       <c r="D3">
-        <v>-2.7</v>
+        <v>1.52</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1049,46 +1060,46 @@
         <v>237.5</v>
       </c>
       <c r="G3">
-        <v>-29.23</v>
+        <v>-28.16</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="I3">
-        <v>-9.35</v>
+        <v>-5.02</v>
       </c>
       <c r="J3">
-        <v>-22.11</v>
+        <v>-22.23</v>
       </c>
       <c r="K3">
-        <v>-22.14</v>
+        <v>-20.27</v>
       </c>
       <c r="L3">
-        <v>-9.880000000000001</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="M3">
-        <v>25.54</v>
+        <v>24.79</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="P3">
-        <v>246.81</v>
+        <v>244.26</v>
       </c>
       <c r="Q3">
-        <v>261.97</v>
+        <v>259.93</v>
       </c>
       <c r="R3">
-        <v>292.3</v>
+        <v>290.77</v>
       </c>
       <c r="S3">
-        <v>288.3</v>
+        <v>287.92</v>
       </c>
       <c r="T3">
-        <v>-17.62</v>
+        <v>-16.26</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1103,43 +1114,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>24.31</v>
+        <v>28.45</v>
       </c>
       <c r="Z3">
-        <v>-13.8</v>
+        <v>-13.87</v>
       </c>
       <c r="AA3">
-        <v>-12.64</v>
+        <v>-12.88</v>
       </c>
       <c r="AB3">
-        <v>-1.16</v>
+        <v>-0.99</v>
       </c>
       <c r="AC3">
-        <v>8.210000000000001</v>
+        <v>14.01</v>
       </c>
       <c r="AD3">
-        <v>22.68</v>
+        <v>15.19</v>
       </c>
       <c r="AE3">
-        <v>8.83</v>
+        <v>9.09</v>
       </c>
       <c r="AF3">
-        <v>-38.45</v>
+        <v>2.08</v>
       </c>
       <c r="AG3">
-        <v>286.02</v>
+        <v>283.76</v>
       </c>
       <c r="AH3">
-        <v>237.92</v>
+        <v>236.09</v>
       </c>
       <c r="AI3">
-        <v>265.9</v>
+        <v>262.7</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>63.47</v>
+        <v>66.27</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1161,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3910.3</v>
+        <v>4035.6</v>
       </c>
       <c r="D4">
-        <v>-1.13</v>
+        <v>3.2</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1162,49 +1173,49 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-15.8</v>
+        <v>-13.1</v>
       </c>
       <c r="H4">
-        <v>28.57</v>
+        <v>32.69</v>
       </c>
       <c r="I4">
-        <v>6.06</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="J4">
-        <v>18.72</v>
+        <v>24.89</v>
       </c>
       <c r="K4">
-        <v>15.85</v>
+        <v>18.07</v>
       </c>
       <c r="L4">
-        <v>-4.41</v>
+        <v>-2.4</v>
       </c>
       <c r="M4">
-        <v>-1.71</v>
+        <v>-1.31</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P4">
-        <v>3837.46</v>
+        <v>3901.66</v>
       </c>
       <c r="Q4">
-        <v>3429.74</v>
+        <v>3471.07</v>
       </c>
       <c r="R4">
-        <v>3450.3</v>
+        <v>3459.43</v>
       </c>
       <c r="S4">
-        <v>3480.6</v>
+        <v>3478.95</v>
       </c>
       <c r="T4">
-        <v>12.35</v>
+        <v>16</v>
       </c>
       <c r="U4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V4" t="s">
         <v>41</v>
@@ -1213,37 +1224,37 @@
         <v>41</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4">
-        <v>69.27</v>
+        <v>72.58</v>
       </c>
       <c r="Z4">
-        <v>139.8</v>
+        <v>159.8</v>
       </c>
       <c r="AA4">
-        <v>61.6</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="AB4">
-        <v>78.19</v>
+        <v>78.55</v>
       </c>
       <c r="AC4">
-        <v>92.43000000000001</v>
+        <v>90.37</v>
       </c>
       <c r="AD4">
-        <v>92.84999999999999</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="AE4">
-        <v>154.96</v>
+        <v>156.29</v>
       </c>
       <c r="AF4">
-        <v>13.22</v>
+        <v>-17.74</v>
       </c>
       <c r="AG4">
-        <v>4008.19</v>
+        <v>4099.11</v>
       </c>
       <c r="AH4">
-        <v>2851.29</v>
+        <v>2843.02</v>
       </c>
       <c r="AI4">
         <v>3511.87</v>
@@ -1252,7 +1263,7 @@
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>57.3</v>
+        <v>60.06</v>
       </c>
     </row>
   </sheetData>
@@ -1393,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1445,450 +1456,470 @@
         <v>53</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="D4" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="E4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="C7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-6.82</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C8" s="7">
         <v>-5.67</v>
       </c>
-      <c r="E7" s="7">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D8" s="7">
+        <v>-6.36</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-20.7</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C9" s="7">
         <v>-22.11</v>
       </c>
-      <c r="E8" s="8">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D9" s="7">
+        <v>-22.23</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>19.59</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C10" s="7">
         <v>18.72</v>
       </c>
-      <c r="E9" s="8">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D10" s="7">
+        <v>24.89</v>
+      </c>
+      <c r="E10" s="9">
+        <v>6.17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C11" s="7">
         <v>0.41</v>
       </c>
-      <c r="E10" s="7">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D11" s="7">
+        <v>1.46</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-5.68</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C12" s="7">
         <v>-9.35</v>
       </c>
-      <c r="E11" s="8">
-        <v>-3.67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D12" s="7">
+        <v>-5.02</v>
+      </c>
+      <c r="E12" s="9">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C13" s="7">
         <v>6.06</v>
       </c>
-      <c r="E12" s="8">
-        <v>-3.39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="D13" s="7">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="E13" s="9">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-4.87</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C14" s="7">
         <v>-4.08</v>
       </c>
-      <c r="E13" s="7">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="D14" s="7">
+        <v>-4.05</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-8.390000000000001</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C15" s="7">
         <v>-9.880000000000001</v>
       </c>
-      <c r="E14" s="8">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="D15" s="7">
+        <v>-8.949999999999999</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-4.29</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C16" s="7">
         <v>-4.41</v>
       </c>
-      <c r="E15" s="8">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="D16" s="7">
+        <v>-2.4</v>
+      </c>
+      <c r="E16" s="9">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>-4.69</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C17" s="7">
         <v>-3.83</v>
       </c>
-      <c r="E16" s="7">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="D17" s="7">
+        <v>-2.79</v>
+      </c>
+      <c r="E17" s="9">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-20.2</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C18" s="7">
         <v>-22.14</v>
       </c>
-      <c r="E17" s="8">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="D18" s="7">
+        <v>-20.27</v>
+      </c>
+      <c r="E18" s="9">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>18.65</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C19" s="7">
         <v>15.85</v>
       </c>
-      <c r="E18" s="8">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="D19" s="7">
+        <v>18.07</v>
+      </c>
+      <c r="E19" s="9">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-16.85</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C20" s="7">
         <v>-16.65</v>
       </c>
-      <c r="E19" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="D20" s="7">
+        <v>-15.89</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-27.26</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C21" s="7">
         <v>-29.23</v>
       </c>
-      <c r="E20" s="8">
-        <v>-1.97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="D21" s="7">
+        <v>-28.16</v>
+      </c>
+      <c r="E21" s="9">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-14.84</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C22" s="7">
         <v>-15.8</v>
       </c>
-      <c r="E21" s="8">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="D22" s="7">
+        <v>-13.1</v>
+      </c>
+      <c r="E22" s="9">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>3638.3</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C23" s="7">
         <v>3647</v>
       </c>
-      <c r="E22" s="7">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="D23" s="7">
+        <v>3680</v>
+      </c>
+      <c r="E23" s="9">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>244.1</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C24" s="7">
         <v>237.5</v>
       </c>
-      <c r="E23" s="8">
-        <v>-6.6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="D24" s="7">
+        <v>241.1</v>
+      </c>
+      <c r="E24" s="9">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>3954.8</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C25" s="7">
         <v>3910.3</v>
       </c>
-      <c r="E24" s="8">
-        <v>-44.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="D25" s="7">
+        <v>4035.6</v>
+      </c>
+      <c r="E25" s="9">
+        <v>125.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="6">
-        <v>38.99</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C26" s="7">
         <v>40.06</v>
       </c>
-      <c r="E25" s="7">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="D26" s="7">
+        <v>44.06</v>
+      </c>
+      <c r="E26" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="6">
-        <v>26.96</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C27" s="7">
         <v>24.31</v>
       </c>
-      <c r="E26" s="8">
-        <v>-2.65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="D27" s="7">
+        <v>28.45</v>
+      </c>
+      <c r="E27" s="9">
+        <v>4.14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B28" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="6">
-        <v>72.15000000000001</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C28" s="7">
         <v>69.27</v>
       </c>
-      <c r="E27" s="8">
-        <v>-2.88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="D28" s="7">
+        <v>72.58</v>
+      </c>
+      <c r="E28" s="9">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>47.77</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C29" s="7">
         <v>8.619999999999999</v>
       </c>
-      <c r="E28" s="8">
-        <v>-39.15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="D29" s="7">
+        <v>-39.54</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-48.16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>-56.95</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C30" s="7">
         <v>-38.45</v>
       </c>
-      <c r="E29" s="7">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="D30" s="7">
+        <v>2.08</v>
+      </c>
+      <c r="E30" s="9">
+        <v>40.53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>209.6</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C31" s="7">
         <v>13.22</v>
       </c>
-      <c r="E30" s="8">
-        <v>-196.38</v>
+      <c r="D31" s="7">
+        <v>-17.74</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-30.96</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1908,60 +1939,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>68</v>
       </c>
+      <c r="G1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>49.72</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>44.5</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>48.4</v>
+      </c>
+      <c r="E2" s="12">
         <v>33.3</v>
       </c>
-      <c r="F2" s="11">
-        <v>-3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-3.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-1.2</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-1.7</v>
+      </c>
+      <c r="H2" s="12">
         <v>66</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2063,25 +2094,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.2554</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1657</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0171</v>
+      <c r="A2" s="15">
+        <v>0.2479</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1661</v>
+      </c>
+      <c r="C2" s="15">
+        <v>-0.0131</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,43 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>69.3 → 72.6</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>69.3</t>
-  </si>
-  <si>
-    <t>72.6</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -248,7 +212,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,20 +253,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -330,12 +287,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -411,23 +362,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -436,7 +385,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -935,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3680</v>
+        <v>3665.1</v>
       </c>
       <c r="D2">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -947,46 +896,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-15.89</v>
+        <v>-16.23</v>
       </c>
       <c r="H2">
-        <v>11.18</v>
+        <v>10.73</v>
       </c>
       <c r="I2">
-        <v>1.46</v>
+        <v>0.09</v>
       </c>
       <c r="J2">
-        <v>-6.36</v>
+        <v>-5.01</v>
       </c>
       <c r="K2">
-        <v>-2.79</v>
+        <v>-3.7</v>
       </c>
       <c r="L2">
-        <v>-4.05</v>
+        <v>-4.82</v>
       </c>
       <c r="M2">
-        <v>16.61</v>
+        <v>16.66</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P2">
-        <v>3652.64</v>
+        <v>3653.28</v>
       </c>
       <c r="Q2">
-        <v>3693.09</v>
+        <v>3682.54</v>
       </c>
       <c r="R2">
-        <v>3866.27</v>
+        <v>3858.15</v>
       </c>
       <c r="S2">
-        <v>3920.2</v>
+        <v>3918.03</v>
       </c>
       <c r="T2">
-        <v>-6.13</v>
+        <v>-6.46</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -1001,34 +950,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>44.06</v>
+        <v>42.68</v>
       </c>
       <c r="Z2">
-        <v>-61.03</v>
+        <v>-56.84</v>
       </c>
       <c r="AA2">
-        <v>-69.01000000000001</v>
+        <v>-66.56999999999999</v>
       </c>
       <c r="AB2">
-        <v>7.98</v>
+        <v>9.73</v>
       </c>
       <c r="AC2">
-        <v>92.39</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="AD2">
-        <v>88.56</v>
+        <v>90.86</v>
       </c>
       <c r="AE2">
-        <v>73.79000000000001</v>
+        <v>73.17</v>
       </c>
       <c r="AF2">
-        <v>-39.54</v>
+        <v>-22.7</v>
       </c>
       <c r="AG2">
-        <v>3827.12</v>
+        <v>3785.49</v>
       </c>
       <c r="AH2">
-        <v>3559.06</v>
+        <v>3579.58</v>
       </c>
       <c r="AI2">
         <v>3852.83</v>
@@ -1037,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>38.2</v>
+        <v>33.71</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1048,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>241.1</v>
+        <v>240.8</v>
       </c>
       <c r="D3">
-        <v>1.52</v>
+        <v>-0.12</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1060,43 +1009,43 @@
         <v>237.5</v>
       </c>
       <c r="G3">
-        <v>-28.16</v>
+        <v>-28.25</v>
       </c>
       <c r="H3">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="I3">
-        <v>-5.02</v>
+        <v>-4.82</v>
       </c>
       <c r="J3">
-        <v>-22.23</v>
+        <v>-14.61</v>
       </c>
       <c r="K3">
-        <v>-20.27</v>
+        <v>-22.88</v>
       </c>
       <c r="L3">
-        <v>-8.949999999999999</v>
+        <v>-9.17</v>
       </c>
       <c r="M3">
-        <v>24.79</v>
+        <v>25.05</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P3">
-        <v>244.26</v>
+        <v>241.82</v>
       </c>
       <c r="Q3">
-        <v>259.93</v>
+        <v>257.77</v>
       </c>
       <c r="R3">
-        <v>290.77</v>
+        <v>289.28</v>
       </c>
       <c r="S3">
-        <v>287.92</v>
+        <v>287.54</v>
       </c>
       <c r="T3">
         <v>-16.26</v>
@@ -1114,34 +1063,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>28.45</v>
+        <v>28.31</v>
       </c>
       <c r="Z3">
-        <v>-13.87</v>
+        <v>-13.8</v>
       </c>
       <c r="AA3">
-        <v>-12.88</v>
+        <v>-13.07</v>
       </c>
       <c r="AB3">
-        <v>-0.99</v>
+        <v>-0.73</v>
       </c>
       <c r="AC3">
-        <v>14.01</v>
+        <v>21.36</v>
       </c>
       <c r="AD3">
-        <v>15.19</v>
+        <v>14.53</v>
       </c>
       <c r="AE3">
-        <v>9.09</v>
+        <v>8.74</v>
       </c>
       <c r="AF3">
-        <v>2.08</v>
+        <v>-38.7</v>
       </c>
       <c r="AG3">
-        <v>283.76</v>
+        <v>280.21</v>
       </c>
       <c r="AH3">
-        <v>236.09</v>
+        <v>235.32</v>
       </c>
       <c r="AI3">
         <v>262.7</v>
@@ -1150,7 +1099,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>66.27</v>
+        <v>67.84999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1161,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>4035.6</v>
+        <v>4174.2</v>
       </c>
       <c r="D4">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1173,46 +1122,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-13.1</v>
+        <v>-10.11</v>
       </c>
       <c r="H4">
-        <v>32.69</v>
+        <v>37.25</v>
       </c>
       <c r="I4">
-        <v>8.640000000000001</v>
+        <v>15.59</v>
       </c>
       <c r="J4">
-        <v>24.89</v>
+        <v>30.07</v>
       </c>
       <c r="K4">
-        <v>18.07</v>
+        <v>19.33</v>
       </c>
       <c r="L4">
-        <v>-2.4</v>
+        <v>0.82</v>
       </c>
       <c r="M4">
-        <v>-1.31</v>
+        <v>-1.2</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P4">
-        <v>3901.66</v>
+        <v>4014.24</v>
       </c>
       <c r="Q4">
-        <v>3471.07</v>
+        <v>3519.47</v>
       </c>
       <c r="R4">
-        <v>3459.43</v>
+        <v>3470.82</v>
       </c>
       <c r="S4">
-        <v>3478.95</v>
+        <v>3478.55</v>
       </c>
       <c r="T4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1227,43 +1176,43 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>72.58</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="Z4">
-        <v>159.8</v>
+        <v>184.7</v>
       </c>
       <c r="AA4">
-        <v>81.23999999999999</v>
+        <v>101.93</v>
       </c>
       <c r="AB4">
-        <v>78.55</v>
+        <v>82.77</v>
       </c>
       <c r="AC4">
-        <v>90.37</v>
+        <v>92.83</v>
       </c>
       <c r="AD4">
-        <v>91.54000000000001</v>
+        <v>91.88</v>
       </c>
       <c r="AE4">
-        <v>156.29</v>
+        <v>159.05</v>
       </c>
       <c r="AF4">
-        <v>-17.74</v>
+        <v>-35.44</v>
       </c>
       <c r="AG4">
-        <v>4099.11</v>
+        <v>4207.86</v>
       </c>
       <c r="AH4">
-        <v>2843.02</v>
+        <v>2831.08</v>
       </c>
       <c r="AI4">
-        <v>3511.87</v>
+        <v>3615.41</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>60.06</v>
+        <v>63.09</v>
       </c>
     </row>
   </sheetData>
@@ -1404,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1424,502 +1373,447 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>63</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-6.36</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-5.01</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.35</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-22.23</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-14.61</v>
+      </c>
+      <c r="E8" s="6">
+        <v>7.62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>24.89</v>
+      </c>
+      <c r="D9" s="5">
+        <v>30.07</v>
+      </c>
+      <c r="E9" s="6">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-5.67</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-6.36</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1.46</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-22.11</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-22.23</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-5.02</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-4.82</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>18.72</v>
-      </c>
-      <c r="D10" s="7">
-        <v>24.89</v>
-      </c>
-      <c r="E10" s="9">
-        <v>6.17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="D12" s="5">
+        <v>15.59</v>
+      </c>
+      <c r="E12" s="6">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="7">
-        <v>0.41</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.46</v>
-      </c>
-      <c r="E11" s="9">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-4.05</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-4.82</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-9.35</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-5.02</v>
-      </c>
-      <c r="E12" s="9">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-8.949999999999999</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-9.17</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="7">
-        <v>6.06</v>
-      </c>
-      <c r="D13" s="7">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="E13" s="9">
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-2.4</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0.82</v>
+      </c>
+      <c r="E15" s="6">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-4.08</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-4.05</v>
-      </c>
-      <c r="E14" s="9">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-2.79</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-3.7</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-9.880000000000001</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-20.27</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-22.88</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-4.41</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-2.4</v>
-      </c>
-      <c r="E16" s="9">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>18.07</v>
+      </c>
+      <c r="D18" s="5">
+        <v>19.33</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-3.83</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-2.79</v>
-      </c>
-      <c r="E17" s="9">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-15.89</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-16.23</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-22.14</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-20.27</v>
-      </c>
-      <c r="E18" s="9">
-        <v>1.87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-28.16</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-28.25</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="7">
-        <v>15.85</v>
-      </c>
-      <c r="D19" s="7">
-        <v>18.07</v>
-      </c>
-      <c r="E19" s="9">
-        <v>2.22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-13.1</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-10.11</v>
+      </c>
+      <c r="E21" s="6">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-16.65</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-15.89</v>
-      </c>
-      <c r="E20" s="9">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>3680</v>
+      </c>
+      <c r="D22" s="5">
+        <v>3665.1</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-14.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-29.23</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-28.16</v>
-      </c>
-      <c r="E21" s="9">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>241.1</v>
+      </c>
+      <c r="D23" s="5">
+        <v>240.8</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-15.8</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-13.1</v>
-      </c>
-      <c r="E22" s="9">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>4035.6</v>
+      </c>
+      <c r="D24" s="5">
+        <v>4174.2</v>
+      </c>
+      <c r="E24" s="6">
+        <v>138.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="7">
-        <v>3647</v>
-      </c>
-      <c r="D23" s="7">
-        <v>3680</v>
-      </c>
-      <c r="E23" s="9">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>44.06</v>
+      </c>
+      <c r="D25" s="5">
+        <v>42.68</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="7">
-        <v>237.5</v>
-      </c>
-      <c r="D24" s="7">
-        <v>241.1</v>
-      </c>
-      <c r="E24" s="9">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>28.45</v>
+      </c>
+      <c r="D26" s="5">
+        <v>28.31</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="7">
-        <v>3910.3</v>
-      </c>
-      <c r="D25" s="7">
-        <v>4035.6</v>
-      </c>
-      <c r="E25" s="9">
-        <v>125.3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>72.58</v>
+      </c>
+      <c r="D27" s="5">
+        <v>75.70999999999999</v>
+      </c>
+      <c r="E27" s="6">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="7">
-        <v>40.06</v>
-      </c>
-      <c r="D26" s="7">
-        <v>44.06</v>
-      </c>
-      <c r="E26" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-39.54</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-22.7</v>
+      </c>
+      <c r="E28" s="6">
+        <v>16.84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="7">
-        <v>24.31</v>
-      </c>
-      <c r="D27" s="7">
-        <v>28.45</v>
-      </c>
-      <c r="E27" s="9">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>2.08</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-38.7</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-40.78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="7">
-        <v>69.27</v>
-      </c>
-      <c r="D28" s="7">
-        <v>72.58</v>
-      </c>
-      <c r="E28" s="9">
-        <v>3.31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="6" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="7">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-39.54</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-48.16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-38.45</v>
-      </c>
-      <c r="D30" s="7">
-        <v>2.08</v>
-      </c>
-      <c r="E30" s="9">
-        <v>40.53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="7">
-        <v>13.22</v>
-      </c>
-      <c r="D31" s="7">
+      <c r="C30" s="5">
         <v>-17.74</v>
       </c>
-      <c r="E31" s="8">
-        <v>-30.96</v>
+      <c r="D30" s="5">
+        <v>-35.44</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-17.7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1939,60 +1833,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="10" t="s">
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="10">
+        <v>49.72</v>
+      </c>
+      <c r="C2" s="11">
+        <v>3</v>
+      </c>
+      <c r="D2" s="10">
+        <v>48.9</v>
+      </c>
+      <c r="E2" s="10">
+        <v>33.3</v>
+      </c>
+      <c r="F2" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-2.4</v>
+      </c>
+      <c r="H2" s="10">
         <v>66</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="12">
-        <v>49.72</v>
-      </c>
-      <c r="C2" s="13">
-        <v>3</v>
-      </c>
-      <c r="D2" s="12">
-        <v>48.4</v>
-      </c>
-      <c r="E2" s="12">
-        <v>33.3</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-1.2</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-1.7</v>
-      </c>
-      <c r="H2" s="12">
-        <v>66</v>
-      </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2094,25 +1988,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="15">
-        <v>0.2479</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.1661</v>
-      </c>
-      <c r="C2" s="15">
-        <v>-0.0131</v>
+      <c r="A2" s="13">
+        <v>0.2505</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1666</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.012</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="76">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,7 +160,55 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 GOLDEN CROSS</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>42.7 → 56.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>42.7</t>
+  </si>
+  <si>
+    <t>56.2</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>28.3 → 34.8</t>
+  </si>
+  <si>
+    <t>28.3</t>
+  </si>
+  <si>
+    <t>34.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -362,14 +410,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -884,10 +933,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3665.1</v>
+        <v>3801.3</v>
       </c>
       <c r="D2">
-        <v>-0.4</v>
+        <v>3.72</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -896,46 +945,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-16.23</v>
+        <v>-13.12</v>
       </c>
       <c r="H2">
-        <v>10.73</v>
+        <v>14.84</v>
       </c>
       <c r="I2">
-        <v>0.09</v>
+        <v>4.55</v>
       </c>
       <c r="J2">
-        <v>-5.01</v>
+        <v>-1.93</v>
       </c>
       <c r="K2">
-        <v>-3.7</v>
+        <v>-0.8</v>
       </c>
       <c r="L2">
-        <v>-4.82</v>
+        <v>-2.05</v>
       </c>
       <c r="M2">
-        <v>16.66</v>
+        <v>17.13</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="P2">
-        <v>3653.28</v>
+        <v>3686.34</v>
       </c>
       <c r="Q2">
-        <v>3682.54</v>
+        <v>3684.28</v>
       </c>
       <c r="R2">
-        <v>3858.15</v>
+        <v>3853.04</v>
       </c>
       <c r="S2">
-        <v>3918.03</v>
+        <v>3916.45</v>
       </c>
       <c r="T2">
-        <v>-6.46</v>
+        <v>-2.94</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,34 +999,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>42.68</v>
+        <v>56.23</v>
       </c>
       <c r="Z2">
-        <v>-56.84</v>
+        <v>-42.05</v>
       </c>
       <c r="AA2">
-        <v>-66.56999999999999</v>
+        <v>-61.67</v>
       </c>
       <c r="AB2">
-        <v>9.73</v>
+        <v>19.62</v>
       </c>
       <c r="AC2">
-        <v>94.48999999999999</v>
+        <v>96.39</v>
       </c>
       <c r="AD2">
-        <v>90.86</v>
+        <v>94.42</v>
       </c>
       <c r="AE2">
-        <v>73.17</v>
+        <v>84.3</v>
       </c>
       <c r="AF2">
-        <v>-22.7</v>
+        <v>225.95</v>
       </c>
       <c r="AG2">
-        <v>3785.49</v>
+        <v>3794.17</v>
       </c>
       <c r="AH2">
-        <v>3579.58</v>
+        <v>3574.39</v>
       </c>
       <c r="AI2">
         <v>3852.83</v>
@@ -986,7 +1035,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>33.71</v>
+        <v>37.35</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +1046,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>240.8</v>
+        <v>246.5</v>
       </c>
       <c r="D3">
-        <v>-0.12</v>
+        <v>2.37</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1009,46 +1058,46 @@
         <v>237.5</v>
       </c>
       <c r="G3">
-        <v>-28.25</v>
+        <v>-26.55</v>
       </c>
       <c r="H3">
-        <v>1.39</v>
+        <v>3.79</v>
       </c>
       <c r="I3">
-        <v>-4.82</v>
+        <v>0.37</v>
       </c>
       <c r="J3">
-        <v>-14.61</v>
+        <v>-13.2</v>
       </c>
       <c r="K3">
-        <v>-22.88</v>
+        <v>-20.74</v>
       </c>
       <c r="L3">
-        <v>-9.17</v>
+        <v>-6.71</v>
       </c>
       <c r="M3">
-        <v>25.05</v>
+        <v>26.45</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P3">
-        <v>241.82</v>
+        <v>242</v>
       </c>
       <c r="Q3">
-        <v>257.77</v>
+        <v>256.05</v>
       </c>
       <c r="R3">
-        <v>289.28</v>
+        <v>288.09</v>
       </c>
       <c r="S3">
-        <v>287.54</v>
+        <v>287.22</v>
       </c>
       <c r="T3">
-        <v>-16.26</v>
+        <v>-14.18</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,34 +1112,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>28.31</v>
+        <v>34.83</v>
       </c>
       <c r="Z3">
-        <v>-13.8</v>
+        <v>-13.13</v>
       </c>
       <c r="AA3">
-        <v>-13.07</v>
+        <v>-13.08</v>
       </c>
       <c r="AB3">
-        <v>-0.73</v>
+        <v>-0.05</v>
       </c>
       <c r="AC3">
-        <v>21.36</v>
+        <v>48.95</v>
       </c>
       <c r="AD3">
-        <v>14.53</v>
+        <v>28.11</v>
       </c>
       <c r="AE3">
-        <v>8.74</v>
+        <v>8.92</v>
       </c>
       <c r="AF3">
-        <v>-38.7</v>
+        <v>-35.36</v>
       </c>
       <c r="AG3">
-        <v>280.21</v>
+        <v>276.19</v>
       </c>
       <c r="AH3">
-        <v>235.32</v>
+        <v>235.91</v>
       </c>
       <c r="AI3">
         <v>262.7</v>
@@ -1099,7 +1148,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>67.84999999999999</v>
+        <v>64.86</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1159,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>4174.2</v>
+        <v>4088.1</v>
       </c>
       <c r="D4">
-        <v>3.43</v>
+        <v>-2.06</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1122,88 +1171,88 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-10.11</v>
+        <v>-11.97</v>
       </c>
       <c r="H4">
-        <v>37.25</v>
+        <v>34.42</v>
       </c>
       <c r="I4">
-        <v>15.59</v>
+        <v>2.3</v>
       </c>
       <c r="J4">
-        <v>30.07</v>
+        <v>27.51</v>
       </c>
       <c r="K4">
-        <v>19.33</v>
+        <v>13.58</v>
       </c>
       <c r="L4">
-        <v>0.82</v>
+        <v>-1.23</v>
       </c>
       <c r="M4">
-        <v>-1.2</v>
+        <v>-1.47</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P4">
-        <v>4014.24</v>
+        <v>4032.6</v>
       </c>
       <c r="Q4">
-        <v>3519.47</v>
+        <v>3563.3</v>
       </c>
       <c r="R4">
-        <v>3470.82</v>
+        <v>3483.05</v>
       </c>
       <c r="S4">
-        <v>3478.55</v>
+        <v>3477.27</v>
       </c>
       <c r="T4">
-        <v>20</v>
+        <v>17.57</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
       </c>
       <c r="V4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="X4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y4">
-        <v>75.70999999999999</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="Z4">
-        <v>184.7</v>
+        <v>195.24</v>
       </c>
       <c r="AA4">
-        <v>101.93</v>
+        <v>120.59</v>
       </c>
       <c r="AB4">
-        <v>82.77</v>
+        <v>74.64</v>
       </c>
       <c r="AC4">
-        <v>92.83</v>
+        <v>93.14</v>
       </c>
       <c r="AD4">
-        <v>91.88</v>
+        <v>92.11</v>
       </c>
       <c r="AE4">
-        <v>159.05</v>
+        <v>158.39</v>
       </c>
       <c r="AF4">
-        <v>-35.44</v>
+        <v>-63.64</v>
       </c>
       <c r="AG4">
-        <v>4207.86</v>
+        <v>4280.17</v>
       </c>
       <c r="AH4">
-        <v>2831.08</v>
+        <v>2846.42</v>
       </c>
       <c r="AI4">
         <v>3615.41</v>
@@ -1212,7 +1261,7 @@
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>63.09</v>
+        <v>65.70999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1353,7 +1402,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1373,447 +1422,542 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-6.36</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-5.01</v>
-      </c>
-      <c r="E7" s="6">
-        <v>1.35</v>
+        <v>41</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-22.23</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-14.61</v>
-      </c>
-      <c r="E8" s="6">
-        <v>7.62</v>
-      </c>
+      <c r="A8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-5.01</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-1.93</v>
+      </c>
+      <c r="E10" s="7">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-14.61</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-13.2</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>24.89</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C12" s="6">
         <v>30.07</v>
       </c>
-      <c r="E9" s="6">
-        <v>5.18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D12" s="6">
+        <v>27.51</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-2.56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>1.46</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C13" s="6">
         <v>0.09</v>
       </c>
-      <c r="E10" s="7">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D13" s="6">
+        <v>4.55</v>
+      </c>
+      <c r="E13" s="7">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-5.02</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C14" s="6">
         <v>-4.82</v>
       </c>
-      <c r="E11" s="6">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D14" s="6">
+        <v>0.37</v>
+      </c>
+      <c r="E14" s="7">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C15" s="6">
         <v>15.59</v>
       </c>
-      <c r="E12" s="6">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D15" s="6">
+        <v>2.3</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-13.29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-4.05</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C16" s="6">
         <v>-4.82</v>
       </c>
-      <c r="E13" s="7">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-2.05</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C17" s="6">
         <v>-9.17</v>
       </c>
-      <c r="E14" s="7">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D17" s="6">
+        <v>-6.71</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-2.4</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C18" s="6">
         <v>0.82</v>
       </c>
-      <c r="E15" s="6">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D18" s="6">
+        <v>-1.23</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-2.05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-2.79</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C19" s="6">
         <v>-3.7</v>
       </c>
-      <c r="E16" s="7">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D19" s="6">
+        <v>-0.8</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-20.27</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C20" s="6">
         <v>-22.88</v>
       </c>
-      <c r="E17" s="7">
-        <v>-2.61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D20" s="6">
+        <v>-20.74</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>18.07</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C21" s="6">
         <v>19.33</v>
       </c>
-      <c r="E18" s="6">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D21" s="6">
+        <v>13.58</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-5.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-15.89</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C22" s="6">
         <v>-16.23</v>
       </c>
-      <c r="E19" s="7">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D22" s="6">
+        <v>-13.12</v>
+      </c>
+      <c r="E22" s="7">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-28.16</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C23" s="6">
         <v>-28.25</v>
       </c>
-      <c r="E20" s="7">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D23" s="6">
+        <v>-26.55</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-13.1</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C24" s="6">
         <v>-10.11</v>
       </c>
-      <c r="E21" s="6">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D24" s="6">
+        <v>-11.97</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>3680</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C25" s="6">
         <v>3665.1</v>
       </c>
-      <c r="E22" s="7">
-        <v>-14.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D25" s="6">
+        <v>3801.3</v>
+      </c>
+      <c r="E25" s="7">
+        <v>136.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>241.1</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C26" s="6">
         <v>240.8</v>
       </c>
-      <c r="E23" s="7">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D26" s="6">
+        <v>246.5</v>
+      </c>
+      <c r="E26" s="7">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>4035.6</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C27" s="6">
         <v>4174.2</v>
       </c>
-      <c r="E24" s="6">
-        <v>138.6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D27" s="6">
+        <v>4088.1</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-86.09999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="5">
-        <v>44.06</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C28" s="6">
         <v>42.68</v>
       </c>
-      <c r="E25" s="7">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D28" s="6">
+        <v>56.23</v>
+      </c>
+      <c r="E28" s="7">
+        <v>13.55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="5">
-        <v>28.45</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C29" s="6">
         <v>28.31</v>
       </c>
-      <c r="E26" s="7">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D29" s="6">
+        <v>34.83</v>
+      </c>
+      <c r="E29" s="7">
+        <v>6.52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="5">
-        <v>72.58</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C30" s="6">
         <v>75.70999999999999</v>
       </c>
-      <c r="E27" s="6">
-        <v>3.13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D30" s="6">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-5.36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>-39.54</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C31" s="6">
         <v>-22.7</v>
       </c>
-      <c r="E28" s="6">
-        <v>16.84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D31" s="6">
+        <v>225.95</v>
+      </c>
+      <c r="E31" s="7">
+        <v>248.65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5">
-        <v>2.08</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C32" s="6">
         <v>-38.7</v>
       </c>
-      <c r="E29" s="7">
-        <v>-40.78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="D32" s="6">
+        <v>-35.36</v>
+      </c>
+      <c r="E32" s="7">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B33" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>-17.74</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C33" s="6">
         <v>-35.44</v>
       </c>
-      <c r="E30" s="7">
-        <v>-17.7</v>
+      <c r="D33" s="6">
+        <v>-63.64</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-28.2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1833,61 +1977,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
+      <c r="B1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>49.72</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>48.9</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>53.8</v>
+      </c>
+      <c r="E2" s="11">
         <v>33.3</v>
       </c>
-      <c r="F2" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-2.4</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>4.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-2.7</v>
+      </c>
+      <c r="H2" s="11">
         <v>66</v>
       </c>
-      <c r="I2" s="10">
-        <v>0</v>
+      <c r="I2" s="11">
+        <v>33.3</v>
       </c>
     </row>
   </sheetData>
@@ -1988,25 +2132,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.2505</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1666</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.012</v>
+      <c r="A2" s="14">
+        <v>0.2645</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1713</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0147</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="67">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,37 +178,10 @@
     <t>50 DMA &gt; 200 DMA</t>
   </si>
   <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 GOLDEN CROSS</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>42.7 → 56.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>42.7</t>
-  </si>
-  <si>
-    <t>56.2</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>28.3 → 34.8</t>
-  </si>
-  <si>
-    <t>28.3</t>
-  </si>
-  <si>
-    <t>34.8</t>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 DEATH CROSS</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -294,14 +267,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -334,13 +307,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -420,8 +393,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -933,10 +906,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3801.3</v>
+        <v>3837.1</v>
       </c>
       <c r="D2">
-        <v>3.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -945,25 +918,25 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-13.12</v>
+        <v>-12.3</v>
       </c>
       <c r="H2">
-        <v>14.84</v>
+        <v>15.92</v>
       </c>
       <c r="I2">
-        <v>4.55</v>
+        <v>5.46</v>
       </c>
       <c r="J2">
-        <v>-1.93</v>
+        <v>1.88</v>
       </c>
       <c r="K2">
-        <v>-0.8</v>
+        <v>-2.4</v>
       </c>
       <c r="L2">
-        <v>-2.05</v>
+        <v>-0.78</v>
       </c>
       <c r="M2">
-        <v>17.13</v>
+        <v>17.98</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -972,19 +945,19 @@
         <v>69</v>
       </c>
       <c r="P2">
-        <v>3686.34</v>
+        <v>3726.1</v>
       </c>
       <c r="Q2">
-        <v>3684.28</v>
+        <v>3688.68</v>
       </c>
       <c r="R2">
-        <v>3853.04</v>
+        <v>3848.05</v>
       </c>
       <c r="S2">
-        <v>3916.45</v>
+        <v>3915.69</v>
       </c>
       <c r="T2">
-        <v>-2.94</v>
+        <v>-2.01</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -999,34 +972,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>56.23</v>
+        <v>58.98</v>
       </c>
       <c r="Z2">
-        <v>-42.05</v>
+        <v>-27.13</v>
       </c>
       <c r="AA2">
-        <v>-61.67</v>
+        <v>-54.76</v>
       </c>
       <c r="AB2">
-        <v>19.62</v>
+        <v>27.63</v>
       </c>
       <c r="AC2">
         <v>96.39</v>
       </c>
       <c r="AD2">
-        <v>94.42</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="AE2">
-        <v>84.3</v>
+        <v>83.87</v>
       </c>
       <c r="AF2">
-        <v>225.95</v>
+        <v>-17.62</v>
       </c>
       <c r="AG2">
-        <v>3794.17</v>
+        <v>3815.28</v>
       </c>
       <c r="AH2">
-        <v>3574.39</v>
+        <v>3562.08</v>
       </c>
       <c r="AI2">
         <v>3852.83</v>
@@ -1035,7 +1008,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>37.35</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1046,10 +1019,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>246.5</v>
+        <v>251.05</v>
       </c>
       <c r="D3">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1058,88 +1031,88 @@
         <v>237.5</v>
       </c>
       <c r="G3">
-        <v>-26.55</v>
+        <v>-25.19</v>
       </c>
       <c r="H3">
-        <v>3.79</v>
+        <v>5.71</v>
       </c>
       <c r="I3">
-        <v>0.37</v>
+        <v>2.85</v>
       </c>
       <c r="J3">
-        <v>-13.2</v>
+        <v>-10.61</v>
       </c>
       <c r="K3">
-        <v>-20.74</v>
+        <v>-18.79</v>
       </c>
       <c r="L3">
-        <v>-6.71</v>
+        <v>-5.01</v>
       </c>
       <c r="M3">
-        <v>26.45</v>
+        <v>26.65</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="P3">
-        <v>242</v>
+        <v>243.39</v>
       </c>
       <c r="Q3">
-        <v>256.05</v>
+        <v>255.05</v>
       </c>
       <c r="R3">
-        <v>288.09</v>
+        <v>286.81</v>
       </c>
       <c r="S3">
-        <v>287.22</v>
+        <v>286.96</v>
       </c>
       <c r="T3">
-        <v>-14.18</v>
+        <v>-12.51</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
       </c>
       <c r="V3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W3" t="s">
         <v>41</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>34.83</v>
+        <v>39.55</v>
       </c>
       <c r="Z3">
-        <v>-13.13</v>
+        <v>-12.09</v>
       </c>
       <c r="AA3">
-        <v>-13.08</v>
+        <v>-12.88</v>
       </c>
       <c r="AB3">
-        <v>-0.05</v>
+        <v>0.79</v>
       </c>
       <c r="AC3">
-        <v>48.95</v>
+        <v>71.42</v>
       </c>
       <c r="AD3">
-        <v>28.11</v>
+        <v>47.24</v>
       </c>
       <c r="AE3">
-        <v>8.92</v>
+        <v>8.82</v>
       </c>
       <c r="AF3">
-        <v>-35.36</v>
+        <v>-3.93</v>
       </c>
       <c r="AG3">
-        <v>276.19</v>
+        <v>274</v>
       </c>
       <c r="AH3">
-        <v>235.91</v>
+        <v>236.09</v>
       </c>
       <c r="AI3">
         <v>262.7</v>
@@ -1148,7 +1121,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>64.86</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1159,10 +1132,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>4088.1</v>
+        <v>4182.6</v>
       </c>
       <c r="D4">
-        <v>-2.06</v>
+        <v>2.31</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1171,46 +1144,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-11.97</v>
+        <v>-9.93</v>
       </c>
       <c r="H4">
-        <v>34.42</v>
+        <v>37.53</v>
       </c>
       <c r="I4">
-        <v>2.3</v>
+        <v>5.76</v>
       </c>
       <c r="J4">
-        <v>27.51</v>
+        <v>30.23</v>
       </c>
       <c r="K4">
-        <v>13.58</v>
+        <v>16.67</v>
       </c>
       <c r="L4">
-        <v>-1.23</v>
+        <v>1.81</v>
       </c>
       <c r="M4">
-        <v>-1.47</v>
+        <v>-1.28</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P4">
-        <v>4032.6</v>
+        <v>4078.16</v>
       </c>
       <c r="Q4">
-        <v>3563.3</v>
+        <v>3618.35</v>
       </c>
       <c r="R4">
-        <v>3483.05</v>
+        <v>3497.16</v>
       </c>
       <c r="S4">
-        <v>3477.27</v>
+        <v>3476.32</v>
       </c>
       <c r="T4">
-        <v>17.57</v>
+        <v>20.32</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1225,43 +1198,43 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>70.34999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="Z4">
-        <v>195.24</v>
+        <v>208.81</v>
       </c>
       <c r="AA4">
-        <v>120.59</v>
+        <v>138.24</v>
       </c>
       <c r="AB4">
-        <v>74.64</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="AC4">
-        <v>93.14</v>
+        <v>91.61</v>
       </c>
       <c r="AD4">
-        <v>92.11</v>
+        <v>92.53</v>
       </c>
       <c r="AE4">
-        <v>158.39</v>
+        <v>156.7</v>
       </c>
       <c r="AF4">
-        <v>-63.64</v>
+        <v>-52.05</v>
       </c>
       <c r="AG4">
-        <v>4280.17</v>
+        <v>4348.44</v>
       </c>
       <c r="AH4">
-        <v>2846.42</v>
+        <v>2888.25</v>
       </c>
       <c r="AI4">
-        <v>3615.41</v>
+        <v>3669.85</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>65.70999999999999</v>
+        <v>68.23</v>
       </c>
     </row>
   </sheetData>
@@ -1402,7 +1375,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1442,7 +1415,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>51</v>
@@ -1454,96 +1427,87 @@
         <v>53</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-1.93</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1.88</v>
+      </c>
+      <c r="E7" s="7">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-13.2</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-10.61</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>67</v>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>27.51</v>
+      </c>
+      <c r="D9" s="6">
+        <v>30.23</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2.72</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1551,16 +1515,16 @@
         <v>37</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>-5.01</v>
+        <v>4.55</v>
       </c>
       <c r="D10" s="6">
-        <v>-1.93</v>
+        <v>5.46</v>
       </c>
       <c r="E10" s="7">
-        <v>3.08</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1568,16 +1532,16 @@
         <v>38</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>-14.61</v>
+        <v>0.37</v>
       </c>
       <c r="D11" s="6">
-        <v>-13.2</v>
+        <v>2.85</v>
       </c>
       <c r="E11" s="7">
-        <v>1.41</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1585,16 +1549,16 @@
         <v>39</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>30.07</v>
+        <v>2.3</v>
       </c>
       <c r="D12" s="6">
-        <v>27.51</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-2.56</v>
+        <v>5.76</v>
+      </c>
+      <c r="E12" s="7">
+        <v>3.46</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1602,16 +1566,16 @@
         <v>37</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>0.09</v>
+        <v>-2.05</v>
       </c>
       <c r="D13" s="6">
-        <v>4.55</v>
+        <v>-0.78</v>
       </c>
       <c r="E13" s="7">
-        <v>4.46</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1619,16 +1583,16 @@
         <v>38</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>-4.82</v>
+        <v>-6.71</v>
       </c>
       <c r="D14" s="6">
-        <v>0.37</v>
+        <v>-5.01</v>
       </c>
       <c r="E14" s="7">
-        <v>5.19</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1636,16 +1600,16 @@
         <v>39</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>15.59</v>
+        <v>-1.23</v>
       </c>
       <c r="D15" s="6">
-        <v>2.3</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-13.29</v>
+        <v>1.81</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3.04</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1653,16 +1617,16 @@
         <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-4.82</v>
+        <v>-0.8</v>
       </c>
       <c r="D16" s="6">
-        <v>-2.05</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2.77</v>
+        <v>-2.4</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1670,16 +1634,16 @@
         <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-9.17</v>
+        <v>-20.74</v>
       </c>
       <c r="D17" s="6">
-        <v>-6.71</v>
+        <v>-18.79</v>
       </c>
       <c r="E17" s="7">
-        <v>2.46</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1687,16 +1651,16 @@
         <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>0.82</v>
+        <v>13.58</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.23</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-2.05</v>
+        <v>16.67</v>
+      </c>
+      <c r="E18" s="7">
+        <v>3.09</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1704,16 +1668,16 @@
         <v>37</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>-3.7</v>
+        <v>-13.12</v>
       </c>
       <c r="D19" s="6">
-        <v>-0.8</v>
+        <v>-12.3</v>
       </c>
       <c r="E19" s="7">
-        <v>2.9</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1721,16 +1685,16 @@
         <v>38</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-22.88</v>
+        <v>-26.55</v>
       </c>
       <c r="D20" s="6">
-        <v>-20.74</v>
+        <v>-25.19</v>
       </c>
       <c r="E20" s="7">
-        <v>2.14</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1738,16 +1702,16 @@
         <v>39</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>19.33</v>
+        <v>-11.97</v>
       </c>
       <c r="D21" s="6">
-        <v>13.58</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-5.75</v>
+        <v>-9.93</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2.04</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1755,16 +1719,16 @@
         <v>37</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>-16.23</v>
+        <v>3801.3</v>
       </c>
       <c r="D22" s="6">
-        <v>-13.12</v>
+        <v>3837.1</v>
       </c>
       <c r="E22" s="7">
-        <v>3.11</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1772,16 +1736,16 @@
         <v>38</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>-28.25</v>
+        <v>246.5</v>
       </c>
       <c r="D23" s="6">
-        <v>-26.55</v>
+        <v>251.05</v>
       </c>
       <c r="E23" s="7">
-        <v>1.7</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1789,16 +1753,16 @@
         <v>39</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>-10.11</v>
+        <v>4088.1</v>
       </c>
       <c r="D24" s="6">
-        <v>-11.97</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.86</v>
+        <v>4182.6</v>
+      </c>
+      <c r="E24" s="7">
+        <v>94.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1806,16 +1770,16 @@
         <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C25" s="6">
-        <v>3665.1</v>
+        <v>56.23</v>
       </c>
       <c r="D25" s="6">
-        <v>3801.3</v>
+        <v>58.98</v>
       </c>
       <c r="E25" s="7">
-        <v>136.2</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1823,16 +1787,16 @@
         <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>240.8</v>
+        <v>34.83</v>
       </c>
       <c r="D26" s="6">
-        <v>246.5</v>
+        <v>39.55</v>
       </c>
       <c r="E26" s="7">
-        <v>5.7</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1840,16 +1804,16 @@
         <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>4174.2</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="D27" s="6">
-        <v>4088.1</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-86.09999999999999</v>
+        <v>72.64</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.29</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1857,16 +1821,16 @@
         <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C28" s="6">
-        <v>42.68</v>
+        <v>225.95</v>
       </c>
       <c r="D28" s="6">
-        <v>56.23</v>
-      </c>
-      <c r="E28" s="7">
-        <v>13.55</v>
+        <v>-17.62</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-243.57</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1874,16 +1838,16 @@
         <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>28.31</v>
+        <v>-35.36</v>
       </c>
       <c r="D29" s="6">
-        <v>34.83</v>
+        <v>-3.93</v>
       </c>
       <c r="E29" s="7">
-        <v>6.52</v>
+        <v>31.43</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1891,73 +1855,22 @@
         <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>75.70999999999999</v>
+        <v>-63.64</v>
       </c>
       <c r="D30" s="6">
-        <v>70.34999999999999</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-5.36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-22.7</v>
-      </c>
-      <c r="D31" s="6">
-        <v>225.95</v>
-      </c>
-      <c r="E31" s="7">
-        <v>248.65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-38.7</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-35.36</v>
-      </c>
-      <c r="E32" s="7">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-35.44</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-63.64</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-28.2</v>
+        <v>-52.05</v>
+      </c>
+      <c r="E30" s="7">
+        <v>11.59</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1981,28 +1894,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2016,16 +1929,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>53.8</v>
+        <v>57.1</v>
       </c>
       <c r="E2" s="11">
         <v>33.3</v>
       </c>
       <c r="F2" s="11">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="G2" s="11">
-        <v>-2.7</v>
+        <v>-1.5</v>
       </c>
       <c r="H2" s="11">
         <v>66</v>
@@ -2144,13 +2057,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.2645</v>
+        <v>0.2665</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1713</v>
+        <v>0.1798</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0147</v>
+        <v>-0.0128</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -151,37 +151,16 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 DEATH CROSS</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -267,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -307,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -383,18 +362,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -906,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3837.1</v>
+        <v>3871.7</v>
       </c>
       <c r="D2">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -918,46 +896,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-12.3</v>
+        <v>-11.51</v>
       </c>
       <c r="H2">
-        <v>15.92</v>
+        <v>16.97</v>
       </c>
       <c r="I2">
-        <v>5.46</v>
+        <v>6.16</v>
       </c>
       <c r="J2">
-        <v>1.88</v>
+        <v>3.27</v>
       </c>
       <c r="K2">
-        <v>-2.4</v>
+        <v>-1.68</v>
       </c>
       <c r="L2">
-        <v>-0.78</v>
+        <v>-0.36</v>
       </c>
       <c r="M2">
-        <v>17.98</v>
+        <v>17.83</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P2">
-        <v>3726.1</v>
+        <v>3771.04</v>
       </c>
       <c r="Q2">
-        <v>3688.68</v>
+        <v>3694.27</v>
       </c>
       <c r="R2">
-        <v>3848.05</v>
+        <v>3844.2</v>
       </c>
       <c r="S2">
-        <v>3915.69</v>
+        <v>3915.11</v>
       </c>
       <c r="T2">
-        <v>-2.01</v>
+        <v>-1.11</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -972,43 +950,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>58.98</v>
+        <v>61.49</v>
       </c>
       <c r="Z2">
-        <v>-27.13</v>
+        <v>-12.37</v>
       </c>
       <c r="AA2">
-        <v>-54.76</v>
+        <v>-46.28</v>
       </c>
       <c r="AB2">
-        <v>27.63</v>
+        <v>33.92</v>
       </c>
       <c r="AC2">
-        <v>96.39</v>
+        <v>100</v>
       </c>
       <c r="AD2">
-        <v>95.76000000000001</v>
+        <v>97.59</v>
       </c>
       <c r="AE2">
-        <v>83.87</v>
+        <v>82.63</v>
       </c>
       <c r="AF2">
-        <v>-17.62</v>
+        <v>-17.99</v>
       </c>
       <c r="AG2">
-        <v>3815.28</v>
+        <v>3842.17</v>
       </c>
       <c r="AH2">
-        <v>3562.08</v>
+        <v>3546.36</v>
       </c>
       <c r="AI2">
-        <v>3852.83</v>
+        <v>3591.55</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>40.16</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1019,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>251.05</v>
+        <v>244.4</v>
       </c>
       <c r="D3">
-        <v>1.85</v>
+        <v>-2.65</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1031,46 +1009,46 @@
         <v>237.5</v>
       </c>
       <c r="G3">
-        <v>-25.19</v>
+        <v>-27.18</v>
       </c>
       <c r="H3">
-        <v>5.71</v>
+        <v>2.91</v>
       </c>
       <c r="I3">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="J3">
-        <v>-10.61</v>
+        <v>-9.83</v>
       </c>
       <c r="K3">
-        <v>-18.79</v>
+        <v>-20.2</v>
       </c>
       <c r="L3">
-        <v>-5.01</v>
+        <v>-7.57</v>
       </c>
       <c r="M3">
-        <v>26.65</v>
+        <v>25.59</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P3">
-        <v>243.39</v>
+        <v>244.77</v>
       </c>
       <c r="Q3">
-        <v>255.05</v>
+        <v>254.02</v>
       </c>
       <c r="R3">
-        <v>286.81</v>
+        <v>285.19</v>
       </c>
       <c r="S3">
-        <v>286.96</v>
+        <v>286.7</v>
       </c>
       <c r="T3">
-        <v>-12.51</v>
+        <v>-14.75</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1085,43 +1063,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>39.55</v>
+        <v>35.5</v>
       </c>
       <c r="Z3">
-        <v>-12.09</v>
+        <v>-11.67</v>
       </c>
       <c r="AA3">
-        <v>-12.88</v>
+        <v>-12.64</v>
       </c>
       <c r="AB3">
-        <v>0.79</v>
+        <v>0.97</v>
       </c>
       <c r="AC3">
-        <v>71.42</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AD3">
-        <v>47.24</v>
+        <v>68.59</v>
       </c>
       <c r="AE3">
-        <v>8.82</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AF3">
-        <v>-3.93</v>
+        <v>-42.92</v>
       </c>
       <c r="AG3">
-        <v>274</v>
+        <v>272.94</v>
       </c>
       <c r="AH3">
-        <v>236.09</v>
+        <v>235.1</v>
       </c>
       <c r="AI3">
         <v>262.7</v>
       </c>
       <c r="AJ3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AK3">
-        <v>58.75</v>
+        <v>54.62</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1132,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>4182.6</v>
+        <v>4280.2</v>
       </c>
       <c r="D4">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1144,46 +1122,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-9.93</v>
+        <v>-7.83</v>
       </c>
       <c r="H4">
-        <v>37.53</v>
+        <v>40.74</v>
       </c>
       <c r="I4">
-        <v>5.76</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="J4">
-        <v>30.23</v>
+        <v>38.9</v>
       </c>
       <c r="K4">
-        <v>16.67</v>
+        <v>20.26</v>
       </c>
       <c r="L4">
-        <v>1.81</v>
+        <v>3.2</v>
       </c>
       <c r="M4">
-        <v>-1.28</v>
+        <v>-1.56</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="P4">
-        <v>4078.16</v>
+        <v>4152.14</v>
       </c>
       <c r="Q4">
-        <v>3618.35</v>
+        <v>3670.93</v>
       </c>
       <c r="R4">
-        <v>3497.16</v>
+        <v>3512.57</v>
       </c>
       <c r="S4">
-        <v>3476.32</v>
+        <v>3476.19</v>
       </c>
       <c r="T4">
-        <v>20.32</v>
+        <v>23.13</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1198,43 +1176,43 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>72.64</v>
+        <v>74.8</v>
       </c>
       <c r="Z4">
-        <v>208.81</v>
+        <v>224.85</v>
       </c>
       <c r="AA4">
-        <v>138.24</v>
+        <v>155.56</v>
       </c>
       <c r="AB4">
-        <v>70.56999999999999</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="AC4">
-        <v>91.61</v>
+        <v>90.42</v>
       </c>
       <c r="AD4">
-        <v>92.53</v>
+        <v>91.72</v>
       </c>
       <c r="AE4">
-        <v>156.7</v>
+        <v>154.61</v>
       </c>
       <c r="AF4">
-        <v>-52.05</v>
+        <v>-57.49</v>
       </c>
       <c r="AG4">
-        <v>4348.44</v>
+        <v>4433.58</v>
       </c>
       <c r="AH4">
-        <v>2888.25</v>
+        <v>2908.27</v>
       </c>
       <c r="AI4">
-        <v>3669.85</v>
+        <v>3769.88</v>
       </c>
       <c r="AJ4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AK4">
-        <v>68.23</v>
+        <v>70.76000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1338,27 +1316,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U4">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="16" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V4">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="18" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W4">
-    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y4">
@@ -1395,47 +1373,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1443,428 +1386,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>58</v>
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-1.93</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>1.88</v>
       </c>
-      <c r="E7" s="7">
-        <v>3.81</v>
+      <c r="D7" s="5">
+        <v>3.27</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.39</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-13.2</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-10.61</v>
       </c>
-      <c r="E8" s="7">
-        <v>2.59</v>
+      <c r="D8" s="5">
+        <v>-9.83</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.78</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>27.51</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>30.23</v>
       </c>
-      <c r="E9" s="7">
-        <v>2.72</v>
+      <c r="D9" s="5">
+        <v>38.9</v>
+      </c>
+      <c r="E9" s="6">
+        <v>8.67</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>4.55</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>5.46</v>
       </c>
-      <c r="E10" s="7">
-        <v>0.91</v>
+      <c r="D10" s="5">
+        <v>6.16</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.7</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>0.37</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>2.85</v>
       </c>
-      <c r="E11" s="7">
-        <v>2.48</v>
+      <c r="D11" s="5">
+        <v>2.91</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.06</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>2.3</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>5.76</v>
       </c>
-      <c r="E12" s="7">
-        <v>3.46</v>
+      <c r="D12" s="5">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="E12" s="6">
+        <v>3.7</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-2.05</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-0.78</v>
       </c>
-      <c r="E13" s="7">
-        <v>1.27</v>
+      <c r="D13" s="5">
+        <v>-0.36</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.42</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-6.71</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-5.01</v>
       </c>
+      <c r="D14" s="5">
+        <v>-7.57</v>
+      </c>
       <c r="E14" s="7">
-        <v>1.7</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-1.23</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>1.81</v>
       </c>
-      <c r="E15" s="7">
-        <v>3.04</v>
+      <c r="D15" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1.39</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>-0.8</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-2.4</v>
       </c>
-      <c r="E16" s="8">
-        <v>-1.6</v>
+      <c r="D16" s="5">
+        <v>-1.68</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.72</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-20.74</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-18.79</v>
       </c>
+      <c r="D17" s="5">
+        <v>-20.2</v>
+      </c>
       <c r="E17" s="7">
-        <v>1.95</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>13.58</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>16.67</v>
       </c>
-      <c r="E18" s="7">
-        <v>3.09</v>
+      <c r="D18" s="5">
+        <v>20.26</v>
+      </c>
+      <c r="E18" s="6">
+        <v>3.59</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-13.12</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-12.3</v>
       </c>
-      <c r="E19" s="7">
-        <v>0.82</v>
+      <c r="D19" s="5">
+        <v>-11.51</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.79</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-26.55</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-25.19</v>
       </c>
+      <c r="D20" s="5">
+        <v>-27.18</v>
+      </c>
       <c r="E20" s="7">
-        <v>1.36</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-11.97</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>-9.93</v>
       </c>
-      <c r="E21" s="7">
-        <v>2.04</v>
+      <c r="D21" s="5">
+        <v>-7.83</v>
+      </c>
+      <c r="E21" s="6">
+        <v>2.1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>3801.3</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>3837.1</v>
       </c>
-      <c r="E22" s="7">
-        <v>35.8</v>
+      <c r="D22" s="5">
+        <v>3871.7</v>
+      </c>
+      <c r="E22" s="6">
+        <v>34.6</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>246.5</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>251.05</v>
       </c>
+      <c r="D23" s="5">
+        <v>244.4</v>
+      </c>
       <c r="E23" s="7">
-        <v>4.55</v>
+        <v>-6.65</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>4088.1</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>4182.6</v>
       </c>
-      <c r="E24" s="7">
-        <v>94.5</v>
+      <c r="D24" s="5">
+        <v>4280.2</v>
+      </c>
+      <c r="E24" s="6">
+        <v>97.59999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="6">
-        <v>56.23</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="5">
         <v>58.98</v>
       </c>
-      <c r="E25" s="7">
-        <v>2.75</v>
+      <c r="D25" s="5">
+        <v>61.49</v>
+      </c>
+      <c r="E25" s="6">
+        <v>2.51</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="6">
-        <v>34.83</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="5">
         <v>39.55</v>
       </c>
+      <c r="D26" s="5">
+        <v>35.5</v>
+      </c>
       <c r="E26" s="7">
-        <v>4.72</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="6">
-        <v>70.34999999999999</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C27" s="5">
         <v>72.64</v>
       </c>
-      <c r="E27" s="7">
-        <v>2.29</v>
+      <c r="D27" s="5">
+        <v>74.8</v>
+      </c>
+      <c r="E27" s="6">
+        <v>2.16</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>225.95</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" s="5">
         <v>-17.62</v>
       </c>
-      <c r="E28" s="8">
-        <v>-243.57</v>
+      <c r="D28" s="5">
+        <v>-17.99</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>-35.36</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="5">
         <v>-3.93</v>
       </c>
+      <c r="D29" s="5">
+        <v>-42.92</v>
+      </c>
       <c r="E29" s="7">
-        <v>31.43</v>
+        <v>-38.99</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>-63.64</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>-52.05</v>
       </c>
+      <c r="D30" s="5">
+        <v>-57.49</v>
+      </c>
       <c r="E30" s="7">
-        <v>11.59</v>
+        <v>-5.44</v>
       </c>
     </row>
   </sheetData>
@@ -1890,60 +1833,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="I1" s="9" t="s">
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="10">
+        <v>49.7</v>
+      </c>
+      <c r="C2" s="11">
+        <v>3</v>
+      </c>
+      <c r="D2" s="10">
+        <v>57.3</v>
+      </c>
+      <c r="E2" s="10">
+        <v>33.3</v>
+      </c>
+      <c r="F2" s="10">
+        <v>10.8</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-0.5</v>
+      </c>
+      <c r="H2" s="10">
         <v>66</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="11">
-        <v>49.72</v>
-      </c>
-      <c r="C2" s="12">
-        <v>3</v>
-      </c>
-      <c r="D2" s="11">
-        <v>57.1</v>
-      </c>
-      <c r="E2" s="11">
-        <v>33.3</v>
-      </c>
-      <c r="F2" s="11">
-        <v>7.2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-1.5</v>
-      </c>
-      <c r="H2" s="11">
-        <v>66</v>
-      </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>33.3</v>
       </c>
     </row>
@@ -2045,25 +1988,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.2665</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1798</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0128</v>
+      <c r="A2" s="13">
+        <v>0.2559</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1783</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0156</v>
       </c>
     </row>
   </sheetData>
